--- a/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
+++ b/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Evidence_Hub/02.FOMD/02.metadata_structure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1070" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D907EECA-8246-4FF6-8EA3-FD9974D046C9}"/>
+  <xr:revisionPtr revIDLastSave="1072" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24B07677-2A5B-4054-8CF7-63162C500B31}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="15700" activeTab="1" xr2:uid="{FAB1A633-BA4D-4813-8605-DC3F4755D7C7}"/>
+    <workbookView minimized="1" xWindow="1755" yWindow="3735" windowWidth="21600" windowHeight="11295" xr2:uid="{FAB1A633-BA4D-4813-8605-DC3F4755D7C7}"/>
   </bookViews>
   <sheets>
     <sheet name="10_FOMD_metadata_synthesis" sheetId="1" r:id="rId1"/>
@@ -173,7 +173,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3088" uniqueCount="1373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3088" uniqueCount="1375">
   <si>
     <t>Example</t>
   </si>
@@ -9531,6 +9531,12 @@
   </si>
   <si>
     <t>here it should be the column representing the Product (The full name of the product, including aspect of the component such as grain, meat or milk) for the treatment system</t>
+  </si>
+  <si>
+    <t>C_residues_OC_unit</t>
+  </si>
+  <si>
+    <t>C_residues_OC</t>
   </si>
 </sst>
 </file>
@@ -10411,7 +10417,7 @@
     <xf numFmtId="0" fontId="33" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -10621,24 +10627,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="59" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="48" fillId="59" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="48" fillId="59" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -10686,29 +10681,7 @@
     <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="15" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="5">
     <dxf>
       <font>
         <b val="0"/>
@@ -10837,10 +10810,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
-<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14"/>
-</file>
-
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="Sanchez, Andrea Cecilia (Alliance Bioversity-CIAT)" id="{8754E5AB-4123-45AF-A584-AD9CD6F7A032}" userId="S::andrea.sanchez@cgiar.org::1c01d433-d123-45b5-bcb7-0c97fcfb82b9" providerId="AD"/>
@@ -10848,13 +10817,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8928106E-6D55-41E8-B2AB-A43DFE6088B9}" name="_10_FOMD_metadata_synthesis" displayName="_10_FOMD_metadata_synthesis" ref="A1:KQ2" insertRow="1" totalsRowShown="0" headerRowDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8928106E-6D55-41E8-B2AB-A43DFE6088B9}" name="_10_FOMD_metadata_synthesis" displayName="_10_FOMD_metadata_synthesis" ref="A1:KQ2" insertRow="1" totalsRowShown="0" headerRowDxfId="4">
   <autoFilter ref="A1:KQ2" xr:uid="{8928106E-6D55-41E8-B2AB-A43DFE6088B9}"/>
   <tableColumns count="303">
-    <tableColumn id="1" xr3:uid="{DB6FE6A4-4D26-4D1A-B52B-9ADA10D5F808}" name="study_id" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{70B873D9-C41B-42D1-B78B-33E4B7975633}" name="effect_size_id" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{7BFC1135-E57F-4C97-BD83-843AC387A429}" name="authors" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{883A94AD-C617-4A6C-86FB-47E972FFE80F}" name="year" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{DB6FE6A4-4D26-4D1A-B52B-9ADA10D5F808}" name="study_id" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{70B873D9-C41B-42D1-B78B-33E4B7975633}" name="effect_size_id" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{7BFC1135-E57F-4C97-BD83-843AC387A429}" name="authors" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{883A94AD-C617-4A6C-86FB-47E972FFE80F}" name="year" dataDxfId="0"/>
     <tableColumn id="5" xr3:uid="{2E8FEB31-CDE6-4F6E-9CE5-1A215D75D367}" name="journal"/>
     <tableColumn id="6" xr3:uid="{6E81B9F5-7064-4F0E-B712-65740CB351D8}" name="doi"/>
     <tableColumn id="7" xr3:uid="{E0947224-5770-4E2B-A4A7-C0A71900C8BD}" name="country"/>
@@ -11509,14 +11478,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{487E46BC-52D3-4EF1-8B98-2DA697255E52}">
   <dimension ref="A1:PR2"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="23.1796875" customWidth="1"/>
-    <col min="3" max="3" width="19.453125" customWidth="1"/>
-    <col min="4" max="5" width="23.1796875" customWidth="1"/>
+    <col min="1" max="2" width="23.140625" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" customWidth="1"/>
+    <col min="4" max="5" width="23.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:434" s="83" customFormat="1" ht="58.5" thickBot="1">
+    <row r="1" spans="1:434" s="83" customFormat="1" ht="60.75" thickBot="1">
       <c r="A1" s="63" t="s">
         <v>157</v>
       </c>
@@ -12558,7 +12527,7 @@
       <c r="PQ1" s="71"/>
       <c r="PR1" s="71"/>
     </row>
-    <row r="2" spans="1:434" ht="15.5">
+    <row r="2" spans="1:434" ht="15.75">
       <c r="A2" s="61"/>
       <c r="B2" s="1"/>
       <c r="C2" s="61"/>
@@ -12576,14 +12545,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82619C4B-D6B1-486E-87C6-D2252668E253}">
   <dimension ref="A1:I610"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34.36328125" customWidth="1"/>
-    <col min="2" max="3" width="32.81640625" customWidth="1"/>
-    <col min="4" max="4" width="20.54296875" customWidth="1"/>
-    <col min="5" max="5" width="36.453125" customWidth="1"/>
+    <col min="1" max="1" width="34.42578125" customWidth="1"/>
+    <col min="2" max="3" width="32.85546875" customWidth="1"/>
+    <col min="4" max="4" width="20.5703125" customWidth="1"/>
+    <col min="5" max="5" width="36.42578125" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="121.81640625" style="10" customWidth="1"/>
+    <col min="7" max="7" width="121.85546875" style="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -12610,7 +12579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="25" customHeight="1">
+    <row r="2" spans="1:8" ht="24.95" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>930</v>
       </c>
@@ -12634,7 +12603,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.5">
+    <row r="3" spans="1:8" ht="15.75">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -12680,7 +12649,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.5">
+    <row r="5" spans="1:8" ht="15.75">
       <c r="A5" s="3" t="s">
         <v>931</v>
       </c>
@@ -12726,7 +12695,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.5">
+    <row r="7" spans="1:8" ht="15.75">
       <c r="A7" s="3" t="s">
         <v>933</v>
       </c>
@@ -12912,7 +12881,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:8" ht="15.5">
+    <row r="15" spans="1:8" ht="15.75">
       <c r="A15" s="3" t="s">
         <v>937</v>
       </c>
@@ -12934,7 +12903,7 @@
       </c>
       <c r="H15" s="5"/>
     </row>
-    <row r="16" spans="1:8" ht="15.5">
+    <row r="16" spans="1:8" ht="15.75">
       <c r="A16" s="3" t="s">
         <v>938</v>
       </c>
@@ -12956,7 +12925,7 @@
       </c>
       <c r="H16" s="5"/>
     </row>
-    <row r="17" spans="1:9" ht="15.5">
+    <row r="17" spans="1:9" ht="15.75">
       <c r="A17" s="3" t="s">
         <v>939</v>
       </c>
@@ -13027,7 +12996,7 @@
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
     </row>
-    <row r="20" spans="1:9" ht="15" thickBot="1">
+    <row r="20" spans="1:9" ht="15.75" thickBot="1">
       <c r="A20" s="3" t="s">
         <v>941</v>
       </c>
@@ -13050,7 +13019,7 @@
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
     </row>
-    <row r="21" spans="1:9" ht="15" thickBot="1">
+    <row r="21" spans="1:9" ht="15.75" thickBot="1">
       <c r="A21" s="89" t="s">
         <v>1038</v>
       </c>
@@ -13102,7 +13071,7 @@
       </c>
       <c r="I22" s="4"/>
     </row>
-    <row r="23" spans="1:9" ht="15" thickBot="1">
+    <row r="23" spans="1:9" ht="15.75" thickBot="1">
       <c r="A23" s="89" t="s">
         <v>1038</v>
       </c>
@@ -13125,7 +13094,7 @@
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
     </row>
-    <row r="24" spans="1:9" ht="15" thickBot="1">
+    <row r="24" spans="1:9" ht="15.75" thickBot="1">
       <c r="A24" s="3" t="s">
         <v>943</v>
       </c>
@@ -13146,7 +13115,7 @@
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
     </row>
-    <row r="25" spans="1:9" ht="15" thickBot="1">
+    <row r="25" spans="1:9" ht="15.75" thickBot="1">
       <c r="A25" s="3" t="s">
         <v>944</v>
       </c>
@@ -13167,7 +13136,7 @@
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
     </row>
-    <row r="26" spans="1:9" ht="16" thickBot="1">
+    <row r="26" spans="1:9" ht="16.5" thickBot="1">
       <c r="A26" t="s">
         <v>1080</v>
       </c>
@@ -13440,7 +13409,7 @@
         <v>1278</v>
       </c>
       <c r="C37" s="1"/>
-      <c r="D37" s="124" t="s">
+      <c r="D37" s="35" t="s">
         <v>1287</v>
       </c>
       <c r="E37" s="35" t="s">
@@ -13462,7 +13431,7 @@
         <v>1281</v>
       </c>
       <c r="C38" s="1"/>
-      <c r="D38" s="124" t="s">
+      <c r="D38" s="35" t="s">
         <v>1287</v>
       </c>
       <c r="E38" s="35" t="s">
@@ -13484,7 +13453,7 @@
         <v>1284</v>
       </c>
       <c r="C39" s="1"/>
-      <c r="D39" s="124" t="s">
+      <c r="D39" s="35" t="s">
         <v>1287</v>
       </c>
       <c r="E39" s="35" t="s">
@@ -13502,7 +13471,7 @@
         <v>1279</v>
       </c>
       <c r="C40" s="1"/>
-      <c r="D40" s="124" t="s">
+      <c r="D40" s="35" t="s">
         <v>1287</v>
       </c>
       <c r="E40" s="35" t="s">
@@ -13524,7 +13493,7 @@
         <v>1285</v>
       </c>
       <c r="C41" s="1"/>
-      <c r="D41" s="124" t="s">
+      <c r="D41" s="35" t="s">
         <v>1287</v>
       </c>
       <c r="E41" s="35" t="s">
@@ -13546,7 +13515,7 @@
         <v>1286</v>
       </c>
       <c r="C42" s="1"/>
-      <c r="D42" s="124" t="s">
+      <c r="D42" s="35" t="s">
         <v>1287</v>
       </c>
       <c r="E42" s="35" t="s">
@@ -13656,7 +13625,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15" thickBot="1">
+    <row r="48" spans="1:8" ht="15.75" thickBot="1">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -13676,7 +13645,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15" thickBot="1">
+    <row r="49" spans="1:8" ht="15.75" thickBot="1">
       <c r="A49" s="3" t="s">
         <v>1100</v>
       </c>
@@ -13795,7 +13764,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="16" thickBot="1">
+    <row r="54" spans="1:8" ht="16.5" thickBot="1">
       <c r="A54" s="3" t="s">
         <v>1054</v>
       </c>
@@ -13819,7 +13788,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="16" thickBot="1">
+    <row r="55" spans="1:8" ht="16.5" thickBot="1">
       <c r="A55" s="3" t="s">
         <v>1101</v>
       </c>
@@ -13939,7 +13908,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15.5">
+    <row r="60" spans="1:8" ht="15.75">
       <c r="A60" s="3" t="s">
         <v>1058</v>
       </c>
@@ -13963,7 +13932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="15.5">
+    <row r="61" spans="1:8" ht="15.75">
       <c r="A61" t="s">
         <v>1106</v>
       </c>
@@ -13998,7 +13967,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15.5">
+    <row r="63" spans="1:8" ht="15.75">
       <c r="A63" t="s">
         <v>1104</v>
       </c>
@@ -14262,7 +14231,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="15.5">
+    <row r="75" spans="1:8" ht="15.75">
       <c r="A75" s="3" t="s">
         <v>1060</v>
       </c>
@@ -14342,7 +14311,7 @@
       <c r="G78"/>
       <c r="H78" s="32"/>
     </row>
-    <row r="79" spans="1:8" ht="15.5">
+    <row r="79" spans="1:8" ht="15.75">
       <c r="A79" t="s">
         <v>1082</v>
       </c>
@@ -14364,7 +14333,7 @@
       </c>
       <c r="H79" s="5"/>
     </row>
-    <row r="80" spans="1:8" ht="15.5">
+    <row r="80" spans="1:8" ht="15.75">
       <c r="A80" s="3" t="s">
         <v>1061</v>
       </c>
@@ -14410,7 +14379,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="15.5">
+    <row r="82" spans="1:8" ht="15.75">
       <c r="A82" s="3" t="s">
         <v>1098</v>
       </c>
@@ -14524,7 +14493,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="15" thickBot="1">
+    <row r="88" spans="1:8" ht="15.75" thickBot="1">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -14542,7 +14511,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="15" thickBot="1">
+    <row r="89" spans="1:8" ht="15.75" thickBot="1">
       <c r="A89" t="s">
         <v>1122</v>
       </c>
@@ -14562,7 +14531,7 @@
       <c r="G89"/>
       <c r="H89" s="32"/>
     </row>
-    <row r="90" spans="1:8" ht="16" thickBot="1">
+    <row r="90" spans="1:8" ht="16.5" thickBot="1">
       <c r="B90" s="104" t="s">
         <v>1126</v>
       </c>
@@ -14585,7 +14554,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="15" thickBot="1">
+    <row r="91" spans="1:8" ht="15.75" thickBot="1">
       <c r="A91" s="89" t="s">
         <v>1038</v>
       </c>
@@ -14608,7 +14577,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="15" thickBot="1">
+    <row r="92" spans="1:8" ht="15.75" thickBot="1">
       <c r="A92" s="89" t="s">
         <v>1038</v>
       </c>
@@ -14631,7 +14600,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="15" thickBot="1">
+    <row r="93" spans="1:8" ht="15.75" thickBot="1">
       <c r="A93" s="3" t="s">
         <v>924</v>
       </c>
@@ -14652,7 +14621,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="16" thickBot="1">
+    <row r="94" spans="1:8" ht="16.5" thickBot="1">
       <c r="A94" t="s">
         <v>1124</v>
       </c>
@@ -14674,7 +14643,7 @@
       </c>
       <c r="H94" s="5"/>
     </row>
-    <row r="95" spans="1:8" ht="15" thickBot="1">
+    <row r="95" spans="1:8" ht="15.75" thickBot="1">
       <c r="A95" s="3" t="s">
         <v>923</v>
       </c>
@@ -14695,7 +14664,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="15" thickBot="1">
+    <row r="96" spans="1:8" ht="15.75" thickBot="1">
       <c r="A96" t="s">
         <v>1123</v>
       </c>
@@ -14714,7 +14683,7 @@
       </c>
       <c r="G96"/>
     </row>
-    <row r="97" spans="1:8" ht="16" thickBot="1">
+    <row r="97" spans="1:8" ht="16.5" thickBot="1">
       <c r="A97" s="3"/>
       <c r="B97" s="104" t="s">
         <v>1127</v>
@@ -14738,7 +14707,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15" thickBot="1">
+    <row r="98" spans="1:8" ht="15.75" thickBot="1">
       <c r="A98" s="89" t="s">
         <v>1038</v>
       </c>
@@ -14764,7 +14733,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="15" thickBot="1">
+    <row r="99" spans="1:8" ht="15.75" thickBot="1">
       <c r="A99" s="89" t="s">
         <v>1038</v>
       </c>
@@ -14790,7 +14759,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="16" thickBot="1">
+    <row r="100" spans="1:8" ht="16.5" thickBot="1">
       <c r="A100" s="3" t="s">
         <v>922</v>
       </c>
@@ -14814,7 +14783,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="16" thickBot="1">
+    <row r="101" spans="1:8" ht="16.5" thickBot="1">
       <c r="A101" t="s">
         <v>1125</v>
       </c>
@@ -14838,7 +14807,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="15" thickBot="1">
+    <row r="102" spans="1:8" ht="15.75" thickBot="1">
       <c r="A102" s="3" t="s">
         <v>921</v>
       </c>
@@ -14879,7 +14848,7 @@
       <c r="F103" s="3"/>
       <c r="G103"/>
     </row>
-    <row r="104" spans="1:8" ht="15.5">
+    <row r="104" spans="1:8" ht="15.75">
       <c r="A104" t="s">
         <v>1267</v>
       </c>
@@ -14903,7 +14872,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="15.5">
+    <row r="105" spans="1:8" ht="15.75">
       <c r="A105" t="s">
         <v>1129</v>
       </c>
@@ -14925,7 +14894,7 @@
       </c>
       <c r="H105" s="5"/>
     </row>
-    <row r="106" spans="1:8" ht="15.5">
+    <row r="106" spans="1:8" ht="15.75">
       <c r="A106" t="s">
         <v>1131</v>
       </c>
@@ -14946,7 +14915,7 @@
       </c>
       <c r="H106" s="5"/>
     </row>
-    <row r="107" spans="1:8" ht="15.5">
+    <row r="107" spans="1:8" ht="15.75">
       <c r="A107" s="1"/>
       <c r="B107" s="112" t="s">
         <v>1272</v>
@@ -14968,7 +14937,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="15.5">
+    <row r="108" spans="1:8" ht="15.75">
       <c r="A108" s="107" t="s">
         <v>919</v>
       </c>
@@ -15010,7 +14979,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="15.5">
+    <row r="110" spans="1:8" ht="15.75">
       <c r="A110" t="s">
         <v>1130</v>
       </c>
@@ -15034,7 +15003,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="15.5">
+    <row r="111" spans="1:8" ht="15.75">
       <c r="A111" t="s">
         <v>1132</v>
       </c>
@@ -15097,7 +15066,7 @@
       </c>
       <c r="G113"/>
     </row>
-    <row r="114" spans="1:8" ht="15.5">
+    <row r="114" spans="1:8" ht="15.75">
       <c r="A114" s="1" t="s">
         <v>1345</v>
       </c>
@@ -15191,7 +15160,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="15" thickBot="1">
+    <row r="118" spans="1:8" ht="15.75" thickBot="1">
       <c r="A118" s="1" t="s">
         <v>1277</v>
       </c>
@@ -15208,7 +15177,7 @@
       </c>
       <c r="G118" s="48"/>
     </row>
-    <row r="119" spans="1:8" ht="15" thickBot="1">
+    <row r="119" spans="1:8" ht="15.75" thickBot="1">
       <c r="A119" s="1" t="s">
         <v>1347</v>
       </c>
@@ -15278,7 +15247,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="15" thickBot="1">
+    <row r="122" spans="1:8" ht="15.75" thickBot="1">
       <c r="A122" s="89" t="s">
         <v>1038</v>
       </c>
@@ -15302,8 +15271,8 @@
         <v>438</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="15" thickBot="1">
-      <c r="A123" s="122" t="s">
+    <row r="123" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A123" t="s">
         <v>1301</v>
       </c>
       <c r="B123" s="112" t="s">
@@ -15317,7 +15286,7 @@
       <c r="F123" s="3"/>
       <c r="G123"/>
     </row>
-    <row r="124" spans="1:8" ht="15" thickBot="1">
+    <row r="124" spans="1:8" ht="15.75" thickBot="1">
       <c r="A124" s="1" t="s">
         <v>1342</v>
       </c>
@@ -15339,7 +15308,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="125" spans="1:8" ht="15" thickBot="1">
+    <row r="125" spans="1:8" ht="15.75" thickBot="1">
       <c r="A125" s="107" t="s">
         <v>1318</v>
       </c>
@@ -15361,8 +15330,8 @@
         <v>439</v>
       </c>
     </row>
-    <row r="126" spans="1:8" ht="15" thickBot="1">
-      <c r="A126" s="122" t="s">
+    <row r="126" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A126" t="s">
         <v>1323</v>
       </c>
       <c r="B126" s="112" t="s">
@@ -15383,8 +15352,8 @@
         <v>440</v>
       </c>
     </row>
-    <row r="127" spans="1:8" ht="15" thickBot="1">
-      <c r="A127" s="122" t="s">
+    <row r="127" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A127" t="s">
         <v>1327</v>
       </c>
       <c r="B127" s="112" t="s">
@@ -15405,8 +15374,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="128" spans="1:8" ht="15" thickBot="1">
-      <c r="A128" s="122" t="s">
+    <row r="128" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A128" t="s">
         <v>1328</v>
       </c>
       <c r="B128" s="112" t="s">
@@ -15427,7 +15396,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="129" spans="1:8" ht="15" thickBot="1">
+    <row r="129" spans="1:8" ht="15.75" thickBot="1">
       <c r="A129" s="1" t="s">
         <v>909</v>
       </c>
@@ -15449,8 +15418,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="130" spans="1:8" ht="15" thickBot="1">
-      <c r="A130" s="122" t="s">
+    <row r="130" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A130" t="s">
         <v>910</v>
       </c>
       <c r="B130" s="112" t="s">
@@ -15471,7 +15440,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="15" thickBot="1">
+    <row r="131" spans="1:8" ht="15.75" thickBot="1">
       <c r="A131" s="1" t="s">
         <v>911</v>
       </c>
@@ -15493,7 +15462,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="132" spans="1:8" ht="15" thickBot="1">
+    <row r="132" spans="1:8" ht="15.75" thickBot="1">
       <c r="A132" s="1" t="s">
         <v>912</v>
       </c>
@@ -15515,7 +15484,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="15" thickBot="1">
+    <row r="133" spans="1:8" ht="15.75" thickBot="1">
       <c r="A133" s="1" t="s">
         <v>913</v>
       </c>
@@ -15537,8 +15506,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="15" thickBot="1">
-      <c r="A134" s="122" t="s">
+    <row r="134" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A134" t="s">
         <v>1313</v>
       </c>
       <c r="B134" s="112" t="s">
@@ -15559,7 +15528,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="15" thickBot="1">
+    <row r="135" spans="1:8" ht="15.75" thickBot="1">
       <c r="A135" s="107" t="s">
         <v>1318</v>
       </c>
@@ -15578,8 +15547,8 @@
         <v>463</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="15" thickBot="1">
-      <c r="A136" s="122" t="s">
+    <row r="136" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A136" t="s">
         <v>1323</v>
       </c>
       <c r="B136" s="112" t="s">
@@ -15597,8 +15566,8 @@
         <v>464</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="15" thickBot="1">
-      <c r="A137" s="122" t="s">
+    <row r="137" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A137" t="s">
         <v>1327</v>
       </c>
       <c r="B137" s="112" t="s">
@@ -15616,8 +15585,8 @@
         <v>467</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="15" thickBot="1">
-      <c r="A138" s="122" t="s">
+    <row r="138" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A138" t="s">
         <v>1328</v>
       </c>
       <c r="B138" s="112" t="s">
@@ -15635,8 +15604,8 @@
         <v>498</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="15" thickBot="1">
-      <c r="A139" s="122" t="s">
+    <row r="139" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A139" t="s">
         <v>925</v>
       </c>
       <c r="B139" s="112" t="s">
@@ -15654,7 +15623,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="15" thickBot="1">
+    <row r="140" spans="1:8" ht="15.75" thickBot="1">
       <c r="A140" s="107" t="s">
         <v>1303</v>
       </c>
@@ -15673,8 +15642,8 @@
         <v>469</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="15" thickBot="1">
-      <c r="A141" s="122" t="s">
+    <row r="141" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A141" t="s">
         <v>1304</v>
       </c>
       <c r="B141" s="114" t="s">
@@ -15692,8 +15661,8 @@
         <v>470</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="15" thickBot="1">
-      <c r="A142" s="122" t="s">
+    <row r="142" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A142" t="s">
         <v>1308</v>
       </c>
       <c r="B142" s="114" t="s">
@@ -15711,11 +15680,11 @@
         <v>471</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="15" thickBot="1">
-      <c r="A143" s="122" t="s">
+    <row r="143" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A143" t="s">
         <v>1311</v>
       </c>
-      <c r="B143" s="121" t="s">
+      <c r="B143" s="115" t="s">
         <v>1004</v>
       </c>
       <c r="C143" s="1"/>
@@ -15731,8 +15700,8 @@
       </c>
       <c r="H143" s="42"/>
     </row>
-    <row r="144" spans="1:8" ht="15" thickBot="1">
-      <c r="A144" s="120" t="s">
+    <row r="144" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A144" t="s">
         <v>1302</v>
       </c>
       <c r="B144" s="114" t="s">
@@ -15747,7 +15716,7 @@
       <c r="G144"/>
       <c r="H144" s="42"/>
     </row>
-    <row r="145" spans="1:8" ht="15" thickBot="1">
+    <row r="145" spans="1:8" ht="15.75" thickBot="1">
       <c r="A145" s="1" t="s">
         <v>1343</v>
       </c>
@@ -15769,8 +15738,8 @@
         <v>452</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="15" thickBot="1">
-      <c r="A146" s="125" t="s">
+    <row r="146" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A146" s="107" t="s">
         <v>1321</v>
       </c>
       <c r="B146" s="112" t="s">
@@ -15788,8 +15757,8 @@
         <v>501</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="15" thickBot="1">
-      <c r="A147" s="122" t="s">
+    <row r="147" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A147" t="s">
         <v>1324</v>
       </c>
       <c r="B147" s="112" t="s">
@@ -15808,8 +15777,8 @@
       </c>
       <c r="H147" s="40"/>
     </row>
-    <row r="148" spans="1:8" ht="15" thickBot="1">
-      <c r="A148" s="122" t="s">
+    <row r="148" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A148" t="s">
         <v>1335</v>
       </c>
       <c r="B148" s="112" t="s">
@@ -15828,8 +15797,8 @@
       </c>
       <c r="H148" s="41"/>
     </row>
-    <row r="149" spans="1:8" ht="15" thickBot="1">
-      <c r="A149" s="122" t="s">
+    <row r="149" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A149" t="s">
         <v>1336</v>
       </c>
       <c r="B149" s="112" t="s">
@@ -15848,8 +15817,8 @@
       </c>
       <c r="H149" s="33"/>
     </row>
-    <row r="150" spans="1:8" ht="15" thickBot="1">
-      <c r="A150" s="119" t="s">
+    <row r="150" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A150" s="1" t="s">
         <v>914</v>
       </c>
       <c r="B150" s="112" t="s">
@@ -15867,8 +15836,8 @@
         <v>457</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="15" thickBot="1">
-      <c r="A151" s="119" t="s">
+    <row r="151" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A151" s="1" t="s">
         <v>915</v>
       </c>
       <c r="B151" s="112" t="s">
@@ -15886,8 +15855,8 @@
         <v>480</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="15" thickBot="1">
-      <c r="A152" s="119" t="s">
+    <row r="152" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A152" s="1" t="s">
         <v>916</v>
       </c>
       <c r="B152" s="112" t="s">
@@ -15905,8 +15874,8 @@
         <v>482</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="15" thickBot="1">
-      <c r="A153" s="119" t="s">
+    <row r="153" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A153" s="1" t="s">
         <v>917</v>
       </c>
       <c r="B153" s="112" t="s">
@@ -15924,8 +15893,8 @@
         <v>484</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="15" thickBot="1">
-      <c r="A154" s="119" t="s">
+    <row r="154" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A154" s="1" t="s">
         <v>918</v>
       </c>
       <c r="B154" s="112" t="s">
@@ -15943,8 +15912,8 @@
         <v>486</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="15" thickBot="1">
-      <c r="A155" s="122" t="s">
+    <row r="155" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A155" t="s">
         <v>1314</v>
       </c>
       <c r="B155" s="112" t="s">
@@ -15962,7 +15931,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="15" thickBot="1">
+    <row r="156" spans="1:8" ht="15.75" thickBot="1">
       <c r="A156" s="107" t="s">
         <v>1321</v>
       </c>
@@ -15984,8 +15953,8 @@
         <v>465</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="15" thickBot="1">
-      <c r="A157" s="122" t="s">
+    <row r="157" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A157" t="s">
         <v>1324</v>
       </c>
       <c r="B157" s="112" t="s">
@@ -16006,8 +15975,8 @@
         <v>466</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="15" thickBot="1">
-      <c r="A158" s="122" t="s">
+    <row r="158" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A158" t="s">
         <v>1335</v>
       </c>
       <c r="B158" s="112" t="s">
@@ -16028,8 +15997,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="159" spans="1:8" ht="15" thickBot="1">
-      <c r="A159" s="122" t="s">
+    <row r="159" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A159" t="s">
         <v>1336</v>
       </c>
       <c r="B159" s="112" t="s">
@@ -16050,8 +16019,8 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="15" thickBot="1">
-      <c r="A160" s="122" t="s">
+    <row r="160" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A160" t="s">
         <v>926</v>
       </c>
       <c r="B160" s="112" t="s">
@@ -16072,7 +16041,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="161" spans="1:8" ht="15" thickBot="1">
+    <row r="161" spans="1:8" ht="15.75" thickBot="1">
       <c r="A161" s="107" t="s">
         <v>1305</v>
       </c>
@@ -16094,8 +16063,8 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="162" spans="1:8" ht="15" thickBot="1">
-      <c r="A162" s="122" t="s">
+    <row r="162" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A162" t="s">
         <v>1306</v>
       </c>
       <c r="B162" s="114" t="s">
@@ -16116,8 +16085,8 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="163" spans="1:8" ht="15" thickBot="1">
-      <c r="A163" s="122" t="s">
+    <row r="163" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A163" t="s">
         <v>1307</v>
       </c>
       <c r="B163" s="114" t="s">
@@ -16138,8 +16107,8 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="164" spans="1:8" ht="15" thickBot="1">
-      <c r="A164" s="122" t="s">
+    <row r="164" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A164" t="s">
         <v>1312</v>
       </c>
       <c r="B164" s="112" t="s">
@@ -16160,7 +16129,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="15" thickBot="1">
+    <row r="165" spans="1:8" ht="15.75" thickBot="1">
       <c r="A165" t="s">
         <v>1172</v>
       </c>
@@ -16184,7 +16153,7 @@
       </c>
       <c r="H165" s="42"/>
     </row>
-    <row r="166" spans="1:8" ht="15" thickBot="1">
+    <row r="166" spans="1:8" ht="15.75" thickBot="1">
       <c r="A166" t="s">
         <v>1168</v>
       </c>
@@ -16208,7 +16177,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="167" spans="1:8" ht="15" thickBot="1">
+    <row r="167" spans="1:8" ht="15.75" thickBot="1">
       <c r="A167" t="s">
         <v>1183</v>
       </c>
@@ -16234,7 +16203,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="15" thickBot="1">
+    <row r="168" spans="1:8" ht="15.75" thickBot="1">
       <c r="A168" t="s">
         <v>1179</v>
       </c>
@@ -16255,7 +16224,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="169" spans="1:8" ht="15" thickBot="1">
+    <row r="169" spans="1:8" ht="15.75" thickBot="1">
       <c r="A169" t="s">
         <v>1173</v>
       </c>
@@ -16278,7 +16247,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="170" spans="1:8" ht="15" thickBot="1">
+    <row r="170" spans="1:8" ht="15.75" thickBot="1">
       <c r="A170" t="s">
         <v>1169</v>
       </c>
@@ -16302,7 +16271,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="171" spans="1:8" ht="15" thickBot="1">
+    <row r="171" spans="1:8" ht="15.75" thickBot="1">
       <c r="A171" t="s">
         <v>1184</v>
       </c>
@@ -16328,7 +16297,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="172" spans="1:8" ht="15" thickBot="1">
+    <row r="172" spans="1:8" ht="15.75" thickBot="1">
       <c r="A172" t="s">
         <v>1180</v>
       </c>
@@ -16349,8 +16318,8 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="173" spans="1:8" ht="15" thickBot="1">
-      <c r="A173" s="122" t="s">
+    <row r="173" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A173" t="s">
         <v>1290</v>
       </c>
       <c r="B173" s="112" t="s">
@@ -16366,8 +16335,8 @@
       <c r="F173" s="17"/>
       <c r="G173"/>
     </row>
-    <row r="174" spans="1:8" ht="15" thickBot="1">
-      <c r="A174" s="123" t="s">
+    <row r="174" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A174" s="49" t="s">
         <v>1289</v>
       </c>
       <c r="B174" s="112" t="s">
@@ -16390,8 +16359,8 @@
         <v>510</v>
       </c>
     </row>
-    <row r="175" spans="1:8" ht="15" thickBot="1">
-      <c r="A175" s="122" t="s">
+    <row r="175" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A175" t="s">
         <v>1292</v>
       </c>
       <c r="B175" s="112" t="s">
@@ -16407,8 +16376,8 @@
       <c r="F175" s="17"/>
       <c r="G175" s="48"/>
     </row>
-    <row r="176" spans="1:8" ht="15" thickBot="1">
-      <c r="A176" s="122" t="s">
+    <row r="176" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A176" t="s">
         <v>1296</v>
       </c>
       <c r="B176" s="112" t="s">
@@ -16424,8 +16393,8 @@
       <c r="F176" s="17"/>
       <c r="G176" s="48"/>
     </row>
-    <row r="177" spans="1:8" ht="15" thickBot="1">
-      <c r="A177" s="122" t="s">
+    <row r="177" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A177" t="s">
         <v>1294</v>
       </c>
       <c r="B177" s="112" t="s">
@@ -16448,8 +16417,8 @@
         <v>517</v>
       </c>
     </row>
-    <row r="178" spans="1:8" ht="15" thickBot="1">
-      <c r="A178" s="122" t="s">
+    <row r="178" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A178" t="s">
         <v>1291</v>
       </c>
       <c r="B178" s="112" t="s">
@@ -16465,8 +16434,8 @@
       <c r="F178" s="17"/>
       <c r="G178" s="48"/>
     </row>
-    <row r="179" spans="1:8" ht="15" thickBot="1">
-      <c r="A179" s="123" t="s">
+    <row r="179" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A179" s="49" t="s">
         <v>1300</v>
       </c>
       <c r="B179" s="112" t="s">
@@ -16489,8 +16458,8 @@
         <v>513</v>
       </c>
     </row>
-    <row r="180" spans="1:8" ht="15" thickBot="1">
-      <c r="A180" s="122" t="s">
+    <row r="180" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A180" t="s">
         <v>1293</v>
       </c>
       <c r="B180" s="112" t="s">
@@ -16507,8 +16476,8 @@
       <c r="G180"/>
       <c r="H180" s="70"/>
     </row>
-    <row r="181" spans="1:8" ht="15" thickBot="1">
-      <c r="A181" s="122" t="s">
+    <row r="181" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A181" t="s">
         <v>1297</v>
       </c>
       <c r="B181" s="112" t="s">
@@ -16525,8 +16494,8 @@
       <c r="G181"/>
       <c r="H181" s="70"/>
     </row>
-    <row r="182" spans="1:8" ht="15" thickBot="1">
-      <c r="A182" s="122" t="s">
+    <row r="182" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A182" t="s">
         <v>1295</v>
       </c>
       <c r="B182" s="112" t="s">
@@ -16549,7 +16518,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="183" spans="1:8" ht="15" thickBot="1">
+    <row r="183" spans="1:8" ht="15.75" thickBot="1">
       <c r="A183" t="s">
         <v>1185</v>
       </c>
@@ -16566,7 +16535,7 @@
       <c r="F183" s="17"/>
       <c r="G183"/>
     </row>
-    <row r="184" spans="1:8" ht="15" thickBot="1">
+    <row r="184" spans="1:8" ht="15.75" thickBot="1">
       <c r="A184" s="1" t="s">
         <v>1207</v>
       </c>
@@ -16590,7 +16559,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="185" spans="1:8" ht="15" thickBot="1">
+    <row r="185" spans="1:8" ht="15.75" thickBot="1">
       <c r="A185" s="1" t="s">
         <v>966</v>
       </c>
@@ -16602,7 +16571,7 @@
         <v>953</v>
       </c>
       <c r="E185" s="21" t="s">
-        <v>955</v>
+        <v>1373</v>
       </c>
       <c r="F185" s="17" t="s">
         <v>4</v>
@@ -16612,11 +16581,11 @@
       </c>
       <c r="H185" s="70"/>
     </row>
-    <row r="186" spans="1:8" ht="15" thickBot="1">
+    <row r="186" spans="1:8" ht="15.75" thickBot="1">
       <c r="A186" s="1" t="s">
         <v>967</v>
       </c>
-      <c r="B186" s="119" t="s">
+      <c r="B186" s="1" t="s">
         <v>1004</v>
       </c>
       <c r="C186" s="1"/>
@@ -16624,7 +16593,7 @@
         <v>953</v>
       </c>
       <c r="E186" s="21" t="s">
-        <v>964</v>
+        <v>1374</v>
       </c>
       <c r="F186" s="17" t="s">
         <v>2</v>
@@ -16634,7 +16603,7 @@
       </c>
       <c r="H186" s="70"/>
     </row>
-    <row r="187" spans="1:8" ht="15" thickBot="1">
+    <row r="187" spans="1:8" ht="15.75" thickBot="1">
       <c r="A187" s="1" t="s">
         <v>968</v>
       </c>
@@ -16655,7 +16624,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="188" spans="1:8" ht="15" thickBot="1">
+    <row r="188" spans="1:8" ht="15.75" thickBot="1">
       <c r="A188" s="1" t="s">
         <v>969</v>
       </c>
@@ -16677,7 +16646,7 @@
       </c>
       <c r="H188" s="44"/>
     </row>
-    <row r="189" spans="1:8" ht="15" thickBot="1">
+    <row r="189" spans="1:8" ht="15.75" thickBot="1">
       <c r="A189" s="1" t="s">
         <v>970</v>
       </c>
@@ -16695,11 +16664,11 @@
       <c r="G189"/>
       <c r="H189" s="87"/>
     </row>
-    <row r="190" spans="1:8" ht="15" thickBot="1">
+    <row r="190" spans="1:8" ht="15.75" thickBot="1">
       <c r="A190" s="1" t="s">
         <v>971</v>
       </c>
-      <c r="B190" s="119" t="s">
+      <c r="B190" s="1" t="s">
         <v>1004</v>
       </c>
       <c r="C190" s="1"/>
@@ -16717,7 +16686,7 @@
       </c>
       <c r="H190" s="45"/>
     </row>
-    <row r="191" spans="1:8" ht="15" thickBot="1">
+    <row r="191" spans="1:8" ht="15.75" thickBot="1">
       <c r="A191" s="1" t="s">
         <v>972</v>
       </c>
@@ -16735,11 +16704,11 @@
       <c r="G191"/>
       <c r="H191" s="45"/>
     </row>
-    <row r="192" spans="1:8" ht="15" thickBot="1">
+    <row r="192" spans="1:8" ht="15.75" thickBot="1">
       <c r="A192" s="1" t="s">
         <v>973</v>
       </c>
-      <c r="B192" s="119" t="s">
+      <c r="B192" s="1" t="s">
         <v>1004</v>
       </c>
       <c r="C192" s="1"/>
@@ -16757,7 +16726,7 @@
       </c>
       <c r="H192" s="45"/>
     </row>
-    <row r="193" spans="1:8" ht="15" thickBot="1">
+    <row r="193" spans="1:8" ht="15.75" thickBot="1">
       <c r="A193" t="s">
         <v>1191</v>
       </c>
@@ -16778,7 +16747,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="194" spans="1:8" ht="15" thickBot="1">
+    <row r="194" spans="1:8" ht="15.75" thickBot="1">
       <c r="A194" t="s">
         <v>1187</v>
       </c>
@@ -16799,7 +16768,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="195" spans="1:8" ht="15" thickBot="1">
+    <row r="195" spans="1:8" ht="15.75" thickBot="1">
       <c r="A195" t="s">
         <v>1189</v>
       </c>
@@ -16820,7 +16789,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="196" spans="1:8" ht="15" thickBot="1">
+    <row r="196" spans="1:8" ht="15.75" thickBot="1">
       <c r="A196" t="s">
         <v>1194</v>
       </c>
@@ -16841,7 +16810,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="197" spans="1:8" ht="15" thickBot="1">
+    <row r="197" spans="1:8" ht="15.75" thickBot="1">
       <c r="A197" t="s">
         <v>1201</v>
       </c>
@@ -16865,7 +16834,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="198" spans="1:8" ht="15" thickBot="1">
+    <row r="198" spans="1:8" ht="15.75" thickBot="1">
       <c r="A198" t="s">
         <v>1198</v>
       </c>
@@ -16887,7 +16856,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="199" spans="1:8" ht="15" thickBot="1">
+    <row r="199" spans="1:8" ht="15.75" thickBot="1">
       <c r="A199" t="s">
         <v>1186</v>
       </c>
@@ -16904,7 +16873,7 @@
       <c r="F199" s="17"/>
       <c r="G199" s="48"/>
     </row>
-    <row r="200" spans="1:8" ht="15" thickBot="1">
+    <row r="200" spans="1:8" ht="15.75" thickBot="1">
       <c r="A200" s="1" t="s">
         <v>1208</v>
       </c>
@@ -16928,11 +16897,11 @@
         <v>540</v>
       </c>
     </row>
-    <row r="201" spans="1:8" ht="15" thickBot="1">
+    <row r="201" spans="1:8" ht="15.75" thickBot="1">
       <c r="A201" s="1" t="s">
         <v>974</v>
       </c>
-      <c r="B201" s="119" t="s">
+      <c r="B201" s="1" t="s">
         <v>1004</v>
       </c>
       <c r="C201" s="1"/>
@@ -16950,11 +16919,11 @@
       </c>
       <c r="H201" s="87"/>
     </row>
-    <row r="202" spans="1:8" ht="15" thickBot="1">
+    <row r="202" spans="1:8" ht="15.75" thickBot="1">
       <c r="A202" s="1" t="s">
         <v>975</v>
       </c>
-      <c r="B202" s="119" t="s">
+      <c r="B202" s="1" t="s">
         <v>1004</v>
       </c>
       <c r="C202" s="1"/>
@@ -16972,11 +16941,11 @@
       </c>
       <c r="H202" s="87"/>
     </row>
-    <row r="203" spans="1:8" ht="15" thickBot="1">
+    <row r="203" spans="1:8" ht="15.75" thickBot="1">
       <c r="A203" s="1" t="s">
         <v>976</v>
       </c>
-      <c r="B203" s="119" t="s">
+      <c r="B203" s="1" t="s">
         <v>1004</v>
       </c>
       <c r="C203" s="1"/>
@@ -16993,11 +16962,11 @@
         <v>545</v>
       </c>
     </row>
-    <row r="204" spans="1:8" ht="15" thickBot="1">
+    <row r="204" spans="1:8" ht="15.75" thickBot="1">
       <c r="A204" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="B204" s="119" t="s">
+      <c r="B204" s="1" t="s">
         <v>1004</v>
       </c>
       <c r="C204" s="1"/>
@@ -17017,11 +16986,11 @@
         <v>531</v>
       </c>
     </row>
-    <row r="205" spans="1:8" ht="15" thickBot="1">
+    <row r="205" spans="1:8" ht="15.75" thickBot="1">
       <c r="A205" s="1" t="s">
         <v>978</v>
       </c>
-      <c r="B205" s="119" t="s">
+      <c r="B205" s="1" t="s">
         <v>1004</v>
       </c>
       <c r="C205" s="1"/>
@@ -17035,11 +17004,11 @@
       <c r="G205"/>
       <c r="H205" s="87"/>
     </row>
-    <row r="206" spans="1:8" ht="15" thickBot="1">
+    <row r="206" spans="1:8" ht="15.75" thickBot="1">
       <c r="A206" s="1" t="s">
         <v>979</v>
       </c>
-      <c r="B206" s="119" t="s">
+      <c r="B206" s="1" t="s">
         <v>1004</v>
       </c>
       <c r="C206" s="1"/>
@@ -17059,11 +17028,11 @@
         <v>531</v>
       </c>
     </row>
-    <row r="207" spans="1:8" ht="15" thickBot="1">
+    <row r="207" spans="1:8" ht="15.75" thickBot="1">
       <c r="A207" s="1" t="s">
         <v>980</v>
       </c>
-      <c r="B207" s="119" t="s">
+      <c r="B207" s="1" t="s">
         <v>1004</v>
       </c>
       <c r="C207" s="1"/>
@@ -17077,11 +17046,11 @@
       <c r="G207"/>
       <c r="H207" s="45"/>
     </row>
-    <row r="208" spans="1:8" ht="15" thickBot="1">
+    <row r="208" spans="1:8" ht="15.75" thickBot="1">
       <c r="A208" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="B208" s="119" t="s">
+      <c r="B208" s="1" t="s">
         <v>1004</v>
       </c>
       <c r="C208" s="1"/>
@@ -17101,7 +17070,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="209" spans="1:8" ht="15" thickBot="1">
+    <row r="209" spans="1:8" ht="15.75" thickBot="1">
       <c r="A209" t="s">
         <v>1192</v>
       </c>
@@ -17122,7 +17091,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="210" spans="1:8" ht="15" thickBot="1">
+    <row r="210" spans="1:8" ht="15.75" thickBot="1">
       <c r="A210" t="s">
         <v>1188</v>
       </c>
@@ -17146,7 +17115,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="211" spans="1:8" ht="15" thickBot="1">
+    <row r="211" spans="1:8" ht="15.75" thickBot="1">
       <c r="A211" t="s">
         <v>1190</v>
       </c>
@@ -17170,7 +17139,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="212" spans="1:8" ht="15" thickBot="1">
+    <row r="212" spans="1:8" ht="15.75" thickBot="1">
       <c r="A212" t="s">
         <v>1195</v>
       </c>
@@ -17194,7 +17163,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="213" spans="1:8" ht="15" thickBot="1">
+    <row r="213" spans="1:8" ht="15.75" thickBot="1">
       <c r="A213" t="s">
         <v>1202</v>
       </c>
@@ -17218,7 +17187,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="214" spans="1:8" ht="15" thickBot="1">
+    <row r="214" spans="1:8" ht="15.75" thickBot="1">
       <c r="A214" t="s">
         <v>1199</v>
       </c>
@@ -17240,7 +17209,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="215" spans="1:8" ht="15" thickBot="1">
+    <row r="215" spans="1:8" ht="15.75" thickBot="1">
       <c r="A215" t="s">
         <v>1133</v>
       </c>
@@ -17260,7 +17229,7 @@
       <c r="G215" s="14"/>
       <c r="H215" s="42"/>
     </row>
-    <row r="216" spans="1:8" ht="15" thickBot="1">
+    <row r="216" spans="1:8" ht="15.75" thickBot="1">
       <c r="A216" s="1"/>
       <c r="B216" s="104" t="s">
         <v>1203</v>
@@ -17284,7 +17253,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="217" spans="1:8" ht="15" thickBot="1">
+    <row r="217" spans="1:8" ht="15.75" thickBot="1">
       <c r="A217" t="s">
         <v>1138</v>
       </c>
@@ -17310,7 +17279,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="218" spans="1:8" ht="15" thickBot="1">
+    <row r="218" spans="1:8" ht="15.75" thickBot="1">
       <c r="A218" t="s">
         <v>1142</v>
       </c>
@@ -17336,7 +17305,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="219" spans="1:8" ht="15" thickBot="1">
+    <row r="219" spans="1:8" ht="15.75" thickBot="1">
       <c r="A219" t="s">
         <v>1140</v>
       </c>
@@ -17356,7 +17325,7 @@
       <c r="G219" s="48"/>
       <c r="H219" s="30"/>
     </row>
-    <row r="220" spans="1:8" ht="15" thickBot="1">
+    <row r="220" spans="1:8" ht="15.75" thickBot="1">
       <c r="A220" t="s">
         <v>1134</v>
       </c>
@@ -17376,7 +17345,7 @@
       <c r="G220" s="48"/>
       <c r="H220" s="30"/>
     </row>
-    <row r="221" spans="1:8" ht="15" thickBot="1">
+    <row r="221" spans="1:8" ht="15.75" thickBot="1">
       <c r="A221" s="1"/>
       <c r="B221" s="104" t="s">
         <v>1203</v>
@@ -17400,7 +17369,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="222" spans="1:8" ht="15" thickBot="1">
+    <row r="222" spans="1:8" ht="15.75" thickBot="1">
       <c r="A222" t="s">
         <v>1139</v>
       </c>
@@ -17426,7 +17395,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="223" spans="1:8" ht="15" thickBot="1">
+    <row r="223" spans="1:8" ht="15.75" thickBot="1">
       <c r="A223" t="s">
         <v>1143</v>
       </c>
@@ -17452,7 +17421,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="224" spans="1:8" ht="15" thickBot="1">
+    <row r="224" spans="1:8" ht="15.75" thickBot="1">
       <c r="A224" t="s">
         <v>1141</v>
       </c>
@@ -17471,7 +17440,7 @@
       <c r="F224" s="17"/>
       <c r="G224"/>
     </row>
-    <row r="225" spans="1:8" ht="15" thickBot="1">
+    <row r="225" spans="1:8" ht="15.75" thickBot="1">
       <c r="A225" t="s">
         <v>1150</v>
       </c>
@@ -17490,7 +17459,7 @@
       </c>
       <c r="G225"/>
     </row>
-    <row r="226" spans="1:8" ht="15" thickBot="1">
+    <row r="226" spans="1:8" ht="15.75" thickBot="1">
       <c r="A226" s="107" t="s">
         <v>1000</v>
       </c>
@@ -17513,7 +17482,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="227" spans="1:8" ht="15" thickBot="1">
+    <row r="227" spans="1:8" ht="15.75" thickBot="1">
       <c r="A227" t="s">
         <v>1152</v>
       </c>
@@ -17532,7 +17501,7 @@
       </c>
       <c r="G227"/>
     </row>
-    <row r="228" spans="1:8" ht="15" thickBot="1">
+    <row r="228" spans="1:8" ht="15.75" thickBot="1">
       <c r="A228" t="s">
         <v>1160</v>
       </c>
@@ -17556,7 +17525,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="229" spans="1:8" ht="15" thickBot="1">
+    <row r="229" spans="1:8" ht="15.75" thickBot="1">
       <c r="A229" t="s">
         <v>1162</v>
       </c>
@@ -17577,7 +17546,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="230" spans="1:8" ht="15" thickBot="1">
+    <row r="230" spans="1:8" ht="15.75" thickBot="1">
       <c r="A230" t="s">
         <v>1156</v>
       </c>
@@ -17601,7 +17570,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="231" spans="1:8" ht="15" thickBot="1">
+    <row r="231" spans="1:8" ht="15.75" thickBot="1">
       <c r="A231" t="s">
         <v>1154</v>
       </c>
@@ -17620,7 +17589,7 @@
       </c>
       <c r="G231" s="48"/>
     </row>
-    <row r="232" spans="1:8" ht="15" thickBot="1">
+    <row r="232" spans="1:8" ht="15.75" thickBot="1">
       <c r="A232" t="s">
         <v>1158</v>
       </c>
@@ -17644,7 +17613,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="233" spans="1:8" ht="15" thickBot="1">
+    <row r="233" spans="1:8" ht="15.75" thickBot="1">
       <c r="A233" t="s">
         <v>1151</v>
       </c>
@@ -17663,7 +17632,7 @@
       </c>
       <c r="G233"/>
     </row>
-    <row r="234" spans="1:8" ht="15" thickBot="1">
+    <row r="234" spans="1:8" ht="15.75" thickBot="1">
       <c r="A234" s="107" t="s">
         <v>1001</v>
       </c>
@@ -17686,7 +17655,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="235" spans="1:8" ht="15" thickBot="1">
+    <row r="235" spans="1:8" ht="15.75" thickBot="1">
       <c r="A235" t="s">
         <v>1153</v>
       </c>
@@ -17705,7 +17674,7 @@
       </c>
       <c r="G235"/>
     </row>
-    <row r="236" spans="1:8" ht="15" thickBot="1">
+    <row r="236" spans="1:8" ht="15.75" thickBot="1">
       <c r="A236" t="s">
         <v>1161</v>
       </c>
@@ -17729,7 +17698,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="237" spans="1:8" ht="15" thickBot="1">
+    <row r="237" spans="1:8" ht="15.75" thickBot="1">
       <c r="A237" t="s">
         <v>1163</v>
       </c>
@@ -17750,7 +17719,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="238" spans="1:8" ht="15" thickBot="1">
+    <row r="238" spans="1:8" ht="15.75" thickBot="1">
       <c r="A238" t="s">
         <v>1157</v>
       </c>
@@ -17769,7 +17738,7 @@
       </c>
       <c r="G238" s="49"/>
     </row>
-    <row r="239" spans="1:8" ht="15" thickBot="1">
+    <row r="239" spans="1:8" ht="15.75" thickBot="1">
       <c r="A239" t="s">
         <v>1155</v>
       </c>
@@ -17793,7 +17762,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="240" spans="1:8" ht="15" thickBot="1">
+    <row r="240" spans="1:8" ht="15.75" thickBot="1">
       <c r="A240" t="s">
         <v>1159</v>
       </c>
@@ -17814,7 +17783,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="241" spans="1:8" ht="15" thickBot="1">
+    <row r="241" spans="1:8" ht="15.75" thickBot="1">
       <c r="A241" t="s">
         <v>1007</v>
       </c>
@@ -17831,7 +17800,7 @@
       <c r="F241" s="17"/>
       <c r="G241"/>
     </row>
-    <row r="242" spans="1:8" ht="15" thickBot="1">
+    <row r="242" spans="1:8" ht="15.75" thickBot="1">
       <c r="A242" s="107" t="s">
         <v>1008</v>
       </c>
@@ -17854,7 +17823,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="243" spans="1:8" ht="15" thickBot="1">
+    <row r="243" spans="1:8" ht="15.75" thickBot="1">
       <c r="A243" t="s">
         <v>1009</v>
       </c>
@@ -17871,7 +17840,7 @@
       <c r="F243" s="17"/>
       <c r="G243" s="48"/>
     </row>
-    <row r="244" spans="1:8" ht="15" thickBot="1">
+    <row r="244" spans="1:8" ht="15.75" thickBot="1">
       <c r="A244" s="107" t="s">
         <v>1010</v>
       </c>
@@ -17894,7 +17863,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="245" spans="1:8" ht="15" thickBot="1">
+    <row r="245" spans="1:8" ht="15.75" thickBot="1">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -17909,7 +17878,7 @@
       </c>
       <c r="G245"/>
     </row>
-    <row r="246" spans="1:8" ht="15" thickBot="1">
+    <row r="246" spans="1:8" ht="15.75" thickBot="1">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -17926,7 +17895,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="247" spans="1:8" ht="15" thickBot="1">
+    <row r="247" spans="1:8" ht="15.75" thickBot="1">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -17946,7 +17915,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="248" spans="1:8" ht="15" thickBot="1">
+    <row r="248" spans="1:8" ht="15.75" thickBot="1">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -17963,7 +17932,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="249" spans="1:8" ht="15" thickBot="1">
+    <row r="249" spans="1:8" ht="15.75" thickBot="1">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -17980,7 +17949,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="250" spans="1:8" ht="15" thickBot="1">
+    <row r="250" spans="1:8" ht="15.75" thickBot="1">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -17995,7 +17964,7 @@
       </c>
       <c r="G250"/>
     </row>
-    <row r="251" spans="1:8" ht="15" thickBot="1">
+    <row r="251" spans="1:8" ht="15.75" thickBot="1">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -18012,7 +17981,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="252" spans="1:8" ht="15" thickBot="1">
+    <row r="252" spans="1:8" ht="15.75" thickBot="1">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -18032,7 +18001,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="253" spans="1:8" ht="15" thickBot="1">
+    <row r="253" spans="1:8" ht="15.75" thickBot="1">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -18161,7 +18130,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="260" spans="1:7" ht="15" thickBot="1">
+    <row r="260" spans="1:7" ht="15.75" thickBot="1">
       <c r="A260" s="9" t="s">
         <v>1038</v>
       </c>
@@ -18180,7 +18149,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="261" spans="1:7" ht="15" thickBot="1">
+    <row r="261" spans="1:7" ht="15.75" thickBot="1">
       <c r="A261" s="9" t="s">
         <v>1038</v>
       </c>
@@ -18197,7 +18166,7 @@
       <c r="F261" s="19"/>
       <c r="G261"/>
     </row>
-    <row r="262" spans="1:7" ht="15" thickBot="1">
+    <row r="262" spans="1:7" ht="15.75" thickBot="1">
       <c r="A262" s="9" t="s">
         <v>1038</v>
       </c>
@@ -18214,7 +18183,7 @@
       <c r="F262" s="19"/>
       <c r="G262"/>
     </row>
-    <row r="263" spans="1:7" ht="15" thickBot="1">
+    <row r="263" spans="1:7" ht="15.75" thickBot="1">
       <c r="A263" s="9" t="s">
         <v>1038</v>
       </c>
@@ -18231,7 +18200,7 @@
       <c r="F263" s="19"/>
       <c r="G263"/>
     </row>
-    <row r="264" spans="1:7" ht="15" thickBot="1">
+    <row r="264" spans="1:7" ht="15.75" thickBot="1">
       <c r="A264" s="9" t="s">
         <v>1038</v>
       </c>
@@ -18248,7 +18217,7 @@
       <c r="F264" s="19"/>
       <c r="G264"/>
     </row>
-    <row r="265" spans="1:7" ht="15" thickBot="1">
+    <row r="265" spans="1:7" ht="15.75" thickBot="1">
       <c r="A265" s="9" t="s">
         <v>1038</v>
       </c>
@@ -18265,7 +18234,7 @@
       <c r="F265" s="19"/>
       <c r="G265"/>
     </row>
-    <row r="266" spans="1:7" ht="15" thickBot="1">
+    <row r="266" spans="1:7" ht="15.75" thickBot="1">
       <c r="A266" s="9" t="s">
         <v>1038</v>
       </c>
@@ -18282,7 +18251,7 @@
       <c r="F266" s="19"/>
       <c r="G266"/>
     </row>
-    <row r="267" spans="1:7" ht="15" thickBot="1">
+    <row r="267" spans="1:7" ht="15.75" thickBot="1">
       <c r="A267" s="9" t="s">
         <v>1038</v>
       </c>
@@ -18299,7 +18268,7 @@
       <c r="F267" s="19"/>
       <c r="G267"/>
     </row>
-    <row r="268" spans="1:7" ht="15" thickBot="1">
+    <row r="268" spans="1:7" ht="15.75" thickBot="1">
       <c r="A268" s="9" t="s">
         <v>1038</v>
       </c>
@@ -18316,7 +18285,7 @@
       <c r="F268" s="19"/>
       <c r="G268"/>
     </row>
-    <row r="269" spans="1:7" ht="15" thickBot="1">
+    <row r="269" spans="1:7" ht="15.75" thickBot="1">
       <c r="A269" s="9" t="s">
         <v>1038</v>
       </c>
@@ -18333,7 +18302,7 @@
       <c r="F269" s="19"/>
       <c r="G269"/>
     </row>
-    <row r="270" spans="1:7" ht="15" thickBot="1">
+    <row r="270" spans="1:7" ht="15.75" thickBot="1">
       <c r="A270" s="9" t="s">
         <v>1038</v>
       </c>
@@ -18350,7 +18319,7 @@
       <c r="F270" s="19"/>
       <c r="G270"/>
     </row>
-    <row r="271" spans="1:7" ht="15" thickBot="1">
+    <row r="271" spans="1:7" ht="15.75" thickBot="1">
       <c r="A271" t="s">
         <v>1040</v>
       </c>
@@ -18364,14 +18333,14 @@
       <c r="E271" s="92" t="s">
         <v>1349</v>
       </c>
-      <c r="F271" s="127" t="s">
-        <v>4</v>
-      </c>
-      <c r="G271" s="128" t="s">
+      <c r="F271" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G271" s="14" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="272" spans="1:7" ht="15" thickBot="1">
+    <row r="272" spans="1:7" ht="15.75" thickBot="1">
       <c r="A272" t="s">
         <v>1039</v>
       </c>
@@ -18412,7 +18381,7 @@
       </c>
     </row>
     <row r="274" spans="1:9">
-      <c r="A274" s="126" t="s">
+      <c r="A274" t="s">
         <v>1365</v>
       </c>
       <c r="B274" s="112" t="s">
@@ -18436,7 +18405,7 @@
       </c>
     </row>
     <row r="275" spans="1:9">
-      <c r="A275" s="126" t="s">
+      <c r="A275" t="s">
         <v>1361</v>
       </c>
       <c r="B275" s="112" t="s">
@@ -18459,8 +18428,8 @@
         <v>153</v>
       </c>
     </row>
-    <row r="276" spans="1:9" ht="15" thickBot="1">
-      <c r="A276" s="126" t="s">
+    <row r="276" spans="1:9" ht="15.75" thickBot="1">
+      <c r="A276" t="s">
         <v>1362</v>
       </c>
       <c r="B276" s="112" t="s">
@@ -18486,7 +18455,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="277" spans="1:9" ht="15" thickBot="1">
+    <row r="277" spans="1:9" ht="15.75" thickBot="1">
       <c r="A277" s="1" t="s">
         <v>1368</v>
       </c>
@@ -18530,7 +18499,7 @@
       </c>
     </row>
     <row r="279" spans="1:9">
-      <c r="A279" s="126" t="s">
+      <c r="A279" t="s">
         <v>1366</v>
       </c>
       <c r="B279" s="112" t="s">
@@ -18554,7 +18523,7 @@
       </c>
     </row>
     <row r="280" spans="1:9">
-      <c r="A280" s="126" t="s">
+      <c r="A280" t="s">
         <v>1364</v>
       </c>
       <c r="B280" s="112" t="s">
@@ -18577,8 +18546,8 @@
         <v>153</v>
       </c>
     </row>
-    <row r="281" spans="1:9" ht="15" thickBot="1">
-      <c r="A281" s="126" t="s">
+    <row r="281" spans="1:9" ht="15.75" thickBot="1">
+      <c r="A281" t="s">
         <v>1363</v>
       </c>
       <c r="B281" s="112" t="s">
@@ -18601,7 +18570,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="282" spans="1:9" ht="15" thickBot="1">
+    <row r="282" spans="1:9" ht="15.75" thickBot="1">
       <c r="A282" s="1" t="s">
         <v>1369</v>
       </c>
@@ -18946,7 +18915,7 @@
       <c r="G297" s="3"/>
       <c r="H297" s="3"/>
     </row>
-    <row r="298" spans="1:8" ht="14.5" customHeight="1">
+    <row r="298" spans="1:8" ht="14.45" customHeight="1">
       <c r="A298" t="s">
         <v>1046</v>
       </c>
@@ -19076,7 +19045,7 @@
       <c r="G303" s="3"/>
       <c r="H303" s="3"/>
     </row>
-    <row r="304" spans="1:8" ht="14.5" customHeight="1" thickBot="1">
+    <row r="304" spans="1:8" ht="14.45" customHeight="1" thickBot="1">
       <c r="A304" t="s">
         <v>1047</v>
       </c>
@@ -19100,7 +19069,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="305" spans="1:8" ht="14.5" customHeight="1" thickBot="1">
+    <row r="305" spans="1:8" ht="14.45" customHeight="1" thickBot="1">
       <c r="A305" t="s">
         <v>1232</v>
       </c>
@@ -19121,7 +19090,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="306" spans="1:8" ht="14.5" customHeight="1">
+    <row r="306" spans="1:8" ht="14.45" customHeight="1">
       <c r="A306" t="s">
         <v>1240</v>
       </c>
@@ -19138,7 +19107,7 @@
       <c r="F306" s="14"/>
       <c r="G306" s="14"/>
     </row>
-    <row r="307" spans="1:8" ht="14.5" customHeight="1">
+    <row r="307" spans="1:8" ht="14.45" customHeight="1">
       <c r="A307" s="14" t="s">
         <v>1234</v>
       </c>
@@ -19162,7 +19131,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="308" spans="1:8" ht="14.5" customHeight="1">
+    <row r="308" spans="1:8" ht="14.45" customHeight="1">
       <c r="A308" s="14" t="s">
         <v>1242</v>
       </c>
@@ -19360,7 +19329,7 @@
       <c r="G324" s="3"/>
       <c r="H324" s="3"/>
     </row>
-    <row r="325" spans="4:8" ht="15" thickBot="1">
+    <row r="325" spans="4:8" ht="15.75" thickBot="1">
       <c r="D325" s="14" t="s">
         <v>789</v>
       </c>
@@ -19373,7 +19342,7 @@
       <c r="G325" s="3"/>
       <c r="H325" s="3"/>
     </row>
-    <row r="326" spans="4:8" ht="26.5" thickBot="1">
+    <row r="326" spans="4:8" ht="26.25" thickBot="1">
       <c r="D326" s="14"/>
       <c r="E326" s="59" t="s">
         <v>860</v>
@@ -19397,7 +19366,7 @@
       <c r="G327" s="3"/>
       <c r="H327" s="3"/>
     </row>
-    <row r="328" spans="4:8" ht="15" thickBot="1">
+    <row r="328" spans="4:8" ht="15.75" thickBot="1">
       <c r="D328" s="14" t="s">
         <v>789</v>
       </c>
@@ -19410,7 +19379,7 @@
       <c r="G328" s="3"/>
       <c r="H328" s="3"/>
     </row>
-    <row r="329" spans="4:8" ht="26.5" thickBot="1">
+    <row r="329" spans="4:8" ht="26.25" thickBot="1">
       <c r="D329" s="14"/>
       <c r="E329" s="59" t="s">
         <v>861</v>
@@ -20041,7 +20010,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="368" spans="1:8" ht="15.5">
+    <row r="368" spans="1:8" ht="15.75">
       <c r="A368" s="14"/>
       <c r="B368" s="14"/>
       <c r="C368" s="14"/>
@@ -20141,7 +20110,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="373" spans="1:8" ht="15.5">
+    <row r="373" spans="1:8" ht="15.75">
       <c r="A373" s="14"/>
       <c r="B373" s="14"/>
       <c r="C373" s="14"/>
@@ -20178,7 +20147,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="375" spans="1:8" ht="15.5">
+    <row r="375" spans="1:8" ht="15.75">
       <c r="A375" s="14"/>
       <c r="B375" s="14"/>
       <c r="C375" s="14"/>
@@ -20233,7 +20202,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="378" spans="1:8" ht="15.5">
+    <row r="378" spans="1:8" ht="15.75">
       <c r="A378" s="14"/>
       <c r="B378" s="14"/>
       <c r="C378" s="14"/>
@@ -20311,7 +20280,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="382" spans="1:8" ht="15.5">
+    <row r="382" spans="1:8" ht="15.75">
       <c r="A382" s="14"/>
       <c r="B382" s="14"/>
       <c r="C382" s="14"/>
@@ -20389,7 +20358,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="386" spans="1:8" ht="15.5">
+    <row r="386" spans="1:8" ht="15.75">
       <c r="A386" s="14"/>
       <c r="B386" s="14"/>
       <c r="C386" s="14"/>
@@ -20407,7 +20376,7 @@
       </c>
       <c r="H386" s="5"/>
     </row>
-    <row r="387" spans="1:8" ht="15" thickBot="1">
+    <row r="387" spans="1:8" ht="15.75" thickBot="1">
       <c r="A387" s="14"/>
       <c r="B387" s="14"/>
       <c r="C387" s="14"/>
@@ -20427,7 +20396,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="388" spans="1:8" ht="15" thickBot="1">
+    <row r="388" spans="1:8" ht="15.75" thickBot="1">
       <c r="A388" s="14"/>
       <c r="B388" s="14"/>
       <c r="C388" s="14"/>
@@ -20443,7 +20412,7 @@
       <c r="G388" s="47"/>
       <c r="H388" s="14"/>
     </row>
-    <row r="389" spans="1:8" ht="15" thickBot="1">
+    <row r="389" spans="1:8" ht="15.75" thickBot="1">
       <c r="A389" s="14"/>
       <c r="B389" s="14"/>
       <c r="C389" s="14"/>
@@ -20459,7 +20428,7 @@
       <c r="G389" s="47"/>
       <c r="H389" s="14"/>
     </row>
-    <row r="390" spans="1:8" ht="15.5">
+    <row r="390" spans="1:8" ht="15.75">
       <c r="D390" s="14" t="s">
         <v>789</v>
       </c>
@@ -20530,7 +20499,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="394" spans="1:8" ht="15.5">
+    <row r="394" spans="1:8" ht="15.75">
       <c r="A394" s="14"/>
       <c r="B394" s="14"/>
       <c r="C394" s="14"/>
@@ -20590,7 +20559,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="397" spans="1:8" ht="15" thickBot="1">
+    <row r="397" spans="1:8" ht="15.75" thickBot="1">
       <c r="A397" s="14"/>
       <c r="B397" s="14"/>
       <c r="C397" s="14"/>
@@ -20610,7 +20579,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="398" spans="1:8" ht="15" thickBot="1">
+    <row r="398" spans="1:8" ht="15.75" thickBot="1">
       <c r="A398" s="14"/>
       <c r="B398" s="14"/>
       <c r="C398" s="14"/>
@@ -20630,7 +20599,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="399" spans="1:8" ht="15" thickBot="1">
+    <row r="399" spans="1:8" ht="15.75" thickBot="1">
       <c r="A399" s="14"/>
       <c r="B399" s="14"/>
       <c r="C399" s="14"/>
@@ -20650,7 +20619,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="400" spans="1:8" ht="15" thickBot="1">
+    <row r="400" spans="1:8" ht="15.75" thickBot="1">
       <c r="A400" s="14"/>
       <c r="B400" s="14"/>
       <c r="C400" s="14"/>
@@ -20670,7 +20639,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="401" spans="1:8" ht="15" thickBot="1">
+    <row r="401" spans="1:8" ht="15.75" thickBot="1">
       <c r="A401" s="14"/>
       <c r="B401" s="14"/>
       <c r="C401" s="14"/>
@@ -20690,7 +20659,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="402" spans="1:8" ht="15" thickBot="1">
+    <row r="402" spans="1:8" ht="15.75" thickBot="1">
       <c r="A402" s="14"/>
       <c r="B402" s="14"/>
       <c r="C402" s="14"/>
@@ -20710,7 +20679,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="403" spans="1:8" ht="15" thickBot="1">
+    <row r="403" spans="1:8" ht="15.75" thickBot="1">
       <c r="A403" s="14"/>
       <c r="B403" s="14"/>
       <c r="C403" s="14"/>
@@ -20730,7 +20699,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="404" spans="1:8" ht="15" thickBot="1">
+    <row r="404" spans="1:8" ht="15.75" thickBot="1">
       <c r="A404" s="14"/>
       <c r="B404" s="14"/>
       <c r="C404" s="14"/>
@@ -20750,7 +20719,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="405" spans="1:8" ht="15" thickBot="1">
+    <row r="405" spans="1:8" ht="15.75" thickBot="1">
       <c r="A405" s="14"/>
       <c r="B405" s="14"/>
       <c r="C405" s="14"/>
@@ -20770,7 +20739,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="406" spans="1:8" ht="15" thickBot="1">
+    <row r="406" spans="1:8" ht="15.75" thickBot="1">
       <c r="A406" s="14"/>
       <c r="B406" s="14"/>
       <c r="C406" s="14"/>
@@ -20790,7 +20759,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="407" spans="1:8" ht="15" thickBot="1">
+    <row r="407" spans="1:8" ht="15.75" thickBot="1">
       <c r="A407" s="14"/>
       <c r="B407" s="14"/>
       <c r="C407" s="14"/>
@@ -20810,7 +20779,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="408" spans="1:8" ht="15" thickBot="1">
+    <row r="408" spans="1:8" ht="15.75" thickBot="1">
       <c r="A408" s="14"/>
       <c r="B408" s="14"/>
       <c r="C408" s="14"/>
@@ -20830,7 +20799,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="409" spans="1:8" ht="15" thickBot="1">
+    <row r="409" spans="1:8" ht="15.75" thickBot="1">
       <c r="A409" s="14"/>
       <c r="B409" s="14"/>
       <c r="C409" s="14"/>
@@ -20847,7 +20816,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="410" spans="1:8" ht="15" thickBot="1">
+    <row r="410" spans="1:8" ht="15.75" thickBot="1">
       <c r="A410" s="14"/>
       <c r="B410" s="14"/>
       <c r="C410" s="14"/>
@@ -20864,7 +20833,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="411" spans="1:8" ht="15" thickBot="1">
+    <row r="411" spans="1:8" ht="15.75" thickBot="1">
       <c r="A411" s="14"/>
       <c r="B411" s="14"/>
       <c r="C411" s="14"/>
@@ -20881,7 +20850,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="412" spans="1:8" ht="15" thickBot="1">
+    <row r="412" spans="1:8" ht="15.75" thickBot="1">
       <c r="A412" s="14"/>
       <c r="B412" s="14"/>
       <c r="C412" s="14"/>
@@ -20898,7 +20867,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="413" spans="1:8" ht="15" thickBot="1">
+    <row r="413" spans="1:8" ht="15.75" thickBot="1">
       <c r="A413" s="14"/>
       <c r="B413" s="14"/>
       <c r="C413" s="14"/>
@@ -20915,7 +20884,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="414" spans="1:8" ht="15" thickBot="1">
+    <row r="414" spans="1:8" ht="15.75" thickBot="1">
       <c r="A414" s="14"/>
       <c r="B414" s="14"/>
       <c r="C414" s="14"/>
@@ -20932,7 +20901,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="415" spans="1:8" ht="15" thickBot="1">
+    <row r="415" spans="1:8" ht="15.75" thickBot="1">
       <c r="A415" s="14"/>
       <c r="B415" s="14"/>
       <c r="C415" s="14"/>
@@ -20949,7 +20918,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="416" spans="1:8" ht="15" thickBot="1">
+    <row r="416" spans="1:8" ht="15.75" thickBot="1">
       <c r="A416" s="14"/>
       <c r="B416" s="14"/>
       <c r="C416" s="14"/>
@@ -20966,7 +20935,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="417" spans="1:8" ht="15" thickBot="1">
+    <row r="417" spans="1:8" ht="15.75" thickBot="1">
       <c r="A417" s="14"/>
       <c r="B417" s="14"/>
       <c r="C417" s="14"/>
@@ -20984,7 +20953,7 @@
       </c>
       <c r="H417" s="42"/>
     </row>
-    <row r="418" spans="1:8" ht="15" thickBot="1">
+    <row r="418" spans="1:8" ht="15.75" thickBot="1">
       <c r="A418" s="14"/>
       <c r="B418" s="14"/>
       <c r="C418" s="14"/>
@@ -21004,7 +20973,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="419" spans="1:8" ht="15" thickBot="1">
+    <row r="419" spans="1:8" ht="15.75" thickBot="1">
       <c r="A419" s="14"/>
       <c r="B419" s="14"/>
       <c r="C419" s="14"/>
@@ -21024,7 +20993,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="420" spans="1:8" ht="15" thickBot="1">
+    <row r="420" spans="1:8" ht="15.75" thickBot="1">
       <c r="A420" s="14"/>
       <c r="B420" s="14"/>
       <c r="C420" s="14"/>
@@ -21044,7 +21013,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="421" spans="1:8" ht="15" thickBot="1">
+    <row r="421" spans="1:8" ht="15.75" thickBot="1">
       <c r="A421" s="14"/>
       <c r="B421" s="14"/>
       <c r="C421" s="14"/>
@@ -21064,7 +21033,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="422" spans="1:8" ht="15" thickBot="1">
+    <row r="422" spans="1:8" ht="15.75" thickBot="1">
       <c r="A422" s="14"/>
       <c r="B422" s="14"/>
       <c r="C422" s="14"/>
@@ -21084,7 +21053,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="423" spans="1:8" ht="15" thickBot="1">
+    <row r="423" spans="1:8" ht="15.75" thickBot="1">
       <c r="A423" s="14"/>
       <c r="B423" s="14"/>
       <c r="C423" s="14"/>
@@ -21104,7 +21073,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="424" spans="1:8" ht="15" thickBot="1">
+    <row r="424" spans="1:8" ht="15.75" thickBot="1">
       <c r="A424" s="14"/>
       <c r="B424" s="14"/>
       <c r="C424" s="14"/>
@@ -21124,7 +21093,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="425" spans="1:8" ht="15" thickBot="1">
+    <row r="425" spans="1:8" ht="15.75" thickBot="1">
       <c r="A425" s="14"/>
       <c r="B425" s="14"/>
       <c r="C425" s="14"/>
@@ -21144,7 +21113,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="426" spans="1:8" ht="15" thickBot="1">
+    <row r="426" spans="1:8" ht="15.75" thickBot="1">
       <c r="A426" s="14"/>
       <c r="B426" s="14"/>
       <c r="C426" s="14"/>
@@ -21164,7 +21133,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="427" spans="1:8" ht="15" thickBot="1">
+    <row r="427" spans="1:8" ht="15.75" thickBot="1">
       <c r="A427" s="14"/>
       <c r="B427" s="14"/>
       <c r="C427" s="14"/>
@@ -21184,7 +21153,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="428" spans="1:8" ht="15" thickBot="1">
+    <row r="428" spans="1:8" ht="15.75" thickBot="1">
       <c r="A428" s="14"/>
       <c r="B428" s="14"/>
       <c r="C428" s="14"/>
@@ -21204,7 +21173,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="429" spans="1:8" ht="15" thickBot="1">
+    <row r="429" spans="1:8" ht="15.75" thickBot="1">
       <c r="A429" s="14"/>
       <c r="B429" s="14"/>
       <c r="C429" s="14"/>
@@ -21221,7 +21190,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="430" spans="1:8" ht="15" thickBot="1">
+    <row r="430" spans="1:8" ht="15.75" thickBot="1">
       <c r="A430" s="14"/>
       <c r="B430" s="14"/>
       <c r="C430" s="14"/>
@@ -21238,7 +21207,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="431" spans="1:8" ht="15" thickBot="1">
+    <row r="431" spans="1:8" ht="15.75" thickBot="1">
       <c r="A431" s="14"/>
       <c r="B431" s="14"/>
       <c r="C431" s="14"/>
@@ -21255,7 +21224,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="432" spans="1:8" ht="15" thickBot="1">
+    <row r="432" spans="1:8" ht="15.75" thickBot="1">
       <c r="A432" s="14"/>
       <c r="B432" s="14"/>
       <c r="C432" s="14"/>
@@ -21272,7 +21241,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="433" spans="1:8" ht="15" thickBot="1">
+    <row r="433" spans="1:8" ht="15.75" thickBot="1">
       <c r="A433" s="14"/>
       <c r="B433" s="14"/>
       <c r="C433" s="14"/>
@@ -21289,7 +21258,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="434" spans="1:8" ht="15" thickBot="1">
+    <row r="434" spans="1:8" ht="15.75" thickBot="1">
       <c r="A434" s="14"/>
       <c r="B434" s="14"/>
       <c r="C434" s="14"/>
@@ -21306,7 +21275,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="435" spans="1:8" ht="15" thickBot="1">
+    <row r="435" spans="1:8" ht="15.75" thickBot="1">
       <c r="A435" s="14"/>
       <c r="B435" s="14"/>
       <c r="C435" s="14"/>
@@ -21323,7 +21292,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="436" spans="1:8" ht="15" thickBot="1">
+    <row r="436" spans="1:8" ht="15.75" thickBot="1">
       <c r="A436" s="14"/>
       <c r="B436" s="14"/>
       <c r="C436" s="14"/>
@@ -21340,7 +21309,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="437" spans="1:8" ht="15" thickBot="1">
+    <row r="437" spans="1:8" ht="15.75" thickBot="1">
       <c r="A437" s="14"/>
       <c r="B437" s="14"/>
       <c r="C437" s="14"/>
@@ -21358,7 +21327,7 @@
       </c>
       <c r="H437" s="42"/>
     </row>
-    <row r="438" spans="1:8" ht="15" thickBot="1">
+    <row r="438" spans="1:8" ht="15.75" thickBot="1">
       <c r="A438" s="14"/>
       <c r="B438" s="14"/>
       <c r="C438" s="14"/>
@@ -21378,7 +21347,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="439" spans="1:8" ht="15" thickBot="1">
+    <row r="439" spans="1:8" ht="15.75" thickBot="1">
       <c r="A439" s="14"/>
       <c r="B439" s="14"/>
       <c r="C439" s="14"/>
@@ -21398,7 +21367,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="440" spans="1:8" ht="15" thickBot="1">
+    <row r="440" spans="1:8" ht="15.75" thickBot="1">
       <c r="A440" s="14"/>
       <c r="B440" s="14"/>
       <c r="C440" s="14"/>
@@ -21418,7 +21387,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="441" spans="1:8" ht="15" thickBot="1">
+    <row r="441" spans="1:8" ht="15.75" thickBot="1">
       <c r="A441" s="14"/>
       <c r="B441" s="14"/>
       <c r="C441" s="14"/>
@@ -21438,7 +21407,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="442" spans="1:8" ht="15" thickBot="1">
+    <row r="442" spans="1:8" ht="15.75" thickBot="1">
       <c r="A442" s="14"/>
       <c r="B442" s="14"/>
       <c r="C442" s="14"/>
@@ -21458,7 +21427,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="443" spans="1:8" ht="15" thickBot="1">
+    <row r="443" spans="1:8" ht="15.75" thickBot="1">
       <c r="A443" s="14"/>
       <c r="B443" s="14"/>
       <c r="C443" s="14"/>
@@ -21478,7 +21447,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="444" spans="1:8" ht="15" thickBot="1">
+    <row r="444" spans="1:8" ht="15.75" thickBot="1">
       <c r="A444" s="14"/>
       <c r="B444" s="14"/>
       <c r="C444" s="14"/>
@@ -21498,7 +21467,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="445" spans="1:8" ht="15" thickBot="1">
+    <row r="445" spans="1:8" ht="15.75" thickBot="1">
       <c r="A445" s="14"/>
       <c r="B445" s="14"/>
       <c r="C445" s="14"/>
@@ -21518,7 +21487,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="446" spans="1:8" ht="15" thickBot="1">
+    <row r="446" spans="1:8" ht="15.75" thickBot="1">
       <c r="A446" s="14"/>
       <c r="B446" s="14"/>
       <c r="C446" s="14"/>
@@ -21538,7 +21507,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="447" spans="1:8" ht="15" thickBot="1">
+    <row r="447" spans="1:8" ht="15.75" thickBot="1">
       <c r="A447" s="14"/>
       <c r="B447" s="14"/>
       <c r="C447" s="14"/>
@@ -21555,7 +21524,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="448" spans="1:8" ht="15" thickBot="1">
+    <row r="448" spans="1:8" ht="15.75" thickBot="1">
       <c r="A448" s="14"/>
       <c r="B448" s="14"/>
       <c r="C448" s="14"/>
@@ -21573,7 +21542,7 @@
       </c>
       <c r="H448" s="44"/>
     </row>
-    <row r="449" spans="1:8" ht="15" thickBot="1">
+    <row r="449" spans="1:8" ht="15.75" thickBot="1">
       <c r="A449" s="14"/>
       <c r="B449" s="14"/>
       <c r="C449" s="14"/>
@@ -21591,7 +21560,7 @@
       </c>
       <c r="H449" s="45"/>
     </row>
-    <row r="450" spans="1:8" ht="15" thickBot="1">
+    <row r="450" spans="1:8" ht="15.75" thickBot="1">
       <c r="A450" s="14"/>
       <c r="B450" s="14"/>
       <c r="C450" s="14"/>
@@ -21609,7 +21578,7 @@
       </c>
       <c r="H450" s="45"/>
     </row>
-    <row r="451" spans="1:8" ht="15" thickBot="1">
+    <row r="451" spans="1:8" ht="15.75" thickBot="1">
       <c r="A451" s="14"/>
       <c r="B451" s="14"/>
       <c r="C451" s="14"/>
@@ -21626,7 +21595,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="452" spans="1:8" ht="15" thickBot="1">
+    <row r="452" spans="1:8" ht="15.75" thickBot="1">
       <c r="A452" s="14"/>
       <c r="B452" s="14"/>
       <c r="C452" s="14"/>
@@ -21643,7 +21612,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="453" spans="1:8" ht="15" thickBot="1">
+    <row r="453" spans="1:8" ht="15.75" thickBot="1">
       <c r="A453" s="14"/>
       <c r="B453" s="14"/>
       <c r="C453" s="14"/>
@@ -21660,7 +21629,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="454" spans="1:8" ht="15" thickBot="1">
+    <row r="454" spans="1:8" ht="15.75" thickBot="1">
       <c r="A454" s="14"/>
       <c r="B454" s="14"/>
       <c r="C454" s="14"/>
@@ -21677,7 +21646,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="455" spans="1:8" ht="15" thickBot="1">
+    <row r="455" spans="1:8" ht="15.75" thickBot="1">
       <c r="A455" s="14"/>
       <c r="B455" s="14"/>
       <c r="C455" s="14"/>
@@ -21697,7 +21666,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="456" spans="1:8" ht="15" thickBot="1">
+    <row r="456" spans="1:8" ht="15.75" thickBot="1">
       <c r="A456" s="14"/>
       <c r="B456" s="14"/>
       <c r="C456" s="14"/>
@@ -21717,7 +21686,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="457" spans="1:8" ht="15" thickBot="1">
+    <row r="457" spans="1:8" ht="15.75" thickBot="1">
       <c r="A457" s="14"/>
       <c r="B457" s="14"/>
       <c r="C457" s="14"/>
@@ -21734,7 +21703,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="458" spans="1:8" ht="15" thickBot="1">
+    <row r="458" spans="1:8" ht="15.75" thickBot="1">
       <c r="A458" s="14"/>
       <c r="B458" s="14"/>
       <c r="C458" s="14"/>
@@ -21754,7 +21723,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="459" spans="1:8" ht="15" thickBot="1">
+    <row r="459" spans="1:8" ht="15.75" thickBot="1">
       <c r="A459" s="14"/>
       <c r="B459" s="14"/>
       <c r="C459" s="14"/>
@@ -21774,7 +21743,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="460" spans="1:8" ht="15" thickBot="1">
+    <row r="460" spans="1:8" ht="15.75" thickBot="1">
       <c r="A460" s="14"/>
       <c r="B460" s="14"/>
       <c r="C460" s="14"/>
@@ -21794,7 +21763,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="461" spans="1:8" ht="15" thickBot="1">
+    <row r="461" spans="1:8" ht="15.75" thickBot="1">
       <c r="A461" s="14"/>
       <c r="B461" s="14"/>
       <c r="C461" s="14"/>
@@ -21811,7 +21780,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="462" spans="1:8" ht="15" thickBot="1">
+    <row r="462" spans="1:8" ht="15.75" thickBot="1">
       <c r="A462" s="14"/>
       <c r="B462" s="14"/>
       <c r="C462" s="14"/>
@@ -21831,7 +21800,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="463" spans="1:8" ht="15" thickBot="1">
+    <row r="463" spans="1:8" ht="15.75" thickBot="1">
       <c r="A463" s="14"/>
       <c r="B463" s="14"/>
       <c r="C463" s="14"/>
@@ -21851,7 +21820,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="464" spans="1:8" ht="15" thickBot="1">
+    <row r="464" spans="1:8" ht="15.75" thickBot="1">
       <c r="A464" s="14"/>
       <c r="B464" s="14"/>
       <c r="C464" s="14"/>
@@ -21871,7 +21840,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="465" spans="1:8" ht="15" thickBot="1">
+    <row r="465" spans="1:8" ht="15.75" thickBot="1">
       <c r="A465" s="14"/>
       <c r="B465" s="14"/>
       <c r="C465" s="14"/>
@@ -21891,7 +21860,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="466" spans="1:8" ht="15" thickBot="1">
+    <row r="466" spans="1:8" ht="15.75" thickBot="1">
       <c r="A466" s="14"/>
       <c r="B466" s="14"/>
       <c r="C466" s="14"/>
@@ -21911,7 +21880,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="467" spans="1:8" ht="15" thickBot="1">
+    <row r="467" spans="1:8" ht="15.75" thickBot="1">
       <c r="A467" s="14"/>
       <c r="B467" s="14"/>
       <c r="C467" s="14"/>
@@ -21931,7 +21900,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="468" spans="1:8" ht="15" thickBot="1">
+    <row r="468" spans="1:8" ht="15.75" thickBot="1">
       <c r="A468" s="14"/>
       <c r="B468" s="14"/>
       <c r="C468" s="14"/>
@@ -21951,7 +21920,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="469" spans="1:8" ht="15" thickBot="1">
+    <row r="469" spans="1:8" ht="15.75" thickBot="1">
       <c r="A469" s="14"/>
       <c r="B469" s="14"/>
       <c r="C469" s="14"/>
@@ -21971,7 +21940,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="470" spans="1:8" ht="15" thickBot="1">
+    <row r="470" spans="1:8" ht="15.75" thickBot="1">
       <c r="A470" s="14"/>
       <c r="B470" s="14"/>
       <c r="C470" s="14"/>
@@ -21991,7 +21960,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="471" spans="1:8" ht="15" thickBot="1">
+    <row r="471" spans="1:8" ht="15.75" thickBot="1">
       <c r="A471" s="14"/>
       <c r="B471" s="14"/>
       <c r="C471" s="14"/>
@@ -22011,7 +21980,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="472" spans="1:8" ht="15" thickBot="1">
+    <row r="472" spans="1:8" ht="15.75" thickBot="1">
       <c r="A472" s="14"/>
       <c r="B472" s="14"/>
       <c r="C472" s="14"/>
@@ -22028,7 +21997,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="473" spans="1:8" ht="15" thickBot="1">
+    <row r="473" spans="1:8" ht="15.75" thickBot="1">
       <c r="A473" s="14"/>
       <c r="B473" s="14"/>
       <c r="C473" s="14"/>
@@ -22048,7 +22017,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="474" spans="1:8" ht="15" thickBot="1">
+    <row r="474" spans="1:8" ht="15.75" thickBot="1">
       <c r="A474" s="14"/>
       <c r="B474" s="14"/>
       <c r="C474" s="14"/>
@@ -22068,7 +22037,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="475" spans="1:8" ht="15" thickBot="1">
+    <row r="475" spans="1:8" ht="15.75" thickBot="1">
       <c r="A475" s="14"/>
       <c r="B475" s="14"/>
       <c r="C475" s="14"/>
@@ -22088,7 +22057,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="476" spans="1:8" ht="15" thickBot="1">
+    <row r="476" spans="1:8" ht="15.75" thickBot="1">
       <c r="A476" s="14"/>
       <c r="B476" s="14"/>
       <c r="C476" s="14"/>
@@ -22105,7 +22074,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="477" spans="1:8" ht="15" thickBot="1">
+    <row r="477" spans="1:8" ht="15.75" thickBot="1">
       <c r="A477" s="14"/>
       <c r="B477" s="14"/>
       <c r="C477" s="14"/>
@@ -22125,7 +22094,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="478" spans="1:8" ht="15" thickBot="1">
+    <row r="478" spans="1:8" ht="15.75" thickBot="1">
       <c r="A478" s="14"/>
       <c r="B478" s="14"/>
       <c r="C478" s="14"/>
@@ -22145,7 +22114,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="479" spans="1:8" ht="15" thickBot="1">
+    <row r="479" spans="1:8" ht="15.75" thickBot="1">
       <c r="A479" s="14"/>
       <c r="B479" s="14"/>
       <c r="C479" s="14"/>
@@ -22162,7 +22131,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="480" spans="1:8" ht="15" thickBot="1">
+    <row r="480" spans="1:8" ht="15.75" thickBot="1">
       <c r="A480" s="14"/>
       <c r="B480" s="14"/>
       <c r="C480" s="14"/>
@@ -22179,7 +22148,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="481" spans="1:8" ht="15" thickBot="1">
+    <row r="481" spans="1:8" ht="15.75" thickBot="1">
       <c r="A481" s="14"/>
       <c r="B481" s="14"/>
       <c r="C481" s="14"/>
@@ -22196,7 +22165,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="482" spans="1:8" ht="15" thickBot="1">
+    <row r="482" spans="1:8" ht="15.75" thickBot="1">
       <c r="A482" s="14"/>
       <c r="B482" s="14"/>
       <c r="C482" s="14"/>
@@ -22213,7 +22182,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="483" spans="1:8" ht="15" thickBot="1">
+    <row r="483" spans="1:8" ht="15.75" thickBot="1">
       <c r="A483" s="14"/>
       <c r="B483" s="14"/>
       <c r="C483" s="14"/>
@@ -22233,7 +22202,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="484" spans="1:8" ht="15" thickBot="1">
+    <row r="484" spans="1:8" ht="15.75" thickBot="1">
       <c r="A484" s="14"/>
       <c r="B484" s="14"/>
       <c r="C484" s="14"/>
@@ -22250,7 +22219,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="485" spans="1:8" ht="15" thickBot="1">
+    <row r="485" spans="1:8" ht="15.75" thickBot="1">
       <c r="A485" s="14"/>
       <c r="B485" s="14"/>
       <c r="C485" s="14"/>
@@ -22267,7 +22236,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="486" spans="1:8" ht="15" thickBot="1">
+    <row r="486" spans="1:8" ht="15.75" thickBot="1">
       <c r="A486" s="14"/>
       <c r="B486" s="14"/>
       <c r="C486" s="14"/>
@@ -22626,7 +22595,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="506" spans="1:8" ht="15.5">
+    <row r="506" spans="1:8" ht="15.75">
       <c r="A506" s="1"/>
       <c r="B506" s="1"/>
       <c r="C506" s="1"/>
@@ -22865,7 +22834,7 @@
       <c r="G523" s="38"/>
       <c r="H523" s="14"/>
     </row>
-    <row r="524" spans="1:8" ht="15.5">
+    <row r="524" spans="1:8" ht="15.75">
       <c r="A524" s="1"/>
       <c r="B524" s="1"/>
       <c r="C524" s="1"/>
@@ -22881,7 +22850,7 @@
       </c>
       <c r="H524" s="5"/>
     </row>
-    <row r="525" spans="1:8" ht="15.5">
+    <row r="525" spans="1:8" ht="15.75">
       <c r="A525" s="1"/>
       <c r="B525" s="1"/>
       <c r="C525" s="1"/>
@@ -22927,7 +22896,7 @@
       <c r="G528" s="4"/>
       <c r="H528" s="3"/>
     </row>
-    <row r="529" spans="1:8" ht="15.5">
+    <row r="529" spans="1:8" ht="15.75">
       <c r="A529" s="1"/>
       <c r="B529" s="1"/>
       <c r="C529" s="1"/>
@@ -22937,7 +22906,7 @@
       <c r="G529" s="4"/>
       <c r="H529" s="5"/>
     </row>
-    <row r="530" spans="1:8" ht="15.5">
+    <row r="530" spans="1:8" ht="15.75">
       <c r="A530" s="1"/>
       <c r="B530" s="1"/>
       <c r="C530" s="1"/>
@@ -22947,7 +22916,7 @@
       <c r="G530" s="4"/>
       <c r="H530" s="5"/>
     </row>
-    <row r="531" spans="1:8" ht="15.5">
+    <row r="531" spans="1:8" ht="15.75">
       <c r="A531" s="1"/>
       <c r="B531" s="1"/>
       <c r="C531" s="1"/>
@@ -23029,7 +22998,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="536" spans="1:8">
+    <row r="536" spans="1:8" ht="26.25">
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
       <c r="C536" s="1"/>
@@ -23047,7 +23016,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="537" spans="1:8" ht="26">
+    <row r="537" spans="1:8" ht="26.25">
       <c r="A537" s="7"/>
       <c r="B537" s="7"/>
       <c r="C537" s="7"/>
@@ -23070,27 +23039,27 @@
       <c r="B538" s="12"/>
       <c r="C538" s="12"/>
       <c r="D538" s="12"/>
-      <c r="E538" s="115" t="s">
+      <c r="E538" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="F538" s="116" t="s">
-        <v>4</v>
-      </c>
-      <c r="G538" s="117" t="s">
+      <c r="F538" s="117" t="s">
+        <v>4</v>
+      </c>
+      <c r="G538" s="118" t="s">
         <v>36</v>
       </c>
       <c r="H538" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="539" spans="1:8" ht="25" customHeight="1">
+    <row r="539" spans="1:8" ht="24.95" customHeight="1">
       <c r="A539" s="12"/>
       <c r="B539" s="12"/>
       <c r="C539" s="12"/>
       <c r="D539" s="12"/>
-      <c r="E539" s="115"/>
-      <c r="F539" s="116"/>
-      <c r="G539" s="117"/>
+      <c r="E539" s="116"/>
+      <c r="F539" s="117"/>
+      <c r="G539" s="118"/>
       <c r="H539" s="3" t="s">
         <v>38</v>
       </c>
@@ -23118,13 +23087,13 @@
       <c r="B542" s="1"/>
       <c r="C542" s="1"/>
       <c r="D542" s="1"/>
-      <c r="E542" s="118" t="s">
+      <c r="E542" s="119" t="s">
         <v>42</v>
       </c>
-      <c r="F542" s="116" t="s">
-        <v>4</v>
-      </c>
-      <c r="G542" s="117" t="s">
+      <c r="F542" s="117" t="s">
+        <v>4</v>
+      </c>
+      <c r="G542" s="118" t="s">
         <v>43</v>
       </c>
       <c r="H542" s="3">
@@ -23136,9 +23105,9 @@
       <c r="B543" s="1"/>
       <c r="C543" s="1"/>
       <c r="D543" s="1"/>
-      <c r="E543" s="118"/>
-      <c r="F543" s="116"/>
-      <c r="G543" s="117"/>
+      <c r="E543" s="119"/>
+      <c r="F543" s="117"/>
+      <c r="G543" s="118"/>
       <c r="H543" s="3" t="s">
         <v>44</v>
       </c>
@@ -23148,13 +23117,13 @@
       <c r="B544" s="12"/>
       <c r="C544" s="12"/>
       <c r="D544" s="12"/>
-      <c r="E544" s="115" t="s">
+      <c r="E544" s="116" t="s">
         <v>45</v>
       </c>
-      <c r="F544" s="116" t="s">
-        <v>4</v>
-      </c>
-      <c r="G544" s="117" t="s">
+      <c r="F544" s="117" t="s">
+        <v>4</v>
+      </c>
+      <c r="G544" s="118" t="s">
         <v>46</v>
       </c>
       <c r="H544" s="3" t="s">
@@ -23166,9 +23135,9 @@
       <c r="B545" s="12"/>
       <c r="C545" s="12"/>
       <c r="D545" s="12"/>
-      <c r="E545" s="115"/>
-      <c r="F545" s="116"/>
-      <c r="G545" s="117"/>
+      <c r="E545" s="116"/>
+      <c r="F545" s="117"/>
+      <c r="G545" s="118"/>
       <c r="H545" s="3" t="s">
         <v>48</v>
       </c>
@@ -23196,13 +23165,13 @@
       <c r="B548" s="1"/>
       <c r="C548" s="1"/>
       <c r="D548" s="1"/>
-      <c r="E548" s="118" t="s">
+      <c r="E548" s="119" t="s">
         <v>52</v>
       </c>
-      <c r="F548" s="116" t="s">
+      <c r="F548" s="117" t="s">
         <v>2</v>
       </c>
-      <c r="G548" s="117" t="s">
+      <c r="G548" s="118" t="s">
         <v>53</v>
       </c>
       <c r="H548" s="3">
@@ -23214,9 +23183,9 @@
       <c r="B549" s="1"/>
       <c r="C549" s="1"/>
       <c r="D549" s="1"/>
-      <c r="E549" s="118"/>
-      <c r="F549" s="116"/>
-      <c r="G549" s="117"/>
+      <c r="E549" s="119"/>
+      <c r="F549" s="117"/>
+      <c r="G549" s="118"/>
       <c r="H549" s="3" t="s">
         <v>44</v>
       </c>
@@ -23226,13 +23195,13 @@
       <c r="B550" s="1"/>
       <c r="C550" s="1"/>
       <c r="D550" s="1"/>
-      <c r="E550" s="115" t="s">
+      <c r="E550" s="116" t="s">
         <v>54</v>
       </c>
-      <c r="F550" s="116" t="s">
-        <v>4</v>
-      </c>
-      <c r="G550" s="117" t="s">
+      <c r="F550" s="117" t="s">
+        <v>4</v>
+      </c>
+      <c r="G550" s="118" t="s">
         <v>55</v>
       </c>
       <c r="H550" s="3" t="s">
@@ -23244,9 +23213,9 @@
       <c r="B551" s="1"/>
       <c r="C551" s="1"/>
       <c r="D551" s="1"/>
-      <c r="E551" s="115"/>
-      <c r="F551" s="116"/>
-      <c r="G551" s="117"/>
+      <c r="E551" s="116"/>
+      <c r="F551" s="117"/>
+      <c r="G551" s="118"/>
       <c r="H551" s="3" t="s">
         <v>57</v>
       </c>
@@ -23256,13 +23225,13 @@
       <c r="B552" s="1"/>
       <c r="C552" s="1"/>
       <c r="D552" s="1"/>
-      <c r="E552" s="115" t="s">
+      <c r="E552" s="116" t="s">
         <v>58</v>
       </c>
-      <c r="F552" s="116" t="s">
-        <v>4</v>
-      </c>
-      <c r="G552" s="117" t="s">
+      <c r="F552" s="117" t="s">
+        <v>4</v>
+      </c>
+      <c r="G552" s="118" t="s">
         <v>59</v>
       </c>
       <c r="H552" s="3" t="s">
@@ -23274,9 +23243,9 @@
       <c r="B553" s="1"/>
       <c r="C553" s="1"/>
       <c r="D553" s="1"/>
-      <c r="E553" s="115"/>
-      <c r="F553" s="116"/>
-      <c r="G553" s="117"/>
+      <c r="E553" s="116"/>
+      <c r="F553" s="117"/>
+      <c r="G553" s="118"/>
       <c r="H553" s="3" t="s">
         <v>61</v>
       </c>
@@ -23286,13 +23255,13 @@
       <c r="B554" s="1"/>
       <c r="C554" s="1"/>
       <c r="D554" s="1"/>
-      <c r="E554" s="115" t="s">
+      <c r="E554" s="116" t="s">
         <v>62</v>
       </c>
-      <c r="F554" s="116" t="s">
-        <v>4</v>
-      </c>
-      <c r="G554" s="117" t="s">
+      <c r="F554" s="117" t="s">
+        <v>4</v>
+      </c>
+      <c r="G554" s="118" t="s">
         <v>63</v>
       </c>
       <c r="H554" s="3" t="s">
@@ -23304,14 +23273,14 @@
       <c r="B555" s="1"/>
       <c r="C555" s="1"/>
       <c r="D555" s="1"/>
-      <c r="E555" s="115"/>
-      <c r="F555" s="116"/>
-      <c r="G555" s="117"/>
+      <c r="E555" s="116"/>
+      <c r="F555" s="117"/>
+      <c r="G555" s="118"/>
       <c r="H555" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="556" spans="1:8" ht="51">
+    <row r="556" spans="1:8" ht="51.75">
       <c r="A556" s="1"/>
       <c r="B556" s="1"/>
       <c r="C556" s="1"/>
@@ -23327,7 +23296,7 @@
       </c>
       <c r="H556" s="5"/>
     </row>
-    <row r="557" spans="1:8">
+    <row r="557" spans="1:8" ht="26.25">
       <c r="A557" s="1"/>
       <c r="B557" s="1"/>
       <c r="C557" s="1"/>
@@ -23345,7 +23314,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="558" spans="1:8">
+    <row r="558" spans="1:8" ht="26.25">
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
       <c r="C558" s="1"/>
@@ -23363,7 +23332,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="559" spans="1:8" ht="26">
+    <row r="559" spans="1:8" ht="26.25">
       <c r="A559" s="1"/>
       <c r="B559" s="1"/>
       <c r="C559" s="1"/>
@@ -23386,13 +23355,13 @@
       <c r="B560" s="1"/>
       <c r="C560" s="1"/>
       <c r="D560" s="1"/>
-      <c r="E560" s="118" t="s">
+      <c r="E560" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="F560" s="116" t="s">
-        <v>4</v>
-      </c>
-      <c r="G560" s="117" t="s">
+      <c r="F560" s="117" t="s">
+        <v>4</v>
+      </c>
+      <c r="G560" s="118" t="s">
         <v>87</v>
       </c>
       <c r="H560" s="3" t="s">
@@ -23404,9 +23373,9 @@
       <c r="B561" s="1"/>
       <c r="C561" s="1"/>
       <c r="D561" s="1"/>
-      <c r="E561" s="118"/>
-      <c r="F561" s="116"/>
-      <c r="G561" s="117"/>
+      <c r="E561" s="119"/>
+      <c r="F561" s="117"/>
+      <c r="G561" s="118"/>
       <c r="H561" s="3" t="s">
         <v>89</v>
       </c>
@@ -23416,9 +23385,9 @@
       <c r="B562" s="1"/>
       <c r="C562" s="1"/>
       <c r="D562" s="1"/>
-      <c r="E562" s="118"/>
-      <c r="F562" s="116"/>
-      <c r="G562" s="117"/>
+      <c r="E562" s="119"/>
+      <c r="F562" s="117"/>
+      <c r="G562" s="118"/>
       <c r="H562" s="3" t="s">
         <v>90</v>
       </c>
@@ -23428,13 +23397,13 @@
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
       <c r="D563" s="1"/>
-      <c r="E563" s="118" t="s">
+      <c r="E563" s="119" t="s">
         <v>91</v>
       </c>
-      <c r="F563" s="116" t="s">
-        <v>4</v>
-      </c>
-      <c r="G563" s="117" t="s">
+      <c r="F563" s="117" t="s">
+        <v>4</v>
+      </c>
+      <c r="G563" s="118" t="s">
         <v>92</v>
       </c>
       <c r="H563" s="3" t="s">
@@ -23446,9 +23415,9 @@
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
       <c r="D564" s="1"/>
-      <c r="E564" s="118"/>
-      <c r="F564" s="116"/>
-      <c r="G564" s="117"/>
+      <c r="E564" s="119"/>
+      <c r="F564" s="117"/>
+      <c r="G564" s="118"/>
       <c r="H564" s="3" t="s">
         <v>89</v>
       </c>
@@ -23458,14 +23427,14 @@
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
       <c r="D565" s="1"/>
-      <c r="E565" s="118"/>
-      <c r="F565" s="116"/>
-      <c r="G565" s="117"/>
+      <c r="E565" s="119"/>
+      <c r="F565" s="117"/>
+      <c r="G565" s="118"/>
       <c r="H565" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="566" spans="1:8" ht="15.5">
+    <row r="566" spans="1:8" ht="15.75">
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
@@ -23481,7 +23450,7 @@
       </c>
       <c r="H566" s="5"/>
     </row>
-    <row r="567" spans="1:8" ht="15.5">
+    <row r="567" spans="1:8" ht="15.75">
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
       <c r="C567" s="1"/>
@@ -23497,7 +23466,7 @@
       </c>
       <c r="H567" s="5"/>
     </row>
-    <row r="568" spans="1:8" ht="15.5">
+    <row r="568" spans="1:8" ht="15.75">
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
       <c r="C568" s="1"/>
@@ -23513,7 +23482,7 @@
       </c>
       <c r="H568" s="5"/>
     </row>
-    <row r="569" spans="1:8" ht="15.5">
+    <row r="569" spans="1:8" ht="15.75">
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
       <c r="C569" s="1"/>
@@ -23529,7 +23498,7 @@
       </c>
       <c r="H569" s="5"/>
     </row>
-    <row r="570" spans="1:8" ht="15.5">
+    <row r="570" spans="1:8" ht="15.75">
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
       <c r="C570" s="1"/>
@@ -23545,7 +23514,7 @@
       </c>
       <c r="H570" s="5"/>
     </row>
-    <row r="571" spans="1:8" ht="15.5">
+    <row r="571" spans="1:8" ht="15.75">
       <c r="A571" s="1"/>
       <c r="B571" s="1"/>
       <c r="C571" s="1"/>
@@ -23561,7 +23530,7 @@
       </c>
       <c r="H571" s="5"/>
     </row>
-    <row r="572" spans="1:8" ht="15.5">
+    <row r="572" spans="1:8" ht="15.75">
       <c r="A572" s="1"/>
       <c r="B572" s="1"/>
       <c r="C572" s="1"/>
@@ -23577,7 +23546,7 @@
       </c>
       <c r="H572" s="5"/>
     </row>
-    <row r="573" spans="1:8" ht="15.5">
+    <row r="573" spans="1:8" ht="15.75">
       <c r="A573" s="1"/>
       <c r="B573" s="1"/>
       <c r="C573" s="1"/>
@@ -23633,7 +23602,7 @@
       <c r="G578" s="8"/>
       <c r="H578" s="3"/>
     </row>
-    <row r="581" spans="1:8" ht="15.5">
+    <row r="581" spans="1:8" ht="15.75">
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
@@ -23649,7 +23618,7 @@
       </c>
       <c r="H581" s="5"/>
     </row>
-    <row r="582" spans="1:8" ht="15.5">
+    <row r="582" spans="1:8" ht="15.75">
       <c r="A582" s="1"/>
       <c r="B582" s="1"/>
       <c r="C582" s="1"/>
@@ -23665,7 +23634,7 @@
       </c>
       <c r="H582" s="5"/>
     </row>
-    <row r="583" spans="1:8" ht="15.5">
+    <row r="583" spans="1:8" ht="15.75">
       <c r="A583" s="1"/>
       <c r="B583" s="1"/>
       <c r="C583" s="1"/>
@@ -23681,7 +23650,7 @@
       </c>
       <c r="H583" s="5"/>
     </row>
-    <row r="586" spans="1:8" ht="15.5">
+    <row r="586" spans="1:8" ht="15.75">
       <c r="A586" s="1"/>
       <c r="B586" s="1"/>
       <c r="C586" s="1"/>
@@ -23697,7 +23666,7 @@
       </c>
       <c r="H586" s="5"/>
     </row>
-    <row r="587" spans="1:8" ht="15.5">
+    <row r="587" spans="1:8" ht="15.75">
       <c r="A587" s="1"/>
       <c r="B587" s="1"/>
       <c r="C587" s="1"/>
@@ -23713,7 +23682,7 @@
       </c>
       <c r="H587" s="5"/>
     </row>
-    <row r="588" spans="1:8" ht="15.5">
+    <row r="588" spans="1:8" ht="15.75">
       <c r="A588" s="1"/>
       <c r="B588" s="1"/>
       <c r="C588" s="1"/>
@@ -23783,7 +23752,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="594" spans="1:8" ht="15.5">
+    <row r="594" spans="1:8" ht="15.75">
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
       <c r="C594" s="1"/>
@@ -23799,7 +23768,7 @@
       </c>
       <c r="H594" s="5"/>
     </row>
-    <row r="595" spans="1:8" ht="15.5">
+    <row r="595" spans="1:8" ht="15.75">
       <c r="A595" s="1"/>
       <c r="B595" s="1"/>
       <c r="C595" s="1"/>
@@ -23815,7 +23784,7 @@
       </c>
       <c r="H595" s="5"/>
     </row>
-    <row r="596" spans="1:8" ht="15.5">
+    <row r="596" spans="1:8" ht="15.75">
       <c r="A596" s="1"/>
       <c r="B596" s="1"/>
       <c r="C596" s="1"/>
@@ -23917,6 +23886,24 @@
   </sheetData>
   <autoFilter ref="A1:I315" xr:uid="{82619C4B-D6B1-486E-87C6-D2252668E253}"/>
   <mergeCells count="27">
+    <mergeCell ref="E538:E539"/>
+    <mergeCell ref="F538:F539"/>
+    <mergeCell ref="G538:G539"/>
+    <mergeCell ref="E542:E543"/>
+    <mergeCell ref="F542:F543"/>
+    <mergeCell ref="G542:G543"/>
+    <mergeCell ref="E552:E553"/>
+    <mergeCell ref="F552:F553"/>
+    <mergeCell ref="G552:G553"/>
+    <mergeCell ref="E554:E555"/>
+    <mergeCell ref="F554:F555"/>
+    <mergeCell ref="G554:G555"/>
+    <mergeCell ref="E560:E562"/>
+    <mergeCell ref="F560:F562"/>
+    <mergeCell ref="G560:G562"/>
+    <mergeCell ref="E563:E565"/>
+    <mergeCell ref="F563:F565"/>
+    <mergeCell ref="G563:G565"/>
     <mergeCell ref="E550:E551"/>
     <mergeCell ref="F550:F551"/>
     <mergeCell ref="G550:G551"/>
@@ -23926,24 +23913,6 @@
     <mergeCell ref="F548:F549"/>
     <mergeCell ref="G548:G549"/>
     <mergeCell ref="E544:E545"/>
-    <mergeCell ref="E560:E562"/>
-    <mergeCell ref="F560:F562"/>
-    <mergeCell ref="G560:G562"/>
-    <mergeCell ref="E563:E565"/>
-    <mergeCell ref="F563:F565"/>
-    <mergeCell ref="G563:G565"/>
-    <mergeCell ref="E552:E553"/>
-    <mergeCell ref="F552:F553"/>
-    <mergeCell ref="G552:G553"/>
-    <mergeCell ref="E554:E555"/>
-    <mergeCell ref="F554:F555"/>
-    <mergeCell ref="G554:G555"/>
-    <mergeCell ref="E538:E539"/>
-    <mergeCell ref="F538:F539"/>
-    <mergeCell ref="G538:G539"/>
-    <mergeCell ref="E542:E543"/>
-    <mergeCell ref="F542:F543"/>
-    <mergeCell ref="G542:G543"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G6" r:id="rId1" display="Abbreviation of the journal name. We use WoS abbreviations that can be found here: https://images.webofknowledge.com/images/help/WOS/A_abrvjt.html" xr:uid="{B4DADD6B-F846-45B3-933B-5F25CC9FEF24}"/>
@@ -23964,17 +23933,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4e0e0d96de7fb32b1678b66c28514d8e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" xmlns:ns3="432dd258-9dce-4cb3-b611-c68c0fbce7f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac451aab8c96dec805c937cbafca7133" ns2:_="" ns3:_="">
     <xsd:import namespace="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
@@ -24175,6 +24133,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0C90B0A-DBBE-4147-B2EE-79946A8DC171}">
   <ds:schemaRefs>
@@ -24184,17 +24153,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63F80AE0-5CF8-441A-8E3E-6D76A3390D5E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
-    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC19592A-9F30-4B32-9428-1D9634B8A0D4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -24211,4 +24169,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63F80AE0-5CF8-441A-8E3E-6D76A3390D5E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
+    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
+++ b/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Evidence_Hub/02.FOMD/02.metadata_structure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1181" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9259760D-F066-4A3B-A18E-3072885704B0}"/>
+  <xr:revisionPtr revIDLastSave="1189" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{627D77C8-84E1-458E-813F-6E0DC709A600}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="870" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{FAB1A633-BA4D-4813-8605-DC3F4755D7C7}"/>
   </bookViews>
@@ -307,7 +307,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5363" uniqueCount="1365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5406" uniqueCount="1365">
   <si>
     <t>Example</t>
   </si>
@@ -9653,7 +9653,7 @@
     <t>NEED TO CHECK, THIS CAN DIFFER FROM T to C</t>
   </si>
   <si>
-    <t># TO CHECK: ver de sacar el "_" que aparece entre los espacios de los crops</t>
+    <t>agroforestry_practice</t>
   </si>
 </sst>
 </file>
@@ -25321,8 +25321,8 @@
       <c r="F31" s="3"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="29" t="s">
-        <v>1364</v>
+      <c r="A32" s="121" t="s">
+        <v>986</v>
       </c>
       <c r="B32" s="16" t="s">
         <v>1060</v>
@@ -26051,7 +26051,9 @@
       <c r="F69" s="31"/>
     </row>
     <row r="70" spans="1:6">
-      <c r="A70" s="1"/>
+      <c r="A70" s="121" t="s">
+        <v>986</v>
+      </c>
       <c r="B70" s="81" t="s">
         <v>880</v>
       </c>
@@ -26063,8 +26065,8 @@
       <c r="F70" s="31"/>
     </row>
     <row r="71" spans="1:6">
-      <c r="A71" s="9" t="s">
-        <v>1364</v>
+      <c r="A71" s="121" t="s">
+        <v>986</v>
       </c>
       <c r="B71" s="81" t="s">
         <v>880</v>
@@ -26077,7 +26079,9 @@
       <c r="F71" s="31"/>
     </row>
     <row r="72" spans="1:6">
-      <c r="A72" s="1"/>
+      <c r="A72" s="121" t="s">
+        <v>986</v>
+      </c>
       <c r="B72" s="81" t="s">
         <v>880</v>
       </c>
@@ -26095,7 +26099,9 @@
       </c>
     </row>
     <row r="73" spans="1:6">
-      <c r="A73" s="1"/>
+      <c r="A73" s="121" t="s">
+        <v>986</v>
+      </c>
       <c r="B73" s="81" t="s">
         <v>880</v>
       </c>
@@ -26113,7 +26119,9 @@
       </c>
     </row>
     <row r="74" spans="1:6" ht="15.75">
-      <c r="A74" s="1"/>
+      <c r="A74" s="121" t="s">
+        <v>986</v>
+      </c>
       <c r="B74" s="81" t="s">
         <v>880</v>
       </c>
@@ -26129,7 +26137,9 @@
       <c r="F74" s="5"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="A75" s="1"/>
+      <c r="A75" s="121" t="s">
+        <v>986</v>
+      </c>
       <c r="B75" s="81" t="s">
         <v>880</v>
       </c>
@@ -26147,7 +26157,9 @@
       </c>
     </row>
     <row r="76" spans="1:6">
-      <c r="A76" s="1"/>
+      <c r="A76" s="121" t="s">
+        <v>986</v>
+      </c>
       <c r="B76" s="81" t="s">
         <v>880</v>
       </c>
@@ -26159,7 +26171,9 @@
       <c r="F76" s="31"/>
     </row>
     <row r="77" spans="1:6">
-      <c r="A77" s="1"/>
+      <c r="A77" s="121" t="s">
+        <v>986</v>
+      </c>
       <c r="B77" s="81" t="s">
         <v>880</v>
       </c>
@@ -26171,7 +26185,9 @@
       <c r="F77" s="31"/>
     </row>
     <row r="78" spans="1:6" ht="15.75">
-      <c r="A78" s="1"/>
+      <c r="A78" s="121" t="s">
+        <v>986</v>
+      </c>
       <c r="B78" s="81" t="s">
         <v>880</v>
       </c>
@@ -26187,7 +26203,9 @@
       <c r="F78" s="5"/>
     </row>
     <row r="79" spans="1:6" ht="15.75">
-      <c r="A79" s="1"/>
+      <c r="A79" s="121" t="s">
+        <v>986</v>
+      </c>
       <c r="B79" s="81" t="s">
         <v>880</v>
       </c>
@@ -26203,7 +26221,9 @@
       <c r="F79" s="5"/>
     </row>
     <row r="80" spans="1:6">
-      <c r="A80" s="1"/>
+      <c r="A80" s="121" t="s">
+        <v>986</v>
+      </c>
       <c r="B80" s="81" t="s">
         <v>880</v>
       </c>
@@ -26221,7 +26241,9 @@
       </c>
     </row>
     <row r="81" spans="1:6" ht="15.75">
-      <c r="A81" s="1"/>
+      <c r="A81" s="121" t="s">
+        <v>986</v>
+      </c>
       <c r="B81" s="81" t="s">
         <v>880</v>
       </c>
@@ -26333,7 +26355,9 @@
       </c>
     </row>
     <row r="88" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A88" s="1"/>
+      <c r="A88" s="122" t="s">
+        <v>986</v>
+      </c>
       <c r="B88" s="83" t="s">
         <v>885</v>
       </c>
@@ -26347,7 +26371,9 @@
       <c r="F88" s="31"/>
     </row>
     <row r="89" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A89" s="1"/>
+      <c r="A89" s="122" t="s">
+        <v>986</v>
+      </c>
       <c r="B89" s="83" t="s">
         <v>885</v>
       </c>
@@ -26365,7 +26391,9 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A90" s="1"/>
+      <c r="A90" s="122" t="s">
+        <v>986</v>
+      </c>
       <c r="B90" s="83" t="s">
         <v>885</v>
       </c>
@@ -26380,7 +26408,9 @@
       </c>
     </row>
     <row r="91" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A91" s="1"/>
+      <c r="A91" s="122" t="s">
+        <v>986</v>
+      </c>
       <c r="B91" s="83" t="s">
         <v>885</v>
       </c>
@@ -26395,7 +26425,9 @@
       </c>
     </row>
     <row r="92" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A92" s="1"/>
+      <c r="A92" s="122" t="s">
+        <v>986</v>
+      </c>
       <c r="B92" s="83" t="s">
         <v>885</v>
       </c>
@@ -26410,7 +26442,9 @@
       </c>
     </row>
     <row r="93" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A93" s="1"/>
+      <c r="A93" s="122" t="s">
+        <v>986</v>
+      </c>
       <c r="B93" s="83" t="s">
         <v>885</v>
       </c>
@@ -26426,7 +26460,9 @@
       <c r="F93" s="5"/>
     </row>
     <row r="94" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A94" s="1"/>
+      <c r="A94" s="122" t="s">
+        <v>986</v>
+      </c>
       <c r="B94" s="83" t="s">
         <v>885</v>
       </c>
@@ -26441,7 +26477,9 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A95" s="1"/>
+      <c r="A95" s="122" t="s">
+        <v>986</v>
+      </c>
       <c r="B95" s="83" t="s">
         <v>885</v>
       </c>
@@ -26454,7 +26492,9 @@
       <c r="E95"/>
     </row>
     <row r="96" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A96" s="1"/>
+      <c r="A96" s="122" t="s">
+        <v>986</v>
+      </c>
       <c r="B96" s="83" t="s">
         <v>885</v>
       </c>
@@ -26472,7 +26512,9 @@
       </c>
     </row>
     <row r="97" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A97" s="1"/>
+      <c r="A97" s="122" t="s">
+        <v>986</v>
+      </c>
       <c r="B97" s="83" t="s">
         <v>885</v>
       </c>
@@ -26490,7 +26532,9 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A98" s="1"/>
+      <c r="A98" s="122" t="s">
+        <v>986</v>
+      </c>
       <c r="B98" s="83" t="s">
         <v>885</v>
       </c>
@@ -26508,7 +26552,9 @@
       </c>
     </row>
     <row r="99" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A99" s="1"/>
+      <c r="A99" s="122" t="s">
+        <v>986</v>
+      </c>
       <c r="B99" s="83" t="s">
         <v>885</v>
       </c>
@@ -26526,7 +26572,9 @@
       </c>
     </row>
     <row r="100" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A100" s="1"/>
+      <c r="A100" s="122" t="s">
+        <v>986</v>
+      </c>
       <c r="B100" s="83" t="s">
         <v>885</v>
       </c>
@@ -26544,7 +26592,9 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A101" s="1"/>
+      <c r="A101" s="122" t="s">
+        <v>986</v>
+      </c>
       <c r="B101" s="83" t="s">
         <v>885</v>
       </c>
@@ -26562,7 +26612,9 @@
       </c>
     </row>
     <row r="102" spans="1:6">
-      <c r="A102" s="1"/>
+      <c r="A102" s="122" t="s">
+        <v>986</v>
+      </c>
       <c r="B102" s="82" t="s">
         <v>886</v>
       </c>
@@ -26593,7 +26645,9 @@
       </c>
     </row>
     <row r="104" spans="1:6" ht="15.75">
-      <c r="A104" s="1"/>
+      <c r="A104" s="122" t="s">
+        <v>986</v>
+      </c>
       <c r="B104" s="82" t="s">
         <v>886</v>
       </c>
@@ -26609,6 +26663,9 @@
       <c r="F104" s="5"/>
     </row>
     <row r="105" spans="1:6" ht="15.75">
+      <c r="A105" s="122" t="s">
+        <v>986</v>
+      </c>
       <c r="B105" s="82" t="s">
         <v>886</v>
       </c>
@@ -26624,7 +26681,9 @@
       <c r="F105" s="5"/>
     </row>
     <row r="106" spans="1:6" ht="15.75">
-      <c r="A106" s="1"/>
+      <c r="A106" s="122" t="s">
+        <v>986</v>
+      </c>
       <c r="B106" s="82" t="s">
         <v>886</v>
       </c>
@@ -26642,7 +26701,9 @@
       </c>
     </row>
     <row r="107" spans="1:6" ht="15.75">
-      <c r="A107" s="1"/>
+      <c r="A107" s="122" t="s">
+        <v>986</v>
+      </c>
       <c r="B107" s="82" t="s">
         <v>888</v>
       </c>
@@ -26674,7 +26735,9 @@
       </c>
     </row>
     <row r="109" spans="1:6" ht="15.75">
-      <c r="A109" s="1"/>
+      <c r="A109" s="122" t="s">
+        <v>986</v>
+      </c>
       <c r="B109" s="82" t="s">
         <v>886</v>
       </c>
@@ -26692,7 +26755,9 @@
       </c>
     </row>
     <row r="110" spans="1:6" ht="15.75">
-      <c r="A110" s="1"/>
+      <c r="A110" s="122" t="s">
+        <v>986</v>
+      </c>
       <c r="B110" s="82" t="s">
         <v>886</v>
       </c>
@@ -26710,7 +26775,9 @@
       </c>
     </row>
     <row r="111" spans="1:6">
-      <c r="A111" s="1"/>
+      <c r="A111" s="122" t="s">
+        <v>986</v>
+      </c>
       <c r="B111" s="82" t="s">
         <v>886</v>
       </c>
@@ -26729,7 +26796,9 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="1"/>
-      <c r="B112" s="82"/>
+      <c r="B112" s="24" t="s">
+        <v>1364</v>
+      </c>
       <c r="C112" s="24" t="s">
         <v>890</v>
       </c>
@@ -26742,7 +26811,9 @@
       <c r="A113" s="1" t="s">
         <v>986</v>
       </c>
-      <c r="B113" s="1"/>
+      <c r="B113" s="24" t="s">
+        <v>1364</v>
+      </c>
       <c r="C113" s="24" t="s">
         <v>189</v>
       </c>
@@ -26760,7 +26831,9 @@
       <c r="A114" s="1" t="s">
         <v>986</v>
       </c>
-      <c r="B114" s="1"/>
+      <c r="B114" s="24" t="s">
+        <v>1364</v>
+      </c>
       <c r="C114" s="24" t="s">
         <v>188</v>
       </c>
@@ -26778,7 +26851,9 @@
       <c r="A115" s="1" t="s">
         <v>986</v>
       </c>
-      <c r="B115" s="1"/>
+      <c r="B115" s="24" t="s">
+        <v>1364</v>
+      </c>
       <c r="C115" s="24" t="s">
         <v>187</v>
       </c>
@@ -26796,7 +26871,9 @@
       <c r="A116" s="1" t="s">
         <v>986</v>
       </c>
-      <c r="B116" s="1"/>
+      <c r="B116" s="24" t="s">
+        <v>1364</v>
+      </c>
       <c r="C116" s="24" t="s">
         <v>186</v>
       </c>
@@ -26812,7 +26889,9 @@
     </row>
     <row r="117" spans="1:6" ht="15.75" thickBot="1">
       <c r="A117" s="1"/>
-      <c r="B117" s="1"/>
+      <c r="B117" s="24" t="s">
+        <v>1364</v>
+      </c>
       <c r="C117" s="24" t="s">
         <v>891</v>
       </c>
@@ -26823,7 +26902,9 @@
     </row>
     <row r="118" spans="1:6" ht="15.75" thickBot="1">
       <c r="A118" s="1"/>
-      <c r="B118" s="1"/>
+      <c r="B118" s="24" t="s">
+        <v>1364</v>
+      </c>
       <c r="C118" s="24" t="s">
         <v>185</v>
       </c>
@@ -26839,7 +26920,9 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="1"/>
-      <c r="B119" s="1"/>
+      <c r="B119" s="24" t="s">
+        <v>1364</v>
+      </c>
       <c r="C119" s="24" t="s">
         <v>184</v>
       </c>
@@ -26855,7 +26938,9 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="1"/>
-      <c r="B120" s="1"/>
+      <c r="B120" s="24" t="s">
+        <v>1364</v>
+      </c>
       <c r="C120" s="24" t="s">
         <v>183</v>
       </c>
@@ -26871,7 +26956,9 @@
     </row>
     <row r="121" spans="1:6" ht="15.75" thickBot="1">
       <c r="A121" s="1"/>
-      <c r="B121" s="1"/>
+      <c r="B121" s="24" t="s">
+        <v>1364</v>
+      </c>
       <c r="C121" s="24" t="s">
         <v>182</v>
       </c>

--- a/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
+++ b/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="2379" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD031357-9AF0-4873-B8E0-C40CA412B31A}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{FAB1A633-BA4D-4813-8605-DC3F4755D7C7}"/>
+    <workbookView minimized="1" xWindow="15" yWindow="0" windowWidth="19170" windowHeight="11385" firstSheet="2" activeTab="2" xr2:uid="{FAB1A633-BA4D-4813-8605-DC3F4755D7C7}"/>
   </bookViews>
   <sheets>
     <sheet name="10_FOMD_metadata_synthesis" sheetId="1" r:id="rId1"/>
@@ -12070,48 +12070,6 @@
   <dxfs count="5">
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFF8AD8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Helvetica Neue"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -12183,6 +12141,48 @@
         <scheme val="none"/>
       </font>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFF8AD8"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -12203,13 +12203,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8928106E-6D55-41E8-B2AB-A43DFE6088B9}" name="_10_FOMD_metadata_synthesis" displayName="_10_FOMD_metadata_synthesis" ref="A1:KE2" insertRow="1" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8928106E-6D55-41E8-B2AB-A43DFE6088B9}" name="_10_FOMD_metadata_synthesis" displayName="_10_FOMD_metadata_synthesis" ref="A1:KE2" insertRow="1" totalsRowShown="0" headerRowDxfId="4">
   <autoFilter ref="A1:KE2" xr:uid="{8928106E-6D55-41E8-B2AB-A43DFE6088B9}"/>
   <tableColumns count="291">
-    <tableColumn id="1" xr3:uid="{DB6FE6A4-4D26-4D1A-B52B-9ADA10D5F808}" name="study_id" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{70B873D9-C41B-42D1-B78B-33E4B7975633}" name="effect_size_id" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{7BFC1135-E57F-4C97-BD83-843AC387A429}" name="authors" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{883A94AD-C617-4A6C-86FB-47E972FFE80F}" name="title" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{DB6FE6A4-4D26-4D1A-B52B-9ADA10D5F808}" name="study_id" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{70B873D9-C41B-42D1-B78B-33E4B7975633}" name="effect_size_id" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{7BFC1135-E57F-4C97-BD83-843AC387A429}" name="authors" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{883A94AD-C617-4A6C-86FB-47E972FFE80F}" name="title" dataDxfId="0"/>
     <tableColumn id="5" xr3:uid="{2E8FEB31-CDE6-4F6E-9CE5-1A215D75D367}" name="year"/>
     <tableColumn id="6" xr3:uid="{6E81B9F5-7064-4F0E-B712-65740CB351D8}" name="journal"/>
     <tableColumn id="7" xr3:uid="{E0947224-5770-4E2B-A4A7-C0A71900C8BD}" name="doi"/>
@@ -12884,14 +12884,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{487E46BC-52D3-4EF1-8B98-2DA697255E52}">
   <dimension ref="A1:PR2"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="23.1796875" customWidth="1"/>
-    <col min="3" max="3" width="19.453125" customWidth="1"/>
-    <col min="4" max="5" width="23.1796875" customWidth="1"/>
+    <col min="1" max="2" width="23.140625" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" customWidth="1"/>
+    <col min="4" max="5" width="23.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:434" s="80" customFormat="1" ht="58.5" thickBot="1">
+    <row r="1" spans="1:434" s="80" customFormat="1" ht="60.75" thickBot="1">
       <c r="A1" s="62" t="s">
         <v>157</v>
       </c>
@@ -13909,7 +13909,7 @@
       <c r="PQ1" s="70"/>
       <c r="PR1" s="70"/>
     </row>
-    <row r="2" spans="1:434" ht="15.5">
+    <row r="2" spans="1:434" ht="15.75">
       <c r="A2" s="60"/>
       <c r="B2" s="1"/>
       <c r="C2" s="60"/>
@@ -13927,19 +13927,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82619C4B-D6B1-486E-87C6-D2252668E253}">
   <dimension ref="A1:N608"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34.453125" customWidth="1"/>
-    <col min="2" max="2" width="32.81640625" customWidth="1"/>
-    <col min="3" max="3" width="23.1796875" customWidth="1"/>
-    <col min="4" max="4" width="13.08984375" customWidth="1"/>
-    <col min="5" max="5" width="11.36328125" customWidth="1"/>
-    <col min="6" max="6" width="32.81640625" customWidth="1"/>
-    <col min="7" max="8" width="25.453125" customWidth="1"/>
-    <col min="9" max="9" width="20.54296875" customWidth="1"/>
-    <col min="10" max="10" width="36.453125" customWidth="1"/>
+    <col min="1" max="1" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" width="32.85546875" customWidth="1"/>
+    <col min="3" max="3" width="23.140625" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" customWidth="1"/>
+    <col min="6" max="6" width="32.85546875" customWidth="1"/>
+    <col min="7" max="8" width="25.42578125" customWidth="1"/>
+    <col min="9" max="9" width="20.5703125" customWidth="1"/>
+    <col min="10" max="10" width="36.42578125" customWidth="1"/>
     <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="121.81640625" style="10" customWidth="1"/>
+    <col min="12" max="12" width="121.85546875" style="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -13981,7 +13981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+    <row r="2" spans="1:13" ht="24.95" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>911</v>
       </c>
@@ -14014,7 +14014,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="15.5">
+    <row r="3" spans="1:13" ht="15.75">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -14104,7 +14104,7 @@
       <c r="L5" s="46"/>
       <c r="M5" s="3"/>
     </row>
-    <row r="6" spans="1:13" ht="15.5">
+    <row r="6" spans="1:13" ht="15.75">
       <c r="A6" s="3" t="s">
         <v>912</v>
       </c>
@@ -14168,7 +14168,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="15.5">
+    <row r="8" spans="1:13" ht="15.75">
       <c r="A8" s="3" t="s">
         <v>914</v>
       </c>
@@ -14199,7 +14199,7 @@
       </c>
       <c r="M8" s="5"/>
     </row>
-    <row r="9" spans="1:13" ht="16">
+    <row r="9" spans="1:13" ht="15.75">
       <c r="A9" s="3" t="s">
         <v>13</v>
       </c>
@@ -14430,7 +14430,7 @@
       </c>
       <c r="M15" s="3"/>
     </row>
-    <row r="16" spans="1:13" ht="15.5">
+    <row r="16" spans="1:13" ht="15.75">
       <c r="A16" s="3" t="s">
         <v>918</v>
       </c>
@@ -14461,7 +14461,7 @@
       </c>
       <c r="M16" s="5"/>
     </row>
-    <row r="17" spans="1:14" ht="15.5">
+    <row r="17" spans="1:14" ht="15.75">
       <c r="A17" s="3" t="s">
         <v>919</v>
       </c>
@@ -14492,7 +14492,7 @@
       </c>
       <c r="M17" s="5"/>
     </row>
-    <row r="18" spans="1:14" ht="15.5">
+    <row r="18" spans="1:14" ht="15.75">
       <c r="A18" s="3" t="s">
         <v>920</v>
       </c>
@@ -14588,7 +14588,7 @@
       <c r="M20" s="4"/>
       <c r="N20" s="4"/>
     </row>
-    <row r="21" spans="1:14" ht="15" thickBot="1">
+    <row r="21" spans="1:14" ht="15.75" thickBot="1">
       <c r="A21" s="3" t="s">
         <v>922</v>
       </c>
@@ -14618,7 +14618,7 @@
       <c r="M21" s="4"/>
       <c r="N21" s="4"/>
     </row>
-    <row r="22" spans="1:14" ht="15" thickBot="1">
+    <row r="22" spans="1:14" ht="15.75" thickBot="1">
       <c r="A22" s="86" t="s">
         <v>1012</v>
       </c>
@@ -14688,7 +14688,7 @@
       </c>
       <c r="N23" s="4"/>
     </row>
-    <row r="24" spans="1:14" ht="15" thickBot="1">
+    <row r="24" spans="1:14" ht="15.75" thickBot="1">
       <c r="A24" s="86" t="s">
         <v>1012</v>
       </c>
@@ -14722,7 +14722,7 @@
       <c r="M24" s="4"/>
       <c r="N24" s="4"/>
     </row>
-    <row r="25" spans="1:14" ht="15" thickBot="1">
+    <row r="25" spans="1:14" ht="15.75" thickBot="1">
       <c r="A25" s="3" t="s">
         <v>924</v>
       </c>
@@ -14750,7 +14750,7 @@
       <c r="M25" s="4"/>
       <c r="N25" s="4"/>
     </row>
-    <row r="26" spans="1:14" ht="15" thickBot="1">
+    <row r="26" spans="1:14" ht="15.75" thickBot="1">
       <c r="A26" s="3" t="s">
         <v>925</v>
       </c>
@@ -14778,7 +14778,7 @@
       <c r="M26" s="4"/>
       <c r="N26" s="4"/>
     </row>
-    <row r="27" spans="1:14" ht="16" thickBot="1">
+    <row r="27" spans="1:14" ht="16.5" thickBot="1">
       <c r="A27" t="s">
         <v>1053</v>
       </c>
@@ -14972,7 +14972,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="16">
+    <row r="33" spans="1:13" ht="15.75">
       <c r="A33" t="s">
         <v>1054</v>
       </c>
@@ -15077,7 +15077,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="16">
+    <row r="36" spans="1:13" ht="15.75">
       <c r="A36" t="s">
         <v>1055</v>
       </c>
@@ -15303,7 +15303,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="16">
+    <row r="43" spans="1:13" ht="15.75">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -15390,7 +15390,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="16">
+    <row r="46" spans="1:13" ht="15.75">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -15421,7 +15421,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="15" thickBot="1">
+    <row r="47" spans="1:13" ht="15.75" thickBot="1">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -15448,7 +15448,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="15" thickBot="1">
+    <row r="48" spans="1:13" ht="15.75" thickBot="1">
       <c r="A48" s="3" t="s">
         <v>1071</v>
       </c>
@@ -15480,7 +15480,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="16">
+    <row r="49" spans="1:13" ht="15.75">
       <c r="A49" s="3"/>
       <c r="B49" s="99" t="s">
         <v>1079</v>
@@ -15614,7 +15614,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="16" thickBot="1">
+    <row r="53" spans="1:13" ht="16.5" thickBot="1">
       <c r="A53" s="3" t="s">
         <v>1027</v>
       </c>
@@ -15647,7 +15647,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="16" thickBot="1">
+    <row r="54" spans="1:13" ht="16.5" thickBot="1">
       <c r="A54" s="3" t="s">
         <v>1072</v>
       </c>
@@ -15680,7 +15680,7 @@
       </c>
       <c r="M54" s="5"/>
     </row>
-    <row r="55" spans="1:13" ht="16">
+    <row r="55" spans="1:13" ht="15.75">
       <c r="A55" s="3"/>
       <c r="B55" s="99" t="s">
         <v>1079</v>
@@ -15814,7 +15814,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="15.5">
+    <row r="59" spans="1:13" ht="15.75">
       <c r="A59" s="3" t="s">
         <v>1031</v>
       </c>
@@ -15847,7 +15847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="15.5">
+    <row r="60" spans="1:13" ht="15.75">
       <c r="A60" t="s">
         <v>1077</v>
       </c>
@@ -15900,7 +15900,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="16">
+    <row r="62" spans="1:13" ht="15.75">
       <c r="A62" t="s">
         <v>1075</v>
       </c>
@@ -16057,7 +16057,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="16">
+    <row r="67" spans="1:13" ht="15.75">
       <c r="A67" t="s">
         <v>1076</v>
       </c>
@@ -16243,7 +16243,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="15.5">
+    <row r="73" spans="1:13" ht="15.75">
       <c r="A73" s="3" t="s">
         <v>1033</v>
       </c>
@@ -16326,7 +16326,7 @@
       <c r="L75"/>
       <c r="M75" s="31"/>
     </row>
-    <row r="76" spans="1:13" ht="15.5">
+    <row r="76" spans="1:13" ht="15.75">
       <c r="A76" t="s">
         <v>1055</v>
       </c>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="M76" s="5"/>
     </row>
-    <row r="77" spans="1:13" ht="15.5">
+    <row r="77" spans="1:13" ht="15.75">
       <c r="A77" s="3" t="s">
         <v>1034</v>
       </c>
@@ -16415,7 +16415,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="79" spans="1:13" ht="15.5">
+    <row r="79" spans="1:13" ht="15.75">
       <c r="A79" s="3" t="s">
         <v>1070</v>
       </c>
@@ -16561,7 +16561,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="85" spans="1:13" ht="15" thickBot="1">
+    <row r="85" spans="1:13" ht="15.75" thickBot="1">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -16584,7 +16584,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="86" spans="1:13" ht="15" thickBot="1">
+    <row r="86" spans="1:13" ht="15.75" thickBot="1">
       <c r="A86" t="s">
         <v>1093</v>
       </c>
@@ -16647,7 +16647,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="88" spans="1:13" ht="15" thickBot="1">
+    <row r="88" spans="1:13" ht="15.75" thickBot="1">
       <c r="A88" s="86" t="s">
         <v>1012</v>
       </c>
@@ -16679,7 +16679,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="89" spans="1:13" ht="15" thickBot="1">
+    <row r="89" spans="1:13" ht="15.75" thickBot="1">
       <c r="A89" s="86" t="s">
         <v>1012</v>
       </c>
@@ -16711,7 +16711,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="90" spans="1:13" ht="15" thickBot="1">
+    <row r="90" spans="1:13" ht="15.75" thickBot="1">
       <c r="A90" s="3" t="s">
         <v>905</v>
       </c>
@@ -16741,7 +16741,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="91" spans="1:13" ht="16" thickBot="1">
+    <row r="91" spans="1:13" ht="16.5" thickBot="1">
       <c r="A91" t="s">
         <v>1095</v>
       </c>
@@ -16772,7 +16772,7 @@
       </c>
       <c r="M91" s="5"/>
     </row>
-    <row r="92" spans="1:13" ht="15" thickBot="1">
+    <row r="92" spans="1:13" ht="15.75" thickBot="1">
       <c r="A92" s="3" t="s">
         <v>904</v>
       </c>
@@ -16802,7 +16802,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="93" spans="1:13" ht="15" thickBot="1">
+    <row r="93" spans="1:13" ht="15.75" thickBot="1">
       <c r="A93" t="s">
         <v>1094</v>
       </c>
@@ -16830,7 +16830,7 @@
       </c>
       <c r="L93"/>
     </row>
-    <row r="94" spans="1:13" ht="16" thickBot="1">
+    <row r="94" spans="1:13" ht="16.5" thickBot="1">
       <c r="A94" s="3"/>
       <c r="B94" s="101" t="s">
         <v>1098</v>
@@ -16863,7 +16863,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="95" spans="1:13" ht="15" thickBot="1">
+    <row r="95" spans="1:13" ht="15.75" thickBot="1">
       <c r="A95" s="86" t="s">
         <v>1012</v>
       </c>
@@ -16898,7 +16898,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="96" spans="1:13" ht="15" thickBot="1">
+    <row r="96" spans="1:13" ht="15.75" thickBot="1">
       <c r="A96" s="86" t="s">
         <v>1012</v>
       </c>
@@ -16933,7 +16933,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="97" spans="1:13" ht="16" thickBot="1">
+    <row r="97" spans="1:13" ht="16.5" thickBot="1">
       <c r="A97" s="3" t="s">
         <v>903</v>
       </c>
@@ -16966,7 +16966,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="98" spans="1:13" ht="16" thickBot="1">
+    <row r="98" spans="1:13" ht="16.5" thickBot="1">
       <c r="A98" t="s">
         <v>1096</v>
       </c>
@@ -16999,7 +16999,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:13" ht="15" thickBot="1">
+    <row r="99" spans="1:13" ht="15.75" thickBot="1">
       <c r="A99" s="3" t="s">
         <v>902</v>
       </c>
@@ -17058,7 +17058,7 @@
       <c r="K100" s="3"/>
       <c r="L100"/>
     </row>
-    <row r="101" spans="1:13" ht="16">
+    <row r="101" spans="1:13" ht="15.75">
       <c r="A101" t="s">
         <v>1236</v>
       </c>
@@ -17093,7 +17093,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="102" spans="1:13" ht="15.5">
+    <row r="102" spans="1:13" ht="15.75">
       <c r="A102" t="s">
         <v>1100</v>
       </c>
@@ -17124,7 +17124,7 @@
       </c>
       <c r="M102" s="5"/>
     </row>
-    <row r="103" spans="1:13" ht="15.5">
+    <row r="103" spans="1:13" ht="15.75">
       <c r="A103" t="s">
         <v>1102</v>
       </c>
@@ -17154,7 +17154,7 @@
       </c>
       <c r="M103" s="5"/>
     </row>
-    <row r="104" spans="1:13" ht="15.5">
+    <row r="104" spans="1:13" ht="15.75">
       <c r="A104" s="1"/>
       <c r="B104" s="109" t="s">
         <v>1241</v>
@@ -17185,7 +17185,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="105" spans="1:13" ht="15.5">
+    <row r="105" spans="1:13" ht="15.75">
       <c r="A105" s="104" t="s">
         <v>900</v>
       </c>
@@ -17212,7 +17212,7 @@
       <c r="L105"/>
       <c r="M105" s="5"/>
     </row>
-    <row r="106" spans="1:13" ht="16">
+    <row r="106" spans="1:13" ht="15.75">
       <c r="A106" t="s">
         <v>1236</v>
       </c>
@@ -17247,7 +17247,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="107" spans="1:13" ht="15.5">
+    <row r="107" spans="1:13" ht="15.75">
       <c r="A107" t="s">
         <v>1101</v>
       </c>
@@ -17280,7 +17280,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="108" spans="1:13" ht="15.5">
+    <row r="108" spans="1:13" ht="15.75">
       <c r="A108" t="s">
         <v>1103</v>
       </c>
@@ -17372,7 +17372,7 @@
       </c>
       <c r="L110"/>
     </row>
-    <row r="111" spans="1:13" ht="16">
+    <row r="111" spans="1:13" ht="15.75">
       <c r="A111" s="1" t="s">
         <v>1310</v>
       </c>
@@ -17514,7 +17514,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="115" spans="1:13" ht="15" thickBot="1">
+    <row r="115" spans="1:13" ht="15.75" thickBot="1">
       <c r="A115" s="1" t="s">
         <v>1246</v>
       </c>
@@ -17647,7 +17647,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="119" spans="1:13" ht="15" thickBot="1">
+    <row r="119" spans="1:13" ht="15.75" thickBot="1">
       <c r="A119" s="86" t="s">
         <v>1012</v>
       </c>
@@ -17682,7 +17682,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="120" spans="1:13" ht="15" thickBot="1">
+    <row r="120" spans="1:13" ht="15.75" thickBot="1">
       <c r="A120" t="s">
         <v>1266</v>
       </c>
@@ -17706,7 +17706,7 @@
       <c r="K120" s="3"/>
       <c r="L120"/>
     </row>
-    <row r="121" spans="1:13" ht="15" thickBot="1">
+    <row r="121" spans="1:13" ht="15.75" thickBot="1">
       <c r="A121" s="1" t="s">
         <v>1307</v>
       </c>
@@ -17741,7 +17741,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="122" spans="1:13" ht="15" thickBot="1">
+    <row r="122" spans="1:13" ht="15.75" thickBot="1">
       <c r="A122" s="104" t="s">
         <v>1283</v>
       </c>
@@ -17776,7 +17776,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="123" spans="1:13" ht="15" thickBot="1">
+    <row r="123" spans="1:13" ht="15.75" thickBot="1">
       <c r="A123" t="s">
         <v>1288</v>
       </c>
@@ -17807,7 +17807,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="124" spans="1:13" ht="15" thickBot="1">
+    <row r="124" spans="1:13" ht="15.75" thickBot="1">
       <c r="A124" t="s">
         <v>1292</v>
       </c>
@@ -17838,7 +17838,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="125" spans="1:13" ht="15" thickBot="1">
+    <row r="125" spans="1:13" ht="15.75" thickBot="1">
       <c r="A125" t="s">
         <v>1293</v>
       </c>
@@ -17869,7 +17869,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="126" spans="1:13" ht="15" thickBot="1">
+    <row r="126" spans="1:13" ht="15.75" thickBot="1">
       <c r="A126" s="1" t="s">
         <v>890</v>
       </c>
@@ -17900,7 +17900,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="127" spans="1:13" ht="15" thickBot="1">
+    <row r="127" spans="1:13" ht="15.75" thickBot="1">
       <c r="A127" t="s">
         <v>891</v>
       </c>
@@ -17931,7 +17931,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="128" spans="1:13" ht="15" thickBot="1">
+    <row r="128" spans="1:13" ht="15.75" thickBot="1">
       <c r="A128" s="1" t="s">
         <v>892</v>
       </c>
@@ -17962,7 +17962,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="129" spans="1:13" ht="15" thickBot="1">
+    <row r="129" spans="1:13" ht="15.75" thickBot="1">
       <c r="A129" s="1" t="s">
         <v>893</v>
       </c>
@@ -17993,7 +17993,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="130" spans="1:13" ht="15" thickBot="1">
+    <row r="130" spans="1:13" ht="15.75" thickBot="1">
       <c r="A130" s="1" t="s">
         <v>894</v>
       </c>
@@ -18024,7 +18024,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="131" spans="1:13" ht="15" thickBot="1">
+    <row r="131" spans="1:13" ht="15.75" thickBot="1">
       <c r="A131" t="s">
         <v>1278</v>
       </c>
@@ -18055,7 +18055,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="132" spans="1:13" ht="15" thickBot="1">
+    <row r="132" spans="1:13" ht="15.75" thickBot="1">
       <c r="A132" s="104" t="s">
         <v>1283</v>
       </c>
@@ -18115,7 +18115,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="134" spans="1:13" ht="15" thickBot="1">
+    <row r="134" spans="1:13" ht="15.75" thickBot="1">
       <c r="A134" t="s">
         <v>1292</v>
       </c>
@@ -18147,7 +18147,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="135" spans="1:13" ht="15" thickBot="1">
+    <row r="135" spans="1:13" ht="15.75" thickBot="1">
       <c r="A135" t="s">
         <v>1293</v>
       </c>
@@ -18179,7 +18179,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="136" spans="1:13" ht="15" thickBot="1">
+    <row r="136" spans="1:13" ht="15.75" thickBot="1">
       <c r="A136" t="s">
         <v>906</v>
       </c>
@@ -18207,7 +18207,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="137" spans="1:13" ht="15" thickBot="1">
+    <row r="137" spans="1:13" ht="15.75" thickBot="1">
       <c r="A137" s="104" t="s">
         <v>1268</v>
       </c>
@@ -18235,7 +18235,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="138" spans="1:13" ht="15" thickBot="1">
+    <row r="138" spans="1:13" ht="15.75" thickBot="1">
       <c r="A138" t="s">
         <v>1269</v>
       </c>
@@ -18263,7 +18263,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="139" spans="1:13" ht="15" thickBot="1">
+    <row r="139" spans="1:13" ht="15.75" thickBot="1">
       <c r="A139" t="s">
         <v>1273</v>
       </c>
@@ -18291,7 +18291,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="140" spans="1:13" ht="15" thickBot="1">
+    <row r="140" spans="1:13" ht="15.75" thickBot="1">
       <c r="A140" t="s">
         <v>1276</v>
       </c>
@@ -18320,7 +18320,7 @@
       </c>
       <c r="M140" s="41"/>
     </row>
-    <row r="141" spans="1:13" ht="15" thickBot="1">
+    <row r="141" spans="1:13" ht="15.75" thickBot="1">
       <c r="A141" t="s">
         <v>1267</v>
       </c>
@@ -18345,7 +18345,7 @@
       <c r="L141"/>
       <c r="M141" s="41"/>
     </row>
-    <row r="142" spans="1:13" ht="15" thickBot="1">
+    <row r="142" spans="1:13" ht="15.75" thickBot="1">
       <c r="A142" s="1" t="s">
         <v>1308</v>
       </c>
@@ -18380,7 +18380,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="143" spans="1:13" ht="15" thickBot="1">
+    <row r="143" spans="1:13" ht="15.75" thickBot="1">
       <c r="A143" s="104" t="s">
         <v>1286</v>
       </c>
@@ -18412,7 +18412,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="144" spans="1:13" ht="15" thickBot="1">
+    <row r="144" spans="1:13" ht="15.75" thickBot="1">
       <c r="A144" t="s">
         <v>1289</v>
       </c>
@@ -18441,7 +18441,7 @@
       </c>
       <c r="M144" s="39"/>
     </row>
-    <row r="145" spans="1:13" ht="15" thickBot="1">
+    <row r="145" spans="1:13" ht="15.75" thickBot="1">
       <c r="A145" t="s">
         <v>1300</v>
       </c>
@@ -18470,7 +18470,7 @@
       </c>
       <c r="M145" s="40"/>
     </row>
-    <row r="146" spans="1:13" ht="15" thickBot="1">
+    <row r="146" spans="1:13" ht="15.75" thickBot="1">
       <c r="A146" t="s">
         <v>1301</v>
       </c>
@@ -18499,7 +18499,7 @@
       </c>
       <c r="M146" s="32"/>
     </row>
-    <row r="147" spans="1:13" ht="15" thickBot="1">
+    <row r="147" spans="1:13" ht="15.75" thickBot="1">
       <c r="A147" s="1" t="s">
         <v>895</v>
       </c>
@@ -18527,7 +18527,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="148" spans="1:13" ht="15" thickBot="1">
+    <row r="148" spans="1:13" ht="15.75" thickBot="1">
       <c r="A148" s="1" t="s">
         <v>896</v>
       </c>
@@ -18555,7 +18555,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="149" spans="1:13" ht="15" thickBot="1">
+    <row r="149" spans="1:13" ht="15.75" thickBot="1">
       <c r="A149" s="1" t="s">
         <v>897</v>
       </c>
@@ -18583,7 +18583,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="150" spans="1:13" ht="15" thickBot="1">
+    <row r="150" spans="1:13" ht="15.75" thickBot="1">
       <c r="A150" s="1" t="s">
         <v>898</v>
       </c>
@@ -18611,7 +18611,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="151" spans="1:13" ht="15" thickBot="1">
+    <row r="151" spans="1:13" ht="15.75" thickBot="1">
       <c r="A151" s="1" t="s">
         <v>899</v>
       </c>
@@ -18639,7 +18639,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="152" spans="1:13" ht="15" thickBot="1">
+    <row r="152" spans="1:13" ht="15.75" thickBot="1">
       <c r="A152" t="s">
         <v>1279</v>
       </c>
@@ -18667,7 +18667,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="153" spans="1:13" ht="15" thickBot="1">
+    <row r="153" spans="1:13" ht="15.75" thickBot="1">
       <c r="A153" s="104" t="s">
         <v>1286</v>
       </c>
@@ -18733,7 +18733,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="155" spans="1:13" ht="15" thickBot="1">
+    <row r="155" spans="1:13" ht="15.75" thickBot="1">
       <c r="A155" t="s">
         <v>1300</v>
       </c>
@@ -18768,7 +18768,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="156" spans="1:13" ht="15" thickBot="1">
+    <row r="156" spans="1:13" ht="15.75" thickBot="1">
       <c r="A156" t="s">
         <v>1301</v>
       </c>
@@ -18803,7 +18803,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="157" spans="1:13" ht="15" thickBot="1">
+    <row r="157" spans="1:13" ht="15.75" thickBot="1">
       <c r="A157" t="s">
         <v>907</v>
       </c>
@@ -18834,7 +18834,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="158" spans="1:13" ht="15" thickBot="1">
+    <row r="158" spans="1:13" ht="15.75" thickBot="1">
       <c r="A158" s="104" t="s">
         <v>1270</v>
       </c>
@@ -18865,7 +18865,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="159" spans="1:13" ht="15" thickBot="1">
+    <row r="159" spans="1:13" ht="15.75" thickBot="1">
       <c r="A159" t="s">
         <v>1271</v>
       </c>
@@ -18896,7 +18896,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="160" spans="1:13" ht="15" thickBot="1">
+    <row r="160" spans="1:13" ht="15.75" thickBot="1">
       <c r="A160" t="s">
         <v>1272</v>
       </c>
@@ -18927,7 +18927,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="161" spans="1:13" ht="15" thickBot="1">
+    <row r="161" spans="1:13" ht="15.75" thickBot="1">
       <c r="A161" t="s">
         <v>1277</v>
       </c>
@@ -18958,7 +18958,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="162" spans="1:13" ht="15" thickBot="1">
+    <row r="162" spans="1:13" ht="15.75" thickBot="1">
       <c r="A162" t="s">
         <v>1143</v>
       </c>
@@ -18989,7 +18989,7 @@
       </c>
       <c r="M162" s="41"/>
     </row>
-    <row r="163" spans="1:13" ht="15" thickBot="1">
+    <row r="163" spans="1:13" ht="15.75" thickBot="1">
       <c r="A163" t="s">
         <v>1139</v>
       </c>
@@ -19020,7 +19020,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="164" spans="1:13" ht="15" thickBot="1">
+    <row r="164" spans="1:13" ht="15.75" thickBot="1">
       <c r="A164" t="s">
         <v>1154</v>
       </c>
@@ -19057,7 +19057,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="165" spans="1:13" ht="15" thickBot="1">
+    <row r="165" spans="1:13" ht="15.75" thickBot="1">
       <c r="A165" t="s">
         <v>1150</v>
       </c>
@@ -19089,7 +19089,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="166" spans="1:13" ht="15" thickBot="1">
+    <row r="166" spans="1:13" ht="15.75" thickBot="1">
       <c r="A166" t="s">
         <v>1144</v>
       </c>
@@ -19119,7 +19119,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="167" spans="1:13" ht="15" thickBot="1">
+    <row r="167" spans="1:13" ht="15.75" thickBot="1">
       <c r="A167" t="s">
         <v>1140</v>
       </c>
@@ -19150,7 +19150,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="168" spans="1:13" ht="15" thickBot="1">
+    <row r="168" spans="1:13" ht="15.75" thickBot="1">
       <c r="A168" t="s">
         <v>1155</v>
       </c>
@@ -19187,7 +19187,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="169" spans="1:13" ht="15" thickBot="1">
+    <row r="169" spans="1:13" ht="15.75" thickBot="1">
       <c r="A169" t="s">
         <v>1151</v>
       </c>
@@ -19219,7 +19219,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="170" spans="1:13" ht="15" thickBot="1">
+    <row r="170" spans="1:13" ht="15.75" thickBot="1">
       <c r="A170" t="s">
         <v>1255</v>
       </c>
@@ -19243,7 +19243,7 @@
       <c r="K170" s="17"/>
       <c r="L170"/>
     </row>
-    <row r="171" spans="1:13" ht="15" thickBot="1">
+    <row r="171" spans="1:13" ht="15.75" thickBot="1">
       <c r="A171" s="48" t="s">
         <v>1254</v>
       </c>
@@ -19276,7 +19276,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="172" spans="1:13" ht="15" thickBot="1">
+    <row r="172" spans="1:13" ht="15.75" thickBot="1">
       <c r="A172" t="s">
         <v>1257</v>
       </c>
@@ -19300,7 +19300,7 @@
       <c r="K172" s="17"/>
       <c r="L172" s="47"/>
     </row>
-    <row r="173" spans="1:13" ht="15" thickBot="1">
+    <row r="173" spans="1:13" ht="15.75" thickBot="1">
       <c r="A173" t="s">
         <v>1261</v>
       </c>
@@ -19324,7 +19324,7 @@
       <c r="K173" s="17"/>
       <c r="L173" s="47"/>
     </row>
-    <row r="174" spans="1:13" ht="15" thickBot="1">
+    <row r="174" spans="1:13" ht="15.75" thickBot="1">
       <c r="A174" t="s">
         <v>1259</v>
       </c>
@@ -19355,7 +19355,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="175" spans="1:13" ht="15" thickBot="1">
+    <row r="175" spans="1:13" ht="15.75" thickBot="1">
       <c r="A175" t="s">
         <v>1256</v>
       </c>
@@ -19379,7 +19379,7 @@
       <c r="K175" s="17"/>
       <c r="L175" s="47"/>
     </row>
-    <row r="176" spans="1:13" ht="15" thickBot="1">
+    <row r="176" spans="1:13" ht="15.75" thickBot="1">
       <c r="A176" s="48" t="s">
         <v>1265</v>
       </c>
@@ -19412,7 +19412,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="177" spans="1:13" ht="15" thickBot="1">
+    <row r="177" spans="1:13" ht="15.75" thickBot="1">
       <c r="A177" t="s">
         <v>1258</v>
       </c>
@@ -19437,7 +19437,7 @@
       <c r="L177"/>
       <c r="M177" s="69"/>
     </row>
-    <row r="178" spans="1:13" ht="15" thickBot="1">
+    <row r="178" spans="1:13" ht="15.75" thickBot="1">
       <c r="A178" t="s">
         <v>1262</v>
       </c>
@@ -19462,7 +19462,7 @@
       <c r="L178"/>
       <c r="M178" s="69"/>
     </row>
-    <row r="179" spans="1:13" ht="15" thickBot="1">
+    <row r="179" spans="1:13" ht="15.75" thickBot="1">
       <c r="A179" t="s">
         <v>1260</v>
       </c>
@@ -19493,7 +19493,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="180" spans="1:13" ht="15" thickBot="1">
+    <row r="180" spans="1:13" ht="15.75" thickBot="1">
       <c r="A180" t="s">
         <v>1156</v>
       </c>
@@ -19517,7 +19517,7 @@
       <c r="K180" s="17"/>
       <c r="L180"/>
     </row>
-    <row r="181" spans="1:13" ht="15" thickBot="1">
+    <row r="181" spans="1:13" ht="15.75" thickBot="1">
       <c r="A181" s="1" t="s">
         <v>1178</v>
       </c>
@@ -19552,7 +19552,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="182" spans="1:13" ht="15" thickBot="1">
+    <row r="182" spans="1:13" ht="15.75" thickBot="1">
       <c r="A182" s="1" t="s">
         <v>945</v>
       </c>
@@ -19581,7 +19581,7 @@
       </c>
       <c r="M182" s="69"/>
     </row>
-    <row r="183" spans="1:13" ht="15" thickBot="1">
+    <row r="183" spans="1:13" ht="15.75" thickBot="1">
       <c r="A183" s="1" t="s">
         <v>946</v>
       </c>
@@ -19610,7 +19610,7 @@
       </c>
       <c r="M183" s="69"/>
     </row>
-    <row r="184" spans="1:13" ht="15" thickBot="1">
+    <row r="184" spans="1:13" ht="15.75" thickBot="1">
       <c r="A184" s="1" t="s">
         <v>947</v>
       </c>
@@ -19638,7 +19638,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="185" spans="1:13" ht="15" thickBot="1">
+    <row r="185" spans="1:13" ht="15.75" thickBot="1">
       <c r="A185" s="1" t="s">
         <v>948</v>
       </c>
@@ -19667,7 +19667,7 @@
       </c>
       <c r="M185" s="43"/>
     </row>
-    <row r="186" spans="1:13" ht="15" thickBot="1">
+    <row r="186" spans="1:13" ht="15.75" thickBot="1">
       <c r="A186" s="1" t="s">
         <v>949</v>
       </c>
@@ -19692,7 +19692,7 @@
       <c r="L186"/>
       <c r="M186" s="84"/>
     </row>
-    <row r="187" spans="1:13" ht="15" thickBot="1">
+    <row r="187" spans="1:13" ht="15.75" thickBot="1">
       <c r="A187" s="1" t="s">
         <v>950</v>
       </c>
@@ -19721,7 +19721,7 @@
       </c>
       <c r="M187" s="44"/>
     </row>
-    <row r="188" spans="1:13" ht="15" thickBot="1">
+    <row r="188" spans="1:13" ht="15.75" thickBot="1">
       <c r="A188" s="1" t="s">
         <v>951</v>
       </c>
@@ -19746,7 +19746,7 @@
       <c r="L188"/>
       <c r="M188" s="44"/>
     </row>
-    <row r="189" spans="1:13" ht="15" thickBot="1">
+    <row r="189" spans="1:13" ht="15.75" thickBot="1">
       <c r="A189" s="1" t="s">
         <v>952</v>
       </c>
@@ -19775,7 +19775,7 @@
       </c>
       <c r="M189" s="44"/>
     </row>
-    <row r="190" spans="1:13" ht="15" thickBot="1">
+    <row r="190" spans="1:13" ht="15.75" thickBot="1">
       <c r="A190" t="s">
         <v>1162</v>
       </c>
@@ -19803,7 +19803,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="191" spans="1:13" ht="15" thickBot="1">
+    <row r="191" spans="1:13" ht="15.75" thickBot="1">
       <c r="A191" t="s">
         <v>1158</v>
       </c>
@@ -19831,7 +19831,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="192" spans="1:13" ht="15" thickBot="1">
+    <row r="192" spans="1:13" ht="15.75" thickBot="1">
       <c r="A192" t="s">
         <v>1160</v>
       </c>
@@ -19859,7 +19859,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="193" spans="1:13" ht="15" thickBot="1">
+    <row r="193" spans="1:13" ht="15.75" thickBot="1">
       <c r="A193" t="s">
         <v>1165</v>
       </c>
@@ -19887,7 +19887,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="194" spans="1:13" ht="15" thickBot="1">
+    <row r="194" spans="1:13" ht="15.75" thickBot="1">
       <c r="A194" t="s">
         <v>1172</v>
       </c>
@@ -19920,7 +19920,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="195" spans="1:13" ht="15" thickBot="1">
+    <row r="195" spans="1:13" ht="15.75" thickBot="1">
       <c r="A195" t="s">
         <v>1169</v>
       </c>
@@ -19951,7 +19951,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="196" spans="1:13" ht="15" thickBot="1">
+    <row r="196" spans="1:13" ht="15.75" thickBot="1">
       <c r="A196" t="s">
         <v>1157</v>
       </c>
@@ -19975,7 +19975,7 @@
       <c r="K196" s="17"/>
       <c r="L196" s="47"/>
     </row>
-    <row r="197" spans="1:13" ht="15" thickBot="1">
+    <row r="197" spans="1:13" ht="15.75" thickBot="1">
       <c r="A197" s="1" t="s">
         <v>1179</v>
       </c>
@@ -20010,7 +20010,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="198" spans="1:13" ht="15" thickBot="1">
+    <row r="198" spans="1:13" ht="15.75" thickBot="1">
       <c r="A198" s="1" t="s">
         <v>953</v>
       </c>
@@ -20039,7 +20039,7 @@
       </c>
       <c r="M198" s="84"/>
     </row>
-    <row r="199" spans="1:13" ht="15" thickBot="1">
+    <row r="199" spans="1:13" ht="15.75" thickBot="1">
       <c r="A199" s="1" t="s">
         <v>954</v>
       </c>
@@ -20068,7 +20068,7 @@
       </c>
       <c r="M199" s="84"/>
     </row>
-    <row r="200" spans="1:13" ht="15" thickBot="1">
+    <row r="200" spans="1:13" ht="15.75" thickBot="1">
       <c r="A200" s="1" t="s">
         <v>955</v>
       </c>
@@ -20096,7 +20096,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="201" spans="1:13" ht="15" thickBot="1">
+    <row r="201" spans="1:13" ht="15.75" thickBot="1">
       <c r="A201" s="1" t="s">
         <v>956</v>
       </c>
@@ -20127,7 +20127,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="202" spans="1:13" ht="15" thickBot="1">
+    <row r="202" spans="1:13" ht="15.75" thickBot="1">
       <c r="A202" s="1" t="s">
         <v>957</v>
       </c>
@@ -20154,7 +20154,7 @@
       <c r="L202"/>
       <c r="M202" s="84"/>
     </row>
-    <row r="203" spans="1:13" ht="15" thickBot="1">
+    <row r="203" spans="1:13" ht="15.75" thickBot="1">
       <c r="A203" s="1" t="s">
         <v>958</v>
       </c>
@@ -20187,7 +20187,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="204" spans="1:13" ht="15" thickBot="1">
+    <row r="204" spans="1:13" ht="15.75" thickBot="1">
       <c r="A204" s="1" t="s">
         <v>959</v>
       </c>
@@ -20212,7 +20212,7 @@
       <c r="L204"/>
       <c r="M204" s="44"/>
     </row>
-    <row r="205" spans="1:13" ht="15" thickBot="1">
+    <row r="205" spans="1:13" ht="15.75" thickBot="1">
       <c r="A205" s="1" t="s">
         <v>960</v>
       </c>
@@ -20243,7 +20243,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="206" spans="1:13" ht="15" thickBot="1">
+    <row r="206" spans="1:13" ht="15.75" thickBot="1">
       <c r="A206" t="s">
         <v>1163</v>
       </c>
@@ -20271,7 +20271,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="207" spans="1:13" ht="15" thickBot="1">
+    <row r="207" spans="1:13" ht="15.75" thickBot="1">
       <c r="A207" t="s">
         <v>1159</v>
       </c>
@@ -20302,7 +20302,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="208" spans="1:13" ht="15" thickBot="1">
+    <row r="208" spans="1:13" ht="15.75" thickBot="1">
       <c r="A208" t="s">
         <v>1161</v>
       </c>
@@ -20333,7 +20333,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="209" spans="1:13" ht="15" thickBot="1">
+    <row r="209" spans="1:13" ht="15.75" thickBot="1">
       <c r="A209" t="s">
         <v>1166</v>
       </c>
@@ -20364,7 +20364,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="210" spans="1:13" ht="15" thickBot="1">
+    <row r="210" spans="1:13" ht="15.75" thickBot="1">
       <c r="A210" t="s">
         <v>1173</v>
       </c>
@@ -20397,7 +20397,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="211" spans="1:13" ht="15" thickBot="1">
+    <row r="211" spans="1:13" ht="15.75" thickBot="1">
       <c r="A211" t="s">
         <v>1170</v>
       </c>
@@ -20428,7 +20428,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="212" spans="1:13" ht="15" thickBot="1">
+    <row r="212" spans="1:13" ht="15.75" thickBot="1">
       <c r="A212" t="s">
         <v>1104</v>
       </c>
@@ -20490,7 +20490,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="214" spans="1:13" ht="15" thickBot="1">
+    <row r="214" spans="1:13" ht="15.75" thickBot="1">
       <c r="A214" t="s">
         <v>1109</v>
       </c>
@@ -20523,7 +20523,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="215" spans="1:13" ht="15" thickBot="1">
+    <row r="215" spans="1:13" ht="15.75" thickBot="1">
       <c r="A215" t="s">
         <v>1113</v>
       </c>
@@ -20556,7 +20556,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="216" spans="1:13" ht="15" thickBot="1">
+    <row r="216" spans="1:13" ht="15.75" thickBot="1">
       <c r="A216" t="s">
         <v>1111</v>
       </c>
@@ -20583,7 +20583,7 @@
       <c r="L216" s="47"/>
       <c r="M216" s="29"/>
     </row>
-    <row r="217" spans="1:13" ht="15" thickBot="1">
+    <row r="217" spans="1:13" ht="15.75" thickBot="1">
       <c r="A217" t="s">
         <v>1105</v>
       </c>
@@ -20645,7 +20645,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="219" spans="1:13" ht="15" thickBot="1">
+    <row r="219" spans="1:13" ht="15.75" thickBot="1">
       <c r="A219" t="s">
         <v>1110</v>
       </c>
@@ -20678,7 +20678,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="220" spans="1:13" ht="15" thickBot="1">
+    <row r="220" spans="1:13" ht="15.75" thickBot="1">
       <c r="A220" t="s">
         <v>1114</v>
       </c>
@@ -20711,7 +20711,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="221" spans="1:13" ht="15" thickBot="1">
+    <row r="221" spans="1:13" ht="15.75" thickBot="1">
       <c r="A221" t="s">
         <v>1112</v>
       </c>
@@ -20737,7 +20737,7 @@
       <c r="K221" s="17"/>
       <c r="L221"/>
     </row>
-    <row r="222" spans="1:13" ht="15" thickBot="1">
+    <row r="222" spans="1:13" ht="15.75" thickBot="1">
       <c r="A222" t="s">
         <v>1121</v>
       </c>
@@ -20827,7 +20827,7 @@
       </c>
       <c r="L224"/>
     </row>
-    <row r="225" spans="1:13" ht="15" thickBot="1">
+    <row r="225" spans="1:13" ht="15.75" thickBot="1">
       <c r="A225" t="s">
         <v>1131</v>
       </c>
@@ -20858,7 +20858,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="226" spans="1:13" ht="15" thickBot="1">
+    <row r="226" spans="1:13" ht="15.75" thickBot="1">
       <c r="A226" t="s">
         <v>1133</v>
       </c>
@@ -20886,7 +20886,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="227" spans="1:13" ht="15" thickBot="1">
+    <row r="227" spans="1:13" ht="15.75" thickBot="1">
       <c r="A227" t="s">
         <v>1127</v>
       </c>
@@ -20917,7 +20917,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="228" spans="1:13" ht="15" thickBot="1">
+    <row r="228" spans="1:13" ht="15.75" thickBot="1">
       <c r="A228" t="s">
         <v>1125</v>
       </c>
@@ -20943,7 +20943,7 @@
       </c>
       <c r="L228" s="47"/>
     </row>
-    <row r="229" spans="1:13" ht="15" thickBot="1">
+    <row r="229" spans="1:13" ht="15.75" thickBot="1">
       <c r="A229" t="s">
         <v>1129</v>
       </c>
@@ -20974,7 +20974,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="230" spans="1:13" ht="15" thickBot="1">
+    <row r="230" spans="1:13" ht="15.75" thickBot="1">
       <c r="A230" t="s">
         <v>1122</v>
       </c>
@@ -21064,7 +21064,7 @@
       </c>
       <c r="L232"/>
     </row>
-    <row r="233" spans="1:13" ht="15" thickBot="1">
+    <row r="233" spans="1:13" ht="15.75" thickBot="1">
       <c r="A233" t="s">
         <v>1132</v>
       </c>
@@ -21095,7 +21095,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="234" spans="1:13" ht="15" thickBot="1">
+    <row r="234" spans="1:13" ht="15.75" thickBot="1">
       <c r="A234" t="s">
         <v>1134</v>
       </c>
@@ -21123,7 +21123,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="235" spans="1:13" ht="15" thickBot="1">
+    <row r="235" spans="1:13" ht="15.75" thickBot="1">
       <c r="A235" t="s">
         <v>1128</v>
       </c>
@@ -21149,7 +21149,7 @@
       </c>
       <c r="L235" s="48"/>
     </row>
-    <row r="236" spans="1:13" ht="15" thickBot="1">
+    <row r="236" spans="1:13" ht="15.75" thickBot="1">
       <c r="A236" t="s">
         <v>1126</v>
       </c>
@@ -21180,7 +21180,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="237" spans="1:13" ht="15" thickBot="1">
+    <row r="237" spans="1:13" ht="15.75" thickBot="1">
       <c r="A237" t="s">
         <v>1130</v>
       </c>
@@ -21208,7 +21208,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="238" spans="1:13" ht="15" thickBot="1">
+    <row r="238" spans="1:13" ht="15.75" thickBot="1">
       <c r="A238" t="s">
         <v>985</v>
       </c>
@@ -21232,7 +21232,7 @@
       <c r="K238" s="17"/>
       <c r="L238"/>
     </row>
-    <row r="239" spans="1:13" ht="15" thickBot="1">
+    <row r="239" spans="1:13" ht="15.75" thickBot="1">
       <c r="A239" s="104" t="s">
         <v>986</v>
       </c>
@@ -21266,7 +21266,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="240" spans="1:13" ht="15" thickBot="1">
+    <row r="240" spans="1:13" ht="15.75" thickBot="1">
       <c r="A240" t="s">
         <v>987</v>
       </c>
@@ -21290,7 +21290,7 @@
       <c r="K240" s="17"/>
       <c r="L240" s="47"/>
     </row>
-    <row r="241" spans="1:13" ht="15" thickBot="1">
+    <row r="241" spans="1:13" ht="15.75" thickBot="1">
       <c r="A241" s="104" t="s">
         <v>988</v>
       </c>
@@ -21324,7 +21324,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="242" spans="1:13" ht="15" thickBot="1">
+    <row r="242" spans="1:13" ht="15.75" thickBot="1">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -21344,7 +21344,7 @@
       </c>
       <c r="L242"/>
     </row>
-    <row r="243" spans="1:13" ht="15" thickBot="1">
+    <row r="243" spans="1:13" ht="15.75" thickBot="1">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -21366,7 +21366,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="244" spans="1:13" ht="15" thickBot="1">
+    <row r="244" spans="1:13" ht="15.75" thickBot="1">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -21391,7 +21391,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="245" spans="1:13" ht="15" thickBot="1">
+    <row r="245" spans="1:13" ht="15.75" thickBot="1">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -21413,7 +21413,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="246" spans="1:13" ht="15" thickBot="1">
+    <row r="246" spans="1:13" ht="15.75" thickBot="1">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -21435,7 +21435,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="247" spans="1:13" ht="15" thickBot="1">
+    <row r="247" spans="1:13" ht="15.75" thickBot="1">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -21455,7 +21455,7 @@
       </c>
       <c r="L247"/>
     </row>
-    <row r="248" spans="1:13" ht="15" thickBot="1">
+    <row r="248" spans="1:13" ht="15.75" thickBot="1">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -21477,7 +21477,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="249" spans="1:13" ht="15" thickBot="1">
+    <row r="249" spans="1:13" ht="15.75" thickBot="1">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -21502,7 +21502,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="250" spans="1:13" ht="15" thickBot="1">
+    <row r="250" spans="1:13" ht="15.75" thickBot="1">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -21706,7 +21706,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="257" spans="1:13" ht="15" thickBot="1">
+    <row r="257" spans="1:13" ht="15.75" thickBot="1">
       <c r="A257" s="9" t="s">
         <v>1012</v>
       </c>
@@ -21738,7 +21738,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="258" spans="1:13" ht="15" thickBot="1">
+    <row r="258" spans="1:13" ht="15.75" thickBot="1">
       <c r="A258" s="9" t="s">
         <v>1012</v>
       </c>
@@ -21768,7 +21768,7 @@
       <c r="K258" s="19"/>
       <c r="L258"/>
     </row>
-    <row r="259" spans="1:13" ht="15" thickBot="1">
+    <row r="259" spans="1:13" ht="15.75" thickBot="1">
       <c r="A259" s="9" t="s">
         <v>1012</v>
       </c>
@@ -21798,7 +21798,7 @@
       <c r="K259" s="19"/>
       <c r="L259"/>
     </row>
-    <row r="260" spans="1:13" ht="15" thickBot="1">
+    <row r="260" spans="1:13" ht="15.75" thickBot="1">
       <c r="A260" s="9" t="s">
         <v>1012</v>
       </c>
@@ -21828,7 +21828,7 @@
       <c r="K260" s="19"/>
       <c r="L260"/>
     </row>
-    <row r="261" spans="1:13" ht="15" thickBot="1">
+    <row r="261" spans="1:13" ht="15.75" thickBot="1">
       <c r="A261" s="9" t="s">
         <v>1012</v>
       </c>
@@ -21858,7 +21858,7 @@
       <c r="K261" s="19"/>
       <c r="L261"/>
     </row>
-    <row r="262" spans="1:13" ht="15" thickBot="1">
+    <row r="262" spans="1:13" ht="15.75" thickBot="1">
       <c r="A262" s="9" t="s">
         <v>1012</v>
       </c>
@@ -21888,7 +21888,7 @@
       <c r="K262" s="19"/>
       <c r="L262"/>
     </row>
-    <row r="263" spans="1:13" ht="15" thickBot="1">
+    <row r="263" spans="1:13" ht="15.75" thickBot="1">
       <c r="A263" s="9" t="s">
         <v>1012</v>
       </c>
@@ -21918,7 +21918,7 @@
       <c r="K263" s="19"/>
       <c r="L263"/>
     </row>
-    <row r="264" spans="1:13" ht="15" thickBot="1">
+    <row r="264" spans="1:13" ht="15.75" thickBot="1">
       <c r="A264" s="9" t="s">
         <v>1012</v>
       </c>
@@ -21948,7 +21948,7 @@
       <c r="K264" s="19"/>
       <c r="L264"/>
     </row>
-    <row r="265" spans="1:13" ht="15" thickBot="1">
+    <row r="265" spans="1:13" ht="15.75" thickBot="1">
       <c r="A265" s="9" t="s">
         <v>1012</v>
       </c>
@@ -21978,7 +21978,7 @@
       <c r="K265" s="19"/>
       <c r="L265"/>
     </row>
-    <row r="266" spans="1:13" ht="15" thickBot="1">
+    <row r="266" spans="1:13" ht="15.75" thickBot="1">
       <c r="A266" s="9" t="s">
         <v>1012</v>
       </c>
@@ -22008,7 +22008,7 @@
       <c r="K266" s="19"/>
       <c r="L266"/>
     </row>
-    <row r="267" spans="1:13" ht="15" thickBot="1">
+    <row r="267" spans="1:13" ht="15.75" thickBot="1">
       <c r="A267" s="9" t="s">
         <v>1012</v>
       </c>
@@ -22038,7 +22038,7 @@
       <c r="K267" s="19"/>
       <c r="L267"/>
     </row>
-    <row r="268" spans="1:13" ht="15" thickBot="1">
+    <row r="268" spans="1:13" ht="15.75" thickBot="1">
       <c r="A268" t="s">
         <v>1014</v>
       </c>
@@ -22066,7 +22066,7 @@
         <v>1316</v>
       </c>
     </row>
-    <row r="269" spans="1:13" ht="15" thickBot="1">
+    <row r="269" spans="1:13" ht="15.75" thickBot="1">
       <c r="A269" t="s">
         <v>1013</v>
       </c>
@@ -22180,7 +22180,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="273" spans="1:14" ht="15" thickBot="1">
+    <row r="273" spans="1:14" ht="15.75" thickBot="1">
       <c r="A273" t="s">
         <v>1327</v>
       </c>
@@ -22212,7 +22212,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="274" spans="1:14" ht="15" thickBot="1">
+    <row r="274" spans="1:14" ht="15.75" thickBot="1">
       <c r="A274" s="1" t="s">
         <v>1333</v>
       </c>
@@ -22329,7 +22329,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="278" spans="1:14" ht="15" thickBot="1">
+    <row r="278" spans="1:14" ht="15.75" thickBot="1">
       <c r="A278" t="s">
         <v>1328</v>
       </c>
@@ -22358,7 +22358,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="279" spans="1:14" ht="15" thickBot="1">
+    <row r="279" spans="1:14" ht="15.75" thickBot="1">
       <c r="A279" s="1" t="s">
         <v>1334</v>
       </c>
@@ -22788,7 +22788,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="293" spans="1:13" ht="16">
+    <row r="293" spans="1:13" ht="15.75">
       <c r="A293" t="s">
         <v>1188</v>
       </c>
@@ -22823,7 +22823,7 @@
       <c r="L293" s="3"/>
       <c r="M293" s="3"/>
     </row>
-    <row r="294" spans="1:13" ht="16">
+    <row r="294" spans="1:13" ht="15.75">
       <c r="A294" t="s">
         <v>1190</v>
       </c>
@@ -22891,7 +22891,7 @@
       <c r="L295" s="3"/>
       <c r="M295" s="3"/>
     </row>
-    <row r="296" spans="1:13" ht="14.5" customHeight="1">
+    <row r="296" spans="1:13" ht="14.45" customHeight="1">
       <c r="A296" t="s">
         <v>1020</v>
       </c>
@@ -22992,7 +22992,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="299" spans="1:13" ht="16">
+    <row r="299" spans="1:13" ht="15.75">
       <c r="A299" t="s">
         <v>1189</v>
       </c>
@@ -23023,7 +23023,7 @@
       <c r="L299" s="3"/>
       <c r="M299" s="3"/>
     </row>
-    <row r="300" spans="1:13" ht="16">
+    <row r="300" spans="1:13" ht="15.75">
       <c r="A300" t="s">
         <v>1191</v>
       </c>
@@ -23091,7 +23091,7 @@
       <c r="L301" s="3"/>
       <c r="M301" s="3"/>
     </row>
-    <row r="302" spans="1:13" ht="14.5" customHeight="1" thickBot="1">
+    <row r="302" spans="1:13" ht="14.45" customHeight="1" thickBot="1">
       <c r="A302" t="s">
         <v>1021</v>
       </c>
@@ -23124,7 +23124,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="303" spans="1:13" ht="14.5" customHeight="1" thickBot="1">
+    <row r="303" spans="1:13" ht="14.45" customHeight="1" thickBot="1">
       <c r="A303" t="s">
         <v>1201</v>
       </c>
@@ -23152,7 +23152,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="304" spans="1:13" ht="14.5" customHeight="1">
+    <row r="304" spans="1:13" ht="14.45" customHeight="1">
       <c r="A304" t="s">
         <v>1209</v>
       </c>
@@ -23176,7 +23176,7 @@
       <c r="K304" s="14"/>
       <c r="L304" s="14"/>
     </row>
-    <row r="305" spans="1:13" ht="14.5" customHeight="1">
+    <row r="305" spans="1:13" ht="14.45" customHeight="1">
       <c r="A305" s="14" t="s">
         <v>1203</v>
       </c>
@@ -23207,7 +23207,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="306" spans="1:13" ht="14.5" customHeight="1">
+    <row r="306" spans="1:13" ht="14.45" customHeight="1">
       <c r="A306" s="14" t="s">
         <v>1211</v>
       </c>
@@ -23473,7 +23473,7 @@
       <c r="L322" s="3"/>
       <c r="M322" s="3"/>
     </row>
-    <row r="323" spans="9:13" ht="15" thickBot="1">
+    <row r="323" spans="9:13" ht="15.75" thickBot="1">
       <c r="I323" s="14" t="s">
         <v>774</v>
       </c>
@@ -23486,7 +23486,7 @@
       <c r="L323" s="3"/>
       <c r="M323" s="3"/>
     </row>
-    <row r="324" spans="9:13" ht="26.5" thickBot="1">
+    <row r="324" spans="9:13" ht="26.25" thickBot="1">
       <c r="I324" s="14"/>
       <c r="J324" s="58" t="s">
         <v>845</v>
@@ -23510,7 +23510,7 @@
       <c r="L325" s="3"/>
       <c r="M325" s="3"/>
     </row>
-    <row r="326" spans="9:13" ht="15" thickBot="1">
+    <row r="326" spans="9:13" ht="15.75" thickBot="1">
       <c r="I326" s="14" t="s">
         <v>774</v>
       </c>
@@ -23523,7 +23523,7 @@
       <c r="L326" s="3"/>
       <c r="M326" s="3"/>
     </row>
-    <row r="327" spans="9:13" ht="26.5" thickBot="1">
+    <row r="327" spans="9:13" ht="26.25" thickBot="1">
       <c r="I327" s="14"/>
       <c r="J327" s="58" t="s">
         <v>846</v>
@@ -24274,7 +24274,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="366" spans="1:13" ht="15.5">
+    <row r="366" spans="1:13" ht="15.75">
       <c r="A366" s="14"/>
       <c r="B366" s="14"/>
       <c r="C366" s="14"/>
@@ -24399,7 +24399,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="371" spans="1:13" ht="15.5">
+    <row r="371" spans="1:13" ht="15.75">
       <c r="A371" s="14"/>
       <c r="B371" s="14"/>
       <c r="C371" s="14"/>
@@ -24446,7 +24446,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="373" spans="1:13" ht="15.5">
+    <row r="373" spans="1:13" ht="15.75">
       <c r="A373" s="14"/>
       <c r="B373" s="14"/>
       <c r="C373" s="14"/>
@@ -24516,7 +24516,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="376" spans="1:13" ht="15.5">
+    <row r="376" spans="1:13" ht="15.75">
       <c r="A376" s="14"/>
       <c r="B376" s="14"/>
       <c r="C376" s="14"/>
@@ -24614,7 +24614,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="380" spans="1:13" ht="15.5">
+    <row r="380" spans="1:13" ht="15.75">
       <c r="A380" s="14"/>
       <c r="B380" s="14"/>
       <c r="C380" s="14"/>
@@ -24712,7 +24712,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="384" spans="1:13" ht="15.5">
+    <row r="384" spans="1:13" ht="15.75">
       <c r="A384" s="14"/>
       <c r="B384" s="14"/>
       <c r="C384" s="14"/>
@@ -24735,7 +24735,7 @@
       </c>
       <c r="M384" s="5"/>
     </row>
-    <row r="385" spans="1:13" ht="15" thickBot="1">
+    <row r="385" spans="1:13" ht="15.75" thickBot="1">
       <c r="A385" s="14"/>
       <c r="B385" s="14"/>
       <c r="C385" s="14"/>
@@ -24760,7 +24760,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="386" spans="1:13" ht="15" thickBot="1">
+    <row r="386" spans="1:13" ht="15.75" thickBot="1">
       <c r="A386" s="14"/>
       <c r="B386" s="14"/>
       <c r="C386" s="14"/>
@@ -24781,7 +24781,7 @@
       <c r="L386" s="46"/>
       <c r="M386" s="14"/>
     </row>
-    <row r="387" spans="1:13" ht="15" thickBot="1">
+    <row r="387" spans="1:13" ht="15.75" thickBot="1">
       <c r="A387" s="14"/>
       <c r="B387" s="14"/>
       <c r="C387" s="14"/>
@@ -24802,7 +24802,7 @@
       <c r="L387" s="46"/>
       <c r="M387" s="14"/>
     </row>
-    <row r="388" spans="1:13" ht="15.5">
+    <row r="388" spans="1:13" ht="15.75">
       <c r="I388" s="14" t="s">
         <v>774</v>
       </c>
@@ -24878,7 +24878,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="392" spans="1:13" ht="15.5">
+    <row r="392" spans="1:13" ht="15.75">
       <c r="A392" s="14"/>
       <c r="B392" s="14"/>
       <c r="C392" s="14"/>
@@ -24953,7 +24953,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="395" spans="1:13" ht="15" thickBot="1">
+    <row r="395" spans="1:13" ht="15.75" thickBot="1">
       <c r="A395" s="14"/>
       <c r="B395" s="14"/>
       <c r="C395" s="14"/>
@@ -24978,7 +24978,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="396" spans="1:13" ht="15" thickBot="1">
+    <row r="396" spans="1:13" ht="15.75" thickBot="1">
       <c r="A396" s="14"/>
       <c r="B396" s="14"/>
       <c r="C396" s="14"/>
@@ -25003,7 +25003,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="397" spans="1:13" ht="15" thickBot="1">
+    <row r="397" spans="1:13" ht="15.75" thickBot="1">
       <c r="A397" s="14"/>
       <c r="B397" s="14"/>
       <c r="C397" s="14"/>
@@ -25028,7 +25028,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="398" spans="1:13" ht="15" thickBot="1">
+    <row r="398" spans="1:13" ht="15.75" thickBot="1">
       <c r="A398" s="14"/>
       <c r="B398" s="14"/>
       <c r="C398" s="14"/>
@@ -25053,7 +25053,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="399" spans="1:13" ht="15" thickBot="1">
+    <row r="399" spans="1:13" ht="15.75" thickBot="1">
       <c r="A399" s="14"/>
       <c r="B399" s="14"/>
       <c r="C399" s="14"/>
@@ -25078,7 +25078,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="400" spans="1:13" ht="15" thickBot="1">
+    <row r="400" spans="1:13" ht="15.75" thickBot="1">
       <c r="A400" s="14"/>
       <c r="B400" s="14"/>
       <c r="C400" s="14"/>
@@ -25103,7 +25103,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="401" spans="1:13" ht="15" thickBot="1">
+    <row r="401" spans="1:13" ht="15.75" thickBot="1">
       <c r="A401" s="14"/>
       <c r="B401" s="14"/>
       <c r="C401" s="14"/>
@@ -25128,7 +25128,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="402" spans="1:13" ht="15" thickBot="1">
+    <row r="402" spans="1:13" ht="15.75" thickBot="1">
       <c r="A402" s="14"/>
       <c r="B402" s="14"/>
       <c r="C402" s="14"/>
@@ -25153,7 +25153,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="403" spans="1:13" ht="15" thickBot="1">
+    <row r="403" spans="1:13" ht="15.75" thickBot="1">
       <c r="A403" s="14"/>
       <c r="B403" s="14"/>
       <c r="C403" s="14"/>
@@ -25178,7 +25178,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="404" spans="1:13" ht="15" thickBot="1">
+    <row r="404" spans="1:13" ht="15.75" thickBot="1">
       <c r="A404" s="14"/>
       <c r="B404" s="14"/>
       <c r="C404" s="14"/>
@@ -25203,7 +25203,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="405" spans="1:13" ht="15" thickBot="1">
+    <row r="405" spans="1:13" ht="15.75" thickBot="1">
       <c r="A405" s="14"/>
       <c r="B405" s="14"/>
       <c r="C405" s="14"/>
@@ -25228,7 +25228,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="406" spans="1:13" ht="15" thickBot="1">
+    <row r="406" spans="1:13" ht="15.75" thickBot="1">
       <c r="A406" s="14"/>
       <c r="B406" s="14"/>
       <c r="C406" s="14"/>
@@ -25253,7 +25253,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="407" spans="1:13" ht="15" thickBot="1">
+    <row r="407" spans="1:13" ht="15.75" thickBot="1">
       <c r="A407" s="14"/>
       <c r="B407" s="14"/>
       <c r="C407" s="14"/>
@@ -25275,7 +25275,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="408" spans="1:13" ht="15" thickBot="1">
+    <row r="408" spans="1:13" ht="15.75" thickBot="1">
       <c r="A408" s="14"/>
       <c r="B408" s="14"/>
       <c r="C408" s="14"/>
@@ -25297,7 +25297,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="409" spans="1:13" ht="15" thickBot="1">
+    <row r="409" spans="1:13" ht="15.75" thickBot="1">
       <c r="A409" s="14"/>
       <c r="B409" s="14"/>
       <c r="C409" s="14"/>
@@ -25319,7 +25319,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="410" spans="1:13" ht="15" thickBot="1">
+    <row r="410" spans="1:13" ht="15.75" thickBot="1">
       <c r="A410" s="14"/>
       <c r="B410" s="14"/>
       <c r="C410" s="14"/>
@@ -25341,7 +25341,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="411" spans="1:13" ht="15" thickBot="1">
+    <row r="411" spans="1:13" ht="15.75" thickBot="1">
       <c r="A411" s="14"/>
       <c r="B411" s="14"/>
       <c r="C411" s="14"/>
@@ -25363,7 +25363,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="412" spans="1:13" ht="15" thickBot="1">
+    <row r="412" spans="1:13" ht="15.75" thickBot="1">
       <c r="A412" s="14"/>
       <c r="B412" s="14"/>
       <c r="C412" s="14"/>
@@ -25385,7 +25385,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="413" spans="1:13" ht="15" thickBot="1">
+    <row r="413" spans="1:13" ht="15.75" thickBot="1">
       <c r="A413" s="14"/>
       <c r="B413" s="14"/>
       <c r="C413" s="14"/>
@@ -25407,7 +25407,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="414" spans="1:13" ht="15" thickBot="1">
+    <row r="414" spans="1:13" ht="15.75" thickBot="1">
       <c r="A414" s="14"/>
       <c r="B414" s="14"/>
       <c r="C414" s="14"/>
@@ -25429,7 +25429,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="415" spans="1:13" ht="15" thickBot="1">
+    <row r="415" spans="1:13" ht="15.75" thickBot="1">
       <c r="A415" s="14"/>
       <c r="B415" s="14"/>
       <c r="C415" s="14"/>
@@ -25452,7 +25452,7 @@
       </c>
       <c r="M415" s="41"/>
     </row>
-    <row r="416" spans="1:13" ht="15" thickBot="1">
+    <row r="416" spans="1:13" ht="15.75" thickBot="1">
       <c r="A416" s="14"/>
       <c r="B416" s="14"/>
       <c r="C416" s="14"/>
@@ -25477,7 +25477,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="417" spans="1:13" ht="15" thickBot="1">
+    <row r="417" spans="1:13" ht="15.75" thickBot="1">
       <c r="A417" s="14"/>
       <c r="B417" s="14"/>
       <c r="C417" s="14"/>
@@ -25502,7 +25502,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="418" spans="1:13" ht="15" thickBot="1">
+    <row r="418" spans="1:13" ht="15.75" thickBot="1">
       <c r="A418" s="14"/>
       <c r="B418" s="14"/>
       <c r="C418" s="14"/>
@@ -25527,7 +25527,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="419" spans="1:13" ht="15" thickBot="1">
+    <row r="419" spans="1:13" ht="15.75" thickBot="1">
       <c r="A419" s="14"/>
       <c r="B419" s="14"/>
       <c r="C419" s="14"/>
@@ -25552,7 +25552,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="420" spans="1:13" ht="15" thickBot="1">
+    <row r="420" spans="1:13" ht="15.75" thickBot="1">
       <c r="A420" s="14"/>
       <c r="B420" s="14"/>
       <c r="C420" s="14"/>
@@ -25577,7 +25577,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="421" spans="1:13" ht="15" thickBot="1">
+    <row r="421" spans="1:13" ht="15.75" thickBot="1">
       <c r="A421" s="14"/>
       <c r="B421" s="14"/>
       <c r="C421" s="14"/>
@@ -25602,7 +25602,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="422" spans="1:13" ht="15" thickBot="1">
+    <row r="422" spans="1:13" ht="15.75" thickBot="1">
       <c r="A422" s="14"/>
       <c r="B422" s="14"/>
       <c r="C422" s="14"/>
@@ -25627,7 +25627,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="423" spans="1:13" ht="15" thickBot="1">
+    <row r="423" spans="1:13" ht="15.75" thickBot="1">
       <c r="A423" s="14"/>
       <c r="B423" s="14"/>
       <c r="C423" s="14"/>
@@ -25652,7 +25652,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="424" spans="1:13" ht="15" thickBot="1">
+    <row r="424" spans="1:13" ht="15.75" thickBot="1">
       <c r="A424" s="14"/>
       <c r="B424" s="14"/>
       <c r="C424" s="14"/>
@@ -25677,7 +25677,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="425" spans="1:13" ht="15" thickBot="1">
+    <row r="425" spans="1:13" ht="15.75" thickBot="1">
       <c r="A425" s="14"/>
       <c r="B425" s="14"/>
       <c r="C425" s="14"/>
@@ -25702,7 +25702,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="426" spans="1:13" ht="15" thickBot="1">
+    <row r="426" spans="1:13" ht="15.75" thickBot="1">
       <c r="A426" s="14"/>
       <c r="B426" s="14"/>
       <c r="C426" s="14"/>
@@ -25727,7 +25727,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="427" spans="1:13" ht="15" thickBot="1">
+    <row r="427" spans="1:13" ht="15.75" thickBot="1">
       <c r="A427" s="14"/>
       <c r="B427" s="14"/>
       <c r="C427" s="14"/>
@@ -25749,7 +25749,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="428" spans="1:13" ht="15" thickBot="1">
+    <row r="428" spans="1:13" ht="15.75" thickBot="1">
       <c r="A428" s="14"/>
       <c r="B428" s="14"/>
       <c r="C428" s="14"/>
@@ -25771,7 +25771,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="429" spans="1:13" ht="15" thickBot="1">
+    <row r="429" spans="1:13" ht="15.75" thickBot="1">
       <c r="A429" s="14"/>
       <c r="B429" s="14"/>
       <c r="C429" s="14"/>
@@ -25793,7 +25793,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="430" spans="1:13" ht="15" thickBot="1">
+    <row r="430" spans="1:13" ht="15.75" thickBot="1">
       <c r="A430" s="14"/>
       <c r="B430" s="14"/>
       <c r="C430" s="14"/>
@@ -25815,7 +25815,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="431" spans="1:13" ht="15" thickBot="1">
+    <row r="431" spans="1:13" ht="15.75" thickBot="1">
       <c r="A431" s="14"/>
       <c r="B431" s="14"/>
       <c r="C431" s="14"/>
@@ -25837,7 +25837,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="432" spans="1:13" ht="15" thickBot="1">
+    <row r="432" spans="1:13" ht="15.75" thickBot="1">
       <c r="A432" s="14"/>
       <c r="B432" s="14"/>
       <c r="C432" s="14"/>
@@ -25859,7 +25859,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="433" spans="1:13" ht="15" thickBot="1">
+    <row r="433" spans="1:13" ht="15.75" thickBot="1">
       <c r="A433" s="14"/>
       <c r="B433" s="14"/>
       <c r="C433" s="14"/>
@@ -25881,7 +25881,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="434" spans="1:13" ht="15" thickBot="1">
+    <row r="434" spans="1:13" ht="15.75" thickBot="1">
       <c r="A434" s="14"/>
       <c r="B434" s="14"/>
       <c r="C434" s="14"/>
@@ -25903,7 +25903,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="435" spans="1:13" ht="15" thickBot="1">
+    <row r="435" spans="1:13" ht="15.75" thickBot="1">
       <c r="A435" s="14"/>
       <c r="B435" s="14"/>
       <c r="C435" s="14"/>
@@ -25926,7 +25926,7 @@
       </c>
       <c r="M435" s="41"/>
     </row>
-    <row r="436" spans="1:13" ht="15" thickBot="1">
+    <row r="436" spans="1:13" ht="15.75" thickBot="1">
       <c r="A436" s="14"/>
       <c r="B436" s="14"/>
       <c r="C436" s="14"/>
@@ -25951,7 +25951,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="437" spans="1:13" ht="15" thickBot="1">
+    <row r="437" spans="1:13" ht="15.75" thickBot="1">
       <c r="A437" s="14"/>
       <c r="B437" s="14"/>
       <c r="C437" s="14"/>
@@ -25976,7 +25976,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="438" spans="1:13" ht="15" thickBot="1">
+    <row r="438" spans="1:13" ht="15.75" thickBot="1">
       <c r="A438" s="14"/>
       <c r="B438" s="14"/>
       <c r="C438" s="14"/>
@@ -26001,7 +26001,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="439" spans="1:13" ht="15" thickBot="1">
+    <row r="439" spans="1:13" ht="15.75" thickBot="1">
       <c r="A439" s="14"/>
       <c r="B439" s="14"/>
       <c r="C439" s="14"/>
@@ -26026,7 +26026,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="440" spans="1:13" ht="15" thickBot="1">
+    <row r="440" spans="1:13" ht="15.75" thickBot="1">
       <c r="A440" s="14"/>
       <c r="B440" s="14"/>
       <c r="C440" s="14"/>
@@ -26051,7 +26051,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="441" spans="1:13" ht="15" thickBot="1">
+    <row r="441" spans="1:13" ht="15.75" thickBot="1">
       <c r="A441" s="14"/>
       <c r="B441" s="14"/>
       <c r="C441" s="14"/>
@@ -26076,7 +26076,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="442" spans="1:13" ht="15" thickBot="1">
+    <row r="442" spans="1:13" ht="15.75" thickBot="1">
       <c r="A442" s="14"/>
       <c r="B442" s="14"/>
       <c r="C442" s="14"/>
@@ -26101,7 +26101,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="443" spans="1:13" ht="15" thickBot="1">
+    <row r="443" spans="1:13" ht="15.75" thickBot="1">
       <c r="A443" s="14"/>
       <c r="B443" s="14"/>
       <c r="C443" s="14"/>
@@ -26126,7 +26126,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="444" spans="1:13" ht="15" thickBot="1">
+    <row r="444" spans="1:13" ht="15.75" thickBot="1">
       <c r="A444" s="14"/>
       <c r="B444" s="14"/>
       <c r="C444" s="14"/>
@@ -26151,7 +26151,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="445" spans="1:13" ht="15" thickBot="1">
+    <row r="445" spans="1:13" ht="15.75" thickBot="1">
       <c r="A445" s="14"/>
       <c r="B445" s="14"/>
       <c r="C445" s="14"/>
@@ -26173,7 +26173,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="446" spans="1:13" ht="15" thickBot="1">
+    <row r="446" spans="1:13" ht="15.75" thickBot="1">
       <c r="A446" s="14"/>
       <c r="B446" s="14"/>
       <c r="C446" s="14"/>
@@ -26196,7 +26196,7 @@
       </c>
       <c r="M446" s="43"/>
     </row>
-    <row r="447" spans="1:13" ht="15" thickBot="1">
+    <row r="447" spans="1:13" ht="15.75" thickBot="1">
       <c r="A447" s="14"/>
       <c r="B447" s="14"/>
       <c r="C447" s="14"/>
@@ -26219,7 +26219,7 @@
       </c>
       <c r="M447" s="44"/>
     </row>
-    <row r="448" spans="1:13" ht="15" thickBot="1">
+    <row r="448" spans="1:13" ht="15.75" thickBot="1">
       <c r="A448" s="14"/>
       <c r="B448" s="14"/>
       <c r="C448" s="14"/>
@@ -26242,7 +26242,7 @@
       </c>
       <c r="M448" s="44"/>
     </row>
-    <row r="449" spans="1:13" ht="15" thickBot="1">
+    <row r="449" spans="1:13" ht="15.75" thickBot="1">
       <c r="A449" s="14"/>
       <c r="B449" s="14"/>
       <c r="C449" s="14"/>
@@ -26264,7 +26264,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="450" spans="1:13" ht="15" thickBot="1">
+    <row r="450" spans="1:13" ht="15.75" thickBot="1">
       <c r="A450" s="14"/>
       <c r="B450" s="14"/>
       <c r="C450" s="14"/>
@@ -26286,7 +26286,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="451" spans="1:13" ht="15" thickBot="1">
+    <row r="451" spans="1:13" ht="15.75" thickBot="1">
       <c r="A451" s="14"/>
       <c r="B451" s="14"/>
       <c r="C451" s="14"/>
@@ -26308,7 +26308,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="452" spans="1:13" ht="15" thickBot="1">
+    <row r="452" spans="1:13" ht="15.75" thickBot="1">
       <c r="A452" s="14"/>
       <c r="B452" s="14"/>
       <c r="C452" s="14"/>
@@ -26330,7 +26330,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="453" spans="1:13" ht="15" thickBot="1">
+    <row r="453" spans="1:13" ht="15.75" thickBot="1">
       <c r="A453" s="14"/>
       <c r="B453" s="14"/>
       <c r="C453" s="14"/>
@@ -26355,7 +26355,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="454" spans="1:13" ht="15" thickBot="1">
+    <row r="454" spans="1:13" ht="15.75" thickBot="1">
       <c r="A454" s="14"/>
       <c r="B454" s="14"/>
       <c r="C454" s="14"/>
@@ -26380,7 +26380,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="455" spans="1:13" ht="15" thickBot="1">
+    <row r="455" spans="1:13" ht="15.75" thickBot="1">
       <c r="A455" s="14"/>
       <c r="B455" s="14"/>
       <c r="C455" s="14"/>
@@ -26402,7 +26402,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="456" spans="1:13" ht="15" thickBot="1">
+    <row r="456" spans="1:13" ht="15.75" thickBot="1">
       <c r="A456" s="14"/>
       <c r="B456" s="14"/>
       <c r="C456" s="14"/>
@@ -26427,7 +26427,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="457" spans="1:13" ht="15" thickBot="1">
+    <row r="457" spans="1:13" ht="15.75" thickBot="1">
       <c r="A457" s="14"/>
       <c r="B457" s="14"/>
       <c r="C457" s="14"/>
@@ -26452,7 +26452,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="458" spans="1:13" ht="15" thickBot="1">
+    <row r="458" spans="1:13" ht="15.75" thickBot="1">
       <c r="A458" s="14"/>
       <c r="B458" s="14"/>
       <c r="C458" s="14"/>
@@ -26477,7 +26477,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="459" spans="1:13" ht="15" thickBot="1">
+    <row r="459" spans="1:13" ht="15.75" thickBot="1">
       <c r="A459" s="14"/>
       <c r="B459" s="14"/>
       <c r="C459" s="14"/>
@@ -26499,7 +26499,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="460" spans="1:13" ht="15" thickBot="1">
+    <row r="460" spans="1:13" ht="15.75" thickBot="1">
       <c r="A460" s="14"/>
       <c r="B460" s="14"/>
       <c r="C460" s="14"/>
@@ -26524,7 +26524,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="461" spans="1:13" ht="15" thickBot="1">
+    <row r="461" spans="1:13" ht="15.75" thickBot="1">
       <c r="A461" s="14"/>
       <c r="B461" s="14"/>
       <c r="C461" s="14"/>
@@ -26549,7 +26549,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="462" spans="1:13" ht="15" thickBot="1">
+    <row r="462" spans="1:13" ht="15.75" thickBot="1">
       <c r="A462" s="14"/>
       <c r="B462" s="14"/>
       <c r="C462" s="14"/>
@@ -26574,7 +26574,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="463" spans="1:13" ht="15" thickBot="1">
+    <row r="463" spans="1:13" ht="15.75" thickBot="1">
       <c r="A463" s="14"/>
       <c r="B463" s="14"/>
       <c r="C463" s="14"/>
@@ -26599,7 +26599,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="464" spans="1:13" ht="15" thickBot="1">
+    <row r="464" spans="1:13" ht="15.75" thickBot="1">
       <c r="A464" s="14"/>
       <c r="B464" s="14"/>
       <c r="C464" s="14"/>
@@ -26624,7 +26624,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="465" spans="1:13" ht="15" thickBot="1">
+    <row r="465" spans="1:13" ht="15.75" thickBot="1">
       <c r="A465" s="14"/>
       <c r="B465" s="14"/>
       <c r="C465" s="14"/>
@@ -26649,7 +26649,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="466" spans="1:13" ht="15" thickBot="1">
+    <row r="466" spans="1:13" ht="15.75" thickBot="1">
       <c r="A466" s="14"/>
       <c r="B466" s="14"/>
       <c r="C466" s="14"/>
@@ -26674,7 +26674,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="467" spans="1:13" ht="15" thickBot="1">
+    <row r="467" spans="1:13" ht="15.75" thickBot="1">
       <c r="A467" s="14"/>
       <c r="B467" s="14"/>
       <c r="C467" s="14"/>
@@ -26699,7 +26699,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="468" spans="1:13" ht="15" thickBot="1">
+    <row r="468" spans="1:13" ht="15.75" thickBot="1">
       <c r="A468" s="14"/>
       <c r="B468" s="14"/>
       <c r="C468" s="14"/>
@@ -26724,7 +26724,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="469" spans="1:13" ht="15" thickBot="1">
+    <row r="469" spans="1:13" ht="15.75" thickBot="1">
       <c r="A469" s="14"/>
       <c r="B469" s="14"/>
       <c r="C469" s="14"/>
@@ -26749,7 +26749,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="470" spans="1:13" ht="15" thickBot="1">
+    <row r="470" spans="1:13" ht="15.75" thickBot="1">
       <c r="A470" s="14"/>
       <c r="B470" s="14"/>
       <c r="C470" s="14"/>
@@ -26771,7 +26771,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="471" spans="1:13" ht="15" thickBot="1">
+    <row r="471" spans="1:13" ht="15.75" thickBot="1">
       <c r="A471" s="14"/>
       <c r="B471" s="14"/>
       <c r="C471" s="14"/>
@@ -26796,7 +26796,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="472" spans="1:13" ht="15" thickBot="1">
+    <row r="472" spans="1:13" ht="15.75" thickBot="1">
       <c r="A472" s="14"/>
       <c r="B472" s="14"/>
       <c r="C472" s="14"/>
@@ -26821,7 +26821,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="473" spans="1:13" ht="15" thickBot="1">
+    <row r="473" spans="1:13" ht="15.75" thickBot="1">
       <c r="A473" s="14"/>
       <c r="B473" s="14"/>
       <c r="C473" s="14"/>
@@ -26846,7 +26846,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="474" spans="1:13" ht="15" thickBot="1">
+    <row r="474" spans="1:13" ht="15.75" thickBot="1">
       <c r="A474" s="14"/>
       <c r="B474" s="14"/>
       <c r="C474" s="14"/>
@@ -26868,7 +26868,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="475" spans="1:13" ht="15" thickBot="1">
+    <row r="475" spans="1:13" ht="15.75" thickBot="1">
       <c r="A475" s="14"/>
       <c r="B475" s="14"/>
       <c r="C475" s="14"/>
@@ -26893,7 +26893,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="476" spans="1:13" ht="15" thickBot="1">
+    <row r="476" spans="1:13" ht="15.75" thickBot="1">
       <c r="A476" s="14"/>
       <c r="B476" s="14"/>
       <c r="C476" s="14"/>
@@ -26918,7 +26918,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="477" spans="1:13" ht="15" thickBot="1">
+    <row r="477" spans="1:13" ht="15.75" thickBot="1">
       <c r="A477" s="14"/>
       <c r="B477" s="14"/>
       <c r="C477" s="14"/>
@@ -26940,7 +26940,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="478" spans="1:13" ht="15" thickBot="1">
+    <row r="478" spans="1:13" ht="15.75" thickBot="1">
       <c r="A478" s="14"/>
       <c r="B478" s="14"/>
       <c r="C478" s="14"/>
@@ -26962,7 +26962,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="479" spans="1:13" ht="15" thickBot="1">
+    <row r="479" spans="1:13" ht="15.75" thickBot="1">
       <c r="A479" s="14"/>
       <c r="B479" s="14"/>
       <c r="C479" s="14"/>
@@ -26984,7 +26984,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="480" spans="1:13" ht="15" thickBot="1">
+    <row r="480" spans="1:13" ht="15.75" thickBot="1">
       <c r="A480" s="14"/>
       <c r="B480" s="14"/>
       <c r="C480" s="14"/>
@@ -27006,7 +27006,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="481" spans="1:13" ht="15" thickBot="1">
+    <row r="481" spans="1:13" ht="15.75" thickBot="1">
       <c r="A481" s="14"/>
       <c r="B481" s="14"/>
       <c r="C481" s="14"/>
@@ -27031,7 +27031,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="482" spans="1:13" ht="15" thickBot="1">
+    <row r="482" spans="1:13" ht="15.75" thickBot="1">
       <c r="A482" s="14"/>
       <c r="B482" s="14"/>
       <c r="C482" s="14"/>
@@ -27053,7 +27053,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="483" spans="1:13" ht="15" thickBot="1">
+    <row r="483" spans="1:13" ht="15.75" thickBot="1">
       <c r="A483" s="14"/>
       <c r="B483" s="14"/>
       <c r="C483" s="14"/>
@@ -27075,7 +27075,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="484" spans="1:13" ht="15" thickBot="1">
+    <row r="484" spans="1:13" ht="15.75" thickBot="1">
       <c r="A484" s="14"/>
       <c r="B484" s="14"/>
       <c r="C484" s="14"/>
@@ -27534,7 +27534,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="504" spans="1:13" ht="15.5">
+    <row r="504" spans="1:13" ht="15.75">
       <c r="A504" s="1"/>
       <c r="B504" s="1"/>
       <c r="C504" s="1"/>
@@ -27858,7 +27858,7 @@
       <c r="L521" s="37"/>
       <c r="M521" s="14"/>
     </row>
-    <row r="522" spans="1:13" ht="15.5">
+    <row r="522" spans="1:13" ht="15.75">
       <c r="A522" s="1"/>
       <c r="B522" s="1"/>
       <c r="C522" s="1"/>
@@ -27879,7 +27879,7 @@
       </c>
       <c r="M522" s="5"/>
     </row>
-    <row r="523" spans="1:13" ht="15.5">
+    <row r="523" spans="1:13" ht="15.75">
       <c r="A523" s="1"/>
       <c r="B523" s="1"/>
       <c r="C523" s="1"/>
@@ -27945,7 +27945,7 @@
       <c r="L526" s="4"/>
       <c r="M526" s="3"/>
     </row>
-    <row r="527" spans="1:13" ht="15.5">
+    <row r="527" spans="1:13" ht="15.75">
       <c r="A527" s="1"/>
       <c r="B527" s="1"/>
       <c r="C527" s="1"/>
@@ -27960,7 +27960,7 @@
       <c r="L527" s="4"/>
       <c r="M527" s="5"/>
     </row>
-    <row r="528" spans="1:13" ht="15.5">
+    <row r="528" spans="1:13" ht="15.75">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="1"/>
@@ -27975,7 +27975,7 @@
       <c r="L528" s="4"/>
       <c r="M528" s="5"/>
     </row>
-    <row r="529" spans="1:13" ht="15.5">
+    <row r="529" spans="1:13" ht="15.75">
       <c r="A529" s="1"/>
       <c r="B529" s="1"/>
       <c r="C529" s="1"/>
@@ -28082,7 +28082,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="534" spans="1:13">
+    <row r="534" spans="1:13" ht="26.25">
       <c r="A534" s="1"/>
       <c r="B534" s="1"/>
       <c r="C534" s="1"/>
@@ -28105,7 +28105,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="535" spans="1:13" ht="26">
+    <row r="535" spans="1:13" ht="26.25">
       <c r="A535" s="7"/>
       <c r="B535" s="7"/>
       <c r="C535" s="7"/>
@@ -28151,7 +28151,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="537" spans="1:13" ht="25" customHeight="1">
+    <row r="537" spans="1:13" ht="24.95" customHeight="1">
       <c r="A537" s="12"/>
       <c r="B537" s="12"/>
       <c r="C537" s="12"/>
@@ -28454,7 +28454,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="554" spans="1:13" ht="51">
+    <row r="554" spans="1:13" ht="51.75">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="1"/>
@@ -28475,7 +28475,7 @@
       </c>
       <c r="M554" s="5"/>
     </row>
-    <row r="555" spans="1:13">
+    <row r="555" spans="1:13" ht="26.25">
       <c r="A555" s="1"/>
       <c r="B555" s="1"/>
       <c r="C555" s="1"/>
@@ -28498,7 +28498,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="556" spans="1:13">
+    <row r="556" spans="1:13" ht="26.25">
       <c r="A556" s="1"/>
       <c r="B556" s="1"/>
       <c r="C556" s="1"/>
@@ -28521,7 +28521,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="557" spans="1:13" ht="26">
+    <row r="557" spans="1:13" ht="26.25">
       <c r="A557" s="1"/>
       <c r="B557" s="1"/>
       <c r="C557" s="1"/>
@@ -28658,7 +28658,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="564" spans="1:13" ht="15.5">
+    <row r="564" spans="1:13" ht="15.75">
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
@@ -28679,7 +28679,7 @@
       </c>
       <c r="M564" s="5"/>
     </row>
-    <row r="565" spans="1:13" ht="15.5">
+    <row r="565" spans="1:13" ht="15.75">
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
@@ -28700,7 +28700,7 @@
       </c>
       <c r="M565" s="5"/>
     </row>
-    <row r="566" spans="1:13" ht="15.5">
+    <row r="566" spans="1:13" ht="15.75">
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
@@ -28721,7 +28721,7 @@
       </c>
       <c r="M566" s="5"/>
     </row>
-    <row r="567" spans="1:13" ht="15.5">
+    <row r="567" spans="1:13" ht="15.75">
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
       <c r="C567" s="1"/>
@@ -28742,7 +28742,7 @@
       </c>
       <c r="M567" s="5"/>
     </row>
-    <row r="568" spans="1:13" ht="15.5">
+    <row r="568" spans="1:13" ht="15.75">
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
       <c r="C568" s="1"/>
@@ -28763,7 +28763,7 @@
       </c>
       <c r="M568" s="5"/>
     </row>
-    <row r="569" spans="1:13" ht="15.5">
+    <row r="569" spans="1:13" ht="15.75">
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
       <c r="C569" s="1"/>
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M569" s="5"/>
     </row>
-    <row r="570" spans="1:13" ht="15.5">
+    <row r="570" spans="1:13" ht="15.75">
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
       <c r="C570" s="1"/>
@@ -28805,7 +28805,7 @@
       </c>
       <c r="M570" s="5"/>
     </row>
-    <row r="571" spans="1:13" ht="15.5">
+    <row r="571" spans="1:13" ht="15.75">
       <c r="A571" s="1"/>
       <c r="B571" s="1"/>
       <c r="C571" s="1"/>
@@ -28886,7 +28886,7 @@
       <c r="L576" s="8"/>
       <c r="M576" s="3"/>
     </row>
-    <row r="579" spans="1:13" ht="15.5">
+    <row r="579" spans="1:13" ht="15.75">
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
@@ -28907,7 +28907,7 @@
       </c>
       <c r="M579" s="5"/>
     </row>
-    <row r="580" spans="1:13" ht="15.5">
+    <row r="580" spans="1:13" ht="15.75">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
@@ -28928,7 +28928,7 @@
       </c>
       <c r="M580" s="5"/>
     </row>
-    <row r="581" spans="1:13" ht="15.5">
+    <row r="581" spans="1:13" ht="15.75">
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
@@ -28949,7 +28949,7 @@
       </c>
       <c r="M581" s="5"/>
     </row>
-    <row r="584" spans="1:13" ht="15.5">
+    <row r="584" spans="1:13" ht="15.75">
       <c r="A584" s="1"/>
       <c r="B584" s="1"/>
       <c r="C584" s="1"/>
@@ -28970,7 +28970,7 @@
       </c>
       <c r="M584" s="5"/>
     </row>
-    <row r="585" spans="1:13" ht="15.5">
+    <row r="585" spans="1:13" ht="15.75">
       <c r="A585" s="1"/>
       <c r="B585" s="1"/>
       <c r="C585" s="1"/>
@@ -28991,7 +28991,7 @@
       </c>
       <c r="M585" s="5"/>
     </row>
-    <row r="586" spans="1:13" ht="15.5">
+    <row r="586" spans="1:13" ht="15.75">
       <c r="A586" s="1"/>
       <c r="B586" s="1"/>
       <c r="C586" s="1"/>
@@ -29081,7 +29081,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="592" spans="1:13" ht="15.5">
+    <row r="592" spans="1:13" ht="15.75">
       <c r="A592" s="1"/>
       <c r="B592" s="1"/>
       <c r="C592" s="1"/>
@@ -29102,7 +29102,7 @@
       </c>
       <c r="M592" s="5"/>
     </row>
-    <row r="593" spans="1:13" ht="15.5">
+    <row r="593" spans="1:13" ht="15.75">
       <c r="A593" s="1"/>
       <c r="B593" s="1"/>
       <c r="C593" s="1"/>
@@ -29123,7 +29123,7 @@
       </c>
       <c r="M593" s="5"/>
     </row>
-    <row r="594" spans="1:13" ht="15.5">
+    <row r="594" spans="1:13" ht="15.75">
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
       <c r="C594" s="1"/>
@@ -29265,24 +29265,6 @@
   </sheetData>
   <autoFilter ref="A1:N313" xr:uid="{82619C4B-D6B1-486E-87C6-D2252668E253}"/>
   <mergeCells count="27">
-    <mergeCell ref="J536:J537"/>
-    <mergeCell ref="K536:K537"/>
-    <mergeCell ref="L536:L537"/>
-    <mergeCell ref="J540:J541"/>
-    <mergeCell ref="K540:K541"/>
-    <mergeCell ref="L540:L541"/>
-    <mergeCell ref="J550:J551"/>
-    <mergeCell ref="K550:K551"/>
-    <mergeCell ref="L550:L551"/>
-    <mergeCell ref="J552:J553"/>
-    <mergeCell ref="K552:K553"/>
-    <mergeCell ref="L552:L553"/>
-    <mergeCell ref="J558:J560"/>
-    <mergeCell ref="K558:K560"/>
-    <mergeCell ref="L558:L560"/>
-    <mergeCell ref="J561:J563"/>
-    <mergeCell ref="K561:K563"/>
-    <mergeCell ref="L561:L563"/>
     <mergeCell ref="J548:J549"/>
     <mergeCell ref="K548:K549"/>
     <mergeCell ref="L548:L549"/>
@@ -29292,6 +29274,24 @@
     <mergeCell ref="K546:K547"/>
     <mergeCell ref="L546:L547"/>
     <mergeCell ref="J542:J543"/>
+    <mergeCell ref="J558:J560"/>
+    <mergeCell ref="K558:K560"/>
+    <mergeCell ref="L558:L560"/>
+    <mergeCell ref="J561:J563"/>
+    <mergeCell ref="K561:K563"/>
+    <mergeCell ref="L561:L563"/>
+    <mergeCell ref="J550:J551"/>
+    <mergeCell ref="K550:K551"/>
+    <mergeCell ref="L550:L551"/>
+    <mergeCell ref="J552:J553"/>
+    <mergeCell ref="K552:K553"/>
+    <mergeCell ref="L552:L553"/>
+    <mergeCell ref="J536:J537"/>
+    <mergeCell ref="K536:K537"/>
+    <mergeCell ref="L536:L537"/>
+    <mergeCell ref="J540:J541"/>
+    <mergeCell ref="K540:K541"/>
+    <mergeCell ref="L540:L541"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="L7" r:id="rId1" display="Abbreviation of the journal name. We use WoS abbreviations that can be found here: https://images.webofknowledge.com/images/help/WOS/A_abrvjt.html" xr:uid="{B4DADD6B-F846-45B3-933B-5F25CC9FEF24}"/>
@@ -29305,13 +29305,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14A586C8-08A0-4640-80FB-651A99A88EA6}">
   <dimension ref="A1:H587"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="32.81640625" customWidth="1"/>
-    <col min="3" max="3" width="20.54296875" customWidth="1"/>
-    <col min="4" max="4" width="36.453125" customWidth="1"/>
+    <col min="1" max="2" width="32.85546875" customWidth="1"/>
+    <col min="3" max="3" width="20.5703125" customWidth="1"/>
+    <col min="4" max="4" width="36.42578125" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="121.81640625" style="10" customWidth="1"/>
+    <col min="6" max="6" width="121.85546875" style="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -29358,7 +29358,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.5">
+    <row r="3" spans="1:7" ht="15.75">
       <c r="A3" s="1" t="s">
         <v>983</v>
       </c>
@@ -29419,7 +29419,7 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
     </row>
-    <row r="6" spans="1:7" ht="15.5">
+    <row r="6" spans="1:7" ht="15.75">
       <c r="A6" s="1" t="s">
         <v>983</v>
       </c>
@@ -29463,7 +29463,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.5">
+    <row r="8" spans="1:7" ht="15.75">
       <c r="A8" s="1" t="s">
         <v>983</v>
       </c>
@@ -29952,7 +29952,7 @@
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
     </row>
-    <row r="33" spans="1:8" ht="15" thickBot="1">
+    <row r="33" spans="1:8" ht="15.75" thickBot="1">
       <c r="A33" s="1" t="s">
         <v>983</v>
       </c>
@@ -29974,7 +29974,7 @@
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
     </row>
-    <row r="34" spans="1:8" ht="15" thickBot="1">
+    <row r="34" spans="1:8" ht="15.75" thickBot="1">
       <c r="A34" s="1" t="s">
         <v>983</v>
       </c>
@@ -29998,7 +29998,7 @@
       </c>
       <c r="H34" s="4"/>
     </row>
-    <row r="35" spans="1:8" ht="15" thickBot="1">
+    <row r="35" spans="1:8" ht="15.75" thickBot="1">
       <c r="A35" s="1" t="s">
         <v>983</v>
       </c>
@@ -30022,7 +30022,7 @@
       </c>
       <c r="H35" s="4"/>
     </row>
-    <row r="36" spans="1:8" ht="15" thickBot="1">
+    <row r="36" spans="1:8" ht="15.75" thickBot="1">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="34" t="s">
@@ -30042,7 +30042,7 @@
       </c>
       <c r="H36" s="4"/>
     </row>
-    <row r="37" spans="1:8" ht="15" thickBot="1">
+    <row r="37" spans="1:8" ht="15.75" thickBot="1">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="82" t="s">
@@ -30058,7 +30058,7 @@
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
     </row>
-    <row r="38" spans="1:8" ht="15" thickBot="1">
+    <row r="38" spans="1:8" ht="15.75" thickBot="1">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="82" t="s">
@@ -30074,7 +30074,7 @@
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
     </row>
-    <row r="39" spans="1:8" ht="15" thickBot="1">
+    <row r="39" spans="1:8" ht="15.75" thickBot="1">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="82" t="s">
@@ -30090,7 +30090,7 @@
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
     </row>
-    <row r="40" spans="1:8" ht="16" thickBot="1">
+    <row r="40" spans="1:8" ht="16.5" thickBot="1">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="82" t="s">
@@ -30534,7 +30534,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="15" thickBot="1">
+    <row r="60" spans="1:7" ht="15.75" thickBot="1">
       <c r="A60" s="60" t="s">
         <v>983</v>
       </c>
@@ -30557,7 +30557,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="15" thickBot="1">
+    <row r="61" spans="1:7" ht="15.75" thickBot="1">
       <c r="A61" s="60" t="s">
         <v>983</v>
       </c>
@@ -30669,7 +30669,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="16" thickBot="1">
+    <row r="66" spans="1:7" ht="16.5" thickBot="1">
       <c r="A66" s="60" t="s">
         <v>983</v>
       </c>
@@ -30692,7 +30692,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="16" thickBot="1">
+    <row r="67" spans="1:7" ht="16.5" thickBot="1">
       <c r="A67" s="60" t="s">
         <v>983</v>
       </c>
@@ -30805,7 +30805,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="15.5">
+    <row r="72" spans="1:7" ht="15.75">
       <c r="A72" s="60" t="s">
         <v>983</v>
       </c>
@@ -30828,7 +30828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="15.5">
+    <row r="73" spans="1:7" ht="15.75">
       <c r="A73" s="60" t="s">
         <v>983</v>
       </c>
@@ -30865,7 +30865,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="15.5">
+    <row r="75" spans="1:7" ht="15.75">
       <c r="A75" s="60" t="s">
         <v>983</v>
       </c>
@@ -31054,7 +31054,7 @@
       <c r="F83"/>
       <c r="G83" s="31"/>
     </row>
-    <row r="84" spans="1:7" ht="16">
+    <row r="84" spans="1:7" ht="16.5">
       <c r="A84" s="60" t="s">
         <v>983</v>
       </c>
@@ -31100,7 +31100,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="15.5">
+    <row r="86" spans="1:7" ht="15.75">
       <c r="A86" s="60" t="s">
         <v>983</v>
       </c>
@@ -31161,7 +31161,7 @@
       <c r="F88"/>
       <c r="G88" s="31"/>
     </row>
-    <row r="89" spans="1:7" ht="15.5">
+    <row r="89" spans="1:7" ht="15.75">
       <c r="A89" s="60" t="s">
         <v>983</v>
       </c>
@@ -31182,7 +31182,7 @@
       </c>
       <c r="G89" s="5"/>
     </row>
-    <row r="90" spans="1:7" ht="15.5">
+    <row r="90" spans="1:7" ht="15.75">
       <c r="A90" s="60" t="s">
         <v>983</v>
       </c>
@@ -31226,7 +31226,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="15.5">
+    <row r="92" spans="1:7" ht="15.75">
       <c r="A92" s="60" t="s">
         <v>983</v>
       </c>
@@ -31332,7 +31332,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="15" thickBot="1">
+    <row r="98" spans="1:7" ht="15.75" thickBot="1">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -31349,7 +31349,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="15" thickBot="1">
+    <row r="99" spans="1:7" ht="15.75" thickBot="1">
       <c r="A99" s="60" t="s">
         <v>983</v>
       </c>
@@ -31368,7 +31368,7 @@
       <c r="F99"/>
       <c r="G99" s="31"/>
     </row>
-    <row r="100" spans="1:7" ht="16" thickBot="1">
+    <row r="100" spans="1:7" ht="16.5" thickBot="1">
       <c r="A100" s="60" t="s">
         <v>983</v>
       </c>
@@ -31391,7 +31391,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="15" thickBot="1">
+    <row r="101" spans="1:7" ht="15.75" thickBot="1">
       <c r="A101" s="60" t="s">
         <v>983</v>
       </c>
@@ -31411,7 +31411,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="15" thickBot="1">
+    <row r="102" spans="1:7" ht="15.75" thickBot="1">
       <c r="A102" s="60" t="s">
         <v>983</v>
       </c>
@@ -31431,7 +31431,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="15" thickBot="1">
+    <row r="103" spans="1:7" ht="15.75" thickBot="1">
       <c r="A103" s="60" t="s">
         <v>983</v>
       </c>
@@ -31451,7 +31451,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="16" thickBot="1">
+    <row r="104" spans="1:7" ht="16.5" thickBot="1">
       <c r="A104" s="60" t="s">
         <v>983</v>
       </c>
@@ -31472,7 +31472,7 @@
       </c>
       <c r="G104" s="5"/>
     </row>
-    <row r="105" spans="1:7" ht="15" thickBot="1">
+    <row r="105" spans="1:7" ht="15.75" thickBot="1">
       <c r="A105" s="60" t="s">
         <v>983</v>
       </c>
@@ -31492,7 +31492,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="15" thickBot="1">
+    <row r="106" spans="1:7" ht="15.75" thickBot="1">
       <c r="A106" s="60" t="s">
         <v>983</v>
       </c>
@@ -31510,7 +31510,7 @@
       </c>
       <c r="F106"/>
     </row>
-    <row r="107" spans="1:7" ht="15" thickBot="1">
+    <row r="107" spans="1:7" ht="15.75" thickBot="1">
       <c r="A107" s="60" t="s">
         <v>983</v>
       </c>
@@ -31533,7 +31533,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="15" thickBot="1">
+    <row r="108" spans="1:7" ht="15.75" thickBot="1">
       <c r="A108" s="60" t="s">
         <v>983</v>
       </c>
@@ -31556,7 +31556,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="15" thickBot="1">
+    <row r="109" spans="1:7" ht="15.75" thickBot="1">
       <c r="A109" s="60" t="s">
         <v>983</v>
       </c>
@@ -31579,7 +31579,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="16" thickBot="1">
+    <row r="110" spans="1:7" ht="16.5" thickBot="1">
       <c r="A110" s="60" t="s">
         <v>983</v>
       </c>
@@ -31602,7 +31602,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="16" thickBot="1">
+    <row r="111" spans="1:7" ht="16.5" thickBot="1">
       <c r="A111" s="60" t="s">
         <v>983</v>
       </c>
@@ -31625,7 +31625,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="15" thickBot="1">
+    <row r="112" spans="1:7" ht="15.75" thickBot="1">
       <c r="A112" s="60" t="s">
         <v>983</v>
       </c>
@@ -31687,7 +31687,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="15.5">
+    <row r="115" spans="1:7" ht="15.75">
       <c r="A115" s="60" t="s">
         <v>983</v>
       </c>
@@ -31708,7 +31708,7 @@
       </c>
       <c r="G115" s="5"/>
     </row>
-    <row r="116" spans="1:7" ht="15.5">
+    <row r="116" spans="1:7" ht="15.75">
       <c r="A116" s="60" t="s">
         <v>983</v>
       </c>
@@ -31729,7 +31729,7 @@
       </c>
       <c r="G116" s="5"/>
     </row>
-    <row r="117" spans="1:7" ht="15.5">
+    <row r="117" spans="1:7" ht="15.75">
       <c r="A117" s="60" t="s">
         <v>983</v>
       </c>
@@ -31752,7 +31752,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="15.5">
+    <row r="118" spans="1:7" ht="15.75">
       <c r="A118" s="60" t="s">
         <v>983</v>
       </c>
@@ -31792,7 +31792,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="15.5">
+    <row r="120" spans="1:7" ht="15.75">
       <c r="A120" s="60" t="s">
         <v>983</v>
       </c>
@@ -31815,7 +31815,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="15.5">
+    <row r="121" spans="1:7" ht="15.75">
       <c r="A121" s="60" t="s">
         <v>983</v>
       </c>
@@ -31879,7 +31879,7 @@
       </c>
       <c r="F123"/>
     </row>
-    <row r="124" spans="1:7" ht="15.5">
+    <row r="124" spans="1:7" ht="15.75">
       <c r="A124" s="60" t="s">
         <v>983</v>
       </c>
@@ -31989,7 +31989,7 @@
       </c>
       <c r="F128"/>
     </row>
-    <row r="129" spans="1:7" ht="16">
+    <row r="129" spans="1:7" ht="16.5">
       <c r="A129" s="60" t="s">
         <v>983</v>
       </c>
@@ -32058,7 +32058,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="15" thickBot="1">
+    <row r="132" spans="1:7" ht="15.75" thickBot="1">
       <c r="A132" s="60" t="s">
         <v>983</v>
       </c>
@@ -32081,7 +32081,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="15" thickBot="1">
+    <row r="133" spans="1:7" ht="15.75" thickBot="1">
       <c r="A133" s="60" t="s">
         <v>983</v>
       </c>
@@ -32097,7 +32097,7 @@
       <c r="E133" s="3"/>
       <c r="F133"/>
     </row>
-    <row r="134" spans="1:7" ht="15" thickBot="1">
+    <row r="134" spans="1:7" ht="15.75" thickBot="1">
       <c r="A134" s="60" t="s">
         <v>983</v>
       </c>
@@ -32120,7 +32120,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="15" thickBot="1">
+    <row r="135" spans="1:7" ht="15.75" thickBot="1">
       <c r="A135" s="60" t="s">
         <v>983</v>
       </c>
@@ -32143,7 +32143,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="16.5" thickBot="1">
+    <row r="136" spans="1:7" ht="17.25" thickBot="1">
       <c r="A136" s="60" t="s">
         <v>983</v>
       </c>
@@ -32166,7 +32166,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="16.5" thickBot="1">
+    <row r="137" spans="1:7" ht="17.25" thickBot="1">
       <c r="A137" s="60" t="s">
         <v>983</v>
       </c>
@@ -32189,7 +32189,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="16.5" thickBot="1">
+    <row r="138" spans="1:7" ht="17.25" thickBot="1">
       <c r="A138" s="60" t="s">
         <v>983</v>
       </c>
@@ -32212,7 +32212,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="16.5" thickBot="1">
+    <row r="139" spans="1:7" ht="17.25" thickBot="1">
       <c r="A139" s="60" t="s">
         <v>983</v>
       </c>
@@ -32235,7 +32235,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="16.5" thickBot="1">
+    <row r="140" spans="1:7" ht="17.25" thickBot="1">
       <c r="A140" s="60" t="s">
         <v>983</v>
       </c>
@@ -32258,7 +32258,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="141" spans="1:7" ht="16.5" thickBot="1">
+    <row r="141" spans="1:7" ht="17.25" thickBot="1">
       <c r="A141" s="60" t="s">
         <v>983</v>
       </c>
@@ -32281,7 +32281,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="142" spans="1:7" ht="15" thickBot="1">
+    <row r="142" spans="1:7" ht="15.75" thickBot="1">
       <c r="A142" s="60" t="s">
         <v>983</v>
       </c>
@@ -32301,7 +32301,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="16.5" thickBot="1">
+    <row r="143" spans="1:7" ht="17.25" thickBot="1">
       <c r="A143" s="60" t="s">
         <v>983</v>
       </c>
@@ -32324,7 +32324,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="144" spans="1:7" ht="16.5" thickBot="1">
+    <row r="144" spans="1:7" ht="17.25" thickBot="1">
       <c r="A144" s="60" t="s">
         <v>983</v>
       </c>
@@ -32347,7 +32347,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="145" spans="1:7" ht="16.5" thickBot="1">
+    <row r="145" spans="1:7" ht="17.25" thickBot="1">
       <c r="A145" s="60" t="s">
         <v>983</v>
       </c>
@@ -32370,7 +32370,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="146" spans="1:7" ht="16.5" thickBot="1">
+    <row r="146" spans="1:7" ht="17.25" thickBot="1">
       <c r="A146" s="60" t="s">
         <v>983</v>
       </c>
@@ -32393,7 +32393,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="147" spans="1:7" ht="15" thickBot="1">
+    <row r="147" spans="1:7" ht="15.75" thickBot="1">
       <c r="A147" s="60" t="s">
         <v>983</v>
       </c>
@@ -32414,7 +32414,7 @@
       </c>
       <c r="G147" s="41"/>
     </row>
-    <row r="148" spans="1:7" ht="15" thickBot="1">
+    <row r="148" spans="1:7" ht="15.75" thickBot="1">
       <c r="A148" s="60" t="s">
         <v>983</v>
       </c>
@@ -32431,7 +32431,7 @@
       <c r="F148"/>
       <c r="G148" s="41"/>
     </row>
-    <row r="149" spans="1:7" ht="15" thickBot="1">
+    <row r="149" spans="1:7" ht="15.75" thickBot="1">
       <c r="A149" s="60" t="s">
         <v>983</v>
       </c>
@@ -32454,7 +32454,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="150" spans="1:7" ht="15" thickBot="1">
+    <row r="150" spans="1:7" ht="15.75" thickBot="1">
       <c r="A150" s="60" t="s">
         <v>983</v>
       </c>
@@ -32474,7 +32474,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="151" spans="1:7" ht="16.5" thickBot="1">
+    <row r="151" spans="1:7" ht="17.25" thickBot="1">
       <c r="A151" s="60" t="s">
         <v>983</v>
       </c>
@@ -32497,7 +32497,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="152" spans="1:7" ht="16.5" thickBot="1">
+    <row r="152" spans="1:7" ht="17.25" thickBot="1">
       <c r="A152" s="60" t="s">
         <v>983</v>
       </c>
@@ -32520,7 +32520,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="153" spans="1:7" ht="16.5" thickBot="1">
+    <row r="153" spans="1:7" ht="17.25" thickBot="1">
       <c r="A153" s="60" t="s">
         <v>983</v>
       </c>
@@ -32543,7 +32543,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="154" spans="1:7" ht="16.5" thickBot="1">
+    <row r="154" spans="1:7" ht="17.25" thickBot="1">
       <c r="A154" s="60" t="s">
         <v>983</v>
       </c>
@@ -32566,7 +32566,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="155" spans="1:7" ht="16.5" thickBot="1">
+    <row r="155" spans="1:7" ht="17.25" thickBot="1">
       <c r="A155" s="60" t="s">
         <v>983</v>
       </c>
@@ -32589,7 +32589,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="156" spans="1:7" ht="16.5" thickBot="1">
+    <row r="156" spans="1:7" ht="17.25" thickBot="1">
       <c r="A156" s="60" t="s">
         <v>983</v>
       </c>
@@ -32612,7 +32612,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="157" spans="1:7" ht="15" thickBot="1">
+    <row r="157" spans="1:7" ht="15.75" thickBot="1">
       <c r="A157" s="60" t="s">
         <v>983</v>
       </c>
@@ -32635,7 +32635,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="158" spans="1:7" ht="16.5" thickBot="1">
+    <row r="158" spans="1:7" ht="17.25" thickBot="1">
       <c r="A158" s="60" t="s">
         <v>983</v>
       </c>
@@ -32658,7 +32658,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="159" spans="1:7" ht="16.5" thickBot="1">
+    <row r="159" spans="1:7" ht="17.25" thickBot="1">
       <c r="A159" s="60" t="s">
         <v>983</v>
       </c>
@@ -32681,7 +32681,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="160" spans="1:7" ht="16.5" thickBot="1">
+    <row r="160" spans="1:7" ht="17.25" thickBot="1">
       <c r="A160" s="60" t="s">
         <v>983</v>
       </c>
@@ -32704,7 +32704,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="161" spans="1:7" ht="16.5" thickBot="1">
+    <row r="161" spans="1:7" ht="17.25" thickBot="1">
       <c r="A161" s="60" t="s">
         <v>983</v>
       </c>
@@ -32727,7 +32727,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="162" spans="1:7" ht="15" thickBot="1">
+    <row r="162" spans="1:7" ht="15.75" thickBot="1">
       <c r="A162" s="60" t="s">
         <v>983</v>
       </c>
@@ -32748,7 +32748,7 @@
       </c>
       <c r="G162" s="41"/>
     </row>
-    <row r="163" spans="1:7" ht="15" thickBot="1">
+    <row r="163" spans="1:7" ht="15.75" thickBot="1">
       <c r="A163" s="60" t="s">
         <v>983</v>
       </c>
@@ -32769,7 +32769,7 @@
       </c>
       <c r="G163" s="41"/>
     </row>
-    <row r="164" spans="1:7" ht="15" thickBot="1">
+    <row r="164" spans="1:7" ht="15.75" thickBot="1">
       <c r="A164" s="60" t="s">
         <v>983</v>
       </c>
@@ -32792,7 +32792,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="165" spans="1:7" ht="15" thickBot="1">
+    <row r="165" spans="1:7" ht="15.75" thickBot="1">
       <c r="A165" s="60" t="s">
         <v>983</v>
       </c>
@@ -32815,7 +32815,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="166" spans="1:7" ht="15" thickBot="1">
+    <row r="166" spans="1:7" ht="15.75" thickBot="1">
       <c r="A166" s="60" t="s">
         <v>983</v>
       </c>
@@ -32835,7 +32835,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="167" spans="1:7" ht="15" thickBot="1">
+    <row r="167" spans="1:7" ht="15.75" thickBot="1">
       <c r="A167" s="60" t="s">
         <v>983</v>
       </c>
@@ -32858,7 +32858,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="168" spans="1:7" ht="15" thickBot="1">
+    <row r="168" spans="1:7" ht="15.75" thickBot="1">
       <c r="A168" s="60" t="s">
         <v>983</v>
       </c>
@@ -32881,7 +32881,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="169" spans="1:7" ht="15" thickBot="1">
+    <row r="169" spans="1:7" ht="15.75" thickBot="1">
       <c r="A169" s="1"/>
       <c r="B169" s="126" t="s">
         <v>983</v>
@@ -32897,7 +32897,7 @@
       </c>
       <c r="F169"/>
     </row>
-    <row r="170" spans="1:7" ht="15" thickBot="1">
+    <row r="170" spans="1:7" ht="15.75" thickBot="1">
       <c r="A170" s="1"/>
       <c r="B170" s="126" t="s">
         <v>983</v>
@@ -32918,7 +32918,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="171" spans="1:7" ht="16.5" thickBot="1">
+    <row r="171" spans="1:7" ht="17.25" thickBot="1">
       <c r="A171" s="1"/>
       <c r="B171" s="1" t="s">
         <v>1463</v>
@@ -32939,7 +32939,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="172" spans="1:7" ht="15" thickBot="1">
+    <row r="172" spans="1:7" ht="15.75" thickBot="1">
       <c r="A172" s="1"/>
       <c r="B172" s="126" t="s">
         <v>983</v>
@@ -32953,7 +32953,7 @@
       <c r="E172" s="17"/>
       <c r="F172"/>
     </row>
-    <row r="173" spans="1:7" ht="15" thickBot="1">
+    <row r="173" spans="1:7" ht="15.75" thickBot="1">
       <c r="A173" s="1"/>
       <c r="B173" s="126" t="s">
         <v>983</v>
@@ -32974,7 +32974,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="174" spans="1:7" ht="16.5" thickBot="1">
+    <row r="174" spans="1:7" ht="17.25" thickBot="1">
       <c r="A174" s="1"/>
       <c r="B174" s="1" t="s">
         <v>1463</v>
@@ -32995,7 +32995,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="175" spans="1:7" ht="15" thickBot="1">
+    <row r="175" spans="1:7" ht="15.75" thickBot="1">
       <c r="A175" s="1"/>
       <c r="B175" s="126" t="s">
         <v>983</v>
@@ -33009,7 +33009,7 @@
       <c r="E175" s="17"/>
       <c r="F175"/>
     </row>
-    <row r="176" spans="1:7" ht="15" thickBot="1">
+    <row r="176" spans="1:7" ht="15.75" thickBot="1">
       <c r="A176" s="1"/>
       <c r="B176" s="126" t="s">
         <v>983</v>
@@ -33030,7 +33030,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="177" spans="1:7" ht="15" thickBot="1">
+    <row r="177" spans="1:7" ht="15.75" thickBot="1">
       <c r="A177" s="1"/>
       <c r="B177" s="1" t="s">
         <v>1463</v>
@@ -33049,7 +33049,7 @@
       </c>
       <c r="G177" s="69"/>
     </row>
-    <row r="178" spans="1:7" ht="15" thickBot="1">
+    <row r="178" spans="1:7" ht="15.75" thickBot="1">
       <c r="A178" s="1"/>
       <c r="B178" s="126" t="s">
         <v>983</v>
@@ -33068,7 +33068,7 @@
       </c>
       <c r="G178" s="43"/>
     </row>
-    <row r="179" spans="1:7" ht="15" thickBot="1">
+    <row r="179" spans="1:7" ht="15.75" thickBot="1">
       <c r="A179" s="1"/>
       <c r="B179" s="126" t="s">
         <v>983</v>
@@ -33087,7 +33087,7 @@
       </c>
       <c r="G179" s="44"/>
     </row>
-    <row r="180" spans="1:7" ht="15" thickBot="1">
+    <row r="180" spans="1:7" ht="15.75" thickBot="1">
       <c r="A180" s="1"/>
       <c r="B180" s="1" t="s">
         <v>1463</v>
@@ -33106,7 +33106,7 @@
       </c>
       <c r="G180" s="44"/>
     </row>
-    <row r="181" spans="1:7" ht="15" thickBot="1">
+    <row r="181" spans="1:7" ht="15.75" thickBot="1">
       <c r="A181" s="1"/>
       <c r="B181" s="126" t="s">
         <v>983</v>
@@ -33124,7 +33124,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="182" spans="1:7" ht="15" thickBot="1">
+    <row r="182" spans="1:7" ht="15.75" thickBot="1">
       <c r="A182" s="1"/>
       <c r="B182" s="126" t="s">
         <v>983</v>
@@ -33142,7 +33142,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="183" spans="1:7" ht="15" thickBot="1">
+    <row r="183" spans="1:7" ht="15.75" thickBot="1">
       <c r="A183" s="1"/>
       <c r="B183" s="126" t="s">
         <v>983</v>
@@ -33163,7 +33163,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="184" spans="1:7" ht="15" thickBot="1">
+    <row r="184" spans="1:7" ht="15.75" thickBot="1">
       <c r="A184" s="120"/>
       <c r="B184" s="126" t="s">
         <v>983</v>
@@ -33181,7 +33181,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="185" spans="1:7" ht="15" thickBot="1">
+    <row r="185" spans="1:7" ht="15.75" thickBot="1">
       <c r="A185" s="1"/>
       <c r="B185" s="126" t="s">
         <v>983</v>
@@ -33199,7 +33199,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="186" spans="1:7" ht="15" thickBot="1">
+    <row r="186" spans="1:7" ht="15.75" thickBot="1">
       <c r="A186" s="1"/>
       <c r="B186" s="126" t="s">
         <v>983</v>
@@ -33215,7 +33215,7 @@
       </c>
       <c r="F186"/>
     </row>
-    <row r="187" spans="1:7" ht="15" thickBot="1">
+    <row r="187" spans="1:7" ht="15.75" thickBot="1">
       <c r="A187" s="1"/>
       <c r="B187" s="126" t="s">
         <v>983</v>
@@ -33236,7 +33236,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="188" spans="1:7" ht="15" thickBot="1">
+    <row r="188" spans="1:7" ht="15.75" thickBot="1">
       <c r="A188" s="1"/>
       <c r="B188" s="1" t="s">
         <v>1463</v>
@@ -33255,7 +33255,7 @@
       </c>
       <c r="G188" s="84"/>
     </row>
-    <row r="189" spans="1:7" ht="15" thickBot="1">
+    <row r="189" spans="1:7" ht="15.75" thickBot="1">
       <c r="A189" s="1"/>
       <c r="B189" s="1" t="s">
         <v>1463</v>
@@ -33276,7 +33276,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="190" spans="1:7" ht="15" thickBot="1">
+    <row r="190" spans="1:7" ht="15.75" thickBot="1">
       <c r="A190" s="1"/>
       <c r="B190" s="126" t="s">
         <v>983</v>
@@ -33297,7 +33297,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="191" spans="1:7" ht="15" thickBot="1">
+    <row r="191" spans="1:7" ht="15.75" thickBot="1">
       <c r="A191" s="1"/>
       <c r="B191" s="1" t="s">
         <v>1463</v>
@@ -33318,7 +33318,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="192" spans="1:7" ht="15" thickBot="1">
+    <row r="192" spans="1:7" ht="15.75" thickBot="1">
       <c r="A192" s="1"/>
       <c r="B192" s="126" t="s">
         <v>983</v>
@@ -33336,7 +33336,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="193" spans="1:7" ht="15" thickBot="1">
+    <row r="193" spans="1:7" ht="15.75" thickBot="1">
       <c r="A193" s="1"/>
       <c r="B193" s="126" t="s">
         <v>983</v>
@@ -33357,7 +33357,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="194" spans="1:7" ht="15" thickBot="1">
+    <row r="194" spans="1:7" ht="15.75" thickBot="1">
       <c r="A194" s="1"/>
       <c r="B194" s="126" t="s">
         <v>983</v>
@@ -33378,7 +33378,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="195" spans="1:7" ht="15" thickBot="1">
+    <row r="195" spans="1:7" ht="15.75" thickBot="1">
       <c r="A195" s="120"/>
       <c r="B195" s="126" t="s">
         <v>983</v>
@@ -33399,7 +33399,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="196" spans="1:7" ht="15" thickBot="1">
+    <row r="196" spans="1:7" ht="15.75" thickBot="1">
       <c r="A196" s="1"/>
       <c r="B196" s="126" t="s">
         <v>983</v>
@@ -33420,7 +33420,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="197" spans="1:7" ht="15" thickBot="1">
+    <row r="197" spans="1:7" ht="15.75" thickBot="1">
       <c r="A197" s="1"/>
       <c r="B197" s="126" t="s">
         <v>983</v>
@@ -33436,7 +33436,7 @@
       </c>
       <c r="G197" s="41"/>
     </row>
-    <row r="198" spans="1:7" ht="15" thickBot="1">
+    <row r="198" spans="1:7" ht="15.75" thickBot="1">
       <c r="A198" s="1"/>
       <c r="B198" s="126" t="s">
         <v>983</v>
@@ -33457,7 +33457,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="199" spans="1:7" ht="15" thickBot="1">
+    <row r="199" spans="1:7" ht="15.75" thickBot="1">
       <c r="A199" s="1"/>
       <c r="B199" s="126" t="s">
         <v>983</v>
@@ -33478,7 +33478,7 @@
         <v>1457</v>
       </c>
     </row>
-    <row r="200" spans="1:7" ht="15" thickBot="1">
+    <row r="200" spans="1:7" ht="15.75" thickBot="1">
       <c r="A200" s="1"/>
       <c r="B200" s="126" t="s">
         <v>983</v>
@@ -33495,7 +33495,7 @@
       <c r="F200"/>
       <c r="G200" s="29"/>
     </row>
-    <row r="201" spans="1:7" ht="15" thickBot="1">
+    <row r="201" spans="1:7" ht="15.75" thickBot="1">
       <c r="A201" s="1"/>
       <c r="B201" s="126" t="s">
         <v>983</v>
@@ -33516,7 +33516,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="202" spans="1:7" ht="15" thickBot="1">
+    <row r="202" spans="1:7" ht="15.75" thickBot="1">
       <c r="A202" s="1"/>
       <c r="B202" s="126" t="s">
         <v>983</v>
@@ -33537,7 +33537,7 @@
         <v>1457</v>
       </c>
     </row>
-    <row r="203" spans="1:7" ht="15" thickBot="1">
+    <row r="203" spans="1:7" ht="15.75" thickBot="1">
       <c r="A203" s="1"/>
       <c r="B203" s="126" t="s">
         <v>983</v>
@@ -33553,7 +33553,7 @@
       </c>
       <c r="F203"/>
     </row>
-    <row r="204" spans="1:7" ht="15" thickBot="1">
+    <row r="204" spans="1:7" ht="15.75" thickBot="1">
       <c r="A204" s="1"/>
       <c r="B204" s="126" t="s">
         <v>983</v>
@@ -33571,7 +33571,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="205" spans="1:7" ht="15" thickBot="1">
+    <row r="205" spans="1:7" ht="15.75" thickBot="1">
       <c r="A205" s="1"/>
       <c r="B205" s="126" t="s">
         <v>983</v>
@@ -33587,7 +33587,7 @@
       </c>
       <c r="F205"/>
     </row>
-    <row r="206" spans="1:7" ht="15" thickBot="1">
+    <row r="206" spans="1:7" ht="15.75" thickBot="1">
       <c r="A206" s="1"/>
       <c r="B206" s="126" t="s">
         <v>983</v>
@@ -33608,7 +33608,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="207" spans="1:7" ht="15" thickBot="1">
+    <row r="207" spans="1:7" ht="15.75" thickBot="1">
       <c r="A207" s="1"/>
       <c r="B207" s="126" t="s">
         <v>983</v>
@@ -33626,7 +33626,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="208" spans="1:7" ht="15" thickBot="1">
+    <row r="208" spans="1:7" ht="15.75" thickBot="1">
       <c r="A208" s="1"/>
       <c r="B208" s="126" t="s">
         <v>983</v>
@@ -33647,7 +33647,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="209" spans="1:7" ht="15" thickBot="1">
+    <row r="209" spans="1:7" ht="15.75" thickBot="1">
       <c r="A209" s="1"/>
       <c r="B209" s="126" t="s">
         <v>983</v>
@@ -33668,7 +33668,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="210" spans="1:7" ht="15" thickBot="1">
+    <row r="210" spans="1:7" ht="15.75" thickBot="1">
       <c r="A210" s="1"/>
       <c r="B210" s="126" t="s">
         <v>983</v>
@@ -33684,7 +33684,7 @@
       </c>
       <c r="F210"/>
     </row>
-    <row r="211" spans="1:7" ht="15" thickBot="1">
+    <row r="211" spans="1:7" ht="15.75" thickBot="1">
       <c r="A211" s="1"/>
       <c r="B211" s="126" t="s">
         <v>983</v>
@@ -33702,7 +33702,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="212" spans="1:7" ht="15" thickBot="1">
+    <row r="212" spans="1:7" ht="15.75" thickBot="1">
       <c r="A212" s="1"/>
       <c r="B212" s="126" t="s">
         <v>983</v>
@@ -33718,7 +33718,7 @@
       </c>
       <c r="F212"/>
     </row>
-    <row r="213" spans="1:7" ht="15" thickBot="1">
+    <row r="213" spans="1:7" ht="15.75" thickBot="1">
       <c r="A213" s="1"/>
       <c r="B213" s="126" t="s">
         <v>983</v>
@@ -33739,7 +33739,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="214" spans="1:7" ht="15" thickBot="1">
+    <row r="214" spans="1:7" ht="15.75" thickBot="1">
       <c r="A214" s="1"/>
       <c r="B214" s="126" t="s">
         <v>983</v>
@@ -33757,7 +33757,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="215" spans="1:7" ht="15" thickBot="1">
+    <row r="215" spans="1:7" ht="15.75" thickBot="1">
       <c r="A215" s="1"/>
       <c r="B215" s="126" t="s">
         <v>983</v>
@@ -33778,7 +33778,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="216" spans="1:7" ht="15" thickBot="1">
+    <row r="216" spans="1:7" ht="15.75" thickBot="1">
       <c r="A216" s="1"/>
       <c r="B216" s="126" t="s">
         <v>983</v>
@@ -33796,7 +33796,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="217" spans="1:7" ht="15" thickBot="1">
+    <row r="217" spans="1:7" ht="15.75" thickBot="1">
       <c r="A217" s="1"/>
       <c r="B217" s="126" t="s">
         <v>983</v>
@@ -33810,7 +33810,7 @@
       <c r="E217" s="17"/>
       <c r="F217"/>
     </row>
-    <row r="218" spans="1:7" ht="15" thickBot="1">
+    <row r="218" spans="1:7" ht="15.75" thickBot="1">
       <c r="A218" s="1"/>
       <c r="B218" s="126" t="s">
         <v>983</v>
@@ -33828,7 +33828,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="219" spans="1:7" ht="15" thickBot="1">
+    <row r="219" spans="1:7" ht="15.75" thickBot="1">
       <c r="A219" s="1"/>
       <c r="B219" s="126" t="s">
         <v>983</v>
@@ -33842,7 +33842,7 @@
       <c r="E219" s="17"/>
       <c r="F219"/>
     </row>
-    <row r="220" spans="1:7" ht="15" thickBot="1">
+    <row r="220" spans="1:7" ht="15.75" thickBot="1">
       <c r="A220" s="1"/>
       <c r="B220" s="126" t="s">
         <v>983</v>
@@ -33860,7 +33860,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="221" spans="1:7" ht="15" thickBot="1">
+    <row r="221" spans="1:7" ht="15.75" thickBot="1">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="82" t="s">
@@ -33874,7 +33874,7 @@
       </c>
       <c r="F221"/>
     </row>
-    <row r="222" spans="1:7" ht="15" thickBot="1">
+    <row r="222" spans="1:7" ht="15.75" thickBot="1">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="82" t="s">
@@ -33890,7 +33890,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="223" spans="1:7" ht="15" thickBot="1">
+    <row r="223" spans="1:7" ht="15.75" thickBot="1">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="82" t="s">
@@ -33909,7 +33909,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="224" spans="1:7" ht="15" thickBot="1">
+    <row r="224" spans="1:7" ht="15.75" thickBot="1">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="82" t="s">
@@ -33925,7 +33925,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="225" spans="1:7" ht="15" thickBot="1">
+    <row r="225" spans="1:7" ht="15.75" thickBot="1">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="82" t="s">
@@ -33941,7 +33941,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="226" spans="1:7" ht="15" thickBot="1">
+    <row r="226" spans="1:7" ht="15.75" thickBot="1">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="82" t="s">
@@ -33955,7 +33955,7 @@
       </c>
       <c r="F226"/>
     </row>
-    <row r="227" spans="1:7" ht="15" thickBot="1">
+    <row r="227" spans="1:7" ht="15.75" thickBot="1">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="82" t="s">
@@ -33971,7 +33971,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="228" spans="1:7" ht="15" thickBot="1">
+    <row r="228" spans="1:7" ht="15.75" thickBot="1">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="82" t="s">
@@ -33990,7 +33990,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="229" spans="1:7" ht="15" thickBot="1">
+    <row r="229" spans="1:7" ht="15.75" thickBot="1">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="82" t="s">
@@ -34102,7 +34102,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="236" spans="1:7" ht="15" thickBot="1">
+    <row r="236" spans="1:7" ht="15.75" thickBot="1">
       <c r="A236" s="1"/>
       <c r="B236" s="137" t="s">
         <v>1012</v>
@@ -34118,7 +34118,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="237" spans="1:7" ht="15" thickBot="1">
+    <row r="237" spans="1:7" ht="15.75" thickBot="1">
       <c r="A237" s="1"/>
       <c r="B237" s="137" t="s">
         <v>1012</v>
@@ -34132,7 +34132,7 @@
       <c r="E237" s="19"/>
       <c r="F237"/>
     </row>
-    <row r="238" spans="1:7" ht="15" thickBot="1">
+    <row r="238" spans="1:7" ht="15.75" thickBot="1">
       <c r="A238" s="1"/>
       <c r="B238" s="137" t="s">
         <v>1012</v>
@@ -34146,7 +34146,7 @@
       <c r="E238" s="19"/>
       <c r="F238"/>
     </row>
-    <row r="239" spans="1:7" ht="15" thickBot="1">
+    <row r="239" spans="1:7" ht="15.75" thickBot="1">
       <c r="A239" s="1"/>
       <c r="B239" s="137" t="s">
         <v>1012</v>
@@ -34160,7 +34160,7 @@
       <c r="E239" s="19"/>
       <c r="F239"/>
     </row>
-    <row r="240" spans="1:7" ht="15" thickBot="1">
+    <row r="240" spans="1:7" ht="15.75" thickBot="1">
       <c r="A240" s="1"/>
       <c r="B240" s="137" t="s">
         <v>1012</v>
@@ -34174,7 +34174,7 @@
       <c r="E240" s="19"/>
       <c r="F240"/>
     </row>
-    <row r="241" spans="1:8" ht="15" thickBot="1">
+    <row r="241" spans="1:8" ht="15.75" thickBot="1">
       <c r="A241" s="1"/>
       <c r="B241" s="137" t="s">
         <v>1012</v>
@@ -34188,7 +34188,7 @@
       <c r="E241" s="19"/>
       <c r="F241"/>
     </row>
-    <row r="242" spans="1:8" ht="15" thickBot="1">
+    <row r="242" spans="1:8" ht="15.75" thickBot="1">
       <c r="A242" s="1"/>
       <c r="B242" s="137" t="s">
         <v>1012</v>
@@ -34202,7 +34202,7 @@
       <c r="E242" s="19"/>
       <c r="F242"/>
     </row>
-    <row r="243" spans="1:8" ht="15" thickBot="1">
+    <row r="243" spans="1:8" ht="15.75" thickBot="1">
       <c r="A243" s="1"/>
       <c r="B243" s="137" t="s">
         <v>1012</v>
@@ -34216,7 +34216,7 @@
       <c r="E243" s="19"/>
       <c r="F243"/>
     </row>
-    <row r="244" spans="1:8" ht="15" thickBot="1">
+    <row r="244" spans="1:8" ht="15.75" thickBot="1">
       <c r="A244" s="1"/>
       <c r="B244" s="137" t="s">
         <v>1012</v>
@@ -34230,7 +34230,7 @@
       <c r="E244" s="19"/>
       <c r="F244"/>
     </row>
-    <row r="245" spans="1:8" ht="15" thickBot="1">
+    <row r="245" spans="1:8" ht="15.75" thickBot="1">
       <c r="A245" s="1"/>
       <c r="B245" s="137" t="s">
         <v>1012</v>
@@ -34244,7 +34244,7 @@
       <c r="E245" s="19"/>
       <c r="F245"/>
     </row>
-    <row r="246" spans="1:8" ht="15" thickBot="1">
+    <row r="246" spans="1:8" ht="15.75" thickBot="1">
       <c r="A246" s="1"/>
       <c r="B246" s="137" t="s">
         <v>1012</v>
@@ -34258,7 +34258,7 @@
       <c r="E246" s="19"/>
       <c r="F246"/>
     </row>
-    <row r="247" spans="1:8" ht="15" thickBot="1">
+    <row r="247" spans="1:8" ht="15.75" thickBot="1">
       <c r="A247" s="1" t="s">
         <v>1447</v>
       </c>
@@ -34278,7 +34278,7 @@
         <v>1316</v>
       </c>
     </row>
-    <row r="248" spans="1:8" ht="15" thickBot="1">
+    <row r="248" spans="1:8" ht="15.75" thickBot="1">
       <c r="A248" s="1" t="s">
         <v>1447</v>
       </c>
@@ -34352,7 +34352,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="252" spans="1:8" ht="15" thickBot="1">
+    <row r="252" spans="1:8" ht="15.75" thickBot="1">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="92" t="s">
@@ -34374,7 +34374,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="253" spans="1:8" ht="15" thickBot="1">
+    <row r="253" spans="1:8" ht="15.75" thickBot="1">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="92" t="s">
@@ -34447,7 +34447,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="257" spans="1:7" ht="15" thickBot="1">
+    <row r="257" spans="1:7" ht="15.75" thickBot="1">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="92" t="s">
@@ -34466,7 +34466,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="258" spans="1:7" ht="15" thickBot="1">
+    <row r="258" spans="1:7" ht="15.75" thickBot="1">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="92" t="s">
@@ -34849,7 +34849,7 @@
       <c r="F280" s="3"/>
       <c r="G280" s="3"/>
     </row>
-    <row r="281" spans="1:7" ht="15" thickBot="1">
+    <row r="281" spans="1:7" ht="15.75" thickBot="1">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="95" t="s">
@@ -34868,7 +34868,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="282" spans="1:7" ht="15" thickBot="1">
+    <row r="282" spans="1:7" ht="15.75" thickBot="1">
       <c r="A282" s="14"/>
       <c r="B282" s="14"/>
       <c r="C282" s="34" t="s">
@@ -35079,7 +35079,7 @@
       <c r="F301" s="3"/>
       <c r="G301" s="3"/>
     </row>
-    <row r="302" spans="1:7" ht="15" thickBot="1">
+    <row r="302" spans="1:7" ht="15.75" thickBot="1">
       <c r="C302" s="14" t="s">
         <v>774</v>
       </c>
@@ -35092,7 +35092,7 @@
       <c r="F302" s="3"/>
       <c r="G302" s="3"/>
     </row>
-    <row r="303" spans="1:7" ht="26.5" thickBot="1">
+    <row r="303" spans="1:7" ht="26.25" thickBot="1">
       <c r="C303" s="14"/>
       <c r="D303" s="58" t="s">
         <v>845</v>
@@ -35116,7 +35116,7 @@
       <c r="F304" s="3"/>
       <c r="G304" s="3"/>
     </row>
-    <row r="305" spans="3:7" ht="15" thickBot="1">
+    <row r="305" spans="3:7" ht="15.75" thickBot="1">
       <c r="C305" s="14" t="s">
         <v>774</v>
       </c>
@@ -35129,7 +35129,7 @@
       <c r="F305" s="3"/>
       <c r="G305" s="3"/>
     </row>
-    <row r="306" spans="3:7" ht="26.5" thickBot="1">
+    <row r="306" spans="3:7" ht="26.25" thickBot="1">
       <c r="C306" s="14"/>
       <c r="D306" s="58" t="s">
         <v>846</v>
@@ -35736,7 +35736,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="345" spans="1:7" ht="15.5">
+    <row r="345" spans="1:7" ht="15.75">
       <c r="A345" s="14"/>
       <c r="B345" s="14"/>
       <c r="C345" s="14" t="s">
@@ -35831,7 +35831,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="350" spans="1:7" ht="15.5">
+    <row r="350" spans="1:7" ht="15.75">
       <c r="A350" s="14"/>
       <c r="B350" s="14"/>
       <c r="C350" s="14" t="s">
@@ -35866,7 +35866,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="352" spans="1:7" ht="15.5">
+    <row r="352" spans="1:7" ht="15.75">
       <c r="A352" s="14"/>
       <c r="B352" s="14"/>
       <c r="C352" s="14" t="s">
@@ -35918,7 +35918,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="355" spans="1:7" ht="15.5">
+    <row r="355" spans="1:7" ht="15.75">
       <c r="A355" s="14"/>
       <c r="B355" s="14"/>
       <c r="C355" s="14" t="s">
@@ -35992,7 +35992,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="359" spans="1:7" ht="15.5">
+    <row r="359" spans="1:7" ht="15.75">
       <c r="A359" s="14"/>
       <c r="B359" s="14"/>
       <c r="C359" s="14" t="s">
@@ -36066,7 +36066,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="363" spans="1:7" ht="15.5">
+    <row r="363" spans="1:7" ht="15.75">
       <c r="A363" s="14"/>
       <c r="B363" s="14"/>
       <c r="C363" s="14" t="s">
@@ -36083,7 +36083,7 @@
       </c>
       <c r="G363" s="5"/>
     </row>
-    <row r="364" spans="1:7" ht="15" thickBot="1">
+    <row r="364" spans="1:7" ht="15.75" thickBot="1">
       <c r="A364" s="14"/>
       <c r="B364" s="14"/>
       <c r="C364" s="14" t="s">
@@ -36102,7 +36102,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="365" spans="1:7" ht="15" thickBot="1">
+    <row r="365" spans="1:7" ht="15.75" thickBot="1">
       <c r="A365" s="14"/>
       <c r="B365" s="14"/>
       <c r="C365" s="14" t="s">
@@ -36117,7 +36117,7 @@
       <c r="F365" s="3"/>
       <c r="G365" s="14"/>
     </row>
-    <row r="366" spans="1:7" ht="15" thickBot="1">
+    <row r="366" spans="1:7" ht="15.75" thickBot="1">
       <c r="A366" s="14"/>
       <c r="B366" s="14"/>
       <c r="C366" s="14" t="s">
@@ -36132,7 +36132,7 @@
       <c r="F366" s="3"/>
       <c r="G366" s="14"/>
     </row>
-    <row r="367" spans="1:7" ht="15.5">
+    <row r="367" spans="1:7" ht="15.75">
       <c r="C367" s="14" t="s">
         <v>774</v>
       </c>
@@ -36202,7 +36202,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="371" spans="1:7" ht="15.5">
+    <row r="371" spans="1:7" ht="15.75">
       <c r="A371" s="14"/>
       <c r="B371" s="14"/>
       <c r="C371" s="14" t="s">
@@ -36259,7 +36259,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="374" spans="1:7" ht="15" thickBot="1">
+    <row r="374" spans="1:7" ht="15.75" thickBot="1">
       <c r="A374" s="14"/>
       <c r="B374" s="14"/>
       <c r="C374" s="14" t="s">
@@ -36278,7 +36278,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="375" spans="1:7" ht="15" thickBot="1">
+    <row r="375" spans="1:7" ht="15.75" thickBot="1">
       <c r="A375" s="14"/>
       <c r="B375" s="14"/>
       <c r="C375" s="14" t="s">
@@ -36297,7 +36297,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="376" spans="1:7" ht="15" thickBot="1">
+    <row r="376" spans="1:7" ht="15.75" thickBot="1">
       <c r="A376" s="14"/>
       <c r="B376" s="14"/>
       <c r="C376" s="14" t="s">
@@ -36316,7 +36316,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="377" spans="1:7" ht="15" thickBot="1">
+    <row r="377" spans="1:7" ht="15.75" thickBot="1">
       <c r="A377" s="14"/>
       <c r="B377" s="14"/>
       <c r="C377" s="14" t="s">
@@ -36335,7 +36335,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="378" spans="1:7" ht="15" thickBot="1">
+    <row r="378" spans="1:7" ht="15.75" thickBot="1">
       <c r="A378" s="14"/>
       <c r="B378" s="14"/>
       <c r="C378" s="14" t="s">
@@ -36354,7 +36354,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="379" spans="1:7" ht="15" thickBot="1">
+    <row r="379" spans="1:7" ht="15.75" thickBot="1">
       <c r="A379" s="14"/>
       <c r="B379" s="14"/>
       <c r="C379" s="14" t="s">
@@ -36373,7 +36373,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="380" spans="1:7" ht="15" thickBot="1">
+    <row r="380" spans="1:7" ht="15.75" thickBot="1">
       <c r="A380" s="14"/>
       <c r="B380" s="14"/>
       <c r="C380" s="14" t="s">
@@ -36392,7 +36392,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="381" spans="1:7" ht="15" thickBot="1">
+    <row r="381" spans="1:7" ht="15.75" thickBot="1">
       <c r="A381" s="14"/>
       <c r="B381" s="14"/>
       <c r="C381" s="14" t="s">
@@ -36411,7 +36411,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="382" spans="1:7" ht="15" thickBot="1">
+    <row r="382" spans="1:7" ht="15.75" thickBot="1">
       <c r="A382" s="14"/>
       <c r="B382" s="14"/>
       <c r="C382" s="14" t="s">
@@ -36430,7 +36430,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="383" spans="1:7" ht="15" thickBot="1">
+    <row r="383" spans="1:7" ht="15.75" thickBot="1">
       <c r="A383" s="14"/>
       <c r="B383" s="14"/>
       <c r="C383" s="14" t="s">
@@ -36449,7 +36449,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="384" spans="1:7" ht="15" thickBot="1">
+    <row r="384" spans="1:7" ht="15.75" thickBot="1">
       <c r="A384" s="14"/>
       <c r="B384" s="14"/>
       <c r="C384" s="14" t="s">
@@ -36468,7 +36468,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="385" spans="1:7" ht="15" thickBot="1">
+    <row r="385" spans="1:7" ht="15.75" thickBot="1">
       <c r="A385" s="14"/>
       <c r="B385" s="14"/>
       <c r="C385" s="14" t="s">
@@ -36487,7 +36487,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="386" spans="1:7" ht="15" thickBot="1">
+    <row r="386" spans="1:7" ht="15.75" thickBot="1">
       <c r="A386" s="14"/>
       <c r="B386" s="14"/>
       <c r="C386" s="14" t="s">
@@ -36503,7 +36503,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="387" spans="1:7" ht="15" thickBot="1">
+    <row r="387" spans="1:7" ht="15.75" thickBot="1">
       <c r="A387" s="14"/>
       <c r="B387" s="14"/>
       <c r="C387" s="14" t="s">
@@ -36519,7 +36519,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="388" spans="1:7" ht="15" thickBot="1">
+    <row r="388" spans="1:7" ht="15.75" thickBot="1">
       <c r="A388" s="14"/>
       <c r="B388" s="14"/>
       <c r="C388" s="14" t="s">
@@ -36535,7 +36535,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="389" spans="1:7" ht="15" thickBot="1">
+    <row r="389" spans="1:7" ht="15.75" thickBot="1">
       <c r="A389" s="14"/>
       <c r="B389" s="14"/>
       <c r="C389" s="14" t="s">
@@ -36551,7 +36551,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="390" spans="1:7" ht="15" thickBot="1">
+    <row r="390" spans="1:7" ht="15.75" thickBot="1">
       <c r="A390" s="14"/>
       <c r="B390" s="14"/>
       <c r="C390" s="14" t="s">
@@ -36567,7 +36567,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="391" spans="1:7" ht="15" thickBot="1">
+    <row r="391" spans="1:7" ht="15.75" thickBot="1">
       <c r="A391" s="14"/>
       <c r="B391" s="14"/>
       <c r="C391" s="14" t="s">
@@ -36583,7 +36583,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="392" spans="1:7" ht="15" thickBot="1">
+    <row r="392" spans="1:7" ht="15.75" thickBot="1">
       <c r="A392" s="14"/>
       <c r="B392" s="14"/>
       <c r="C392" s="14" t="s">
@@ -36599,7 +36599,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="393" spans="1:7" ht="15" thickBot="1">
+    <row r="393" spans="1:7" ht="15.75" thickBot="1">
       <c r="A393" s="14"/>
       <c r="B393" s="14"/>
       <c r="C393" s="14" t="s">
@@ -36615,7 +36615,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="394" spans="1:7" ht="15" thickBot="1">
+    <row r="394" spans="1:7" ht="15.75" thickBot="1">
       <c r="A394" s="14"/>
       <c r="B394" s="14"/>
       <c r="C394" s="14" t="s">
@@ -36632,7 +36632,7 @@
       </c>
       <c r="G394" s="41"/>
     </row>
-    <row r="395" spans="1:7" ht="15" thickBot="1">
+    <row r="395" spans="1:7" ht="15.75" thickBot="1">
       <c r="A395" s="14"/>
       <c r="B395" s="14"/>
       <c r="C395" s="14" t="s">
@@ -36651,7 +36651,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="396" spans="1:7" ht="15" thickBot="1">
+    <row r="396" spans="1:7" ht="15.75" thickBot="1">
       <c r="A396" s="14"/>
       <c r="B396" s="14"/>
       <c r="C396" s="14" t="s">
@@ -36670,7 +36670,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="397" spans="1:7" ht="15" thickBot="1">
+    <row r="397" spans="1:7" ht="15.75" thickBot="1">
       <c r="A397" s="14"/>
       <c r="B397" s="14"/>
       <c r="C397" s="14" t="s">
@@ -36689,7 +36689,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="398" spans="1:7" ht="15" thickBot="1">
+    <row r="398" spans="1:7" ht="15.75" thickBot="1">
       <c r="A398" s="14"/>
       <c r="B398" s="14"/>
       <c r="C398" s="14" t="s">
@@ -36708,7 +36708,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="399" spans="1:7" ht="15" thickBot="1">
+    <row r="399" spans="1:7" ht="15.75" thickBot="1">
       <c r="A399" s="14"/>
       <c r="B399" s="14"/>
       <c r="C399" s="14" t="s">
@@ -36727,7 +36727,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="400" spans="1:7" ht="15" thickBot="1">
+    <row r="400" spans="1:7" ht="15.75" thickBot="1">
       <c r="A400" s="14"/>
       <c r="B400" s="14"/>
       <c r="C400" s="14" t="s">
@@ -36746,7 +36746,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="401" spans="1:7" ht="15" thickBot="1">
+    <row r="401" spans="1:7" ht="15.75" thickBot="1">
       <c r="A401" s="14"/>
       <c r="B401" s="14"/>
       <c r="C401" s="14" t="s">
@@ -36765,7 +36765,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="402" spans="1:7" ht="15" thickBot="1">
+    <row r="402" spans="1:7" ht="15.75" thickBot="1">
       <c r="A402" s="14"/>
       <c r="B402" s="14"/>
       <c r="C402" s="14" t="s">
@@ -36784,7 +36784,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="403" spans="1:7" ht="15" thickBot="1">
+    <row r="403" spans="1:7" ht="15.75" thickBot="1">
       <c r="A403" s="14"/>
       <c r="B403" s="14"/>
       <c r="C403" s="14" t="s">
@@ -36803,7 +36803,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="404" spans="1:7" ht="15" thickBot="1">
+    <row r="404" spans="1:7" ht="15.75" thickBot="1">
       <c r="A404" s="14"/>
       <c r="B404" s="14"/>
       <c r="C404" s="14" t="s">
@@ -36822,7 +36822,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="405" spans="1:7" ht="15" thickBot="1">
+    <row r="405" spans="1:7" ht="15.75" thickBot="1">
       <c r="A405" s="14"/>
       <c r="B405" s="14"/>
       <c r="C405" s="14" t="s">
@@ -36841,7 +36841,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="406" spans="1:7" ht="15" thickBot="1">
+    <row r="406" spans="1:7" ht="15.75" thickBot="1">
       <c r="A406" s="14"/>
       <c r="B406" s="14"/>
       <c r="C406" s="14" t="s">
@@ -36857,7 +36857,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="407" spans="1:7" ht="15" thickBot="1">
+    <row r="407" spans="1:7" ht="15.75" thickBot="1">
       <c r="A407" s="14"/>
       <c r="B407" s="14"/>
       <c r="C407" s="14" t="s">
@@ -36873,7 +36873,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="408" spans="1:7" ht="15" thickBot="1">
+    <row r="408" spans="1:7" ht="15.75" thickBot="1">
       <c r="A408" s="14"/>
       <c r="B408" s="14"/>
       <c r="C408" s="14" t="s">
@@ -36889,7 +36889,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="409" spans="1:7" ht="15" thickBot="1">
+    <row r="409" spans="1:7" ht="15.75" thickBot="1">
       <c r="A409" s="14"/>
       <c r="B409" s="14"/>
       <c r="C409" s="14" t="s">
@@ -36905,7 +36905,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="410" spans="1:7" ht="15" thickBot="1">
+    <row r="410" spans="1:7" ht="15.75" thickBot="1">
       <c r="A410" s="14"/>
       <c r="B410" s="14"/>
       <c r="C410" s="14" t="s">
@@ -36921,7 +36921,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="411" spans="1:7" ht="15" thickBot="1">
+    <row r="411" spans="1:7" ht="15.75" thickBot="1">
       <c r="A411" s="14"/>
       <c r="B411" s="14"/>
       <c r="C411" s="14" t="s">
@@ -36937,7 +36937,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="412" spans="1:7" ht="15" thickBot="1">
+    <row r="412" spans="1:7" ht="15.75" thickBot="1">
       <c r="A412" s="14"/>
       <c r="B412" s="14"/>
       <c r="C412" s="14" t="s">
@@ -36953,7 +36953,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="413" spans="1:7" ht="15" thickBot="1">
+    <row r="413" spans="1:7" ht="15.75" thickBot="1">
       <c r="A413" s="14"/>
       <c r="B413" s="14"/>
       <c r="C413" s="14" t="s">
@@ -36969,7 +36969,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="414" spans="1:7" ht="15" thickBot="1">
+    <row r="414" spans="1:7" ht="15.75" thickBot="1">
       <c r="A414" s="14"/>
       <c r="B414" s="14"/>
       <c r="C414" s="14" t="s">
@@ -36986,7 +36986,7 @@
       </c>
       <c r="G414" s="41"/>
     </row>
-    <row r="415" spans="1:7" ht="15" thickBot="1">
+    <row r="415" spans="1:7" ht="15.75" thickBot="1">
       <c r="A415" s="14"/>
       <c r="B415" s="14"/>
       <c r="C415" s="14" t="s">
@@ -37005,7 +37005,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="416" spans="1:7" ht="15" thickBot="1">
+    <row r="416" spans="1:7" ht="15.75" thickBot="1">
       <c r="A416" s="14"/>
       <c r="B416" s="14"/>
       <c r="C416" s="14" t="s">
@@ -37024,7 +37024,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="417" spans="1:7" ht="15" thickBot="1">
+    <row r="417" spans="1:7" ht="15.75" thickBot="1">
       <c r="A417" s="14"/>
       <c r="B417" s="14"/>
       <c r="C417" s="14" t="s">
@@ -37043,7 +37043,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="418" spans="1:7" ht="15" thickBot="1">
+    <row r="418" spans="1:7" ht="15.75" thickBot="1">
       <c r="A418" s="14"/>
       <c r="B418" s="14"/>
       <c r="C418" s="14" t="s">
@@ -37062,7 +37062,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="419" spans="1:7" ht="15" thickBot="1">
+    <row r="419" spans="1:7" ht="15.75" thickBot="1">
       <c r="A419" s="14"/>
       <c r="B419" s="14"/>
       <c r="C419" s="14" t="s">
@@ -37081,7 +37081,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="420" spans="1:7" ht="15" thickBot="1">
+    <row r="420" spans="1:7" ht="15.75" thickBot="1">
       <c r="A420" s="14"/>
       <c r="B420" s="14"/>
       <c r="C420" s="14" t="s">
@@ -37100,7 +37100,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="421" spans="1:7" ht="15" thickBot="1">
+    <row r="421" spans="1:7" ht="15.75" thickBot="1">
       <c r="A421" s="14"/>
       <c r="B421" s="14"/>
       <c r="C421" s="14" t="s">
@@ -37119,7 +37119,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="422" spans="1:7" ht="15" thickBot="1">
+    <row r="422" spans="1:7" ht="15.75" thickBot="1">
       <c r="A422" s="14"/>
       <c r="B422" s="14"/>
       <c r="C422" s="14" t="s">
@@ -37138,7 +37138,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="423" spans="1:7" ht="15" thickBot="1">
+    <row r="423" spans="1:7" ht="15.75" thickBot="1">
       <c r="A423" s="14"/>
       <c r="B423" s="14"/>
       <c r="C423" s="14" t="s">
@@ -37157,7 +37157,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="424" spans="1:7" ht="15" thickBot="1">
+    <row r="424" spans="1:7" ht="15.75" thickBot="1">
       <c r="A424" s="14"/>
       <c r="B424" s="14"/>
       <c r="C424" s="14" t="s">
@@ -37173,7 +37173,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="425" spans="1:7" ht="15" thickBot="1">
+    <row r="425" spans="1:7" ht="15.75" thickBot="1">
       <c r="A425" s="14"/>
       <c r="B425" s="14"/>
       <c r="C425" s="14" t="s">
@@ -37190,7 +37190,7 @@
       </c>
       <c r="G425" s="43"/>
     </row>
-    <row r="426" spans="1:7" ht="15" thickBot="1">
+    <row r="426" spans="1:7" ht="15.75" thickBot="1">
       <c r="A426" s="14"/>
       <c r="B426" s="14"/>
       <c r="C426" s="14" t="s">
@@ -37207,7 +37207,7 @@
       </c>
       <c r="G426" s="44"/>
     </row>
-    <row r="427" spans="1:7" ht="15" thickBot="1">
+    <row r="427" spans="1:7" ht="15.75" thickBot="1">
       <c r="A427" s="14"/>
       <c r="B427" s="14"/>
       <c r="C427" s="14" t="s">
@@ -37224,7 +37224,7 @@
       </c>
       <c r="G427" s="44"/>
     </row>
-    <row r="428" spans="1:7" ht="15" thickBot="1">
+    <row r="428" spans="1:7" ht="15.75" thickBot="1">
       <c r="A428" s="14"/>
       <c r="B428" s="14"/>
       <c r="C428" s="14" t="s">
@@ -37240,7 +37240,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="429" spans="1:7" ht="15" thickBot="1">
+    <row r="429" spans="1:7" ht="15.75" thickBot="1">
       <c r="A429" s="14"/>
       <c r="B429" s="14"/>
       <c r="C429" s="14" t="s">
@@ -37256,7 +37256,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="430" spans="1:7" ht="15" thickBot="1">
+    <row r="430" spans="1:7" ht="15.75" thickBot="1">
       <c r="A430" s="14"/>
       <c r="B430" s="14"/>
       <c r="C430" s="14" t="s">
@@ -37272,7 +37272,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="431" spans="1:7" ht="15" thickBot="1">
+    <row r="431" spans="1:7" ht="15.75" thickBot="1">
       <c r="A431" s="14"/>
       <c r="B431" s="14"/>
       <c r="C431" s="14" t="s">
@@ -37288,7 +37288,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="432" spans="1:7" ht="15" thickBot="1">
+    <row r="432" spans="1:7" ht="15.75" thickBot="1">
       <c r="A432" s="14"/>
       <c r="B432" s="14"/>
       <c r="C432" s="14" t="s">
@@ -37307,7 +37307,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="433" spans="1:7" ht="15" thickBot="1">
+    <row r="433" spans="1:7" ht="15.75" thickBot="1">
       <c r="A433" s="14"/>
       <c r="B433" s="14"/>
       <c r="C433" s="14" t="s">
@@ -37326,7 +37326,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="434" spans="1:7" ht="15" thickBot="1">
+    <row r="434" spans="1:7" ht="15.75" thickBot="1">
       <c r="A434" s="14"/>
       <c r="B434" s="14"/>
       <c r="C434" s="14" t="s">
@@ -37342,7 +37342,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="435" spans="1:7" ht="15" thickBot="1">
+    <row r="435" spans="1:7" ht="15.75" thickBot="1">
       <c r="A435" s="14"/>
       <c r="B435" s="14"/>
       <c r="C435" s="14" t="s">
@@ -37361,7 +37361,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="436" spans="1:7" ht="15" thickBot="1">
+    <row r="436" spans="1:7" ht="15.75" thickBot="1">
       <c r="A436" s="14"/>
       <c r="B436" s="14"/>
       <c r="C436" s="14" t="s">
@@ -37380,7 +37380,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="437" spans="1:7" ht="15" thickBot="1">
+    <row r="437" spans="1:7" ht="15.75" thickBot="1">
       <c r="A437" s="14"/>
       <c r="B437" s="14"/>
       <c r="C437" s="14" t="s">
@@ -37399,7 +37399,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="438" spans="1:7" ht="15" thickBot="1">
+    <row r="438" spans="1:7" ht="15.75" thickBot="1">
       <c r="A438" s="14"/>
       <c r="B438" s="14"/>
       <c r="C438" s="14" t="s">
@@ -37415,7 +37415,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="439" spans="1:7" ht="15" thickBot="1">
+    <row r="439" spans="1:7" ht="15.75" thickBot="1">
       <c r="A439" s="14"/>
       <c r="B439" s="14"/>
       <c r="C439" s="14" t="s">
@@ -37434,7 +37434,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="440" spans="1:7" ht="15" thickBot="1">
+    <row r="440" spans="1:7" ht="15.75" thickBot="1">
       <c r="A440" s="14"/>
       <c r="B440" s="14"/>
       <c r="C440" s="14" t="s">
@@ -37453,7 +37453,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="441" spans="1:7" ht="15" thickBot="1">
+    <row r="441" spans="1:7" ht="15.75" thickBot="1">
       <c r="A441" s="14"/>
       <c r="B441" s="14"/>
       <c r="C441" s="14" t="s">
@@ -37472,7 +37472,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="442" spans="1:7" ht="15" thickBot="1">
+    <row r="442" spans="1:7" ht="15.75" thickBot="1">
       <c r="A442" s="14"/>
       <c r="B442" s="14"/>
       <c r="C442" s="14" t="s">
@@ -37491,7 +37491,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="443" spans="1:7" ht="15" thickBot="1">
+    <row r="443" spans="1:7" ht="15.75" thickBot="1">
       <c r="A443" s="14"/>
       <c r="B443" s="14"/>
       <c r="C443" s="14" t="s">
@@ -37510,7 +37510,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="444" spans="1:7" ht="15" thickBot="1">
+    <row r="444" spans="1:7" ht="15.75" thickBot="1">
       <c r="A444" s="14"/>
       <c r="B444" s="14"/>
       <c r="C444" s="14" t="s">
@@ -37529,7 +37529,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="445" spans="1:7" ht="15" thickBot="1">
+    <row r="445" spans="1:7" ht="15.75" thickBot="1">
       <c r="A445" s="14"/>
       <c r="B445" s="14"/>
       <c r="C445" s="14" t="s">
@@ -37548,7 +37548,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="446" spans="1:7" ht="15" thickBot="1">
+    <row r="446" spans="1:7" ht="15.75" thickBot="1">
       <c r="A446" s="14"/>
       <c r="B446" s="14"/>
       <c r="C446" s="14" t="s">
@@ -37567,7 +37567,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="447" spans="1:7" ht="15" thickBot="1">
+    <row r="447" spans="1:7" ht="15.75" thickBot="1">
       <c r="A447" s="14"/>
       <c r="B447" s="14"/>
       <c r="C447" s="14" t="s">
@@ -37586,7 +37586,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="448" spans="1:7" ht="15" thickBot="1">
+    <row r="448" spans="1:7" ht="15.75" thickBot="1">
       <c r="A448" s="14"/>
       <c r="B448" s="14"/>
       <c r="C448" s="14" t="s">
@@ -37605,7 +37605,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="449" spans="1:7" ht="15" thickBot="1">
+    <row r="449" spans="1:7" ht="15.75" thickBot="1">
       <c r="A449" s="14"/>
       <c r="B449" s="14"/>
       <c r="C449" s="14" t="s">
@@ -37621,7 +37621,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="450" spans="1:7" ht="15" thickBot="1">
+    <row r="450" spans="1:7" ht="15.75" thickBot="1">
       <c r="A450" s="14"/>
       <c r="B450" s="14"/>
       <c r="C450" s="14" t="s">
@@ -37640,7 +37640,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="451" spans="1:7" ht="15" thickBot="1">
+    <row r="451" spans="1:7" ht="15.75" thickBot="1">
       <c r="A451" s="14"/>
       <c r="B451" s="14"/>
       <c r="C451" s="14" t="s">
@@ -37659,7 +37659,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="452" spans="1:7" ht="15" thickBot="1">
+    <row r="452" spans="1:7" ht="15.75" thickBot="1">
       <c r="A452" s="14"/>
       <c r="B452" s="14"/>
       <c r="C452" s="14" t="s">
@@ -37678,7 +37678,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="453" spans="1:7" ht="15" thickBot="1">
+    <row r="453" spans="1:7" ht="15.75" thickBot="1">
       <c r="A453" s="14"/>
       <c r="B453" s="14"/>
       <c r="C453" s="14" t="s">
@@ -37694,7 +37694,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="454" spans="1:7" ht="15" thickBot="1">
+    <row r="454" spans="1:7" ht="15.75" thickBot="1">
       <c r="A454" s="14"/>
       <c r="B454" s="14"/>
       <c r="C454" s="14" t="s">
@@ -37713,7 +37713,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="455" spans="1:7" ht="15" thickBot="1">
+    <row r="455" spans="1:7" ht="15.75" thickBot="1">
       <c r="A455" s="14"/>
       <c r="B455" s="14"/>
       <c r="C455" s="14" t="s">
@@ -37732,7 +37732,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="456" spans="1:7" ht="15" thickBot="1">
+    <row r="456" spans="1:7" ht="15.75" thickBot="1">
       <c r="A456" s="14"/>
       <c r="B456" s="14"/>
       <c r="C456" s="14" t="s">
@@ -37748,7 +37748,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="457" spans="1:7" ht="15" thickBot="1">
+    <row r="457" spans="1:7" ht="15.75" thickBot="1">
       <c r="A457" s="14"/>
       <c r="B457" s="14"/>
       <c r="C457" s="14" t="s">
@@ -37764,7 +37764,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="458" spans="1:7" ht="15" thickBot="1">
+    <row r="458" spans="1:7" ht="15.75" thickBot="1">
       <c r="A458" s="14"/>
       <c r="B458" s="14"/>
       <c r="C458" s="14" t="s">
@@ -37780,7 +37780,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="459" spans="1:7" ht="15" thickBot="1">
+    <row r="459" spans="1:7" ht="15.75" thickBot="1">
       <c r="A459" s="14"/>
       <c r="B459" s="14"/>
       <c r="C459" s="14" t="s">
@@ -37796,7 +37796,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="460" spans="1:7" ht="15" thickBot="1">
+    <row r="460" spans="1:7" ht="15.75" thickBot="1">
       <c r="A460" s="14"/>
       <c r="B460" s="14"/>
       <c r="C460" s="14" t="s">
@@ -37815,7 +37815,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="461" spans="1:7" ht="15" thickBot="1">
+    <row r="461" spans="1:7" ht="15.75" thickBot="1">
       <c r="A461" s="14"/>
       <c r="B461" s="14"/>
       <c r="C461" s="14" t="s">
@@ -37831,7 +37831,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="462" spans="1:7" ht="15" thickBot="1">
+    <row r="462" spans="1:7" ht="15.75" thickBot="1">
       <c r="A462" s="14"/>
       <c r="B462" s="14"/>
       <c r="C462" s="14" t="s">
@@ -37847,7 +37847,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="463" spans="1:7" ht="15" thickBot="1">
+    <row r="463" spans="1:7" ht="15.75" thickBot="1">
       <c r="A463" s="14"/>
       <c r="B463" s="14"/>
       <c r="C463" s="14" t="s">
@@ -38186,7 +38186,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="483" spans="1:7" ht="15.5">
+    <row r="483" spans="1:7" ht="15.75">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="16" t="s">
@@ -38408,7 +38408,7 @@
       <c r="F500" s="13"/>
       <c r="G500" s="14"/>
     </row>
-    <row r="501" spans="1:7" ht="15.5">
+    <row r="501" spans="1:7" ht="15.75">
       <c r="A501" s="1"/>
       <c r="B501" s="1"/>
       <c r="C501" s="1"/>
@@ -38423,7 +38423,7 @@
       </c>
       <c r="G501" s="5"/>
     </row>
-    <row r="502" spans="1:7" ht="15.5">
+    <row r="502" spans="1:7" ht="15.75">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="1"/>
@@ -38465,7 +38465,7 @@
       <c r="F505" s="4"/>
       <c r="G505" s="3"/>
     </row>
-    <row r="506" spans="1:7" ht="15.5">
+    <row r="506" spans="1:7" ht="15.75">
       <c r="A506" s="1"/>
       <c r="B506" s="1"/>
       <c r="C506" s="1"/>
@@ -38474,7 +38474,7 @@
       <c r="F506" s="4"/>
       <c r="G506" s="5"/>
     </row>
-    <row r="507" spans="1:7" ht="15.5">
+    <row r="507" spans="1:7" ht="15.75">
       <c r="A507" s="1"/>
       <c r="B507" s="1"/>
       <c r="C507" s="1"/>
@@ -38483,7 +38483,7 @@
       <c r="F507" s="4"/>
       <c r="G507" s="5"/>
     </row>
-    <row r="508" spans="1:7" ht="15.5">
+    <row r="508" spans="1:7" ht="15.75">
       <c r="A508" s="1"/>
       <c r="B508" s="1"/>
       <c r="C508" s="1"/>
@@ -38560,7 +38560,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="513" spans="1:7">
+    <row r="513" spans="1:7" ht="26.25">
       <c r="A513" s="1"/>
       <c r="B513" s="1"/>
       <c r="C513" s="1"/>
@@ -38577,7 +38577,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="514" spans="1:7" ht="26">
+    <row r="514" spans="1:7" ht="26.25">
       <c r="A514" s="1"/>
       <c r="B514" s="1"/>
       <c r="C514" s="7"/>
@@ -38824,7 +38824,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="533" spans="1:7" ht="51">
+    <row r="533" spans="1:7" ht="51.75">
       <c r="A533" s="1"/>
       <c r="B533" s="1"/>
       <c r="C533" s="1"/>
@@ -38839,7 +38839,7 @@
       </c>
       <c r="G533" s="5"/>
     </row>
-    <row r="534" spans="1:7">
+    <row r="534" spans="1:7" ht="26.25">
       <c r="A534" s="1"/>
       <c r="B534" s="1"/>
       <c r="C534" s="1"/>
@@ -38856,7 +38856,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="535" spans="1:7">
+    <row r="535" spans="1:7" ht="26.25">
       <c r="A535" s="1"/>
       <c r="B535" s="1"/>
       <c r="C535" s="1"/>
@@ -38873,7 +38873,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="536" spans="1:7" ht="26">
+    <row r="536" spans="1:7" ht="26.25">
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
       <c r="C536" s="1"/>
@@ -38968,7 +38968,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="543" spans="1:7" ht="15.5">
+    <row r="543" spans="1:7" ht="15.75">
       <c r="A543" s="1"/>
       <c r="B543" s="1"/>
       <c r="C543" s="1"/>
@@ -38983,7 +38983,7 @@
       </c>
       <c r="G543" s="5"/>
     </row>
-    <row r="544" spans="1:7" ht="15.5">
+    <row r="544" spans="1:7" ht="15.75">
       <c r="A544" s="1"/>
       <c r="B544" s="1"/>
       <c r="C544" s="1"/>
@@ -38998,7 +38998,7 @@
       </c>
       <c r="G544" s="5"/>
     </row>
-    <row r="545" spans="1:7" ht="15.5">
+    <row r="545" spans="1:7" ht="15.75">
       <c r="A545" s="1"/>
       <c r="B545" s="1"/>
       <c r="C545" s="1"/>
@@ -39013,7 +39013,7 @@
       </c>
       <c r="G545" s="5"/>
     </row>
-    <row r="546" spans="1:7" ht="15.5">
+    <row r="546" spans="1:7" ht="15.75">
       <c r="A546" s="1"/>
       <c r="B546" s="1"/>
       <c r="C546" s="1"/>
@@ -39028,7 +39028,7 @@
       </c>
       <c r="G546" s="5"/>
     </row>
-    <row r="547" spans="1:7" ht="15.5">
+    <row r="547" spans="1:7" ht="15.75">
       <c r="A547" s="1"/>
       <c r="B547" s="1"/>
       <c r="C547" s="1"/>
@@ -39043,7 +39043,7 @@
       </c>
       <c r="G547" s="5"/>
     </row>
-    <row r="548" spans="1:7" ht="15.5">
+    <row r="548" spans="1:7" ht="15.75">
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
       <c r="C548" s="1"/>
@@ -39058,7 +39058,7 @@
       </c>
       <c r="G548" s="5"/>
     </row>
-    <row r="549" spans="1:7" ht="15.5">
+    <row r="549" spans="1:7" ht="15.75">
       <c r="A549" s="1"/>
       <c r="B549" s="1"/>
       <c r="C549" s="1"/>
@@ -39073,7 +39073,7 @@
       </c>
       <c r="G549" s="5"/>
     </row>
-    <row r="550" spans="1:7" ht="15.5">
+    <row r="550" spans="1:7" ht="15.75">
       <c r="A550" s="1"/>
       <c r="B550" s="1"/>
       <c r="C550" s="1"/>
@@ -39124,7 +39124,7 @@
       <c r="F555" s="4"/>
       <c r="G555" s="3"/>
     </row>
-    <row r="558" spans="1:7" ht="15.5">
+    <row r="558" spans="1:7" ht="15.75">
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
       <c r="C558" s="1"/>
@@ -39139,7 +39139,7 @@
       </c>
       <c r="G558" s="5"/>
     </row>
-    <row r="559" spans="1:7" ht="15.5">
+    <row r="559" spans="1:7" ht="15.75">
       <c r="A559" s="1"/>
       <c r="B559" s="1"/>
       <c r="C559" s="1"/>
@@ -39154,7 +39154,7 @@
       </c>
       <c r="G559" s="5"/>
     </row>
-    <row r="560" spans="1:7" ht="15.5">
+    <row r="560" spans="1:7" ht="15.75">
       <c r="A560" s="1"/>
       <c r="B560" s="1"/>
       <c r="C560" s="1"/>
@@ -39169,7 +39169,7 @@
       </c>
       <c r="G560" s="5"/>
     </row>
-    <row r="563" spans="1:7" ht="15.5">
+    <row r="563" spans="1:7" ht="15.75">
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
@@ -39184,7 +39184,7 @@
       </c>
       <c r="G563" s="5"/>
     </row>
-    <row r="564" spans="1:7" ht="15.5">
+    <row r="564" spans="1:7" ht="15.75">
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
@@ -39199,7 +39199,7 @@
       </c>
       <c r="G564" s="5"/>
     </row>
-    <row r="565" spans="1:7" ht="15.5">
+    <row r="565" spans="1:7" ht="15.75">
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
@@ -39265,7 +39265,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="571" spans="1:7" ht="15.5">
+    <row r="571" spans="1:7" ht="15.75">
       <c r="A571" s="1"/>
       <c r="B571" s="1"/>
       <c r="C571" s="1"/>
@@ -39280,7 +39280,7 @@
       </c>
       <c r="G571" s="5"/>
     </row>
-    <row r="572" spans="1:7" ht="15.5">
+    <row r="572" spans="1:7" ht="15.75">
       <c r="A572" s="1"/>
       <c r="B572" s="1"/>
       <c r="C572" s="1"/>
@@ -39295,7 +39295,7 @@
       </c>
       <c r="G572" s="5"/>
     </row>
-    <row r="573" spans="1:7" ht="15.5">
+    <row r="573" spans="1:7" ht="15.75">
       <c r="A573" s="1"/>
       <c r="B573" s="1"/>
       <c r="C573" s="1"/>
@@ -39388,6 +39388,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D515:D516"/>
+    <mergeCell ref="E515:E516"/>
+    <mergeCell ref="F515:F516"/>
+    <mergeCell ref="D519:D520"/>
+    <mergeCell ref="E519:E520"/>
+    <mergeCell ref="F519:F520"/>
+    <mergeCell ref="D521:D522"/>
+    <mergeCell ref="E521:E522"/>
+    <mergeCell ref="F521:F522"/>
+    <mergeCell ref="D525:D526"/>
+    <mergeCell ref="E525:E526"/>
+    <mergeCell ref="F525:F526"/>
+    <mergeCell ref="D527:D528"/>
+    <mergeCell ref="E527:E528"/>
+    <mergeCell ref="F527:F528"/>
+    <mergeCell ref="D529:D530"/>
+    <mergeCell ref="E529:E530"/>
+    <mergeCell ref="F529:F530"/>
     <mergeCell ref="D540:D542"/>
     <mergeCell ref="E540:E542"/>
     <mergeCell ref="F540:F542"/>
@@ -39397,24 +39415,6 @@
     <mergeCell ref="D537:D539"/>
     <mergeCell ref="E537:E539"/>
     <mergeCell ref="F537:F539"/>
-    <mergeCell ref="D527:D528"/>
-    <mergeCell ref="E527:E528"/>
-    <mergeCell ref="F527:F528"/>
-    <mergeCell ref="D529:D530"/>
-    <mergeCell ref="E529:E530"/>
-    <mergeCell ref="F529:F530"/>
-    <mergeCell ref="D521:D522"/>
-    <mergeCell ref="E521:E522"/>
-    <mergeCell ref="F521:F522"/>
-    <mergeCell ref="D525:D526"/>
-    <mergeCell ref="E525:E526"/>
-    <mergeCell ref="F525:F526"/>
-    <mergeCell ref="D515:D516"/>
-    <mergeCell ref="E515:E516"/>
-    <mergeCell ref="F515:F516"/>
-    <mergeCell ref="D519:D520"/>
-    <mergeCell ref="E519:E520"/>
-    <mergeCell ref="F519:F520"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1" display="Abbreviation of the journal name. We use WoS abbreviations that can be found here: https://images.webofknowledge.com/images/help/WOS/A_abrvjt.html" xr:uid="{6BB52E4D-01E2-44A6-B6CC-352383FA2940}"/>
@@ -39426,6 +39426,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4e0e0d96de7fb32b1678b66c28514d8e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" xmlns:ns3="432dd258-9dce-4cb3-b611-c68c0fbce7f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac451aab8c96dec805c937cbafca7133" ns2:_="" ns3:_="">
     <xsd:import namespace="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
@@ -39626,27 +39646,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0C90B0A-DBBE-4147-B2EE-79946A8DC171}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63F80AE0-5CF8-441A-8E3E-6D76A3390D5E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
+    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC19592A-9F30-4B32-9428-1D9634B8A0D4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -39663,23 +39682,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63F80AE0-5CF8-441A-8E3E-6D76A3390D5E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
-    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0C90B0A-DBBE-4147-B2EE-79946A8DC171}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
+++ b/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Evidence_Hub/02.FOMD/02.metadata_structure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2389" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79BBC8AD-D0EB-4BED-AA14-72235B4CB193}"/>
+  <xr:revisionPtr revIDLastSave="2407" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1018D2B-DBCA-4E68-8AE2-F7F6441933FF}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="870" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{FAB1A633-BA4D-4813-8605-DC3F4755D7C7}"/>
   </bookViews>
@@ -307,7 +307,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6229" uniqueCount="1523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6241" uniqueCount="1525">
   <si>
     <t>Example</t>
   </si>
@@ -10798,6 +10798,12 @@
   </si>
   <si>
     <t>ERA_v16_LM_2026.06.11</t>
+  </si>
+  <si>
+    <t>The control plot (no trees) was coming up blank. It's now labelled "Monoculture", the same idea as the intercropping control. Real practices like Silvopasture and Natural/Bare Fallow were kept.</t>
+  </si>
+  <si>
+    <t>I think we may need to combine the crop and trees section</t>
   </si>
 </sst>
 </file>
@@ -11771,7 +11777,7 @@
     <xf numFmtId="0" fontId="33" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="151">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -12031,6 +12037,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="61" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -15034,7 +15041,9 @@
       <c r="G32" s="126"/>
       <c r="H32" s="126"/>
       <c r="I32" s="126"/>
-      <c r="J32" s="126"/>
+      <c r="J32" s="151" t="s">
+        <v>1524</v>
+      </c>
       <c r="K32" s="16" t="s">
         <v>1056</v>
       </c>
@@ -15073,7 +15082,9 @@
       <c r="G33" s="126"/>
       <c r="H33" s="126"/>
       <c r="I33" s="126"/>
-      <c r="J33" s="126"/>
+      <c r="J33" s="151" t="s">
+        <v>1524</v>
+      </c>
       <c r="K33" s="16" t="s">
         <v>1056</v>
       </c>
@@ -15108,7 +15119,9 @@
       <c r="G34" s="144"/>
       <c r="H34" s="144"/>
       <c r="I34" s="144"/>
-      <c r="J34" s="144"/>
+      <c r="J34" s="151" t="s">
+        <v>1524</v>
+      </c>
       <c r="K34" s="16" t="s">
         <v>1056</v>
       </c>
@@ -15145,7 +15158,9 @@
       <c r="G35" s="126"/>
       <c r="H35" s="126"/>
       <c r="I35" s="126"/>
-      <c r="J35" s="126"/>
+      <c r="J35" s="151" t="s">
+        <v>1524</v>
+      </c>
       <c r="K35" s="16" t="s">
         <v>1056</v>
       </c>
@@ -15184,7 +15199,9 @@
       <c r="G36" s="126"/>
       <c r="H36" s="126"/>
       <c r="I36" s="126"/>
-      <c r="J36" s="126"/>
+      <c r="J36" s="151" t="s">
+        <v>1524</v>
+      </c>
       <c r="K36" s="16" t="s">
         <v>1056</v>
       </c>
@@ -15218,7 +15235,9 @@
       <c r="G37" s="144"/>
       <c r="H37" s="144"/>
       <c r="I37" s="144"/>
-      <c r="J37" s="144"/>
+      <c r="J37" s="151" t="s">
+        <v>1524</v>
+      </c>
       <c r="K37" s="16" t="s">
         <v>1056</v>
       </c>
@@ -15253,7 +15272,9 @@
       <c r="G38" s="126"/>
       <c r="H38" s="126"/>
       <c r="I38" s="126"/>
-      <c r="J38" s="126"/>
+      <c r="J38" s="151" t="s">
+        <v>1524</v>
+      </c>
       <c r="K38" s="34" t="s">
         <v>1252</v>
       </c>
@@ -15286,7 +15307,9 @@
       <c r="G39" s="144"/>
       <c r="H39" s="144"/>
       <c r="I39" s="144"/>
-      <c r="J39" s="144"/>
+      <c r="J39" s="151" t="s">
+        <v>1524</v>
+      </c>
       <c r="K39" s="34" t="s">
         <v>1252</v>
       </c>
@@ -15321,7 +15344,9 @@
       <c r="G40" s="144"/>
       <c r="H40" s="144"/>
       <c r="I40" s="144"/>
-      <c r="J40" s="144"/>
+      <c r="J40" s="151" t="s">
+        <v>1524</v>
+      </c>
       <c r="K40" s="34" t="s">
         <v>1252</v>
       </c>
@@ -15354,7 +15379,9 @@
       <c r="G41" s="144"/>
       <c r="H41" s="144"/>
       <c r="I41" s="144"/>
-      <c r="J41" s="144"/>
+      <c r="J41" s="151" t="s">
+        <v>1524</v>
+      </c>
       <c r="K41" s="34" t="s">
         <v>1252</v>
       </c>
@@ -17628,8 +17655,12 @@
       <c r="H111" s="133" t="s">
         <v>1437</v>
       </c>
-      <c r="I111" s="133"/>
-      <c r="J111" s="133"/>
+      <c r="I111" s="133" t="s">
+        <v>1523</v>
+      </c>
+      <c r="J111" s="126" t="s">
+        <v>983</v>
+      </c>
       <c r="K111" s="134" t="s">
         <v>1350</v>
       </c>

--- a/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
+++ b/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Evidence_Hub/02.FOMD/02.metadata_structure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2552" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9510F41F-DD00-4867-8A5F-2983C5C9FB6E}"/>
+  <xr:revisionPtr revIDLastSave="2589" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2DAD5A2-0003-458B-BE4D-549F5575355A}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="870" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{FAB1A633-BA4D-4813-8605-DC3F4755D7C7}"/>
   </bookViews>
@@ -307,7 +307,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6310" uniqueCount="1555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6328" uniqueCount="1560">
   <si>
     <t>Example</t>
   </si>
@@ -10799,6 +10799,21 @@
   </si>
   <si>
     <t>there crops and trees that appear in the era dataset, but are missing from the ontology. I sent the report</t>
+  </si>
+  <si>
+    <t>Yes, ERA captures this. The practice is in C/T_varietal_animal_subpractice, with values Improved Breeds (2,666 rows), Hybridization or Cross Breeding (3,109), and Unimproved Breed (13,530). The actual breed names are in C/T_animal_breed. There are also 2,183 rows across 33 studies with direct improved-vs-unimproved comparisons (e.g. NN0165 indigenous goat vs Boer; NN0334 Wollo vs Wollo×Awassi cross) — you can pull them by filtering where varietal_animal_subpractice differs between C and T.</t>
+  </si>
+  <si>
+    <t>Could you please complete the C_varietal_animal_subpractice_raw and T_varietal_animal_subpractice_raw columns</t>
+  </si>
+  <si>
+    <t> Could you please move Alley Cropping, Multistrata Agroforestry, and Other Agroforestry — currently entered under C and T intercrop_subpractice — to the corresponding C and T agrof_subpractice columns? (High priority)</t>
+  </si>
+  <si>
+    <t>NOT READY, DECIDE WHICH TYPE OF PRACTICES SHOULD BE IN C AND T</t>
+  </si>
+  <si>
+    <t>FALTA PASAR LOS AGROFORESTRY DE INTERCROPPING A ESTA SECCION</t>
   </si>
 </sst>
 </file>
@@ -12031,13 +12046,13 @@
     <xf numFmtId="0" fontId="29" fillId="57" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="61" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="62" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="62" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -15108,7 +15123,7 @@
       <c r="J32" s="146" t="s">
         <v>1522</v>
       </c>
-      <c r="K32" s="152" t="s">
+      <c r="K32" s="148" t="s">
         <v>1553</v>
       </c>
       <c r="L32" s="146" t="s">
@@ -15155,7 +15170,7 @@
       <c r="J33" s="146" t="s">
         <v>1522</v>
       </c>
-      <c r="K33" s="152" t="s">
+      <c r="K33" s="148" t="s">
         <v>1553</v>
       </c>
       <c r="L33" s="146" t="s">
@@ -15198,7 +15213,7 @@
       <c r="J34" s="146" t="s">
         <v>1522</v>
       </c>
-      <c r="K34" s="152" t="s">
+      <c r="K34" s="148" t="s">
         <v>1553</v>
       </c>
       <c r="L34" s="146" t="s">
@@ -15243,7 +15258,7 @@
       <c r="J35" s="146" t="s">
         <v>1522</v>
       </c>
-      <c r="K35" s="152" t="s">
+      <c r="K35" s="148" t="s">
         <v>1553</v>
       </c>
       <c r="L35" s="146" t="s">
@@ -15290,7 +15305,7 @@
       <c r="J36" s="146" t="s">
         <v>1522</v>
       </c>
-      <c r="K36" s="152" t="s">
+      <c r="K36" s="148" t="s">
         <v>1553</v>
       </c>
       <c r="L36" s="146" t="s">
@@ -15332,7 +15347,7 @@
       <c r="J37" s="146" t="s">
         <v>1522</v>
       </c>
-      <c r="K37" s="152" t="s">
+      <c r="K37" s="148" t="s">
         <v>1553</v>
       </c>
       <c r="L37" s="146" t="s">
@@ -16841,8 +16856,12 @@
       <c r="H80" s="126"/>
       <c r="I80" s="126"/>
       <c r="J80" s="126"/>
-      <c r="K80" s="126"/>
-      <c r="L80" s="126"/>
+      <c r="K80" s="148" t="s">
+        <v>1555</v>
+      </c>
+      <c r="L80" s="133" t="s">
+        <v>1556</v>
+      </c>
       <c r="M80" s="22" t="s">
         <v>1530</v>
       </c>
@@ -16864,8 +16883,9 @@
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
       <c r="J81" s="1"/>
-      <c r="K81" s="1"/>
-      <c r="L81" s="1"/>
+      <c r="K81" s="148" t="s">
+        <v>1555</v>
+      </c>
       <c r="M81" s="22" t="s">
         <v>1530</v>
       </c>
@@ -16893,7 +16913,9 @@
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
-      <c r="K82" s="1"/>
+      <c r="K82" s="148" t="s">
+        <v>1555</v>
+      </c>
       <c r="L82" s="1"/>
       <c r="M82" s="22" t="s">
         <v>1530</v>
@@ -16922,7 +16944,9 @@
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
-      <c r="K83" s="1"/>
+      <c r="K83" s="148" t="s">
+        <v>1555</v>
+      </c>
       <c r="L83" s="1"/>
       <c r="M83" s="22" t="s">
         <v>1530</v>
@@ -16951,8 +16975,12 @@
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
       <c r="J84" s="1"/>
-      <c r="K84" s="1"/>
-      <c r="L84" s="1"/>
+      <c r="K84" s="148" t="s">
+        <v>1555</v>
+      </c>
+      <c r="L84" s="133" t="s">
+        <v>1556</v>
+      </c>
       <c r="M84" s="22" t="s">
         <v>1530</v>
       </c>
@@ -16974,7 +17002,9 @@
       <c r="H85" s="1"/>
       <c r="I85" s="1"/>
       <c r="J85" s="1"/>
-      <c r="K85" s="1"/>
+      <c r="K85" s="148" t="s">
+        <v>1555</v>
+      </c>
       <c r="L85" s="1"/>
       <c r="M85" s="22" t="s">
         <v>1530</v>
@@ -17003,7 +17033,9 @@
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
       <c r="J86" s="1"/>
-      <c r="K86" s="1"/>
+      <c r="K86" s="148" t="s">
+        <v>1555</v>
+      </c>
       <c r="L86" s="1"/>
       <c r="M86" s="22" t="s">
         <v>1530</v>
@@ -17032,7 +17064,9 @@
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
       <c r="J87" s="1"/>
-      <c r="K87" s="1"/>
+      <c r="K87" s="148" t="s">
+        <v>1555</v>
+      </c>
       <c r="L87" s="1"/>
       <c r="M87" s="22" t="s">
         <v>1530</v>
@@ -17962,11 +17996,11 @@
       <c r="I113" s="133" t="s">
         <v>1521</v>
       </c>
-      <c r="J113" s="126" t="s">
-        <v>982</v>
-      </c>
+      <c r="J113" s="126"/>
       <c r="K113" s="126"/>
-      <c r="L113" s="126"/>
+      <c r="L113" s="133" t="s">
+        <v>1557</v>
+      </c>
       <c r="M113" s="134" t="s">
         <v>1349</v>
       </c>
@@ -19842,7 +19876,9 @@
         <v>1526</v>
       </c>
       <c r="K166" s="133"/>
-      <c r="L166" s="133"/>
+      <c r="L166" s="126" t="s">
+        <v>982</v>
+      </c>
       <c r="M166" s="83" t="s">
         <v>907</v>
       </c>
@@ -19883,7 +19919,9 @@
         <v>1526</v>
       </c>
       <c r="K167" s="133"/>
-      <c r="L167" s="133"/>
+      <c r="L167" s="126" t="s">
+        <v>982</v>
+      </c>
       <c r="M167" s="83" t="s">
         <v>907</v>
       </c>
@@ -19992,7 +20030,9 @@
         <v>1526</v>
       </c>
       <c r="K170" s="133"/>
-      <c r="L170" s="133"/>
+      <c r="L170" s="126" t="s">
+        <v>982</v>
+      </c>
       <c r="M170" s="83" t="s">
         <v>907</v>
       </c>
@@ -20033,7 +20073,9 @@
         <v>1526</v>
       </c>
       <c r="K171" s="133"/>
-      <c r="L171" s="133"/>
+      <c r="L171" s="126" t="s">
+        <v>982</v>
+      </c>
       <c r="M171" s="83" t="s">
         <v>907</v>
       </c>
@@ -21078,7 +21120,9 @@
         <v>1526</v>
       </c>
       <c r="K202" s="133"/>
-      <c r="L202" s="133"/>
+      <c r="L202" s="144" t="s">
+        <v>1523</v>
+      </c>
       <c r="M202" s="83" t="s">
         <v>933</v>
       </c>
@@ -21114,7 +21158,9 @@
         <v>1526</v>
       </c>
       <c r="K203" s="133"/>
-      <c r="L203" s="133"/>
+      <c r="L203" s="144" t="s">
+        <v>1523</v>
+      </c>
       <c r="M203" s="83" t="s">
         <v>933</v>
       </c>
@@ -30514,13 +30560,13 @@
       <c r="K542" s="12"/>
       <c r="L542" s="12"/>
       <c r="M542" s="12"/>
-      <c r="N542" s="148" t="s">
+      <c r="N542" s="149" t="s">
         <v>35</v>
       </c>
-      <c r="O542" s="149" t="s">
-        <v>4</v>
-      </c>
-      <c r="P542" s="150" t="s">
+      <c r="O542" s="150" t="s">
+        <v>4</v>
+      </c>
+      <c r="P542" s="151" t="s">
         <v>36</v>
       </c>
       <c r="Q542" s="3" t="s">
@@ -30541,9 +30587,9 @@
       <c r="K543" s="12"/>
       <c r="L543" s="12"/>
       <c r="M543" s="12"/>
-      <c r="N543" s="148"/>
-      <c r="O543" s="149"/>
-      <c r="P543" s="150"/>
+      <c r="N543" s="149"/>
+      <c r="O543" s="150"/>
+      <c r="P543" s="151"/>
       <c r="Q543" s="3" t="s">
         <v>38</v>
       </c>
@@ -30589,13 +30635,13 @@
       <c r="K546" s="1"/>
       <c r="L546" s="1"/>
       <c r="M546" s="1"/>
-      <c r="N546" s="151" t="s">
+      <c r="N546" s="152" t="s">
         <v>42</v>
       </c>
-      <c r="O546" s="149" t="s">
-        <v>4</v>
-      </c>
-      <c r="P546" s="150" t="s">
+      <c r="O546" s="150" t="s">
+        <v>4</v>
+      </c>
+      <c r="P546" s="151" t="s">
         <v>43</v>
       </c>
       <c r="Q546" s="3">
@@ -30616,9 +30662,9 @@
       <c r="K547" s="1"/>
       <c r="L547" s="1"/>
       <c r="M547" s="1"/>
-      <c r="N547" s="151"/>
-      <c r="O547" s="149"/>
-      <c r="P547" s="150"/>
+      <c r="N547" s="152"/>
+      <c r="O547" s="150"/>
+      <c r="P547" s="151"/>
       <c r="Q547" s="3" t="s">
         <v>44</v>
       </c>
@@ -30637,13 +30683,13 @@
       <c r="K548" s="12"/>
       <c r="L548" s="12"/>
       <c r="M548" s="12"/>
-      <c r="N548" s="148" t="s">
+      <c r="N548" s="149" t="s">
         <v>45</v>
       </c>
-      <c r="O548" s="149" t="s">
-        <v>4</v>
-      </c>
-      <c r="P548" s="150" t="s">
+      <c r="O548" s="150" t="s">
+        <v>4</v>
+      </c>
+      <c r="P548" s="151" t="s">
         <v>46</v>
       </c>
       <c r="Q548" s="3" t="s">
@@ -30664,9 +30710,9 @@
       <c r="K549" s="12"/>
       <c r="L549" s="12"/>
       <c r="M549" s="12"/>
-      <c r="N549" s="148"/>
-      <c r="O549" s="149"/>
-      <c r="P549" s="150"/>
+      <c r="N549" s="149"/>
+      <c r="O549" s="150"/>
+      <c r="P549" s="151"/>
       <c r="Q549" s="3" t="s">
         <v>48</v>
       </c>
@@ -30712,13 +30758,13 @@
       <c r="K552" s="1"/>
       <c r="L552" s="1"/>
       <c r="M552" s="1"/>
-      <c r="N552" s="151" t="s">
+      <c r="N552" s="152" t="s">
         <v>52</v>
       </c>
-      <c r="O552" s="149" t="s">
+      <c r="O552" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="P552" s="150" t="s">
+      <c r="P552" s="151" t="s">
         <v>53</v>
       </c>
       <c r="Q552" s="3">
@@ -30739,9 +30785,9 @@
       <c r="K553" s="1"/>
       <c r="L553" s="1"/>
       <c r="M553" s="1"/>
-      <c r="N553" s="151"/>
-      <c r="O553" s="149"/>
-      <c r="P553" s="150"/>
+      <c r="N553" s="152"/>
+      <c r="O553" s="150"/>
+      <c r="P553" s="151"/>
       <c r="Q553" s="3" t="s">
         <v>44</v>
       </c>
@@ -30760,13 +30806,13 @@
       <c r="K554" s="1"/>
       <c r="L554" s="1"/>
       <c r="M554" s="1"/>
-      <c r="N554" s="148" t="s">
+      <c r="N554" s="149" t="s">
         <v>54</v>
       </c>
-      <c r="O554" s="149" t="s">
-        <v>4</v>
-      </c>
-      <c r="P554" s="150" t="s">
+      <c r="O554" s="150" t="s">
+        <v>4</v>
+      </c>
+      <c r="P554" s="151" t="s">
         <v>55</v>
       </c>
       <c r="Q554" s="3" t="s">
@@ -30787,9 +30833,9 @@
       <c r="K555" s="1"/>
       <c r="L555" s="1"/>
       <c r="M555" s="1"/>
-      <c r="N555" s="148"/>
-      <c r="O555" s="149"/>
-      <c r="P555" s="150"/>
+      <c r="N555" s="149"/>
+      <c r="O555" s="150"/>
+      <c r="P555" s="151"/>
       <c r="Q555" s="3" t="s">
         <v>57</v>
       </c>
@@ -30808,13 +30854,13 @@
       <c r="K556" s="1"/>
       <c r="L556" s="1"/>
       <c r="M556" s="1"/>
-      <c r="N556" s="148" t="s">
+      <c r="N556" s="149" t="s">
         <v>58</v>
       </c>
-      <c r="O556" s="149" t="s">
-        <v>4</v>
-      </c>
-      <c r="P556" s="150" t="s">
+      <c r="O556" s="150" t="s">
+        <v>4</v>
+      </c>
+      <c r="P556" s="151" t="s">
         <v>59</v>
       </c>
       <c r="Q556" s="3" t="s">
@@ -30835,9 +30881,9 @@
       <c r="K557" s="1"/>
       <c r="L557" s="1"/>
       <c r="M557" s="1"/>
-      <c r="N557" s="148"/>
-      <c r="O557" s="149"/>
-      <c r="P557" s="150"/>
+      <c r="N557" s="149"/>
+      <c r="O557" s="150"/>
+      <c r="P557" s="151"/>
       <c r="Q557" s="3" t="s">
         <v>61</v>
       </c>
@@ -30856,13 +30902,13 @@
       <c r="K558" s="1"/>
       <c r="L558" s="1"/>
       <c r="M558" s="1"/>
-      <c r="N558" s="148" t="s">
+      <c r="N558" s="149" t="s">
         <v>62</v>
       </c>
-      <c r="O558" s="149" t="s">
-        <v>4</v>
-      </c>
-      <c r="P558" s="150" t="s">
+      <c r="O558" s="150" t="s">
+        <v>4</v>
+      </c>
+      <c r="P558" s="151" t="s">
         <v>63</v>
       </c>
       <c r="Q558" s="3" t="s">
@@ -30883,9 +30929,9 @@
       <c r="K559" s="1"/>
       <c r="L559" s="1"/>
       <c r="M559" s="1"/>
-      <c r="N559" s="148"/>
-      <c r="O559" s="149"/>
-      <c r="P559" s="150"/>
+      <c r="N559" s="149"/>
+      <c r="O559" s="150"/>
+      <c r="P559" s="151"/>
       <c r="Q559" s="3" t="s">
         <v>65</v>
       </c>
@@ -31010,13 +31056,13 @@
       <c r="K564" s="1"/>
       <c r="L564" s="1"/>
       <c r="M564" s="1"/>
-      <c r="N564" s="151" t="s">
+      <c r="N564" s="152" t="s">
         <v>86</v>
       </c>
-      <c r="O564" s="149" t="s">
-        <v>4</v>
-      </c>
-      <c r="P564" s="150" t="s">
+      <c r="O564" s="150" t="s">
+        <v>4</v>
+      </c>
+      <c r="P564" s="151" t="s">
         <v>87</v>
       </c>
       <c r="Q564" s="3" t="s">
@@ -31037,9 +31083,9 @@
       <c r="K565" s="1"/>
       <c r="L565" s="1"/>
       <c r="M565" s="1"/>
-      <c r="N565" s="151"/>
-      <c r="O565" s="149"/>
-      <c r="P565" s="150"/>
+      <c r="N565" s="152"/>
+      <c r="O565" s="150"/>
+      <c r="P565" s="151"/>
       <c r="Q565" s="3" t="s">
         <v>89</v>
       </c>
@@ -31058,9 +31104,9 @@
       <c r="K566" s="1"/>
       <c r="L566" s="1"/>
       <c r="M566" s="1"/>
-      <c r="N566" s="151"/>
-      <c r="O566" s="149"/>
-      <c r="P566" s="150"/>
+      <c r="N566" s="152"/>
+      <c r="O566" s="150"/>
+      <c r="P566" s="151"/>
       <c r="Q566" s="3" t="s">
         <v>90</v>
       </c>
@@ -31079,13 +31125,13 @@
       <c r="K567" s="1"/>
       <c r="L567" s="1"/>
       <c r="M567" s="1"/>
-      <c r="N567" s="151" t="s">
+      <c r="N567" s="152" t="s">
         <v>91</v>
       </c>
-      <c r="O567" s="149" t="s">
-        <v>4</v>
-      </c>
-      <c r="P567" s="150" t="s">
+      <c r="O567" s="150" t="s">
+        <v>4</v>
+      </c>
+      <c r="P567" s="151" t="s">
         <v>92</v>
       </c>
       <c r="Q567" s="3" t="s">
@@ -31106,9 +31152,9 @@
       <c r="K568" s="1"/>
       <c r="L568" s="1"/>
       <c r="M568" s="1"/>
-      <c r="N568" s="151"/>
-      <c r="O568" s="149"/>
-      <c r="P568" s="150"/>
+      <c r="N568" s="152"/>
+      <c r="O568" s="150"/>
+      <c r="P568" s="151"/>
       <c r="Q568" s="3" t="s">
         <v>89</v>
       </c>
@@ -31127,9 +31173,9 @@
       <c r="K569" s="1"/>
       <c r="L569" s="1"/>
       <c r="M569" s="1"/>
-      <c r="N569" s="151"/>
-      <c r="O569" s="149"/>
-      <c r="P569" s="150"/>
+      <c r="N569" s="152"/>
+      <c r="O569" s="150"/>
+      <c r="P569" s="151"/>
       <c r="Q569" s="3" t="s">
         <v>90</v>
       </c>
@@ -31865,24 +31911,6 @@
   </sheetData>
   <autoFilter ref="A1:R319" xr:uid="{82619C4B-D6B1-486E-87C6-D2252668E253}"/>
   <mergeCells count="27">
-    <mergeCell ref="N542:N543"/>
-    <mergeCell ref="O542:O543"/>
-    <mergeCell ref="P542:P543"/>
-    <mergeCell ref="N546:N547"/>
-    <mergeCell ref="O546:O547"/>
-    <mergeCell ref="P546:P547"/>
-    <mergeCell ref="N556:N557"/>
-    <mergeCell ref="O556:O557"/>
-    <mergeCell ref="P556:P557"/>
-    <mergeCell ref="N558:N559"/>
-    <mergeCell ref="O558:O559"/>
-    <mergeCell ref="P558:P559"/>
-    <mergeCell ref="N564:N566"/>
-    <mergeCell ref="O564:O566"/>
-    <mergeCell ref="P564:P566"/>
-    <mergeCell ref="N567:N569"/>
-    <mergeCell ref="O567:O569"/>
-    <mergeCell ref="P567:P569"/>
     <mergeCell ref="N554:N555"/>
     <mergeCell ref="O554:O555"/>
     <mergeCell ref="P554:P555"/>
@@ -31892,6 +31920,24 @@
     <mergeCell ref="O552:O553"/>
     <mergeCell ref="P552:P553"/>
     <mergeCell ref="N548:N549"/>
+    <mergeCell ref="N564:N566"/>
+    <mergeCell ref="O564:O566"/>
+    <mergeCell ref="P564:P566"/>
+    <mergeCell ref="N567:N569"/>
+    <mergeCell ref="O567:O569"/>
+    <mergeCell ref="P567:P569"/>
+    <mergeCell ref="N556:N557"/>
+    <mergeCell ref="O556:O557"/>
+    <mergeCell ref="P556:P557"/>
+    <mergeCell ref="N558:N559"/>
+    <mergeCell ref="O558:O559"/>
+    <mergeCell ref="P558:P559"/>
+    <mergeCell ref="N542:N543"/>
+    <mergeCell ref="O542:O543"/>
+    <mergeCell ref="P542:P543"/>
+    <mergeCell ref="N546:N547"/>
+    <mergeCell ref="O546:O547"/>
+    <mergeCell ref="P546:P547"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="P7" r:id="rId1" display="Abbreviation of the journal name. We use WoS abbreviations that can be found here: https://images.webofknowledge.com/images/help/WOS/A_abrvjt.html" xr:uid="{B4DADD6B-F846-45B3-933B-5F25CC9FEF24}"/>
@@ -33340,7 +33386,7 @@
       <c r="A69" s="60" t="s">
         <v>982</v>
       </c>
-      <c r="B69" s="126" t="s">
+      <c r="B69" s="144" t="s">
         <v>982</v>
       </c>
       <c r="C69" s="34" t="s">
@@ -33357,8 +33403,8 @@
       <c r="A70" s="60" t="s">
         <v>982</v>
       </c>
-      <c r="B70" s="126" t="s">
-        <v>982</v>
+      <c r="B70" s="24" t="s">
+        <v>1558</v>
       </c>
       <c r="C70" s="34" t="s">
         <v>877</v>
@@ -33377,7 +33423,7 @@
       <c r="A71" s="60" t="s">
         <v>982</v>
       </c>
-      <c r="B71" s="126" t="s">
+      <c r="B71" s="144" t="s">
         <v>982</v>
       </c>
       <c r="C71" s="34" t="s">
@@ -33398,7 +33444,7 @@
       <c r="A72" s="60" t="s">
         <v>982</v>
       </c>
-      <c r="B72" s="126" t="s">
+      <c r="B72" s="144" t="s">
         <v>982</v>
       </c>
       <c r="C72" s="34" t="s">
@@ -33421,7 +33467,7 @@
       <c r="A73" s="60" t="s">
         <v>982</v>
       </c>
-      <c r="B73" s="126" t="s">
+      <c r="B73" s="144" t="s">
         <v>982</v>
       </c>
       <c r="C73" s="34" t="s">
@@ -33442,7 +33488,7 @@
       <c r="A74" s="60" t="s">
         <v>982</v>
       </c>
-      <c r="B74" s="126" t="s">
+      <c r="B74" s="144" t="s">
         <v>982</v>
       </c>
       <c r="C74" s="34" t="s">
@@ -33459,8 +33505,8 @@
       <c r="A75" s="60" t="s">
         <v>982</v>
       </c>
-      <c r="B75" s="126" t="s">
-        <v>982</v>
+      <c r="B75" s="24" t="s">
+        <v>1558</v>
       </c>
       <c r="C75" s="34" t="s">
         <v>877</v>
@@ -33482,7 +33528,7 @@
       <c r="A76" s="60" t="s">
         <v>982</v>
       </c>
-      <c r="B76" s="126" t="s">
+      <c r="B76" s="144" t="s">
         <v>982</v>
       </c>
       <c r="C76" s="34" t="s">
@@ -33505,7 +33551,7 @@
       <c r="A77" s="60" t="s">
         <v>982</v>
       </c>
-      <c r="B77" s="126" t="s">
+      <c r="B77" s="144" t="s">
         <v>982</v>
       </c>
       <c r="C77" s="34" t="s">
@@ -33528,7 +33574,7 @@
       <c r="A78" s="60" t="s">
         <v>982</v>
       </c>
-      <c r="B78" s="126" t="s">
+      <c r="B78" s="144" t="s">
         <v>982</v>
       </c>
       <c r="C78" s="34" t="s">
@@ -33589,8 +33635,8 @@
       <c r="A81" s="60" t="s">
         <v>982</v>
       </c>
-      <c r="B81" s="126" t="s">
-        <v>982</v>
+      <c r="B81" s="24" t="s">
+        <v>1558</v>
       </c>
       <c r="C81" s="81" t="s">
         <v>876</v>
@@ -33694,8 +33740,8 @@
       <c r="A86" s="60" t="s">
         <v>982</v>
       </c>
-      <c r="B86" s="126" t="s">
-        <v>982</v>
+      <c r="B86" s="24" t="s">
+        <v>1558</v>
       </c>
       <c r="C86" s="81" t="s">
         <v>876</v>
@@ -33774,7 +33820,9 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="1"/>
-      <c r="B90" s="1"/>
+      <c r="B90" s="24" t="s">
+        <v>1558</v>
+      </c>
       <c r="C90" s="1"/>
       <c r="D90" s="22" t="s">
         <v>214</v>
@@ -33825,7 +33873,9 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="1"/>
-      <c r="B93" s="1"/>
+      <c r="B93" s="24" t="s">
+        <v>1558</v>
+      </c>
       <c r="C93" s="1"/>
       <c r="D93" s="22" t="s">
         <v>211</v>
@@ -34392,7 +34442,7 @@
         <v>982</v>
       </c>
       <c r="B120" s="133" t="s">
-        <v>1436</v>
+        <v>1559</v>
       </c>
       <c r="C120" s="24" t="s">
         <v>1349</v>
@@ -34501,8 +34551,8 @@
       <c r="A125" s="60" t="s">
         <v>982</v>
       </c>
-      <c r="B125" s="126" t="s">
-        <v>982</v>
+      <c r="B125" s="133" t="s">
+        <v>1559</v>
       </c>
       <c r="C125" s="24" t="s">
         <v>1349</v>
@@ -35304,8 +35354,8 @@
       <c r="A161" s="60" t="s">
         <v>982</v>
       </c>
-      <c r="B161" s="60" t="s">
-        <v>1462</v>
+      <c r="B161" s="126" t="s">
+        <v>982</v>
       </c>
       <c r="C161" s="83" t="s">
         <v>907</v>
@@ -35370,8 +35420,8 @@
       <c r="A164" s="60" t="s">
         <v>982</v>
       </c>
-      <c r="B164" s="60" t="s">
-        <v>1462</v>
+      <c r="B164" s="126" t="s">
+        <v>982</v>
       </c>
       <c r="C164" s="83" t="s">
         <v>907</v>
@@ -41106,13 +41156,13 @@
       <c r="A511" s="12"/>
       <c r="B511" s="12"/>
       <c r="C511" s="12"/>
-      <c r="D511" s="148" t="s">
+      <c r="D511" s="149" t="s">
         <v>35</v>
       </c>
-      <c r="E511" s="149" t="s">
-        <v>4</v>
-      </c>
-      <c r="F511" s="150" t="s">
+      <c r="E511" s="150" t="s">
+        <v>4</v>
+      </c>
+      <c r="F511" s="151" t="s">
         <v>36</v>
       </c>
       <c r="G511" s="3" t="s">
@@ -41123,9 +41173,9 @@
       <c r="A512" s="12"/>
       <c r="B512" s="12"/>
       <c r="C512" s="12"/>
-      <c r="D512" s="148"/>
-      <c r="E512" s="149"/>
-      <c r="F512" s="150"/>
+      <c r="D512" s="149"/>
+      <c r="E512" s="150"/>
+      <c r="F512" s="151"/>
       <c r="G512" s="3" t="s">
         <v>38</v>
       </c>
@@ -41151,13 +41201,13 @@
       <c r="A515" s="1"/>
       <c r="B515" s="1"/>
       <c r="C515" s="1"/>
-      <c r="D515" s="151" t="s">
+      <c r="D515" s="152" t="s">
         <v>42</v>
       </c>
-      <c r="E515" s="149" t="s">
-        <v>4</v>
-      </c>
-      <c r="F515" s="150" t="s">
+      <c r="E515" s="150" t="s">
+        <v>4</v>
+      </c>
+      <c r="F515" s="151" t="s">
         <v>43</v>
       </c>
       <c r="G515" s="3">
@@ -41168,9 +41218,9 @@
       <c r="A516" s="1"/>
       <c r="B516" s="1"/>
       <c r="C516" s="1"/>
-      <c r="D516" s="151"/>
-      <c r="E516" s="149"/>
-      <c r="F516" s="150"/>
+      <c r="D516" s="152"/>
+      <c r="E516" s="150"/>
+      <c r="F516" s="151"/>
       <c r="G516" s="3" t="s">
         <v>44</v>
       </c>
@@ -41179,13 +41229,13 @@
       <c r="A517" s="12"/>
       <c r="B517" s="12"/>
       <c r="C517" s="12"/>
-      <c r="D517" s="148" t="s">
+      <c r="D517" s="149" t="s">
         <v>45</v>
       </c>
-      <c r="E517" s="149" t="s">
-        <v>4</v>
-      </c>
-      <c r="F517" s="150" t="s">
+      <c r="E517" s="150" t="s">
+        <v>4</v>
+      </c>
+      <c r="F517" s="151" t="s">
         <v>46</v>
       </c>
       <c r="G517" s="3" t="s">
@@ -41196,9 +41246,9 @@
       <c r="A518" s="12"/>
       <c r="B518" s="12"/>
       <c r="C518" s="12"/>
-      <c r="D518" s="148"/>
-      <c r="E518" s="149"/>
-      <c r="F518" s="150"/>
+      <c r="D518" s="149"/>
+      <c r="E518" s="150"/>
+      <c r="F518" s="151"/>
       <c r="G518" s="3" t="s">
         <v>48</v>
       </c>
@@ -41224,13 +41274,13 @@
       <c r="A521" s="1"/>
       <c r="B521" s="1"/>
       <c r="C521" s="1"/>
-      <c r="D521" s="151" t="s">
+      <c r="D521" s="152" t="s">
         <v>52</v>
       </c>
-      <c r="E521" s="149" t="s">
+      <c r="E521" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="F521" s="150" t="s">
+      <c r="F521" s="151" t="s">
         <v>53</v>
       </c>
       <c r="G521" s="3">
@@ -41241,9 +41291,9 @@
       <c r="A522" s="1"/>
       <c r="B522" s="1"/>
       <c r="C522" s="1"/>
-      <c r="D522" s="151"/>
-      <c r="E522" s="149"/>
-      <c r="F522" s="150"/>
+      <c r="D522" s="152"/>
+      <c r="E522" s="150"/>
+      <c r="F522" s="151"/>
       <c r="G522" s="3" t="s">
         <v>44</v>
       </c>
@@ -41252,13 +41302,13 @@
       <c r="A523" s="1"/>
       <c r="B523" s="1"/>
       <c r="C523" s="1"/>
-      <c r="D523" s="148" t="s">
+      <c r="D523" s="149" t="s">
         <v>54</v>
       </c>
-      <c r="E523" s="149" t="s">
-        <v>4</v>
-      </c>
-      <c r="F523" s="150" t="s">
+      <c r="E523" s="150" t="s">
+        <v>4</v>
+      </c>
+      <c r="F523" s="151" t="s">
         <v>55</v>
       </c>
       <c r="G523" s="3" t="s">
@@ -41269,9 +41319,9 @@
       <c r="A524" s="1"/>
       <c r="B524" s="1"/>
       <c r="C524" s="1"/>
-      <c r="D524" s="148"/>
-      <c r="E524" s="149"/>
-      <c r="F524" s="150"/>
+      <c r="D524" s="149"/>
+      <c r="E524" s="150"/>
+      <c r="F524" s="151"/>
       <c r="G524" s="3" t="s">
         <v>57</v>
       </c>
@@ -41280,13 +41330,13 @@
       <c r="A525" s="1"/>
       <c r="B525" s="1"/>
       <c r="C525" s="1"/>
-      <c r="D525" s="148" t="s">
+      <c r="D525" s="149" t="s">
         <v>58</v>
       </c>
-      <c r="E525" s="149" t="s">
-        <v>4</v>
-      </c>
-      <c r="F525" s="150" t="s">
+      <c r="E525" s="150" t="s">
+        <v>4</v>
+      </c>
+      <c r="F525" s="151" t="s">
         <v>59</v>
       </c>
       <c r="G525" s="3" t="s">
@@ -41297,9 +41347,9 @@
       <c r="A526" s="1"/>
       <c r="B526" s="1"/>
       <c r="C526" s="1"/>
-      <c r="D526" s="148"/>
-      <c r="E526" s="149"/>
-      <c r="F526" s="150"/>
+      <c r="D526" s="149"/>
+      <c r="E526" s="150"/>
+      <c r="F526" s="151"/>
       <c r="G526" s="3" t="s">
         <v>61</v>
       </c>
@@ -41308,13 +41358,13 @@
       <c r="A527" s="1"/>
       <c r="B527" s="1"/>
       <c r="C527" s="1"/>
-      <c r="D527" s="148" t="s">
+      <c r="D527" s="149" t="s">
         <v>62</v>
       </c>
-      <c r="E527" s="149" t="s">
-        <v>4</v>
-      </c>
-      <c r="F527" s="150" t="s">
+      <c r="E527" s="150" t="s">
+        <v>4</v>
+      </c>
+      <c r="F527" s="151" t="s">
         <v>63</v>
       </c>
       <c r="G527" s="3" t="s">
@@ -41325,9 +41375,9 @@
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="1"/>
-      <c r="D528" s="148"/>
-      <c r="E528" s="149"/>
-      <c r="F528" s="150"/>
+      <c r="D528" s="149"/>
+      <c r="E528" s="150"/>
+      <c r="F528" s="151"/>
       <c r="G528" s="3" t="s">
         <v>65</v>
       </c>
@@ -41402,13 +41452,13 @@
       <c r="A533" s="1"/>
       <c r="B533" s="1"/>
       <c r="C533" s="1"/>
-      <c r="D533" s="151" t="s">
+      <c r="D533" s="152" t="s">
         <v>86</v>
       </c>
-      <c r="E533" s="149" t="s">
-        <v>4</v>
-      </c>
-      <c r="F533" s="150" t="s">
+      <c r="E533" s="150" t="s">
+        <v>4</v>
+      </c>
+      <c r="F533" s="151" t="s">
         <v>87</v>
       </c>
       <c r="G533" s="3" t="s">
@@ -41419,9 +41469,9 @@
       <c r="A534" s="1"/>
       <c r="B534" s="1"/>
       <c r="C534" s="1"/>
-      <c r="D534" s="151"/>
-      <c r="E534" s="149"/>
-      <c r="F534" s="150"/>
+      <c r="D534" s="152"/>
+      <c r="E534" s="150"/>
+      <c r="F534" s="151"/>
       <c r="G534" s="3" t="s">
         <v>89</v>
       </c>
@@ -41430,9 +41480,9 @@
       <c r="A535" s="1"/>
       <c r="B535" s="1"/>
       <c r="C535" s="1"/>
-      <c r="D535" s="151"/>
-      <c r="E535" s="149"/>
-      <c r="F535" s="150"/>
+      <c r="D535" s="152"/>
+      <c r="E535" s="150"/>
+      <c r="F535" s="151"/>
       <c r="G535" s="3" t="s">
         <v>90</v>
       </c>
@@ -41441,13 +41491,13 @@
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
       <c r="C536" s="1"/>
-      <c r="D536" s="151" t="s">
+      <c r="D536" s="152" t="s">
         <v>91</v>
       </c>
-      <c r="E536" s="149" t="s">
-        <v>4</v>
-      </c>
-      <c r="F536" s="150" t="s">
+      <c r="E536" s="150" t="s">
+        <v>4</v>
+      </c>
+      <c r="F536" s="151" t="s">
         <v>92</v>
       </c>
       <c r="G536" s="3" t="s">
@@ -41458,9 +41508,9 @@
       <c r="A537" s="1"/>
       <c r="B537" s="1"/>
       <c r="C537" s="1"/>
-      <c r="D537" s="151"/>
-      <c r="E537" s="149"/>
-      <c r="F537" s="150"/>
+      <c r="D537" s="152"/>
+      <c r="E537" s="150"/>
+      <c r="F537" s="151"/>
       <c r="G537" s="3" t="s">
         <v>89</v>
       </c>
@@ -41469,9 +41519,9 @@
       <c r="A538" s="1"/>
       <c r="B538" s="1"/>
       <c r="C538" s="1"/>
-      <c r="D538" s="151"/>
-      <c r="E538" s="149"/>
-      <c r="F538" s="150"/>
+      <c r="D538" s="152"/>
+      <c r="E538" s="150"/>
+      <c r="F538" s="151"/>
       <c r="G538" s="3" t="s">
         <v>90</v>
       </c>
@@ -41896,6 +41946,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D511:D512"/>
+    <mergeCell ref="E511:E512"/>
+    <mergeCell ref="F511:F512"/>
+    <mergeCell ref="D515:D516"/>
+    <mergeCell ref="E515:E516"/>
+    <mergeCell ref="F515:F516"/>
+    <mergeCell ref="D517:D518"/>
+    <mergeCell ref="E517:E518"/>
+    <mergeCell ref="F517:F518"/>
+    <mergeCell ref="D521:D522"/>
+    <mergeCell ref="E521:E522"/>
+    <mergeCell ref="F521:F522"/>
+    <mergeCell ref="D523:D524"/>
+    <mergeCell ref="E523:E524"/>
+    <mergeCell ref="F523:F524"/>
+    <mergeCell ref="D525:D526"/>
+    <mergeCell ref="E525:E526"/>
+    <mergeCell ref="F525:F526"/>
     <mergeCell ref="D536:D538"/>
     <mergeCell ref="E536:E538"/>
     <mergeCell ref="F536:F538"/>
@@ -41905,24 +41973,6 @@
     <mergeCell ref="D533:D535"/>
     <mergeCell ref="E533:E535"/>
     <mergeCell ref="F533:F535"/>
-    <mergeCell ref="D523:D524"/>
-    <mergeCell ref="E523:E524"/>
-    <mergeCell ref="F523:F524"/>
-    <mergeCell ref="D525:D526"/>
-    <mergeCell ref="E525:E526"/>
-    <mergeCell ref="F525:F526"/>
-    <mergeCell ref="D517:D518"/>
-    <mergeCell ref="E517:E518"/>
-    <mergeCell ref="F517:F518"/>
-    <mergeCell ref="D521:D522"/>
-    <mergeCell ref="E521:E522"/>
-    <mergeCell ref="F521:F522"/>
-    <mergeCell ref="D511:D512"/>
-    <mergeCell ref="E511:E512"/>
-    <mergeCell ref="F511:F512"/>
-    <mergeCell ref="D515:D516"/>
-    <mergeCell ref="E515:E516"/>
-    <mergeCell ref="F515:F516"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1" display="Abbreviation of the journal name. We use WoS abbreviations that can be found here: https://images.webofknowledge.com/images/help/WOS/A_abrvjt.html" xr:uid="{6BB52E4D-01E2-44A6-B6CC-352383FA2940}"/>
@@ -41934,6 +41984,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4e0e0d96de7fb32b1678b66c28514d8e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" xmlns:ns3="432dd258-9dce-4cb3-b611-c68c0fbce7f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac451aab8c96dec805c937cbafca7133" ns2:_="" ns3:_="">
     <xsd:import namespace="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
@@ -42134,27 +42204,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0C90B0A-DBBE-4147-B2EE-79946A8DC171}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63F80AE0-5CF8-441A-8E3E-6D76A3390D5E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
+    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC19592A-9F30-4B32-9428-1D9634B8A0D4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -42171,23 +42240,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63F80AE0-5CF8-441A-8E3E-6D76A3390D5E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
-    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0C90B0A-DBBE-4147-B2EE-79946A8DC171}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
+++ b/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="2653" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35766F49-0185-46C4-91F3-6F1C6193772B}"/>
   <bookViews>
-    <workbookView xWindow="57490" yWindow="-110" windowWidth="29020" windowHeight="15700" activeTab="1" xr2:uid="{FAB1A633-BA4D-4813-8605-DC3F4755D7C7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{FAB1A633-BA4D-4813-8605-DC3F4755D7C7}"/>
   </bookViews>
   <sheets>
     <sheet name="10_FOMD_metadata_synthesis" sheetId="1" r:id="rId1"/>
@@ -32535,6 +32535,24 @@
   </sheetData>
   <autoFilter ref="A1:S319" xr:uid="{82619C4B-D6B1-486E-87C6-D2252668E253}"/>
   <mergeCells count="27">
+    <mergeCell ref="O542:O543"/>
+    <mergeCell ref="P542:P543"/>
+    <mergeCell ref="Q542:Q543"/>
+    <mergeCell ref="O546:O547"/>
+    <mergeCell ref="P546:P547"/>
+    <mergeCell ref="Q546:Q547"/>
+    <mergeCell ref="O556:O557"/>
+    <mergeCell ref="P556:P557"/>
+    <mergeCell ref="Q556:Q557"/>
+    <mergeCell ref="O558:O559"/>
+    <mergeCell ref="P558:P559"/>
+    <mergeCell ref="Q558:Q559"/>
+    <mergeCell ref="O564:O566"/>
+    <mergeCell ref="P564:P566"/>
+    <mergeCell ref="Q564:Q566"/>
+    <mergeCell ref="O567:O569"/>
+    <mergeCell ref="P567:P569"/>
+    <mergeCell ref="Q567:Q569"/>
     <mergeCell ref="O554:O555"/>
     <mergeCell ref="P554:P555"/>
     <mergeCell ref="Q554:Q555"/>
@@ -32544,24 +32562,6 @@
     <mergeCell ref="P552:P553"/>
     <mergeCell ref="Q552:Q553"/>
     <mergeCell ref="O548:O549"/>
-    <mergeCell ref="O564:O566"/>
-    <mergeCell ref="P564:P566"/>
-    <mergeCell ref="Q564:Q566"/>
-    <mergeCell ref="O567:O569"/>
-    <mergeCell ref="P567:P569"/>
-    <mergeCell ref="Q567:Q569"/>
-    <mergeCell ref="O556:O557"/>
-    <mergeCell ref="P556:P557"/>
-    <mergeCell ref="Q556:Q557"/>
-    <mergeCell ref="O558:O559"/>
-    <mergeCell ref="P558:P559"/>
-    <mergeCell ref="Q558:Q559"/>
-    <mergeCell ref="O542:O543"/>
-    <mergeCell ref="P542:P543"/>
-    <mergeCell ref="Q542:Q543"/>
-    <mergeCell ref="O546:O547"/>
-    <mergeCell ref="P546:P547"/>
-    <mergeCell ref="Q546:Q547"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="Q7" r:id="rId1" display="Abbreviation of the journal name. We use WoS abbreviations that can be found here: https://images.webofknowledge.com/images/help/WOS/A_abrvjt.html" xr:uid="{B4DADD6B-F846-45B3-933B-5F25CC9FEF24}"/>
@@ -42570,24 +42570,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D511:D512"/>
-    <mergeCell ref="E511:E512"/>
-    <mergeCell ref="F511:F512"/>
-    <mergeCell ref="D515:D516"/>
-    <mergeCell ref="E515:E516"/>
-    <mergeCell ref="F515:F516"/>
-    <mergeCell ref="D517:D518"/>
-    <mergeCell ref="E517:E518"/>
-    <mergeCell ref="F517:F518"/>
-    <mergeCell ref="D521:D522"/>
-    <mergeCell ref="E521:E522"/>
-    <mergeCell ref="F521:F522"/>
-    <mergeCell ref="D523:D524"/>
-    <mergeCell ref="E523:E524"/>
-    <mergeCell ref="F523:F524"/>
-    <mergeCell ref="D525:D526"/>
-    <mergeCell ref="E525:E526"/>
-    <mergeCell ref="F525:F526"/>
     <mergeCell ref="D536:D538"/>
     <mergeCell ref="E536:E538"/>
     <mergeCell ref="F536:F538"/>
@@ -42597,6 +42579,24 @@
     <mergeCell ref="D533:D535"/>
     <mergeCell ref="E533:E535"/>
     <mergeCell ref="F533:F535"/>
+    <mergeCell ref="D523:D524"/>
+    <mergeCell ref="E523:E524"/>
+    <mergeCell ref="F523:F524"/>
+    <mergeCell ref="D525:D526"/>
+    <mergeCell ref="E525:E526"/>
+    <mergeCell ref="F525:F526"/>
+    <mergeCell ref="D517:D518"/>
+    <mergeCell ref="E517:E518"/>
+    <mergeCell ref="F517:F518"/>
+    <mergeCell ref="D521:D522"/>
+    <mergeCell ref="E521:E522"/>
+    <mergeCell ref="F521:F522"/>
+    <mergeCell ref="D511:D512"/>
+    <mergeCell ref="E511:E512"/>
+    <mergeCell ref="F511:F512"/>
+    <mergeCell ref="D515:D516"/>
+    <mergeCell ref="E515:E516"/>
+    <mergeCell ref="F515:F516"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1" display="Abbreviation of the journal name. We use WoS abbreviations that can be found here: https://images.webofknowledge.com/images/help/WOS/A_abrvjt.html" xr:uid="{6BB52E4D-01E2-44A6-B6CC-352383FA2940}"/>
@@ -42608,26 +42608,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4e0e0d96de7fb32b1678b66c28514d8e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" xmlns:ns3="432dd258-9dce-4cb3-b611-c68c0fbce7f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac451aab8c96dec805c937cbafca7133" ns2:_="" ns3:_="">
     <xsd:import namespace="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
@@ -42828,10 +42808,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0C90B0A-DBBE-4147-B2EE-79946A8DC171}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC19592A-9F30-4B32-9428-1D9634B8A0D4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
+    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -42848,20 +42859,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC19592A-9F30-4B32-9428-1D9634B8A0D4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0C90B0A-DBBE-4147-B2EE-79946A8DC171}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
-    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
+++ b/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Evidence_Hub/02.FOMD/02.metadata_structure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2653" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35766F49-0185-46C4-91F3-6F1C6193772B}"/>
+  <xr:revisionPtr revIDLastSave="2766" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4133BF4-8489-4D80-95EF-A6D1878142A5}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{FAB1A633-BA4D-4813-8605-DC3F4755D7C7}"/>
   </bookViews>
@@ -242,7 +242,7 @@
     Not sure what is this</t>
       </text>
     </comment>
-    <comment ref="F339" authorId="1" shapeId="0" xr:uid="{05ADAAF8-AA23-445C-819C-71D52878014A}">
+    <comment ref="F353" authorId="1" shapeId="0" xr:uid="{05ADAAF8-AA23-445C-819C-71D52878014A}">
       <text>
         <r>
           <rPr>
@@ -256,7 +256,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F344" authorId="1" shapeId="0" xr:uid="{75001466-4C34-4F54-9B7C-4BBE6FBB3311}">
+    <comment ref="F358" authorId="1" shapeId="0" xr:uid="{75001466-4C34-4F54-9B7C-4BBE6FBB3311}">
       <text>
         <r>
           <rPr>
@@ -270,7 +270,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F457" authorId="6" shapeId="0" xr:uid="{CE5CE24D-637F-4D3D-9BD9-7662441D05AB}">
+    <comment ref="F471" authorId="6" shapeId="0" xr:uid="{CE5CE24D-637F-4D3D-9BD9-7662441D05AB}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -278,7 +278,7 @@
     Not sure what is this</t>
       </text>
     </comment>
-    <comment ref="F460" authorId="7" shapeId="0" xr:uid="{C0FFB8F0-4213-4080-AB70-B8075981D569}">
+    <comment ref="F474" authorId="7" shapeId="0" xr:uid="{C0FFB8F0-4213-4080-AB70-B8075981D569}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -286,7 +286,7 @@
     Not sure what is this</t>
       </text>
     </comment>
-    <comment ref="F463" authorId="8" shapeId="0" xr:uid="{63BE61FA-9CD1-49AD-95A7-6F9953D136F9}">
+    <comment ref="F477" authorId="8" shapeId="0" xr:uid="{63BE61FA-9CD1-49AD-95A7-6F9953D136F9}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -294,7 +294,7 @@
     Not sure what is this</t>
       </text>
     </comment>
-    <comment ref="F466" authorId="9" shapeId="0" xr:uid="{41477B88-7470-4A29-8291-5BA04E3F99E0}">
+    <comment ref="F480" authorId="9" shapeId="0" xr:uid="{41477B88-7470-4A29-8291-5BA04E3F99E0}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -307,7 +307,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6367" uniqueCount="1554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6406" uniqueCount="1577">
   <si>
     <t>Example</t>
   </si>
@@ -10796,6 +10796,75 @@
   </si>
   <si>
     <t>"Traditional harvesting method", "Harvest Technique" should be part of the harvest section, right?</t>
+  </si>
+  <si>
+    <t>cv_grouping_method</t>
+  </si>
+  <si>
+    <t>outcome_calculated</t>
+  </si>
+  <si>
+    <t>Audit trail: which variables defined the "group" for averaging cv</t>
+  </si>
+  <si>
+    <t>The CV actually used downstream — reported if available, otherwise the group average for the control</t>
+  </si>
+  <si>
+    <t>The CV actually used downstream — reported if available, otherwise the group average for the treatment</t>
+  </si>
+  <si>
+    <t>C_out_cv_final</t>
+  </si>
+  <si>
+    <t>T_out_cv_final</t>
+  </si>
+  <si>
+    <t>The group's average CV, used to fill in missing variance values</t>
+  </si>
+  <si>
+    <t>T_out_cv_group_avg</t>
+  </si>
+  <si>
+    <t>C_out_cv_group_avg</t>
+  </si>
+  <si>
+    <t>C_out_mean</t>
+  </si>
+  <si>
+    <t>T_out_mean</t>
+  </si>
+  <si>
+    <t>C_out_sd</t>
+  </si>
+  <si>
+    <t>T_out_sd</t>
+  </si>
+  <si>
+    <t>C_out_sample_size_imputed</t>
+  </si>
+  <si>
+    <t>T_out_sample_size_imputed</t>
+  </si>
+  <si>
+    <t>Calculated mean from reported values for the control system</t>
+  </si>
+  <si>
+    <t>Calculated mean from reported values for the treatment system</t>
+  </si>
+  <si>
+    <t>Calculated standard deviation from reported values for the control system</t>
+  </si>
+  <si>
+    <t>Calculated standard deviation from reported values for the treatment system</t>
+  </si>
+  <si>
+    <t>Estimated sample size for the control system, estimated only when there was no reported sample size</t>
+  </si>
+  <si>
+    <t>Estimated sample size for the treatment system, estimated only when there was no reported sample size</t>
+  </si>
+  <si>
+    <t>vi</t>
   </si>
 </sst>
 </file>
@@ -11213,7 +11282,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="63">
+  <fills count="64">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -11573,6 +11642,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="13">
     <border>
@@ -11775,7 +11850,7 @@
     <xf numFmtId="0" fontId="33" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -12029,12 +12104,13 @@
     <xf numFmtId="0" fontId="15" fillId="61" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="62" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="63" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -12877,16 +12953,16 @@
   <threadedComment ref="F232" dT="2026-02-20T20:51:05.06" personId="{8754E5AB-4123-45AF-A584-AD9CD6F7A032}" id="{0DE31A08-56CD-4602-A212-84346A0B0705}">
     <text>Not sure what is this</text>
   </threadedComment>
-  <threadedComment ref="F457" dT="2026-02-20T20:50:13.23" personId="{8754E5AB-4123-45AF-A584-AD9CD6F7A032}" id="{CE5CE24D-637F-4D3D-9BD9-7662441D05AB}">
+  <threadedComment ref="F471" dT="2026-02-20T20:50:13.23" personId="{8754E5AB-4123-45AF-A584-AD9CD6F7A032}" id="{CE5CE24D-637F-4D3D-9BD9-7662441D05AB}">
     <text>Not sure what is this</text>
   </threadedComment>
-  <threadedComment ref="F460" dT="2026-02-20T20:50:13.23" personId="{8754E5AB-4123-45AF-A584-AD9CD6F7A032}" id="{C0FFB8F0-4213-4080-AB70-B8075981D569}">
+  <threadedComment ref="F474" dT="2026-02-20T20:50:13.23" personId="{8754E5AB-4123-45AF-A584-AD9CD6F7A032}" id="{C0FFB8F0-4213-4080-AB70-B8075981D569}">
     <text>Not sure what is this</text>
   </threadedComment>
-  <threadedComment ref="F463" dT="2026-02-20T20:51:05.06" personId="{8754E5AB-4123-45AF-A584-AD9CD6F7A032}" id="{63BE61FA-9CD1-49AD-95A7-6F9953D136F9}">
+  <threadedComment ref="F477" dT="2026-02-20T20:51:05.06" personId="{8754E5AB-4123-45AF-A584-AD9CD6F7A032}" id="{63BE61FA-9CD1-49AD-95A7-6F9953D136F9}">
     <text>Not sure what is this</text>
   </threadedComment>
-  <threadedComment ref="F466" dT="2026-02-20T20:51:05.06" personId="{8754E5AB-4123-45AF-A584-AD9CD6F7A032}" id="{41477B88-7470-4A29-8291-5BA04E3F99E0}">
+  <threadedComment ref="F480" dT="2026-02-20T20:51:05.06" personId="{8754E5AB-4123-45AF-A584-AD9CD6F7A032}" id="{41477B88-7470-4A29-8291-5BA04E3F99E0}">
     <text>Not sure what is this</text>
   </threadedComment>
 </ThreadedComments>
@@ -31128,7 +31204,7 @@
       <c r="L542" s="12"/>
       <c r="M542" s="12"/>
       <c r="N542" s="12"/>
-      <c r="O542" s="149" t="s">
+      <c r="O542" s="152" t="s">
         <v>35</v>
       </c>
       <c r="P542" s="150" t="s">
@@ -31156,7 +31232,7 @@
       <c r="L543" s="12"/>
       <c r="M543" s="12"/>
       <c r="N543" s="12"/>
-      <c r="O543" s="149"/>
+      <c r="O543" s="152"/>
       <c r="P543" s="150"/>
       <c r="Q543" s="151"/>
       <c r="R543" s="3" t="s">
@@ -31206,7 +31282,7 @@
       <c r="L546" s="1"/>
       <c r="M546" s="1"/>
       <c r="N546" s="1"/>
-      <c r="O546" s="152" t="s">
+      <c r="O546" s="149" t="s">
         <v>42</v>
       </c>
       <c r="P546" s="150" t="s">
@@ -31234,7 +31310,7 @@
       <c r="L547" s="1"/>
       <c r="M547" s="1"/>
       <c r="N547" s="1"/>
-      <c r="O547" s="152"/>
+      <c r="O547" s="149"/>
       <c r="P547" s="150"/>
       <c r="Q547" s="151"/>
       <c r="R547" s="3" t="s">
@@ -31256,7 +31332,7 @@
       <c r="L548" s="12"/>
       <c r="M548" s="12"/>
       <c r="N548" s="12"/>
-      <c r="O548" s="149" t="s">
+      <c r="O548" s="152" t="s">
         <v>45</v>
       </c>
       <c r="P548" s="150" t="s">
@@ -31284,7 +31360,7 @@
       <c r="L549" s="12"/>
       <c r="M549" s="12"/>
       <c r="N549" s="12"/>
-      <c r="O549" s="149"/>
+      <c r="O549" s="152"/>
       <c r="P549" s="150"/>
       <c r="Q549" s="151"/>
       <c r="R549" s="3" t="s">
@@ -31334,7 +31410,7 @@
       <c r="L552" s="1"/>
       <c r="M552" s="1"/>
       <c r="N552" s="1"/>
-      <c r="O552" s="152" t="s">
+      <c r="O552" s="149" t="s">
         <v>52</v>
       </c>
       <c r="P552" s="150" t="s">
@@ -31362,7 +31438,7 @@
       <c r="L553" s="1"/>
       <c r="M553" s="1"/>
       <c r="N553" s="1"/>
-      <c r="O553" s="152"/>
+      <c r="O553" s="149"/>
       <c r="P553" s="150"/>
       <c r="Q553" s="151"/>
       <c r="R553" s="3" t="s">
@@ -31384,7 +31460,7 @@
       <c r="L554" s="1"/>
       <c r="M554" s="1"/>
       <c r="N554" s="1"/>
-      <c r="O554" s="149" t="s">
+      <c r="O554" s="152" t="s">
         <v>54</v>
       </c>
       <c r="P554" s="150" t="s">
@@ -31412,7 +31488,7 @@
       <c r="L555" s="1"/>
       <c r="M555" s="1"/>
       <c r="N555" s="1"/>
-      <c r="O555" s="149"/>
+      <c r="O555" s="152"/>
       <c r="P555" s="150"/>
       <c r="Q555" s="151"/>
       <c r="R555" s="3" t="s">
@@ -31434,7 +31510,7 @@
       <c r="L556" s="1"/>
       <c r="M556" s="1"/>
       <c r="N556" s="1"/>
-      <c r="O556" s="149" t="s">
+      <c r="O556" s="152" t="s">
         <v>58</v>
       </c>
       <c r="P556" s="150" t="s">
@@ -31462,7 +31538,7 @@
       <c r="L557" s="1"/>
       <c r="M557" s="1"/>
       <c r="N557" s="1"/>
-      <c r="O557" s="149"/>
+      <c r="O557" s="152"/>
       <c r="P557" s="150"/>
       <c r="Q557" s="151"/>
       <c r="R557" s="3" t="s">
@@ -31484,7 +31560,7 @@
       <c r="L558" s="1"/>
       <c r="M558" s="1"/>
       <c r="N558" s="1"/>
-      <c r="O558" s="149" t="s">
+      <c r="O558" s="152" t="s">
         <v>62</v>
       </c>
       <c r="P558" s="150" t="s">
@@ -31512,7 +31588,7 @@
       <c r="L559" s="1"/>
       <c r="M559" s="1"/>
       <c r="N559" s="1"/>
-      <c r="O559" s="149"/>
+      <c r="O559" s="152"/>
       <c r="P559" s="150"/>
       <c r="Q559" s="151"/>
       <c r="R559" s="3" t="s">
@@ -31644,7 +31720,7 @@
       <c r="L564" s="1"/>
       <c r="M564" s="1"/>
       <c r="N564" s="1"/>
-      <c r="O564" s="152" t="s">
+      <c r="O564" s="149" t="s">
         <v>86</v>
       </c>
       <c r="P564" s="150" t="s">
@@ -31672,7 +31748,7 @@
       <c r="L565" s="1"/>
       <c r="M565" s="1"/>
       <c r="N565" s="1"/>
-      <c r="O565" s="152"/>
+      <c r="O565" s="149"/>
       <c r="P565" s="150"/>
       <c r="Q565" s="151"/>
       <c r="R565" s="3" t="s">
@@ -31694,7 +31770,7 @@
       <c r="L566" s="1"/>
       <c r="M566" s="1"/>
       <c r="N566" s="1"/>
-      <c r="O566" s="152"/>
+      <c r="O566" s="149"/>
       <c r="P566" s="150"/>
       <c r="Q566" s="151"/>
       <c r="R566" s="3" t="s">
@@ -31716,7 +31792,7 @@
       <c r="L567" s="1"/>
       <c r="M567" s="1"/>
       <c r="N567" s="1"/>
-      <c r="O567" s="152" t="s">
+      <c r="O567" s="149" t="s">
         <v>91</v>
       </c>
       <c r="P567" s="150" t="s">
@@ -31744,7 +31820,7 @@
       <c r="L568" s="1"/>
       <c r="M568" s="1"/>
       <c r="N568" s="1"/>
-      <c r="O568" s="152"/>
+      <c r="O568" s="149"/>
       <c r="P568" s="150"/>
       <c r="Q568" s="151"/>
       <c r="R568" s="3" t="s">
@@ -31766,7 +31842,7 @@
       <c r="L569" s="1"/>
       <c r="M569" s="1"/>
       <c r="N569" s="1"/>
-      <c r="O569" s="152"/>
+      <c r="O569" s="149"/>
       <c r="P569" s="150"/>
       <c r="Q569" s="151"/>
       <c r="R569" s="3" t="s">
@@ -32535,24 +32611,6 @@
   </sheetData>
   <autoFilter ref="A1:S319" xr:uid="{82619C4B-D6B1-486E-87C6-D2252668E253}"/>
   <mergeCells count="27">
-    <mergeCell ref="O542:O543"/>
-    <mergeCell ref="P542:P543"/>
-    <mergeCell ref="Q542:Q543"/>
-    <mergeCell ref="O546:O547"/>
-    <mergeCell ref="P546:P547"/>
-    <mergeCell ref="Q546:Q547"/>
-    <mergeCell ref="O556:O557"/>
-    <mergeCell ref="P556:P557"/>
-    <mergeCell ref="Q556:Q557"/>
-    <mergeCell ref="O558:O559"/>
-    <mergeCell ref="P558:P559"/>
-    <mergeCell ref="Q558:Q559"/>
-    <mergeCell ref="O564:O566"/>
-    <mergeCell ref="P564:P566"/>
-    <mergeCell ref="Q564:Q566"/>
-    <mergeCell ref="O567:O569"/>
-    <mergeCell ref="P567:P569"/>
-    <mergeCell ref="Q567:Q569"/>
     <mergeCell ref="O554:O555"/>
     <mergeCell ref="P554:P555"/>
     <mergeCell ref="Q554:Q555"/>
@@ -32562,6 +32620,24 @@
     <mergeCell ref="P552:P553"/>
     <mergeCell ref="Q552:Q553"/>
     <mergeCell ref="O548:O549"/>
+    <mergeCell ref="O564:O566"/>
+    <mergeCell ref="P564:P566"/>
+    <mergeCell ref="Q564:Q566"/>
+    <mergeCell ref="O567:O569"/>
+    <mergeCell ref="P567:P569"/>
+    <mergeCell ref="Q567:Q569"/>
+    <mergeCell ref="O556:O557"/>
+    <mergeCell ref="P556:P557"/>
+    <mergeCell ref="Q556:Q557"/>
+    <mergeCell ref="O558:O559"/>
+    <mergeCell ref="P558:P559"/>
+    <mergeCell ref="Q558:Q559"/>
+    <mergeCell ref="O542:O543"/>
+    <mergeCell ref="P542:P543"/>
+    <mergeCell ref="Q542:Q543"/>
+    <mergeCell ref="O546:O547"/>
+    <mergeCell ref="P546:P547"/>
+    <mergeCell ref="Q546:Q547"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="Q7" r:id="rId1" display="Abbreviation of the journal name. We use WoS abbreviations that can be found here: https://images.webofknowledge.com/images/help/WOS/A_abrvjt.html" xr:uid="{B4DADD6B-F846-45B3-933B-5F25CC9FEF24}"/>
@@ -32574,7 +32650,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14A586C8-08A0-4640-80FB-651A99A88EA6}">
-  <dimension ref="A1:H583"/>
+  <dimension ref="A1:H597"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="2" width="32.81640625" customWidth="1"/>
@@ -38210,200 +38286,217 @@
       <c r="G288" s="14"/>
     </row>
     <row r="289" spans="1:7">
-      <c r="A289" s="1"/>
-      <c r="B289" s="1"/>
+      <c r="A289" s="14"/>
+      <c r="B289" s="14"/>
+      <c r="C289" s="153" t="s">
+        <v>1555</v>
+      </c>
+      <c r="D289" s="153" t="s">
+        <v>1564</v>
+      </c>
+      <c r="E289" s="3"/>
+      <c r="F289" s="14" t="s">
+        <v>1570</v>
+      </c>
+      <c r="G289" s="14"/>
     </row>
     <row r="290" spans="1:7">
-      <c r="A290" s="1"/>
-      <c r="B290" s="1"/>
+      <c r="A290" s="14"/>
+      <c r="B290" s="14"/>
+      <c r="C290" s="153" t="s">
+        <v>1555</v>
+      </c>
+      <c r="D290" s="153" t="s">
+        <v>1565</v>
+      </c>
+      <c r="E290" s="3"/>
+      <c r="F290" s="14" t="s">
+        <v>1571</v>
+      </c>
+      <c r="G290" s="14"/>
+    </row>
+    <row r="291" spans="1:7">
+      <c r="A291" s="14"/>
+      <c r="B291" s="14"/>
+      <c r="C291" s="153" t="s">
+        <v>1555</v>
+      </c>
+      <c r="D291" s="153" t="s">
+        <v>1566</v>
+      </c>
+      <c r="E291" s="3"/>
+      <c r="F291" s="14" t="s">
+        <v>1572</v>
+      </c>
+      <c r="G291" s="14"/>
+    </row>
+    <row r="292" spans="1:7">
+      <c r="A292" s="14"/>
+      <c r="B292" s="14"/>
+      <c r="C292" s="153" t="s">
+        <v>1555</v>
+      </c>
+      <c r="D292" s="153" t="s">
+        <v>1567</v>
+      </c>
+      <c r="E292" s="3"/>
+      <c r="F292" s="14" t="s">
+        <v>1573</v>
+      </c>
+      <c r="G292" s="14"/>
     </row>
     <row r="293" spans="1:7">
-      <c r="C293" s="29" t="s">
+      <c r="A293" s="14"/>
+      <c r="B293" s="14"/>
+      <c r="C293" s="153" t="s">
+        <v>1555</v>
+      </c>
+      <c r="D293" s="153" t="s">
+        <v>1568</v>
+      </c>
+      <c r="E293" s="3"/>
+      <c r="F293" t="s">
+        <v>1574</v>
+      </c>
+      <c r="G293" s="14"/>
+    </row>
+    <row r="294" spans="1:7">
+      <c r="A294" s="14"/>
+      <c r="B294" s="14"/>
+      <c r="C294" s="153" t="s">
+        <v>1555</v>
+      </c>
+      <c r="D294" s="153" t="s">
+        <v>1569</v>
+      </c>
+      <c r="E294" s="3"/>
+      <c r="F294" t="s">
+        <v>1575</v>
+      </c>
+      <c r="G294" s="14"/>
+    </row>
+    <row r="295" spans="1:7">
+      <c r="A295" s="14"/>
+      <c r="B295" s="14"/>
+      <c r="C295" s="153" t="s">
+        <v>1555</v>
+      </c>
+      <c r="D295" s="153" t="s">
+        <v>1563</v>
+      </c>
+      <c r="E295" s="3"/>
+      <c r="F295" t="s">
+        <v>1561</v>
+      </c>
+      <c r="G295" s="14"/>
+    </row>
+    <row r="296" spans="1:7">
+      <c r="A296" s="14"/>
+      <c r="B296" s="14"/>
+      <c r="C296" s="153" t="s">
+        <v>1555</v>
+      </c>
+      <c r="D296" s="153" t="s">
+        <v>1562</v>
+      </c>
+      <c r="E296" s="3"/>
+      <c r="F296" t="s">
+        <v>1561</v>
+      </c>
+      <c r="G296" s="14"/>
+    </row>
+    <row r="297" spans="1:7">
+      <c r="A297" s="14"/>
+      <c r="B297" s="14"/>
+      <c r="C297" s="153" t="s">
+        <v>1555</v>
+      </c>
+      <c r="D297" s="153" t="s">
+        <v>1559</v>
+      </c>
+      <c r="E297" s="3"/>
+      <c r="F297" s="14" t="s">
+        <v>1557</v>
+      </c>
+      <c r="G297" s="14"/>
+    </row>
+    <row r="298" spans="1:7">
+      <c r="A298" s="14"/>
+      <c r="B298" s="14"/>
+      <c r="C298" s="153" t="s">
+        <v>1555</v>
+      </c>
+      <c r="D298" s="153" t="s">
+        <v>1560</v>
+      </c>
+      <c r="E298" s="3"/>
+      <c r="F298" s="14" t="s">
+        <v>1558</v>
+      </c>
+      <c r="G298" s="14"/>
+    </row>
+    <row r="299" spans="1:7">
+      <c r="A299" s="1"/>
+      <c r="B299" s="1"/>
+      <c r="C299" s="153" t="s">
+        <v>1555</v>
+      </c>
+      <c r="D299" s="153" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F299" s="10" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7">
+      <c r="A300" s="1"/>
+      <c r="B300" s="1"/>
+      <c r="C300" s="153" t="s">
+        <v>1555</v>
+      </c>
+      <c r="D300" s="153" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7">
+      <c r="A301" s="1"/>
+      <c r="B301" s="1"/>
+      <c r="C301" s="153" t="s">
+        <v>1555</v>
+      </c>
+      <c r="D301" s="153" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7">
+      <c r="A302" s="1"/>
+      <c r="B302" s="1"/>
+      <c r="C302" s="153" t="s">
+        <v>1555</v>
+      </c>
+      <c r="D302" s="153" t="s">
+        <v>1576</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7">
+      <c r="A303" s="1"/>
+      <c r="B303" s="1"/>
+    </row>
+    <row r="304" spans="1:7">
+      <c r="A304" s="1"/>
+      <c r="B304" s="1"/>
+    </row>
+    <row r="307" spans="3:7">
+      <c r="C307" s="29" t="s">
         <v>1029</v>
       </c>
     </row>
-    <row r="295" spans="1:7">
-      <c r="C295" s="14" t="s">
-        <v>767</v>
-      </c>
-      <c r="D295" s="59" t="s">
-        <v>643</v>
-      </c>
-      <c r="E295" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F295" s="3"/>
-      <c r="G295" s="3"/>
-    </row>
-    <row r="296" spans="1:7">
-      <c r="C296" s="14" t="s">
-        <v>767</v>
-      </c>
-      <c r="D296" s="59" t="s">
-        <v>644</v>
-      </c>
-      <c r="E296" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F296" s="3"/>
-      <c r="G296" s="3"/>
-    </row>
-    <row r="297" spans="1:7">
-      <c r="C297" s="14" t="s">
-        <v>767</v>
-      </c>
-      <c r="D297" s="59" t="s">
-        <v>645</v>
-      </c>
-      <c r="E297" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F297" s="3"/>
-      <c r="G297" s="3"/>
-    </row>
-    <row r="298" spans="1:7" ht="15" thickBot="1">
-      <c r="C298" s="14" t="s">
-        <v>767</v>
-      </c>
-      <c r="D298" s="59" t="s">
-        <v>834</v>
-      </c>
-      <c r="E298" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F298" s="3"/>
-      <c r="G298" s="3"/>
-    </row>
-    <row r="299" spans="1:7" ht="26.5" thickBot="1">
-      <c r="C299" s="14"/>
-      <c r="D299" s="58" t="s">
-        <v>838</v>
-      </c>
-      <c r="E299" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F299" s="3"/>
-      <c r="G299" s="3"/>
-    </row>
-    <row r="300" spans="1:7">
-      <c r="C300" s="14" t="s">
-        <v>767</v>
-      </c>
-      <c r="D300" s="59" t="s">
-        <v>835</v>
-      </c>
-      <c r="E300" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F300" s="3"/>
-      <c r="G300" s="3"/>
-    </row>
-    <row r="301" spans="1:7" ht="15" thickBot="1">
-      <c r="C301" s="14" t="s">
-        <v>767</v>
-      </c>
-      <c r="D301" s="59" t="s">
-        <v>836</v>
-      </c>
-      <c r="E301" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F301" s="3"/>
-      <c r="G301" s="3"/>
-    </row>
-    <row r="302" spans="1:7" ht="26.5" thickBot="1">
-      <c r="C302" s="14"/>
-      <c r="D302" s="58" t="s">
-        <v>839</v>
-      </c>
-      <c r="E302" s="3"/>
-      <c r="F302" s="3"/>
-      <c r="G302" s="3"/>
-    </row>
-    <row r="303" spans="1:7">
-      <c r="C303" s="14" t="s">
-        <v>767</v>
-      </c>
-      <c r="D303" s="59" t="s">
-        <v>639</v>
-      </c>
-      <c r="E303" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F303" s="3"/>
-      <c r="G303" s="3"/>
-    </row>
-    <row r="304" spans="1:7">
-      <c r="C304" s="14" t="s">
-        <v>767</v>
-      </c>
-      <c r="D304" s="59" t="s">
-        <v>640</v>
-      </c>
-      <c r="E304" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F304" s="3"/>
-      <c r="G304" s="3"/>
-    </row>
-    <row r="305" spans="1:7">
-      <c r="C305" s="14" t="s">
-        <v>767</v>
-      </c>
-      <c r="D305" s="59" t="s">
-        <v>641</v>
-      </c>
-      <c r="E305" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F305" s="3"/>
-      <c r="G305" s="3"/>
-    </row>
-    <row r="306" spans="1:7">
-      <c r="C306" s="14" t="s">
-        <v>767</v>
-      </c>
-      <c r="D306" s="59" t="s">
-        <v>642</v>
-      </c>
-      <c r="E306" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F306" s="3"/>
-      <c r="G306" s="3"/>
-    </row>
-    <row r="307" spans="1:7">
-      <c r="C307" s="14" t="s">
-        <v>767</v>
-      </c>
-      <c r="D307" s="59" t="s">
-        <v>629</v>
-      </c>
-      <c r="E307" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F307" s="3"/>
-      <c r="G307" s="3"/>
-    </row>
-    <row r="308" spans="1:7">
-      <c r="C308" s="14" t="s">
-        <v>767</v>
-      </c>
-      <c r="D308" s="59" t="s">
-        <v>630</v>
-      </c>
-      <c r="E308" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F308" s="3"/>
-      <c r="G308" s="3"/>
-    </row>
-    <row r="309" spans="1:7">
+    <row r="309" spans="3:7">
       <c r="C309" s="14" t="s">
         <v>767</v>
       </c>
       <c r="D309" s="59" t="s">
-        <v>631</v>
+        <v>643</v>
       </c>
       <c r="E309" s="3" t="s">
         <v>2</v>
@@ -38411,12 +38504,12 @@
       <c r="F309" s="3"/>
       <c r="G309" s="3"/>
     </row>
-    <row r="310" spans="1:7">
+    <row r="310" spans="3:7">
       <c r="C310" s="14" t="s">
         <v>767</v>
       </c>
       <c r="D310" s="59" t="s">
-        <v>632</v>
+        <v>644</v>
       </c>
       <c r="E310" s="3" t="s">
         <v>2</v>
@@ -38424,12 +38517,12 @@
       <c r="F310" s="3"/>
       <c r="G310" s="3"/>
     </row>
-    <row r="311" spans="1:7">
+    <row r="311" spans="3:7">
       <c r="C311" s="14" t="s">
         <v>767</v>
       </c>
       <c r="D311" s="59" t="s">
-        <v>633</v>
+        <v>645</v>
       </c>
       <c r="E311" s="3" t="s">
         <v>2</v>
@@ -38437,12 +38530,12 @@
       <c r="F311" s="3"/>
       <c r="G311" s="3"/>
     </row>
-    <row r="312" spans="1:7">
+    <row r="312" spans="3:7" ht="15" thickBot="1">
       <c r="C312" s="14" t="s">
         <v>767</v>
       </c>
       <c r="D312" s="59" t="s">
-        <v>634</v>
+        <v>834</v>
       </c>
       <c r="E312" s="3" t="s">
         <v>2</v>
@@ -38450,12 +38543,10 @@
       <c r="F312" s="3"/>
       <c r="G312" s="3"/>
     </row>
-    <row r="313" spans="1:7">
-      <c r="C313" s="14" t="s">
-        <v>767</v>
-      </c>
-      <c r="D313" s="59" t="s">
-        <v>635</v>
+    <row r="313" spans="3:7" ht="26.5" thickBot="1">
+      <c r="C313" s="14"/>
+      <c r="D313" s="58" t="s">
+        <v>838</v>
       </c>
       <c r="E313" s="3" t="s">
         <v>2</v>
@@ -38463,12 +38554,12 @@
       <c r="F313" s="3"/>
       <c r="G313" s="3"/>
     </row>
-    <row r="314" spans="1:7">
+    <row r="314" spans="3:7">
       <c r="C314" s="14" t="s">
         <v>767</v>
       </c>
       <c r="D314" s="59" t="s">
-        <v>636</v>
+        <v>835</v>
       </c>
       <c r="E314" s="3" t="s">
         <v>2</v>
@@ -38476,12 +38567,12 @@
       <c r="F314" s="3"/>
       <c r="G314" s="3"/>
     </row>
-    <row r="315" spans="1:7">
+    <row r="315" spans="3:7" ht="15" thickBot="1">
       <c r="C315" s="14" t="s">
         <v>767</v>
       </c>
       <c r="D315" s="59" t="s">
-        <v>637</v>
+        <v>836</v>
       </c>
       <c r="E315" s="3" t="s">
         <v>2</v>
@@ -38489,256 +38580,196 @@
       <c r="F315" s="3"/>
       <c r="G315" s="3"/>
     </row>
-    <row r="316" spans="1:7">
-      <c r="C316" s="14" t="s">
-        <v>767</v>
-      </c>
-      <c r="D316" s="59" t="s">
-        <v>638</v>
-      </c>
-      <c r="E316" s="3" t="s">
-        <v>2</v>
-      </c>
+    <row r="316" spans="3:7" ht="26.5" thickBot="1">
+      <c r="C316" s="14"/>
+      <c r="D316" s="58" t="s">
+        <v>839</v>
+      </c>
+      <c r="E316" s="3"/>
       <c r="F316" s="3"/>
       <c r="G316" s="3"/>
     </row>
-    <row r="317" spans="1:7">
-      <c r="A317" s="14"/>
-      <c r="B317" s="14"/>
+    <row r="317" spans="3:7">
       <c r="C317" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D317" s="36" t="s">
-        <v>646</v>
-      </c>
-      <c r="E317" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F317" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="G317" s="14"/>
-    </row>
-    <row r="318" spans="1:7">
-      <c r="A318" s="14"/>
-      <c r="B318" s="14"/>
+      <c r="D317" s="59" t="s">
+        <v>639</v>
+      </c>
+      <c r="E317" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F317" s="3"/>
+      <c r="G317" s="3"/>
+    </row>
+    <row r="318" spans="3:7">
       <c r="C318" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D318" s="36" t="s">
-        <v>647</v>
-      </c>
-      <c r="E318" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F318" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="G318" s="14"/>
-    </row>
-    <row r="319" spans="1:7">
-      <c r="A319" s="14"/>
-      <c r="B319" s="14"/>
+      <c r="D318" s="59" t="s">
+        <v>640</v>
+      </c>
+      <c r="E318" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F318" s="3"/>
+      <c r="G318" s="3"/>
+    </row>
+    <row r="319" spans="3:7">
       <c r="C319" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D319" s="36" t="s">
-        <v>648</v>
-      </c>
-      <c r="E319" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F319" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="G319" s="14"/>
-    </row>
-    <row r="320" spans="1:7">
-      <c r="A320" s="14"/>
-      <c r="B320" s="14"/>
+      <c r="D319" s="59" t="s">
+        <v>641</v>
+      </c>
+      <c r="E319" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F319" s="3"/>
+      <c r="G319" s="3"/>
+    </row>
+    <row r="320" spans="3:7">
       <c r="C320" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D320" s="36" t="s">
-        <v>649</v>
-      </c>
-      <c r="E320" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F320" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="G320" s="14"/>
+      <c r="D320" s="59" t="s">
+        <v>642</v>
+      </c>
+      <c r="E320" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F320" s="3"/>
+      <c r="G320" s="3"/>
     </row>
     <row r="321" spans="1:7">
-      <c r="A321" s="14"/>
-      <c r="B321" s="14"/>
       <c r="C321" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D321" s="16" t="s">
-        <v>661</v>
+      <c r="D321" s="59" t="s">
+        <v>629</v>
       </c>
       <c r="E321" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F321" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="G321" s="14"/>
+        <v>2</v>
+      </c>
+      <c r="F321" s="3"/>
+      <c r="G321" s="3"/>
     </row>
     <row r="322" spans="1:7">
-      <c r="A322" s="14"/>
-      <c r="B322" s="14"/>
       <c r="C322" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D322" s="16" t="s">
-        <v>664</v>
+      <c r="D322" s="59" t="s">
+        <v>630</v>
       </c>
       <c r="E322" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F322" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="G322" s="14"/>
+        <v>2</v>
+      </c>
+      <c r="F322" s="3"/>
+      <c r="G322" s="3"/>
     </row>
     <row r="323" spans="1:7">
-      <c r="A323" s="14"/>
-      <c r="B323" s="14"/>
       <c r="C323" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D323" s="16" t="s">
-        <v>663</v>
+      <c r="D323" s="59" t="s">
+        <v>631</v>
       </c>
       <c r="E323" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F323" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="G323" s="14"/>
+        <v>2</v>
+      </c>
+      <c r="F323" s="3"/>
+      <c r="G323" s="3"/>
     </row>
     <row r="324" spans="1:7">
-      <c r="A324" s="14"/>
-      <c r="B324" s="14"/>
       <c r="C324" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D324" s="16" t="s">
-        <v>665</v>
+      <c r="D324" s="59" t="s">
+        <v>632</v>
       </c>
       <c r="E324" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F324" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="G324" s="14"/>
+        <v>2</v>
+      </c>
+      <c r="F324" s="3"/>
+      <c r="G324" s="3"/>
     </row>
     <row r="325" spans="1:7">
-      <c r="A325" s="14"/>
-      <c r="B325" s="14"/>
       <c r="C325" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D325" s="16" t="s">
-        <v>662</v>
+      <c r="D325" s="59" t="s">
+        <v>633</v>
       </c>
       <c r="E325" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F325" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="G325" s="14"/>
+        <v>2</v>
+      </c>
+      <c r="F325" s="3"/>
+      <c r="G325" s="3"/>
     </row>
     <row r="326" spans="1:7">
-      <c r="A326" s="14"/>
-      <c r="B326" s="14"/>
       <c r="C326" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D326" s="16" t="s">
-        <v>666</v>
+      <c r="D326" s="59" t="s">
+        <v>634</v>
       </c>
       <c r="E326" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F326" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="G326" s="14"/>
+        <v>2</v>
+      </c>
+      <c r="F326" s="3"/>
+      <c r="G326" s="3"/>
     </row>
     <row r="327" spans="1:7">
-      <c r="A327" s="14"/>
-      <c r="B327" s="14"/>
       <c r="C327" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D327" s="16" t="s">
-        <v>667</v>
+      <c r="D327" s="59" t="s">
+        <v>635</v>
       </c>
       <c r="E327" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F327" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="G327" s="14"/>
+        <v>2</v>
+      </c>
+      <c r="F327" s="3"/>
+      <c r="G327" s="3"/>
     </row>
     <row r="328" spans="1:7">
-      <c r="A328" s="14"/>
-      <c r="B328" s="14"/>
       <c r="C328" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D328" s="16" t="s">
-        <v>668</v>
+      <c r="D328" s="59" t="s">
+        <v>636</v>
       </c>
       <c r="E328" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F328" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="G328" s="14"/>
+        <v>2</v>
+      </c>
+      <c r="F328" s="3"/>
+      <c r="G328" s="3"/>
     </row>
     <row r="329" spans="1:7">
-      <c r="A329" s="14"/>
-      <c r="B329" s="14"/>
       <c r="C329" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D329" s="16" t="s">
-        <v>669</v>
+      <c r="D329" s="59" t="s">
+        <v>637</v>
       </c>
       <c r="E329" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F329" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="G329" s="14"/>
+        <v>2</v>
+      </c>
+      <c r="F329" s="3"/>
+      <c r="G329" s="3"/>
     </row>
     <row r="330" spans="1:7">
-      <c r="A330" s="14"/>
-      <c r="B330" s="14"/>
       <c r="C330" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D330" s="16" t="s">
-        <v>670</v>
+      <c r="D330" s="59" t="s">
+        <v>638</v>
       </c>
       <c r="E330" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F330" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="G330" s="14"/>
+        <v>2</v>
+      </c>
+      <c r="F330" s="3"/>
+      <c r="G330" s="3"/>
     </row>
     <row r="331" spans="1:7">
       <c r="A331" s="14"/>
@@ -38746,14 +38777,14 @@
       <c r="C331" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D331" s="16" t="s">
-        <v>671</v>
-      </c>
-      <c r="E331" s="3" t="s">
+      <c r="D331" s="36" t="s">
+        <v>646</v>
+      </c>
+      <c r="E331" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F331" s="3" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="G331" s="14"/>
     </row>
@@ -38763,14 +38794,14 @@
       <c r="C332" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D332" s="16" t="s">
-        <v>672</v>
-      </c>
-      <c r="E332" s="3" t="s">
+      <c r="D332" s="36" t="s">
+        <v>647</v>
+      </c>
+      <c r="E332" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F332" s="3" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="G332" s="14"/>
     </row>
@@ -38780,14 +38811,14 @@
       <c r="C333" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D333" s="34" t="s">
-        <v>673</v>
-      </c>
-      <c r="E333" s="3" t="s">
+      <c r="D333" s="36" t="s">
+        <v>648</v>
+      </c>
+      <c r="E333" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F333" s="3" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="G333" s="14"/>
     </row>
@@ -38797,14 +38828,14 @@
       <c r="C334" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D334" s="34" t="s">
-        <v>674</v>
-      </c>
-      <c r="E334" s="3" t="s">
+      <c r="D334" s="36" t="s">
+        <v>649</v>
+      </c>
+      <c r="E334" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F334" s="3" t="s">
-        <v>312</v>
+        <v>293</v>
       </c>
       <c r="G334" s="14"/>
     </row>
@@ -38814,14 +38845,14 @@
       <c r="C335" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D335" s="34" t="s">
-        <v>675</v>
+      <c r="D335" s="16" t="s">
+        <v>661</v>
       </c>
       <c r="E335" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F335" s="3" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="G335" s="14"/>
     </row>
@@ -38831,14 +38862,14 @@
       <c r="C336" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D336" s="34" t="s">
-        <v>676</v>
+      <c r="D336" s="16" t="s">
+        <v>664</v>
       </c>
       <c r="E336" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F336" s="3" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="G336" s="14"/>
     </row>
@@ -38848,18 +38879,16 @@
       <c r="C337" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D337" s="20" t="s">
-        <v>677</v>
+      <c r="D337" s="16" t="s">
+        <v>663</v>
       </c>
       <c r="E337" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F337" t="s">
-        <v>325</v>
-      </c>
-      <c r="G337" s="31" t="s">
-        <v>326</v>
-      </c>
+      <c r="F337" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="G337" s="14"/>
     </row>
     <row r="338" spans="1:7">
       <c r="A338" s="14"/>
@@ -38867,18 +38896,16 @@
       <c r="C338" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D338" s="20" t="s">
-        <v>678</v>
+      <c r="D338" s="16" t="s">
+        <v>665</v>
       </c>
       <c r="E338" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F338" t="s">
-        <v>327</v>
-      </c>
-      <c r="G338" s="31" t="s">
-        <v>328</v>
-      </c>
+      <c r="F338" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="G338" s="14"/>
     </row>
     <row r="339" spans="1:7">
       <c r="A339" s="14"/>
@@ -38886,18 +38913,16 @@
       <c r="C339" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D339" s="20" t="s">
-        <v>679</v>
+      <c r="D339" s="16" t="s">
+        <v>662</v>
       </c>
       <c r="E339" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F339" t="s">
-        <v>329</v>
-      </c>
-      <c r="G339" s="31" t="s">
-        <v>330</v>
-      </c>
+      <c r="F339" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="G339" s="14"/>
     </row>
     <row r="340" spans="1:7">
       <c r="A340" s="14"/>
@@ -38905,37 +38930,33 @@
       <c r="C340" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D340" s="20" t="s">
-        <v>680</v>
+      <c r="D340" s="16" t="s">
+        <v>666</v>
       </c>
       <c r="E340" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F340" t="s">
-        <v>331</v>
-      </c>
-      <c r="G340" s="31">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="341" spans="1:7" ht="15.5">
+      <c r="F340" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="G340" s="14"/>
+    </row>
+    <row r="341" spans="1:7">
       <c r="A341" s="14"/>
       <c r="B341" s="14"/>
       <c r="C341" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D341" s="20" t="s">
-        <v>681</v>
+      <c r="D341" s="16" t="s">
+        <v>667</v>
       </c>
       <c r="E341" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F341" t="s">
-        <v>332</v>
-      </c>
-      <c r="G341" s="5">
-        <v>2</v>
-      </c>
+      <c r="F341" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="G341" s="14"/>
     </row>
     <row r="342" spans="1:7">
       <c r="A342" s="14"/>
@@ -38943,18 +38964,16 @@
       <c r="C342" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D342" s="20" t="s">
-        <v>682</v>
+      <c r="D342" s="16" t="s">
+        <v>668</v>
       </c>
       <c r="E342" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F342" t="s">
-        <v>325</v>
-      </c>
-      <c r="G342" s="31" t="s">
-        <v>326</v>
-      </c>
+      <c r="F342" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="G342" s="14"/>
     </row>
     <row r="343" spans="1:7">
       <c r="A343" s="14"/>
@@ -38962,18 +38981,16 @@
       <c r="C343" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D343" s="20" t="s">
-        <v>683</v>
+      <c r="D343" s="16" t="s">
+        <v>669</v>
       </c>
       <c r="E343" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F343" t="s">
-        <v>327</v>
-      </c>
-      <c r="G343" s="31" t="s">
-        <v>328</v>
-      </c>
+      <c r="F343" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="G343" s="14"/>
     </row>
     <row r="344" spans="1:7">
       <c r="A344" s="14"/>
@@ -38981,18 +38998,16 @@
       <c r="C344" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D344" s="20" t="s">
-        <v>684</v>
+      <c r="D344" s="16" t="s">
+        <v>670</v>
       </c>
       <c r="E344" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F344" t="s">
-        <v>329</v>
-      </c>
-      <c r="G344" s="31" t="s">
-        <v>330</v>
-      </c>
+      <c r="F344" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="G344" s="14"/>
     </row>
     <row r="345" spans="1:7">
       <c r="A345" s="14"/>
@@ -39000,37 +39015,33 @@
       <c r="C345" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D345" s="20" t="s">
-        <v>685</v>
+      <c r="D345" s="16" t="s">
+        <v>671</v>
       </c>
       <c r="E345" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F345" t="s">
-        <v>331</v>
-      </c>
-      <c r="G345" s="31">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="346" spans="1:7" ht="15.5">
+      <c r="F345" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="G345" s="14"/>
+    </row>
+    <row r="346" spans="1:7">
       <c r="A346" s="14"/>
       <c r="B346" s="14"/>
       <c r="C346" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D346" s="20" t="s">
-        <v>686</v>
+      <c r="D346" s="16" t="s">
+        <v>672</v>
       </c>
       <c r="E346" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F346" t="s">
-        <v>332</v>
-      </c>
-      <c r="G346" s="5">
-        <v>2</v>
-      </c>
+      <c r="F346" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="G346" s="14"/>
     </row>
     <row r="347" spans="1:7">
       <c r="A347" s="14"/>
@@ -39038,32 +39049,33 @@
       <c r="C347" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D347" s="24" t="s">
-        <v>687</v>
+      <c r="D347" s="34" t="s">
+        <v>673</v>
       </c>
       <c r="E347" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F347" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="348" spans="1:7" ht="15.5">
+      <c r="F347" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="G347" s="14"/>
+    </row>
+    <row r="348" spans="1:7">
       <c r="A348" s="14"/>
       <c r="B348" s="14"/>
       <c r="C348" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D348" s="24" t="s">
-        <v>688</v>
+      <c r="D348" s="34" t="s">
+        <v>674</v>
       </c>
       <c r="E348" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F348" t="s">
-        <v>344</v>
-      </c>
-      <c r="G348" s="5"/>
+      <c r="F348" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="G348" s="14"/>
     </row>
     <row r="349" spans="1:7">
       <c r="A349" s="14"/>
@@ -39071,18 +39083,16 @@
       <c r="C349" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D349" s="24" t="s">
-        <v>689</v>
+      <c r="D349" s="34" t="s">
+        <v>675</v>
       </c>
       <c r="E349" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F349" t="s">
-        <v>603</v>
-      </c>
-      <c r="G349" s="31" t="s">
-        <v>346</v>
-      </c>
+      <c r="F349" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="G349" s="14"/>
     </row>
     <row r="350" spans="1:7">
       <c r="A350" s="14"/>
@@ -39090,32 +39100,35 @@
       <c r="C350" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D350" s="24" t="s">
-        <v>690</v>
+      <c r="D350" s="34" t="s">
+        <v>676</v>
       </c>
       <c r="E350" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F350" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="351" spans="1:7" ht="15.5">
+      <c r="F350" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="G350" s="14"/>
+    </row>
+    <row r="351" spans="1:7">
       <c r="A351" s="14"/>
       <c r="B351" s="14"/>
       <c r="C351" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D351" s="24" t="s">
-        <v>691</v>
+      <c r="D351" s="20" t="s">
+        <v>677</v>
       </c>
       <c r="E351" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F351" t="s">
-        <v>344</v>
-      </c>
-      <c r="G351" s="5"/>
+        <v>325</v>
+      </c>
+      <c r="G351" s="31" t="s">
+        <v>326</v>
+      </c>
     </row>
     <row r="352" spans="1:7">
       <c r="A352" s="14"/>
@@ -39123,17 +39136,17 @@
       <c r="C352" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D352" s="24" t="s">
-        <v>692</v>
+      <c r="D352" s="20" t="s">
+        <v>678</v>
       </c>
       <c r="E352" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F352" t="s">
-        <v>603</v>
+        <v>327</v>
       </c>
       <c r="G352" s="31" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
     </row>
     <row r="353" spans="1:7">
@@ -39142,17 +39155,17 @@
       <c r="C353" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D353" s="23" t="s">
-        <v>693</v>
+      <c r="D353" s="20" t="s">
+        <v>679</v>
       </c>
       <c r="E353" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F353" t="s">
-        <v>350</v>
+        <v>329</v>
       </c>
       <c r="G353" s="31" t="s">
-        <v>352</v>
+        <v>330</v>
       </c>
     </row>
     <row r="354" spans="1:7">
@@ -39161,17 +39174,17 @@
       <c r="C354" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D354" s="23" t="s">
-        <v>694</v>
+      <c r="D354" s="20" t="s">
+        <v>680</v>
       </c>
       <c r="E354" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F354" t="s">
-        <v>351</v>
-      </c>
-      <c r="G354" s="31" t="s">
-        <v>354</v>
+        <v>331</v>
+      </c>
+      <c r="G354" s="31">
+        <v>20</v>
       </c>
     </row>
     <row r="355" spans="1:7" ht="15.5">
@@ -39180,16 +39193,18 @@
       <c r="C355" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D355" s="23" t="s">
-        <v>695</v>
+      <c r="D355" s="20" t="s">
+        <v>681</v>
       </c>
       <c r="E355" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F355" t="s">
-        <v>355</v>
-      </c>
-      <c r="G355" s="5"/>
+        <v>332</v>
+      </c>
+      <c r="G355" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="356" spans="1:7">
       <c r="A356" s="14"/>
@@ -39197,17 +39212,17 @@
       <c r="C356" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D356" s="23" t="s">
-        <v>696</v>
+      <c r="D356" s="20" t="s">
+        <v>682</v>
       </c>
       <c r="E356" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F356" t="s">
-        <v>356</v>
+        <v>325</v>
       </c>
       <c r="G356" s="31" t="s">
-        <v>357</v>
+        <v>326</v>
       </c>
     </row>
     <row r="357" spans="1:7">
@@ -39216,17 +39231,17 @@
       <c r="C357" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D357" s="23" t="s">
-        <v>697</v>
+      <c r="D357" s="20" t="s">
+        <v>683</v>
       </c>
       <c r="E357" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F357" t="s">
-        <v>350</v>
+        <v>327</v>
       </c>
       <c r="G357" s="31" t="s">
-        <v>352</v>
+        <v>328</v>
       </c>
     </row>
     <row r="358" spans="1:7">
@@ -39235,135 +39250,141 @@
       <c r="C358" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D358" s="23" t="s">
-        <v>698</v>
+      <c r="D358" s="20" t="s">
+        <v>684</v>
       </c>
       <c r="E358" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F358" t="s">
-        <v>351</v>
+        <v>329</v>
       </c>
       <c r="G358" s="31" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="359" spans="1:7" ht="15.5">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7">
       <c r="A359" s="14"/>
       <c r="B359" s="14"/>
       <c r="C359" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D359" s="23" t="s">
-        <v>699</v>
+      <c r="D359" s="20" t="s">
+        <v>685</v>
       </c>
       <c r="E359" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F359" t="s">
-        <v>355</v>
-      </c>
-      <c r="G359" s="5"/>
-    </row>
-    <row r="360" spans="1:7" ht="15" thickBot="1">
+        <v>331</v>
+      </c>
+      <c r="G359" s="31">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="360" spans="1:7" ht="15.5">
       <c r="A360" s="14"/>
       <c r="B360" s="14"/>
       <c r="C360" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D360" s="23" t="s">
-        <v>700</v>
+      <c r="D360" s="20" t="s">
+        <v>686</v>
       </c>
       <c r="E360" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F360" t="s">
-        <v>356</v>
-      </c>
-      <c r="G360" s="31" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="361" spans="1:7" ht="15" thickBot="1">
+        <v>332</v>
+      </c>
+      <c r="G360" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="361" spans="1:7">
       <c r="A361" s="14"/>
       <c r="B361" s="14"/>
       <c r="C361" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D361" s="21" t="s">
-        <v>701</v>
+      <c r="D361" s="24" t="s">
+        <v>687</v>
       </c>
       <c r="E361" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F361" s="3"/>
-      <c r="G361" s="14"/>
-    </row>
-    <row r="362" spans="1:7" ht="15" thickBot="1">
+      <c r="F361" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="362" spans="1:7" ht="15.5">
       <c r="A362" s="14"/>
       <c r="B362" s="14"/>
       <c r="C362" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D362" s="21" t="s">
-        <v>702</v>
+      <c r="D362" s="24" t="s">
+        <v>688</v>
       </c>
       <c r="E362" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F362" s="3"/>
-      <c r="G362" s="14"/>
-    </row>
-    <row r="363" spans="1:7" ht="15.5">
+      <c r="F362" t="s">
+        <v>344</v>
+      </c>
+      <c r="G362" s="5"/>
+    </row>
+    <row r="363" spans="1:7">
+      <c r="A363" s="14"/>
+      <c r="B363" s="14"/>
       <c r="C363" s="14" t="s">
         <v>767</v>
       </c>
       <c r="D363" s="24" t="s">
-        <v>703</v>
+        <v>689</v>
       </c>
       <c r="E363" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F363" t="s">
-        <v>397</v>
-      </c>
-      <c r="G363" s="5" t="s">
-        <v>382</v>
+        <v>603</v>
+      </c>
+      <c r="G363" s="31" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="364" spans="1:7">
+      <c r="A364" s="14"/>
+      <c r="B364" s="14"/>
       <c r="C364" s="14" t="s">
         <v>767</v>
       </c>
       <c r="D364" s="24" t="s">
-        <v>704</v>
+        <v>690</v>
       </c>
       <c r="E364" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F364" t="s">
-        <v>399</v>
-      </c>
-      <c r="G364" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="365" spans="1:7">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="365" spans="1:7" ht="15.5">
+      <c r="A365" s="14"/>
+      <c r="B365" s="14"/>
       <c r="C365" s="14" t="s">
         <v>767</v>
       </c>
       <c r="D365" s="24" t="s">
-        <v>705</v>
+        <v>691</v>
       </c>
       <c r="E365" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F365" t="s">
-        <v>400</v>
-      </c>
-      <c r="G365" t="s">
-        <v>597</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="G365" s="5"/>
     </row>
     <row r="366" spans="1:7">
       <c r="A366" s="14"/>
@@ -39372,35 +39393,35 @@
         <v>767</v>
       </c>
       <c r="D366" s="24" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="E366" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F366" t="s">
-        <v>401</v>
-      </c>
-      <c r="G366" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="367" spans="1:7" ht="15.5">
+        <v>603</v>
+      </c>
+      <c r="G366" s="31" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="367" spans="1:7">
       <c r="A367" s="14"/>
       <c r="B367" s="14"/>
       <c r="C367" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D367" s="24" t="s">
-        <v>707</v>
+      <c r="D367" s="23" t="s">
+        <v>693</v>
       </c>
       <c r="E367" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F367" t="s">
-        <v>397</v>
-      </c>
-      <c r="G367" s="5" t="s">
-        <v>382</v>
+        <v>350</v>
+      </c>
+      <c r="G367" s="31" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="368" spans="1:7">
@@ -39409,113 +39430,109 @@
       <c r="C368" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D368" s="24" t="s">
-        <v>708</v>
+      <c r="D368" s="23" t="s">
+        <v>694</v>
       </c>
       <c r="E368" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F368" t="s">
-        <v>399</v>
-      </c>
-      <c r="G368" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="369" spans="1:7">
+        <v>351</v>
+      </c>
+      <c r="G368" s="31" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="369" spans="1:7" ht="15.5">
       <c r="A369" s="14"/>
       <c r="B369" s="14"/>
       <c r="C369" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D369" s="24" t="s">
-        <v>709</v>
+      <c r="D369" s="23" t="s">
+        <v>695</v>
       </c>
       <c r="E369" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F369" t="s">
-        <v>400</v>
-      </c>
-      <c r="G369" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="370" spans="1:7" ht="15" thickBot="1">
+        <v>355</v>
+      </c>
+      <c r="G369" s="5"/>
+    </row>
+    <row r="370" spans="1:7">
       <c r="A370" s="14"/>
       <c r="B370" s="14"/>
       <c r="C370" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D370" s="24" t="s">
-        <v>710</v>
+      <c r="D370" s="23" t="s">
+        <v>696</v>
       </c>
       <c r="E370" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F370" t="s">
-        <v>401</v>
-      </c>
-      <c r="G370" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="371" spans="1:7" ht="15" thickBot="1">
+        <v>356</v>
+      </c>
+      <c r="G370" s="31" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="371" spans="1:7">
       <c r="A371" s="14"/>
       <c r="B371" s="14"/>
       <c r="C371" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D371" s="21" t="s">
-        <v>711</v>
-      </c>
-      <c r="E371" s="17" t="s">
+      <c r="D371" s="23" t="s">
+        <v>697</v>
+      </c>
+      <c r="E371" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F371" t="s">
-        <v>431</v>
-      </c>
-      <c r="G371" s="38" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="372" spans="1:7" ht="15" thickBot="1">
+        <v>350</v>
+      </c>
+      <c r="G371" s="31" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="372" spans="1:7">
       <c r="A372" s="14"/>
       <c r="B372" s="14"/>
       <c r="C372" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D372" s="21" t="s">
-        <v>712</v>
-      </c>
-      <c r="E372" s="17" t="s">
+      <c r="D372" s="23" t="s">
+        <v>698</v>
+      </c>
+      <c r="E372" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F372" t="s">
-        <v>433</v>
-      </c>
-      <c r="G372" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="373" spans="1:7" ht="15" thickBot="1">
+        <v>351</v>
+      </c>
+      <c r="G372" s="31" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="373" spans="1:7" ht="15.5">
       <c r="A373" s="14"/>
       <c r="B373" s="14"/>
       <c r="C373" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D373" s="21" t="s">
-        <v>713</v>
-      </c>
-      <c r="E373" s="17" t="s">
+      <c r="D373" s="23" t="s">
+        <v>699</v>
+      </c>
+      <c r="E373" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F373" t="s">
-        <v>434</v>
-      </c>
-      <c r="G373" s="39" t="s">
-        <v>420</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="G373" s="5"/>
     </row>
     <row r="374" spans="1:7" ht="15" thickBot="1">
       <c r="A374" s="14"/>
@@ -39523,17 +39540,17 @@
       <c r="C374" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D374" s="21" t="s">
-        <v>714</v>
-      </c>
-      <c r="E374" s="17" t="s">
+      <c r="D374" s="23" t="s">
+        <v>700</v>
+      </c>
+      <c r="E374" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F374" t="s">
-        <v>435</v>
-      </c>
-      <c r="G374" s="40" t="s">
-        <v>74</v>
+        <v>356</v>
+      </c>
+      <c r="G374" s="31" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="375" spans="1:7" ht="15" thickBot="1">
@@ -39543,17 +39560,13 @@
         <v>767</v>
       </c>
       <c r="D375" s="21" t="s">
-        <v>715</v>
-      </c>
-      <c r="E375" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F375" t="s">
-        <v>716</v>
-      </c>
-      <c r="G375" s="32" t="s">
-        <v>421</v>
-      </c>
+        <v>701</v>
+      </c>
+      <c r="E375" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F375" s="3"/>
+      <c r="G375" s="14"/>
     </row>
     <row r="376" spans="1:7" ht="15" thickBot="1">
       <c r="A376" s="14"/>
@@ -39562,143 +39575,139 @@
         <v>767</v>
       </c>
       <c r="D376" s="21" t="s">
-        <v>717</v>
-      </c>
-      <c r="E376" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="F376" t="s">
-        <v>437</v>
-      </c>
-      <c r="G376" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="377" spans="1:7" ht="15" thickBot="1">
-      <c r="A377" s="14"/>
-      <c r="B377" s="14"/>
+        <v>702</v>
+      </c>
+      <c r="E376" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F376" s="3"/>
+      <c r="G376" s="14"/>
+    </row>
+    <row r="377" spans="1:7" ht="15.5">
       <c r="C377" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D377" s="21" t="s">
-        <v>718</v>
-      </c>
-      <c r="E377" s="17" t="s">
-        <v>2</v>
+      <c r="D377" s="24" t="s">
+        <v>703</v>
+      </c>
+      <c r="E377" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F377" t="s">
-        <v>719</v>
-      </c>
-      <c r="G377">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="378" spans="1:7" ht="15" thickBot="1">
-      <c r="A378" s="14"/>
-      <c r="B378" s="14"/>
+        <v>397</v>
+      </c>
+      <c r="G377" s="5" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="378" spans="1:7">
       <c r="C378" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D378" s="21" t="s">
-        <v>720</v>
-      </c>
-      <c r="E378" s="17" t="s">
-        <v>2</v>
+      <c r="D378" s="24" t="s">
+        <v>704</v>
+      </c>
+      <c r="E378" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F378" t="s">
-        <v>721</v>
-      </c>
-      <c r="G378">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="379" spans="1:7" ht="15" thickBot="1">
-      <c r="A379" s="14"/>
-      <c r="B379" s="14"/>
+        <v>399</v>
+      </c>
+      <c r="G378" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="379" spans="1:7">
       <c r="C379" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D379" s="21" t="s">
-        <v>722</v>
-      </c>
-      <c r="E379" s="17" t="s">
-        <v>2</v>
+      <c r="D379" s="24" t="s">
+        <v>705</v>
+      </c>
+      <c r="E379" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F379" t="s">
-        <v>723</v>
-      </c>
-      <c r="G379">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="380" spans="1:7" ht="15" thickBot="1">
+        <v>400</v>
+      </c>
+      <c r="G379" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="380" spans="1:7">
       <c r="A380" s="14"/>
       <c r="B380" s="14"/>
       <c r="C380" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D380" s="21" t="s">
-        <v>724</v>
-      </c>
-      <c r="E380" s="17" t="s">
-        <v>2</v>
+      <c r="D380" s="24" t="s">
+        <v>706</v>
+      </c>
+      <c r="E380" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F380" t="s">
-        <v>725</v>
-      </c>
-      <c r="G380">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="381" spans="1:7" ht="15" thickBot="1">
+        <v>401</v>
+      </c>
+      <c r="G380" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="381" spans="1:7" ht="15.5">
       <c r="A381" s="14"/>
       <c r="B381" s="14"/>
       <c r="C381" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D381" s="21" t="s">
-        <v>726</v>
-      </c>
-      <c r="E381" s="17" t="s">
-        <v>2</v>
+      <c r="D381" s="24" t="s">
+        <v>707</v>
+      </c>
+      <c r="E381" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F381" t="s">
-        <v>727</v>
-      </c>
-      <c r="G381">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="382" spans="1:7" ht="15" thickBot="1">
+        <v>397</v>
+      </c>
+      <c r="G381" s="5" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="382" spans="1:7">
       <c r="A382" s="14"/>
       <c r="B382" s="14"/>
       <c r="C382" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D382" s="20" t="s">
-        <v>728</v>
-      </c>
-      <c r="E382" s="17" t="s">
+      <c r="D382" s="24" t="s">
+        <v>708</v>
+      </c>
+      <c r="E382" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F382" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="383" spans="1:7" ht="15" thickBot="1">
+        <v>399</v>
+      </c>
+      <c r="G382" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="383" spans="1:7">
       <c r="A383" s="14"/>
       <c r="B383" s="14"/>
       <c r="C383" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D383" s="20" t="s">
-        <v>729</v>
-      </c>
-      <c r="E383" s="17" t="s">
+      <c r="D383" s="24" t="s">
+        <v>709</v>
+      </c>
+      <c r="E383" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F383" t="s">
-        <v>444</v>
+        <v>400</v>
+      </c>
+      <c r="G383" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="384" spans="1:7" ht="15" thickBot="1">
@@ -39707,14 +39716,17 @@
       <c r="C384" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D384" s="20" t="s">
-        <v>730</v>
-      </c>
-      <c r="E384" s="17" t="s">
+      <c r="D384" s="24" t="s">
+        <v>710</v>
+      </c>
+      <c r="E384" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F384" t="s">
-        <v>447</v>
+        <v>401</v>
+      </c>
+      <c r="G384" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="385" spans="1:7" ht="15" thickBot="1">
@@ -39723,14 +39735,17 @@
       <c r="C385" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D385" s="20" t="s">
-        <v>731</v>
+      <c r="D385" s="21" t="s">
+        <v>711</v>
       </c>
       <c r="E385" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F385" t="s">
-        <v>732</v>
+        <v>431</v>
+      </c>
+      <c r="G385" s="38" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="386" spans="1:7" ht="15" thickBot="1">
@@ -39739,14 +39754,17 @@
       <c r="C386" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D386" s="20" t="s">
-        <v>733</v>
+      <c r="D386" s="21" t="s">
+        <v>712</v>
       </c>
       <c r="E386" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F386" t="s">
-        <v>448</v>
+        <v>433</v>
+      </c>
+      <c r="G386" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="387" spans="1:7" ht="15" thickBot="1">
@@ -39755,14 +39773,17 @@
       <c r="C387" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D387" s="20" t="s">
-        <v>734</v>
+      <c r="D387" s="21" t="s">
+        <v>713</v>
       </c>
       <c r="E387" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F387" t="s">
-        <v>449</v>
+        <v>434</v>
+      </c>
+      <c r="G387" s="39" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="388" spans="1:7" ht="15" thickBot="1">
@@ -39771,14 +39792,17 @@
       <c r="C388" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D388" s="20" t="s">
-        <v>735</v>
+      <c r="D388" s="21" t="s">
+        <v>714</v>
       </c>
       <c r="E388" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F388" t="s">
-        <v>450</v>
+        <v>435</v>
+      </c>
+      <c r="G388" s="40" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="389" spans="1:7" ht="15" thickBot="1">
@@ -39787,14 +39811,17 @@
       <c r="C389" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D389" s="20" t="s">
-        <v>736</v>
+      <c r="D389" s="21" t="s">
+        <v>715</v>
       </c>
       <c r="E389" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F389" t="s">
-        <v>451</v>
+        <v>716</v>
+      </c>
+      <c r="G389" s="32" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="390" spans="1:7" ht="15" thickBot="1">
@@ -39803,16 +39830,18 @@
       <c r="C390" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D390" s="20" t="s">
-        <v>737</v>
+      <c r="D390" s="21" t="s">
+        <v>717</v>
       </c>
       <c r="E390" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F390" t="s">
-        <v>453</v>
-      </c>
-      <c r="G390" s="41"/>
+        <v>437</v>
+      </c>
+      <c r="G390" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="391" spans="1:7" ht="15" thickBot="1">
       <c r="A391" s="14"/>
@@ -39821,16 +39850,16 @@
         <v>767</v>
       </c>
       <c r="D391" s="21" t="s">
-        <v>738</v>
+        <v>718</v>
       </c>
       <c r="E391" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F391" t="s">
-        <v>431</v>
-      </c>
-      <c r="G391" s="38" t="s">
-        <v>408</v>
+        <v>719</v>
+      </c>
+      <c r="G391">
+        <v>120</v>
       </c>
     </row>
     <row r="392" spans="1:7" ht="15" thickBot="1">
@@ -39840,16 +39869,16 @@
         <v>767</v>
       </c>
       <c r="D392" s="21" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="E392" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F392" t="s">
-        <v>433</v>
-      </c>
-      <c r="G392" t="s">
-        <v>419</v>
+        <v>721</v>
+      </c>
+      <c r="G392">
+        <v>30</v>
       </c>
     </row>
     <row r="393" spans="1:7" ht="15" thickBot="1">
@@ -39859,16 +39888,16 @@
         <v>767</v>
       </c>
       <c r="D393" s="21" t="s">
-        <v>740</v>
+        <v>722</v>
       </c>
       <c r="E393" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F393" t="s">
-        <v>434</v>
-      </c>
-      <c r="G393" s="39" t="s">
-        <v>420</v>
+        <v>723</v>
+      </c>
+      <c r="G393">
+        <v>60</v>
       </c>
     </row>
     <row r="394" spans="1:7" ht="15" thickBot="1">
@@ -39878,16 +39907,16 @@
         <v>767</v>
       </c>
       <c r="D394" s="21" t="s">
-        <v>741</v>
+        <v>724</v>
       </c>
       <c r="E394" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F394" t="s">
-        <v>435</v>
-      </c>
-      <c r="G394" s="40" t="s">
-        <v>74</v>
+        <v>725</v>
+      </c>
+      <c r="G394">
+        <v>70</v>
       </c>
     </row>
     <row r="395" spans="1:7" ht="15" thickBot="1">
@@ -39897,16 +39926,16 @@
         <v>767</v>
       </c>
       <c r="D395" s="21" t="s">
-        <v>742</v>
+        <v>726</v>
       </c>
       <c r="E395" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F395" t="s">
-        <v>743</v>
-      </c>
-      <c r="G395" s="32" t="s">
-        <v>421</v>
+        <v>727</v>
+      </c>
+      <c r="G395">
+        <v>90</v>
       </c>
     </row>
     <row r="396" spans="1:7" ht="15" thickBot="1">
@@ -39915,17 +39944,14 @@
       <c r="C396" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D396" s="21" t="s">
-        <v>744</v>
+      <c r="D396" s="20" t="s">
+        <v>728</v>
       </c>
       <c r="E396" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F396" t="s">
-        <v>437</v>
-      </c>
-      <c r="G396" t="s">
-        <v>74</v>
+        <v>443</v>
       </c>
     </row>
     <row r="397" spans="1:7" ht="15" thickBot="1">
@@ -39934,17 +39960,14 @@
       <c r="C397" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D397" s="21" t="s">
-        <v>745</v>
+      <c r="D397" s="20" t="s">
+        <v>729</v>
       </c>
       <c r="E397" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F397" t="s">
-        <v>746</v>
-      </c>
-      <c r="G397">
-        <v>120</v>
+        <v>444</v>
       </c>
     </row>
     <row r="398" spans="1:7" ht="15" thickBot="1">
@@ -39953,17 +39976,14 @@
       <c r="C398" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D398" s="21" t="s">
-        <v>747</v>
+      <c r="D398" s="20" t="s">
+        <v>730</v>
       </c>
       <c r="E398" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F398" t="s">
-        <v>748</v>
-      </c>
-      <c r="G398">
-        <v>30</v>
+        <v>447</v>
       </c>
     </row>
     <row r="399" spans="1:7" ht="15" thickBot="1">
@@ -39972,17 +39992,14 @@
       <c r="C399" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D399" s="21" t="s">
-        <v>749</v>
+      <c r="D399" s="20" t="s">
+        <v>731</v>
       </c>
       <c r="E399" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F399" t="s">
-        <v>750</v>
-      </c>
-      <c r="G399">
-        <v>60</v>
+        <v>732</v>
       </c>
     </row>
     <row r="400" spans="1:7" ht="15" thickBot="1">
@@ -39991,17 +40008,14 @@
       <c r="C400" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D400" s="21" t="s">
-        <v>751</v>
+      <c r="D400" s="20" t="s">
+        <v>733</v>
       </c>
       <c r="E400" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F400" t="s">
-        <v>752</v>
-      </c>
-      <c r="G400">
-        <v>70</v>
+        <v>448</v>
       </c>
     </row>
     <row r="401" spans="1:7" ht="15" thickBot="1">
@@ -40010,17 +40024,14 @@
       <c r="C401" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D401" s="21" t="s">
-        <v>753</v>
+      <c r="D401" s="20" t="s">
+        <v>734</v>
       </c>
       <c r="E401" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F401" t="s">
-        <v>754</v>
-      </c>
-      <c r="G401">
-        <v>90</v>
+        <v>449</v>
       </c>
     </row>
     <row r="402" spans="1:7" ht="15" thickBot="1">
@@ -40030,13 +40041,13 @@
         <v>767</v>
       </c>
       <c r="D402" s="20" t="s">
-        <v>755</v>
+        <v>735</v>
       </c>
       <c r="E402" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F402" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
     </row>
     <row r="403" spans="1:7" ht="15" thickBot="1">
@@ -40046,13 +40057,13 @@
         <v>767</v>
       </c>
       <c r="D403" s="20" t="s">
-        <v>756</v>
+        <v>736</v>
       </c>
       <c r="E403" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F403" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
     </row>
     <row r="404" spans="1:7" ht="15" thickBot="1">
@@ -40062,14 +40073,15 @@
         <v>767</v>
       </c>
       <c r="D404" s="20" t="s">
-        <v>757</v>
+        <v>737</v>
       </c>
       <c r="E404" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F404" t="s">
-        <v>447</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="G404" s="41"/>
     </row>
     <row r="405" spans="1:7" ht="15" thickBot="1">
       <c r="A405" s="14"/>
@@ -40077,14 +40089,17 @@
       <c r="C405" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D405" s="20" t="s">
-        <v>758</v>
+      <c r="D405" s="21" t="s">
+        <v>738</v>
       </c>
       <c r="E405" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F405" t="s">
-        <v>759</v>
+        <v>431</v>
+      </c>
+      <c r="G405" s="38" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="406" spans="1:7" ht="15" thickBot="1">
@@ -40093,14 +40108,17 @@
       <c r="C406" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D406" s="20" t="s">
-        <v>760</v>
+      <c r="D406" s="21" t="s">
+        <v>739</v>
       </c>
       <c r="E406" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F406" t="s">
-        <v>448</v>
+        <v>433</v>
+      </c>
+      <c r="G406" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="407" spans="1:7" ht="15" thickBot="1">
@@ -40109,14 +40127,17 @@
       <c r="C407" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D407" s="20" t="s">
-        <v>761</v>
+      <c r="D407" s="21" t="s">
+        <v>740</v>
       </c>
       <c r="E407" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F407" t="s">
-        <v>449</v>
+        <v>434</v>
+      </c>
+      <c r="G407" s="39" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="408" spans="1:7" ht="15" thickBot="1">
@@ -40125,14 +40146,17 @@
       <c r="C408" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D408" s="20" t="s">
-        <v>762</v>
+      <c r="D408" s="21" t="s">
+        <v>741</v>
       </c>
       <c r="E408" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F408" t="s">
-        <v>450</v>
+        <v>435</v>
+      </c>
+      <c r="G408" s="40" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="409" spans="1:7" ht="15" thickBot="1">
@@ -40141,14 +40165,17 @@
       <c r="C409" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D409" s="20" t="s">
-        <v>763</v>
+      <c r="D409" s="21" t="s">
+        <v>742</v>
       </c>
       <c r="E409" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F409" t="s">
-        <v>451</v>
+        <v>743</v>
+      </c>
+      <c r="G409" s="32" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="410" spans="1:7" ht="15" thickBot="1">
@@ -40157,16 +40184,18 @@
       <c r="C410" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D410" s="20" t="s">
-        <v>764</v>
+      <c r="D410" s="21" t="s">
+        <v>744</v>
       </c>
       <c r="E410" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F410" t="s">
-        <v>453</v>
-      </c>
-      <c r="G410" s="41"/>
+        <v>437</v>
+      </c>
+      <c r="G410" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="411" spans="1:7" ht="15" thickBot="1">
       <c r="A411" s="14"/>
@@ -40175,16 +40204,16 @@
         <v>767</v>
       </c>
       <c r="D411" s="21" t="s">
-        <v>765</v>
+        <v>745</v>
       </c>
       <c r="E411" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F411" t="s">
-        <v>485</v>
-      </c>
-      <c r="G411" t="s">
-        <v>484</v>
+        <v>746</v>
+      </c>
+      <c r="G411">
+        <v>120</v>
       </c>
     </row>
     <row r="412" spans="1:7" ht="15" thickBot="1">
@@ -40194,16 +40223,16 @@
         <v>767</v>
       </c>
       <c r="D412" s="21" t="s">
-        <v>766</v>
+        <v>747</v>
       </c>
       <c r="E412" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F412" t="s">
-        <v>486</v>
-      </c>
-      <c r="G412" t="s">
-        <v>483</v>
+        <v>748</v>
+      </c>
+      <c r="G412">
+        <v>30</v>
       </c>
     </row>
     <row r="413" spans="1:7" ht="15" thickBot="1">
@@ -40213,16 +40242,16 @@
         <v>767</v>
       </c>
       <c r="D413" s="21" t="s">
-        <v>768</v>
+        <v>749</v>
       </c>
       <c r="E413" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F413" t="s">
-        <v>485</v>
-      </c>
-      <c r="G413" t="s">
-        <v>484</v>
+        <v>750</v>
+      </c>
+      <c r="G413">
+        <v>60</v>
       </c>
     </row>
     <row r="414" spans="1:7" ht="15" thickBot="1">
@@ -40232,16 +40261,16 @@
         <v>767</v>
       </c>
       <c r="D414" s="21" t="s">
-        <v>769</v>
+        <v>751</v>
       </c>
       <c r="E414" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F414" t="s">
-        <v>486</v>
-      </c>
-      <c r="G414" t="s">
-        <v>483</v>
+        <v>752</v>
+      </c>
+      <c r="G414">
+        <v>70</v>
       </c>
     </row>
     <row r="415" spans="1:7" ht="15" thickBot="1">
@@ -40250,17 +40279,17 @@
       <c r="C415" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D415" s="20" t="s">
-        <v>770</v>
+      <c r="D415" s="21" t="s">
+        <v>753</v>
       </c>
       <c r="E415" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F415" t="s">
-        <v>495</v>
-      </c>
-      <c r="G415" t="s">
-        <v>490</v>
+        <v>754</v>
+      </c>
+      <c r="G415">
+        <v>90</v>
       </c>
     </row>
     <row r="416" spans="1:7" ht="15" thickBot="1">
@@ -40270,16 +40299,13 @@
         <v>767</v>
       </c>
       <c r="D416" s="20" t="s">
-        <v>771</v>
+        <v>755</v>
       </c>
       <c r="E416" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F416" t="s">
-        <v>496</v>
-      </c>
-      <c r="G416" t="s">
-        <v>497</v>
+        <v>443</v>
       </c>
     </row>
     <row r="417" spans="1:7" ht="15" thickBot="1">
@@ -40289,16 +40315,13 @@
         <v>767</v>
       </c>
       <c r="D417" s="20" t="s">
-        <v>772</v>
+        <v>756</v>
       </c>
       <c r="E417" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F417" t="s">
-        <v>498</v>
-      </c>
-      <c r="G417" s="42" t="s">
-        <v>493</v>
+        <v>444</v>
       </c>
     </row>
     <row r="418" spans="1:7" ht="15" thickBot="1">
@@ -40308,16 +40331,13 @@
         <v>767</v>
       </c>
       <c r="D418" s="20" t="s">
-        <v>773</v>
+        <v>757</v>
       </c>
       <c r="E418" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F418" t="s">
-        <v>499</v>
-      </c>
-      <c r="G418" t="s">
-        <v>494</v>
+        <v>447</v>
       </c>
     </row>
     <row r="419" spans="1:7" ht="15" thickBot="1">
@@ -40326,17 +40346,14 @@
       <c r="C419" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D419" s="21" t="s">
-        <v>774</v>
+      <c r="D419" s="20" t="s">
+        <v>758</v>
       </c>
       <c r="E419" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F419" t="s">
-        <v>524</v>
-      </c>
-      <c r="G419" s="42" t="s">
-        <v>501</v>
+        <v>759</v>
       </c>
     </row>
     <row r="420" spans="1:7" ht="15" thickBot="1">
@@ -40345,14 +40362,14 @@
       <c r="C420" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D420" s="21" t="s">
-        <v>775</v>
+      <c r="D420" s="20" t="s">
+        <v>760</v>
       </c>
       <c r="E420" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F420" t="s">
-        <v>525</v>
+        <v>448</v>
       </c>
     </row>
     <row r="421" spans="1:7" ht="15" thickBot="1">
@@ -40361,16 +40378,15 @@
       <c r="C421" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D421" s="21" t="s">
-        <v>776</v>
+      <c r="D421" s="20" t="s">
+        <v>761</v>
       </c>
       <c r="E421" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F421" t="s">
-        <v>526</v>
-      </c>
-      <c r="G421" s="43"/>
+        <v>449</v>
+      </c>
     </row>
     <row r="422" spans="1:7" ht="15" thickBot="1">
       <c r="A422" s="14"/>
@@ -40378,16 +40394,15 @@
       <c r="C422" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D422" s="21" t="s">
-        <v>777</v>
+      <c r="D422" s="20" t="s">
+        <v>762</v>
       </c>
       <c r="E422" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F422" t="s">
-        <v>527</v>
-      </c>
-      <c r="G422" s="44"/>
+        <v>450</v>
+      </c>
     </row>
     <row r="423" spans="1:7" ht="15" thickBot="1">
       <c r="A423" s="14"/>
@@ -40395,16 +40410,15 @@
       <c r="C423" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D423" s="21" t="s">
-        <v>778</v>
+      <c r="D423" s="20" t="s">
+        <v>763</v>
       </c>
       <c r="E423" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F423" t="s">
-        <v>528</v>
-      </c>
-      <c r="G423" s="44"/>
+        <v>451</v>
+      </c>
     </row>
     <row r="424" spans="1:7" ht="15" thickBot="1">
       <c r="A424" s="14"/>
@@ -40412,15 +40426,16 @@
       <c r="C424" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D424" s="21" t="s">
-        <v>779</v>
+      <c r="D424" s="20" t="s">
+        <v>764</v>
       </c>
       <c r="E424" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F424" t="s">
-        <v>529</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="G424" s="41"/>
     </row>
     <row r="425" spans="1:7" ht="15" thickBot="1">
       <c r="A425" s="14"/>
@@ -40429,13 +40444,16 @@
         <v>767</v>
       </c>
       <c r="D425" s="21" t="s">
-        <v>780</v>
+        <v>765</v>
       </c>
       <c r="E425" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F425" t="s">
-        <v>530</v>
+        <v>485</v>
+      </c>
+      <c r="G425" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="426" spans="1:7" ht="15" thickBot="1">
@@ -40445,13 +40463,16 @@
         <v>767</v>
       </c>
       <c r="D426" s="21" t="s">
-        <v>781</v>
+        <v>766</v>
       </c>
       <c r="E426" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F426" t="s">
-        <v>531</v>
+        <v>486</v>
+      </c>
+      <c r="G426" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="427" spans="1:7" ht="15" thickBot="1">
@@ -40461,13 +40482,16 @@
         <v>767</v>
       </c>
       <c r="D427" s="21" t="s">
-        <v>782</v>
+        <v>768</v>
       </c>
       <c r="E427" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F427" t="s">
-        <v>532</v>
+        <v>485</v>
+      </c>
+      <c r="G427" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="428" spans="1:7" ht="15" thickBot="1">
@@ -40477,16 +40501,16 @@
         <v>767</v>
       </c>
       <c r="D428" s="21" t="s">
-        <v>783</v>
+        <v>769</v>
       </c>
       <c r="E428" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F428" t="s">
-        <v>533</v>
+        <v>486</v>
       </c>
       <c r="G428" t="s">
-        <v>522</v>
+        <v>483</v>
       </c>
     </row>
     <row r="429" spans="1:7" ht="15" thickBot="1">
@@ -40495,17 +40519,17 @@
       <c r="C429" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D429" s="21" t="s">
-        <v>787</v>
+      <c r="D429" s="20" t="s">
+        <v>770</v>
       </c>
       <c r="E429" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F429" t="s">
-        <v>534</v>
-      </c>
-      <c r="G429" s="43" t="s">
-        <v>520</v>
+        <v>495</v>
+      </c>
+      <c r="G429" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="430" spans="1:7" ht="15" thickBot="1">
@@ -40514,14 +40538,17 @@
       <c r="C430" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D430" s="21" t="s">
-        <v>788</v>
+      <c r="D430" s="20" t="s">
+        <v>771</v>
       </c>
       <c r="E430" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F430" t="s">
-        <v>525</v>
+        <v>496</v>
+      </c>
+      <c r="G430" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="431" spans="1:7" ht="15" thickBot="1">
@@ -40530,17 +40557,17 @@
       <c r="C431" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D431" s="21" t="s">
-        <v>789</v>
+      <c r="D431" s="20" t="s">
+        <v>772</v>
       </c>
       <c r="E431" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F431" t="s">
-        <v>535</v>
-      </c>
-      <c r="G431" s="43" t="s">
-        <v>511</v>
+        <v>498</v>
+      </c>
+      <c r="G431" s="42" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="432" spans="1:7" ht="15" thickBot="1">
@@ -40549,17 +40576,17 @@
       <c r="C432" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D432" s="21" t="s">
-        <v>790</v>
+      <c r="D432" s="20" t="s">
+        <v>773</v>
       </c>
       <c r="E432" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F432" t="s">
-        <v>536</v>
-      </c>
-      <c r="G432" s="44" t="s">
-        <v>511</v>
+        <v>499</v>
+      </c>
+      <c r="G432" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="433" spans="1:7" ht="15" thickBot="1">
@@ -40569,16 +40596,16 @@
         <v>767</v>
       </c>
       <c r="D433" s="21" t="s">
-        <v>791</v>
+        <v>774</v>
       </c>
       <c r="E433" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F433" t="s">
-        <v>537</v>
-      </c>
-      <c r="G433" s="44" t="s">
-        <v>511</v>
+        <v>524</v>
+      </c>
+      <c r="G433" s="42" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="434" spans="1:7" ht="15" thickBot="1">
@@ -40588,13 +40615,13 @@
         <v>767</v>
       </c>
       <c r="D434" s="21" t="s">
-        <v>792</v>
+        <v>775</v>
       </c>
       <c r="E434" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F434" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
     </row>
     <row r="435" spans="1:7" ht="15" thickBot="1">
@@ -40604,17 +40631,15 @@
         <v>767</v>
       </c>
       <c r="D435" s="21" t="s">
-        <v>793</v>
+        <v>776</v>
       </c>
       <c r="E435" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F435" t="s">
-        <v>538</v>
-      </c>
-      <c r="G435" s="45" t="s">
-        <v>521</v>
-      </c>
+        <v>526</v>
+      </c>
+      <c r="G435" s="43"/>
     </row>
     <row r="436" spans="1:7" ht="15" thickBot="1">
       <c r="A436" s="14"/>
@@ -40623,17 +40648,15 @@
         <v>767</v>
       </c>
       <c r="D436" s="21" t="s">
-        <v>794</v>
+        <v>777</v>
       </c>
       <c r="E436" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F436" t="s">
-        <v>531</v>
-      </c>
-      <c r="G436" s="44" t="s">
-        <v>511</v>
-      </c>
+        <v>527</v>
+      </c>
+      <c r="G436" s="44"/>
     </row>
     <row r="437" spans="1:7" ht="15" thickBot="1">
       <c r="A437" s="14"/>
@@ -40642,17 +40665,15 @@
         <v>767</v>
       </c>
       <c r="D437" s="21" t="s">
-        <v>795</v>
+        <v>778</v>
       </c>
       <c r="E437" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F437" t="s">
-        <v>539</v>
-      </c>
-      <c r="G437" s="44" t="s">
-        <v>511</v>
-      </c>
+        <v>528</v>
+      </c>
+      <c r="G437" s="44"/>
     </row>
     <row r="438" spans="1:7" ht="15" thickBot="1">
       <c r="A438" s="14"/>
@@ -40661,16 +40682,13 @@
         <v>767</v>
       </c>
       <c r="D438" s="21" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E438" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F438" t="s">
-        <v>540</v>
-      </c>
-      <c r="G438" s="41" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
     </row>
     <row r="439" spans="1:7" ht="15" thickBot="1">
@@ -40679,17 +40697,14 @@
       <c r="C439" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D439" s="50" t="s">
-        <v>784</v>
+      <c r="D439" s="21" t="s">
+        <v>780</v>
       </c>
       <c r="E439" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F439" t="s">
-        <v>545</v>
-      </c>
-      <c r="G439" s="29" t="s">
-        <v>548</v>
+        <v>530</v>
       </c>
     </row>
     <row r="440" spans="1:7" ht="15" thickBot="1">
@@ -40698,17 +40713,14 @@
       <c r="C440" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D440" s="50" t="s">
-        <v>785</v>
+      <c r="D440" s="21" t="s">
+        <v>781</v>
       </c>
       <c r="E440" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F440" t="s">
-        <v>546</v>
-      </c>
-      <c r="G440" s="29" t="s">
-        <v>549</v>
+        <v>531</v>
       </c>
     </row>
     <row r="441" spans="1:7" ht="15" thickBot="1">
@@ -40717,17 +40729,14 @@
       <c r="C441" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D441" s="50" t="s">
-        <v>786</v>
+      <c r="D441" s="21" t="s">
+        <v>782</v>
       </c>
       <c r="E441" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F441" t="s">
-        <v>547</v>
-      </c>
-      <c r="G441" s="29" t="s">
-        <v>550</v>
+        <v>532</v>
       </c>
     </row>
     <row r="442" spans="1:7" ht="15" thickBot="1">
@@ -40736,17 +40745,17 @@
       <c r="C442" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D442" s="50" t="s">
-        <v>797</v>
+      <c r="D442" s="21" t="s">
+        <v>783</v>
       </c>
       <c r="E442" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F442" t="s">
-        <v>551</v>
-      </c>
-      <c r="G442" s="29" t="s">
-        <v>552</v>
+        <v>533</v>
+      </c>
+      <c r="G442" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="443" spans="1:7" ht="15" thickBot="1">
@@ -40755,17 +40764,17 @@
       <c r="C443" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D443" s="50" t="s">
-        <v>798</v>
+      <c r="D443" s="21" t="s">
+        <v>787</v>
       </c>
       <c r="E443" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F443" t="s">
-        <v>553</v>
-      </c>
-      <c r="G443" s="29" t="s">
-        <v>554</v>
+        <v>534</v>
+      </c>
+      <c r="G443" s="43" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="444" spans="1:7" ht="15" thickBot="1">
@@ -40774,17 +40783,14 @@
       <c r="C444" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D444" s="50" t="s">
-        <v>799</v>
+      <c r="D444" s="21" t="s">
+        <v>788</v>
       </c>
       <c r="E444" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F444" t="s">
-        <v>555</v>
-      </c>
-      <c r="G444" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="445" spans="1:7" ht="15" thickBot="1">
@@ -40793,14 +40799,17 @@
       <c r="C445" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D445" s="51" t="s">
-        <v>800</v>
+      <c r="D445" s="21" t="s">
+        <v>789</v>
       </c>
       <c r="E445" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F445" t="s">
-        <v>563</v>
+        <v>535</v>
+      </c>
+      <c r="G445" s="43" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="446" spans="1:7" ht="15" thickBot="1">
@@ -40809,17 +40818,17 @@
       <c r="C446" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D446" s="51" t="s">
-        <v>801</v>
+      <c r="D446" s="21" t="s">
+        <v>790</v>
       </c>
       <c r="E446" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F446" s="48" t="s">
-        <v>572</v>
-      </c>
-      <c r="G446" t="s">
-        <v>558</v>
+        <v>2</v>
+      </c>
+      <c r="F446" t="s">
+        <v>536</v>
+      </c>
+      <c r="G446" s="44" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="447" spans="1:7" ht="15" thickBot="1">
@@ -40828,17 +40837,17 @@
       <c r="C447" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D447" s="51" t="s">
-        <v>802</v>
+      <c r="D447" s="21" t="s">
+        <v>791</v>
       </c>
       <c r="E447" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F447" t="s">
-        <v>564</v>
-      </c>
-      <c r="G447" t="s">
-        <v>565</v>
+        <v>537</v>
+      </c>
+      <c r="G447" s="44" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="448" spans="1:7" ht="15" thickBot="1">
@@ -40847,17 +40856,14 @@
       <c r="C448" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D448" s="51" t="s">
-        <v>803</v>
+      <c r="D448" s="21" t="s">
+        <v>792</v>
       </c>
       <c r="E448" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F448" t="s">
-        <v>566</v>
-      </c>
-      <c r="G448" t="s">
-        <v>567</v>
+        <v>529</v>
       </c>
     </row>
     <row r="449" spans="1:7" ht="15" thickBot="1">
@@ -40866,14 +40872,17 @@
       <c r="C449" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D449" s="51" t="s">
-        <v>813</v>
+      <c r="D449" s="21" t="s">
+        <v>793</v>
       </c>
       <c r="E449" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F449" t="s">
-        <v>568</v>
+        <v>538</v>
+      </c>
+      <c r="G449" s="45" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="450" spans="1:7" ht="15" thickBot="1">
@@ -40882,17 +40891,17 @@
       <c r="C450" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D450" s="51" t="s">
-        <v>814</v>
+      <c r="D450" s="21" t="s">
+        <v>794</v>
       </c>
       <c r="E450" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F450" s="48" t="s">
-        <v>571</v>
-      </c>
-      <c r="G450" t="s">
-        <v>558</v>
+        <v>4</v>
+      </c>
+      <c r="F450" t="s">
+        <v>531</v>
+      </c>
+      <c r="G450" s="44" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="451" spans="1:7" ht="15" thickBot="1">
@@ -40901,17 +40910,17 @@
       <c r="C451" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D451" s="51" t="s">
-        <v>815</v>
+      <c r="D451" s="21" t="s">
+        <v>795</v>
       </c>
       <c r="E451" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F451" t="s">
-        <v>569</v>
-      </c>
-      <c r="G451" t="s">
-        <v>557</v>
+        <v>539</v>
+      </c>
+      <c r="G451" s="44" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="452" spans="1:7" ht="15" thickBot="1">
@@ -40920,14 +40929,17 @@
       <c r="C452" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D452" s="51" t="s">
-        <v>816</v>
+      <c r="D452" s="21" t="s">
+        <v>796</v>
       </c>
       <c r="E452" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F452" t="s">
-        <v>570</v>
+        <v>540</v>
+      </c>
+      <c r="G452" s="41" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="453" spans="1:7" ht="15" thickBot="1">
@@ -40936,14 +40948,17 @@
       <c r="C453" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D453" s="52" t="s">
-        <v>804</v>
+      <c r="D453" s="50" t="s">
+        <v>784</v>
       </c>
       <c r="E453" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F453" t="s">
-        <v>585</v>
+        <v>545</v>
+      </c>
+      <c r="G453" s="29" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="454" spans="1:7" ht="15" thickBot="1">
@@ -40952,14 +40967,17 @@
       <c r="C454" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D454" s="52" t="s">
-        <v>817</v>
+      <c r="D454" s="50" t="s">
+        <v>785</v>
       </c>
       <c r="E454" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F454" t="s">
-        <v>575</v>
+        <v>546</v>
+      </c>
+      <c r="G454" s="29" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="455" spans="1:7" ht="15" thickBot="1">
@@ -40968,14 +40986,17 @@
       <c r="C455" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D455" s="20" t="s">
-        <v>805</v>
+      <c r="D455" s="50" t="s">
+        <v>786</v>
       </c>
       <c r="E455" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F455" t="s">
-        <v>580</v>
+        <v>547</v>
+      </c>
+      <c r="G455" s="29" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="456" spans="1:7" ht="15" thickBot="1">
@@ -40984,17 +41005,17 @@
       <c r="C456" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D456" s="20" t="s">
-        <v>806</v>
+      <c r="D456" s="50" t="s">
+        <v>797</v>
       </c>
       <c r="E456" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F456" s="68" t="s">
-        <v>602</v>
-      </c>
-      <c r="G456" t="s">
-        <v>558</v>
+        <v>4</v>
+      </c>
+      <c r="F456" t="s">
+        <v>551</v>
+      </c>
+      <c r="G456" s="29" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="457" spans="1:7" ht="15" thickBot="1">
@@ -41003,14 +41024,17 @@
       <c r="C457" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D457" s="20" t="s">
-        <v>807</v>
-      </c>
-      <c r="E457" s="19" t="s">
-        <v>12</v>
+      <c r="D457" s="50" t="s">
+        <v>798</v>
+      </c>
+      <c r="E457" s="17" t="s">
+        <v>4</v>
       </c>
       <c r="F457" t="s">
-        <v>581</v>
+        <v>553</v>
+      </c>
+      <c r="G457" s="29" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="458" spans="1:7" ht="15" thickBot="1">
@@ -41019,14 +41043,17 @@
       <c r="C458" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D458" s="20" t="s">
-        <v>818</v>
+      <c r="D458" s="50" t="s">
+        <v>799</v>
       </c>
       <c r="E458" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F458" t="s">
-        <v>582</v>
+        <v>555</v>
+      </c>
+      <c r="G458" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="459" spans="1:7" ht="15" thickBot="1">
@@ -41035,242 +41062,259 @@
       <c r="C459" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D459" s="20" t="s">
-        <v>819</v>
+      <c r="D459" s="51" t="s">
+        <v>800</v>
       </c>
       <c r="E459" s="17" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F459" t="s">
-        <v>583</v>
-      </c>
-      <c r="G459" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="460" spans="1:7">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="460" spans="1:7" ht="15" thickBot="1">
       <c r="A460" s="14"/>
       <c r="B460" s="14"/>
       <c r="C460" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D460" s="20" t="s">
-        <v>820</v>
-      </c>
-      <c r="E460" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="F460" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="461" spans="1:7">
+      <c r="D460" s="51" t="s">
+        <v>801</v>
+      </c>
+      <c r="E460" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F460" s="48" t="s">
+        <v>572</v>
+      </c>
+      <c r="G460" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="461" spans="1:7" ht="15" thickBot="1">
       <c r="A461" s="14"/>
       <c r="B461" s="14"/>
       <c r="C461" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D461" s="53" t="s">
-        <v>808</v>
-      </c>
-      <c r="E461" s="19" t="s">
+      <c r="D461" s="51" t="s">
+        <v>802</v>
+      </c>
+      <c r="E461" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F461" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="462" spans="1:7">
+        <v>564</v>
+      </c>
+      <c r="G461" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="462" spans="1:7" ht="15" thickBot="1">
       <c r="A462" s="14"/>
       <c r="B462" s="14"/>
       <c r="C462" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D462" s="53" t="s">
-        <v>809</v>
-      </c>
-      <c r="E462" s="19" t="s">
-        <v>7</v>
+      <c r="D462" s="51" t="s">
+        <v>803</v>
+      </c>
+      <c r="E462" s="17" t="s">
+        <v>4</v>
       </c>
       <c r="F462" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="463" spans="1:7">
+        <v>566</v>
+      </c>
+      <c r="G462" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="463" spans="1:7" ht="15" thickBot="1">
       <c r="A463" s="14"/>
       <c r="B463" s="14"/>
       <c r="C463" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D463" s="53" t="s">
-        <v>810</v>
-      </c>
-      <c r="E463" s="19" t="s">
-        <v>12</v>
+      <c r="D463" s="51" t="s">
+        <v>813</v>
+      </c>
+      <c r="E463" s="17" t="s">
+        <v>4</v>
       </c>
       <c r="F463" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="464" spans="1:7">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="464" spans="1:7" ht="15" thickBot="1">
       <c r="A464" s="14"/>
       <c r="B464" s="14"/>
       <c r="C464" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D464" s="53" t="s">
-        <v>821</v>
-      </c>
-      <c r="E464" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="F464" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="465" spans="1:7">
+      <c r="D464" s="51" t="s">
+        <v>814</v>
+      </c>
+      <c r="E464" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F464" s="48" t="s">
+        <v>571</v>
+      </c>
+      <c r="G464" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="465" spans="1:7" ht="15" thickBot="1">
       <c r="A465" s="14"/>
       <c r="B465" s="14"/>
       <c r="C465" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D465" s="53" t="s">
-        <v>822</v>
-      </c>
-      <c r="E465" s="19" t="s">
-        <v>7</v>
+      <c r="D465" s="51" t="s">
+        <v>815</v>
+      </c>
+      <c r="E465" s="17" t="s">
+        <v>4</v>
       </c>
       <c r="F465" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="466" spans="1:7">
+        <v>569</v>
+      </c>
+      <c r="G465" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="466" spans="1:7" ht="15" thickBot="1">
       <c r="A466" s="14"/>
       <c r="B466" s="14"/>
       <c r="C466" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D466" s="53" t="s">
-        <v>823</v>
-      </c>
-      <c r="E466" s="19" t="s">
-        <v>12</v>
+      <c r="D466" s="51" t="s">
+        <v>816</v>
+      </c>
+      <c r="E466" s="17" t="s">
+        <v>4</v>
       </c>
       <c r="F466" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="467" spans="1:7">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="467" spans="1:7" ht="15" thickBot="1">
       <c r="A467" s="14"/>
       <c r="B467" s="14"/>
       <c r="C467" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D467" s="36" t="s">
-        <v>811</v>
-      </c>
-      <c r="E467" s="19"/>
+      <c r="D467" s="52" t="s">
+        <v>804</v>
+      </c>
+      <c r="E467" s="17" t="s">
+        <v>4</v>
+      </c>
       <c r="F467" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="468" spans="1:7">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="468" spans="1:7" ht="15" thickBot="1">
       <c r="A468" s="14"/>
       <c r="B468" s="14"/>
       <c r="C468" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D468" s="36" t="s">
-        <v>824</v>
-      </c>
-      <c r="E468" s="19"/>
+      <c r="D468" s="52" t="s">
+        <v>817</v>
+      </c>
+      <c r="E468" s="17" t="s">
+        <v>4</v>
+      </c>
       <c r="F468" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="469" spans="1:7">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="469" spans="1:7" ht="15" thickBot="1">
       <c r="A469" s="14"/>
       <c r="B469" s="14"/>
       <c r="C469" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D469" s="36" t="s">
-        <v>812</v>
-      </c>
-      <c r="E469" s="19"/>
+      <c r="D469" s="20" t="s">
+        <v>805</v>
+      </c>
+      <c r="E469" s="17" t="s">
+        <v>4</v>
+      </c>
       <c r="F469" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="470" spans="1:7">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="470" spans="1:7" ht="15" thickBot="1">
       <c r="A470" s="14"/>
       <c r="B470" s="14"/>
       <c r="C470" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D470" s="36" t="s">
-        <v>825</v>
-      </c>
-      <c r="E470" s="19"/>
-      <c r="F470" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="471" spans="1:7">
+      <c r="D470" s="20" t="s">
+        <v>806</v>
+      </c>
+      <c r="E470" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F470" s="68" t="s">
+        <v>602</v>
+      </c>
+      <c r="G470" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="471" spans="1:7" ht="15" thickBot="1">
       <c r="A471" s="14"/>
       <c r="B471" s="14"/>
       <c r="C471" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D471" s="1" t="s">
-        <v>826</v>
-      </c>
-      <c r="E471" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F471" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="G471" s="3" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="472" spans="1:7">
+      <c r="D471" s="20" t="s">
+        <v>807</v>
+      </c>
+      <c r="E471" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F471" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="472" spans="1:7" ht="15" thickBot="1">
       <c r="A472" s="14"/>
       <c r="B472" s="14"/>
       <c r="C472" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D472" s="18" t="s">
-        <v>827</v>
-      </c>
-      <c r="E472" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F472" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="G472" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="473" spans="1:7">
+      <c r="D472" s="20" t="s">
+        <v>818</v>
+      </c>
+      <c r="E472" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="F472" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="473" spans="1:7" ht="15" thickBot="1">
       <c r="A473" s="14"/>
       <c r="B473" s="14"/>
       <c r="C473" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D473" s="18" t="s">
-        <v>828</v>
-      </c>
-      <c r="E473" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F473" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="G473" s="3" t="s">
-        <v>153</v>
+      <c r="D473" s="20" t="s">
+        <v>819</v>
+      </c>
+      <c r="E473" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F473" t="s">
+        <v>583</v>
+      </c>
+      <c r="G473" t="s">
+        <v>558</v>
       </c>
     </row>
     <row r="474" spans="1:7">
@@ -41279,17 +41323,14 @@
       <c r="C474" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D474" s="18" t="s">
-        <v>829</v>
-      </c>
-      <c r="E474" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F474" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="G474" s="3" t="s">
-        <v>149</v>
+      <c r="D474" s="20" t="s">
+        <v>820</v>
+      </c>
+      <c r="E474" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F474" t="s">
+        <v>584</v>
       </c>
     </row>
     <row r="475" spans="1:7">
@@ -41298,17 +41339,14 @@
       <c r="C475" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D475" s="1" t="s">
-        <v>830</v>
-      </c>
-      <c r="E475" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F475" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="G475" s="3" t="s">
-        <v>149</v>
+      <c r="D475" s="53" t="s">
+        <v>808</v>
+      </c>
+      <c r="E475" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F475" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="476" spans="1:7">
@@ -41317,17 +41355,14 @@
       <c r="C476" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D476" s="18" t="s">
-        <v>831</v>
-      </c>
-      <c r="E476" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F476" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="G476" s="3" t="s">
-        <v>151</v>
+      <c r="D476" s="53" t="s">
+        <v>809</v>
+      </c>
+      <c r="E476" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F476" t="s">
+        <v>588</v>
       </c>
     </row>
     <row r="477" spans="1:7">
@@ -41336,17 +41371,14 @@
       <c r="C477" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D477" s="18" t="s">
-        <v>832</v>
-      </c>
-      <c r="E477" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F477" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="G477" s="3" t="s">
-        <v>153</v>
+      <c r="D477" s="53" t="s">
+        <v>810</v>
+      </c>
+      <c r="E477" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F477" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="478" spans="1:7">
@@ -41355,788 +41387,825 @@
       <c r="C478" s="14" t="s">
         <v>767</v>
       </c>
-      <c r="D478" s="18" t="s">
-        <v>833</v>
-      </c>
-      <c r="E478" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F478" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="G478" s="3" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="479" spans="1:7" ht="15.5">
-      <c r="A479" s="1"/>
-      <c r="B479" s="1"/>
-      <c r="C479" s="16" t="s">
-        <v>650</v>
-      </c>
-      <c r="D479" s="56" t="s">
-        <v>651</v>
-      </c>
-      <c r="E479" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F479" s="4"/>
-      <c r="G479" s="5"/>
+      <c r="D478" s="53" t="s">
+        <v>821</v>
+      </c>
+      <c r="E478" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F478" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="479" spans="1:7">
+      <c r="A479" s="14"/>
+      <c r="B479" s="14"/>
+      <c r="C479" s="14" t="s">
+        <v>767</v>
+      </c>
+      <c r="D479" s="53" t="s">
+        <v>822</v>
+      </c>
+      <c r="E479" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F479" t="s">
+        <v>590</v>
+      </c>
     </row>
     <row r="480" spans="1:7">
-      <c r="C480" s="16" t="s">
-        <v>650</v>
-      </c>
-      <c r="D480" s="15" t="s">
-        <v>840</v>
-      </c>
-      <c r="E480" s="3" t="s">
-        <v>2</v>
+      <c r="A480" s="14"/>
+      <c r="B480" s="14"/>
+      <c r="C480" s="14" t="s">
+        <v>767</v>
+      </c>
+      <c r="D480" s="53" t="s">
+        <v>823</v>
+      </c>
+      <c r="E480" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F480" t="s">
+        <v>591</v>
       </c>
     </row>
     <row r="481" spans="1:7">
       <c r="A481" s="14"/>
       <c r="B481" s="14"/>
-      <c r="C481" s="16" t="s">
-        <v>650</v>
-      </c>
-      <c r="D481" s="15" t="s">
-        <v>841</v>
-      </c>
-      <c r="E481" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F481" s="14"/>
-      <c r="G481" s="14"/>
+      <c r="C481" s="14" t="s">
+        <v>767</v>
+      </c>
+      <c r="D481" s="36" t="s">
+        <v>811</v>
+      </c>
+      <c r="E481" s="19"/>
+      <c r="F481" t="s">
+        <v>615</v>
+      </c>
     </row>
     <row r="482" spans="1:7">
       <c r="A482" s="14"/>
       <c r="B482" s="14"/>
-      <c r="C482" s="16" t="s">
-        <v>650</v>
-      </c>
-      <c r="D482" s="15" t="s">
-        <v>652</v>
-      </c>
-      <c r="E482" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F482" s="14"/>
-      <c r="G482" s="14"/>
+      <c r="C482" s="14" t="s">
+        <v>767</v>
+      </c>
+      <c r="D482" s="36" t="s">
+        <v>824</v>
+      </c>
+      <c r="E482" s="19"/>
+      <c r="F482" t="s">
+        <v>614</v>
+      </c>
     </row>
     <row r="483" spans="1:7">
       <c r="A483" s="14"/>
       <c r="B483" s="14"/>
       <c r="C483" s="14" t="s">
-        <v>837</v>
+        <v>767</v>
       </c>
       <c r="D483" s="36" t="s">
-        <v>626</v>
-      </c>
-      <c r="E483" s="3"/>
-      <c r="F483" s="14"/>
-      <c r="G483" s="14"/>
+        <v>812</v>
+      </c>
+      <c r="E483" s="19"/>
+      <c r="F483" t="s">
+        <v>613</v>
+      </c>
     </row>
     <row r="484" spans="1:7">
       <c r="A484" s="14"/>
       <c r="B484" s="14"/>
       <c r="C484" s="14" t="s">
-        <v>837</v>
+        <v>767</v>
       </c>
       <c r="D484" s="36" t="s">
-        <v>276</v>
-      </c>
-      <c r="E484" s="3"/>
-      <c r="F484" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="G484" s="14"/>
+        <v>825</v>
+      </c>
+      <c r="E484" s="19"/>
+      <c r="F484" t="s">
+        <v>612</v>
+      </c>
     </row>
     <row r="485" spans="1:7">
       <c r="A485" s="14"/>
       <c r="B485" s="14"/>
       <c r="C485" s="14" t="s">
-        <v>837</v>
-      </c>
-      <c r="D485" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="E485" s="3"/>
-      <c r="F485" s="13" t="s">
-        <v>246</v>
-      </c>
-      <c r="G485" s="14"/>
+        <v>767</v>
+      </c>
+      <c r="D485" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="E485" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F485" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="G485" s="3" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="486" spans="1:7">
       <c r="A486" s="14"/>
       <c r="B486" s="14"/>
       <c r="C486" s="14" t="s">
-        <v>837</v>
-      </c>
-      <c r="D486" s="36" t="s">
-        <v>653</v>
-      </c>
-      <c r="E486" s="3"/>
-      <c r="F486" s="13" t="s">
-        <v>657</v>
-      </c>
-      <c r="G486" s="14"/>
+        <v>767</v>
+      </c>
+      <c r="D486" s="18" t="s">
+        <v>827</v>
+      </c>
+      <c r="E486" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F486" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="G486" s="3" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="487" spans="1:7">
       <c r="A487" s="14"/>
       <c r="B487" s="14"/>
       <c r="C487" s="14" t="s">
-        <v>837</v>
-      </c>
-      <c r="D487" s="36" t="s">
-        <v>654</v>
-      </c>
-      <c r="E487" s="3"/>
-      <c r="F487" s="13" t="s">
-        <v>658</v>
-      </c>
-      <c r="G487" s="14"/>
+        <v>767</v>
+      </c>
+      <c r="D487" s="18" t="s">
+        <v>828</v>
+      </c>
+      <c r="E487" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F487" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="G487" s="3" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="488" spans="1:7">
       <c r="A488" s="14"/>
       <c r="B488" s="14"/>
       <c r="C488" s="14" t="s">
-        <v>837</v>
-      </c>
-      <c r="D488" s="36" t="s">
-        <v>655</v>
-      </c>
-      <c r="E488" s="3"/>
-      <c r="F488" s="13" t="s">
-        <v>659</v>
-      </c>
-      <c r="G488" s="14"/>
+        <v>767</v>
+      </c>
+      <c r="D488" s="18" t="s">
+        <v>829</v>
+      </c>
+      <c r="E488" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F488" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="G488" s="3" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="489" spans="1:7">
       <c r="A489" s="14"/>
       <c r="B489" s="14"/>
       <c r="C489" s="14" t="s">
-        <v>837</v>
-      </c>
-      <c r="D489" s="36" t="s">
-        <v>656</v>
-      </c>
-      <c r="E489" s="3"/>
-      <c r="F489" s="13" t="s">
-        <v>660</v>
-      </c>
-      <c r="G489" s="14"/>
+        <v>767</v>
+      </c>
+      <c r="D489" s="1" t="s">
+        <v>830</v>
+      </c>
+      <c r="E489" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F489" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="G489" s="3" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="490" spans="1:7">
       <c r="A490" s="14"/>
       <c r="B490" s="14"/>
-      <c r="C490" s="14"/>
-      <c r="D490" s="36"/>
-      <c r="E490" s="3"/>
-      <c r="F490" s="13"/>
-      <c r="G490" s="14"/>
+      <c r="C490" s="14" t="s">
+        <v>767</v>
+      </c>
+      <c r="D490" s="18" t="s">
+        <v>831</v>
+      </c>
+      <c r="E490" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F490" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="G490" s="3" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="491" spans="1:7">
       <c r="A491" s="14"/>
       <c r="B491" s="14"/>
-      <c r="C491" s="14"/>
-      <c r="D491" s="36"/>
-      <c r="E491" s="3"/>
-      <c r="F491" s="13"/>
-      <c r="G491" s="14"/>
+      <c r="C491" s="14" t="s">
+        <v>767</v>
+      </c>
+      <c r="D491" s="18" t="s">
+        <v>832</v>
+      </c>
+      <c r="E491" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F491" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="G491" s="3" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="492" spans="1:7">
       <c r="A492" s="14"/>
       <c r="B492" s="14"/>
-      <c r="C492" s="14"/>
-      <c r="D492" s="36"/>
-      <c r="E492" s="3"/>
-      <c r="F492" s="13"/>
-      <c r="G492" s="14"/>
-    </row>
-    <row r="493" spans="1:7">
-      <c r="A493" s="14"/>
-      <c r="B493" s="14"/>
-      <c r="C493" s="14"/>
-      <c r="D493" s="36"/>
-      <c r="E493" s="3"/>
-      <c r="F493" s="13"/>
-      <c r="G493" s="14"/>
+      <c r="C492" s="14" t="s">
+        <v>767</v>
+      </c>
+      <c r="D492" s="18" t="s">
+        <v>833</v>
+      </c>
+      <c r="E492" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F492" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="G492" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="493" spans="1:7" ht="15.5">
+      <c r="A493" s="1"/>
+      <c r="B493" s="1"/>
+      <c r="C493" s="16" t="s">
+        <v>650</v>
+      </c>
+      <c r="D493" s="56" t="s">
+        <v>651</v>
+      </c>
+      <c r="E493" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F493" s="4"/>
+      <c r="G493" s="5"/>
     </row>
     <row r="494" spans="1:7">
-      <c r="A494" s="14"/>
-      <c r="B494" s="14"/>
-      <c r="C494" s="14"/>
-      <c r="D494" s="36"/>
-      <c r="E494" s="3"/>
-      <c r="F494" s="13"/>
-      <c r="G494" s="14"/>
+      <c r="C494" s="16" t="s">
+        <v>650</v>
+      </c>
+      <c r="D494" s="15" t="s">
+        <v>840</v>
+      </c>
+      <c r="E494" s="3" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="495" spans="1:7">
       <c r="A495" s="14"/>
       <c r="B495" s="14"/>
-      <c r="C495" s="14"/>
-      <c r="D495" s="36"/>
-      <c r="E495" s="3"/>
-      <c r="F495" s="13"/>
+      <c r="C495" s="16" t="s">
+        <v>650</v>
+      </c>
+      <c r="D495" s="15" t="s">
+        <v>841</v>
+      </c>
+      <c r="E495" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F495" s="14"/>
       <c r="G495" s="14"/>
     </row>
     <row r="496" spans="1:7">
       <c r="A496" s="14"/>
       <c r="B496" s="14"/>
-      <c r="C496" s="14"/>
-      <c r="D496" s="36"/>
-      <c r="E496" s="3"/>
-      <c r="F496" s="13"/>
+      <c r="C496" s="16" t="s">
+        <v>650</v>
+      </c>
+      <c r="D496" s="15" t="s">
+        <v>652</v>
+      </c>
+      <c r="E496" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F496" s="14"/>
       <c r="G496" s="14"/>
     </row>
-    <row r="497" spans="1:7" ht="15.5">
-      <c r="A497" s="1"/>
-      <c r="B497" s="1"/>
-      <c r="C497" s="1"/>
-      <c r="D497" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E497" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F497" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="G497" s="5"/>
-    </row>
-    <row r="498" spans="1:7" ht="15.5">
-      <c r="A498" s="1"/>
-      <c r="B498" s="1"/>
-      <c r="C498" s="1"/>
-      <c r="D498" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E498" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F498" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G498" s="5"/>
+    <row r="497" spans="1:7">
+      <c r="A497" s="14"/>
+      <c r="B497" s="14"/>
+      <c r="C497" s="14" t="s">
+        <v>837</v>
+      </c>
+      <c r="D497" s="36" t="s">
+        <v>626</v>
+      </c>
+      <c r="E497" s="3"/>
+      <c r="F497" s="14"/>
+      <c r="G497" s="14"/>
+    </row>
+    <row r="498" spans="1:7">
+      <c r="A498" s="14"/>
+      <c r="B498" s="14"/>
+      <c r="C498" s="14" t="s">
+        <v>837</v>
+      </c>
+      <c r="D498" s="36" t="s">
+        <v>276</v>
+      </c>
+      <c r="E498" s="3"/>
+      <c r="F498" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="G498" s="14"/>
     </row>
     <row r="499" spans="1:7">
       <c r="A499" s="14"/>
       <c r="B499" s="14"/>
-      <c r="C499" s="14"/>
-      <c r="D499" s="15"/>
+      <c r="C499" s="14" t="s">
+        <v>837</v>
+      </c>
+      <c r="D499" s="36" t="s">
+        <v>277</v>
+      </c>
       <c r="E499" s="3"/>
-      <c r="F499" s="14"/>
+      <c r="F499" s="13" t="s">
+        <v>246</v>
+      </c>
       <c r="G499" s="14"/>
     </row>
     <row r="500" spans="1:7">
       <c r="A500" s="14"/>
       <c r="B500" s="14"/>
-      <c r="C500" s="14"/>
-      <c r="D500" s="15"/>
+      <c r="C500" s="14" t="s">
+        <v>837</v>
+      </c>
+      <c r="D500" s="36" t="s">
+        <v>653</v>
+      </c>
       <c r="E500" s="3"/>
-      <c r="F500" s="14"/>
+      <c r="F500" s="13" t="s">
+        <v>657</v>
+      </c>
       <c r="G500" s="14"/>
     </row>
     <row r="501" spans="1:7">
-      <c r="A501" s="1"/>
-      <c r="B501" s="1"/>
-      <c r="C501" s="1"/>
-      <c r="D501" s="1"/>
+      <c r="A501" s="14"/>
+      <c r="B501" s="14"/>
+      <c r="C501" s="14" t="s">
+        <v>837</v>
+      </c>
+      <c r="D501" s="36" t="s">
+        <v>654</v>
+      </c>
       <c r="E501" s="3"/>
-      <c r="F501" s="4"/>
-      <c r="G501" s="3"/>
-    </row>
-    <row r="502" spans="1:7" ht="15.5">
-      <c r="A502" s="1"/>
-      <c r="B502" s="1"/>
-      <c r="C502" s="1"/>
-      <c r="D502" s="13"/>
+      <c r="F501" s="13" t="s">
+        <v>658</v>
+      </c>
+      <c r="G501" s="14"/>
+    </row>
+    <row r="502" spans="1:7">
+      <c r="A502" s="14"/>
+      <c r="B502" s="14"/>
+      <c r="C502" s="14" t="s">
+        <v>837</v>
+      </c>
+      <c r="D502" s="36" t="s">
+        <v>655</v>
+      </c>
       <c r="E502" s="3"/>
-      <c r="F502" s="4"/>
-      <c r="G502" s="5"/>
-    </row>
-    <row r="503" spans="1:7" ht="15.5">
-      <c r="A503" s="1"/>
-      <c r="B503" s="1"/>
-      <c r="C503" s="1"/>
-      <c r="D503" s="13"/>
+      <c r="F502" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="G502" s="14"/>
+    </row>
+    <row r="503" spans="1:7">
+      <c r="A503" s="14"/>
+      <c r="B503" s="14"/>
+      <c r="C503" s="14" t="s">
+        <v>837</v>
+      </c>
+      <c r="D503" s="36" t="s">
+        <v>656</v>
+      </c>
       <c r="E503" s="3"/>
-      <c r="F503" s="4"/>
-      <c r="G503" s="5"/>
-    </row>
-    <row r="504" spans="1:7" ht="15.5">
-      <c r="A504" s="1"/>
-      <c r="B504" s="1"/>
-      <c r="C504" s="1"/>
-      <c r="D504" s="13"/>
+      <c r="F503" s="13" t="s">
+        <v>660</v>
+      </c>
+      <c r="G503" s="14"/>
+    </row>
+    <row r="504" spans="1:7">
+      <c r="A504" s="14"/>
+      <c r="B504" s="14"/>
+      <c r="C504" s="14"/>
+      <c r="D504" s="36"/>
       <c r="E504" s="3"/>
-      <c r="F504" s="4"/>
-      <c r="G504" s="5"/>
+      <c r="F504" s="13"/>
+      <c r="G504" s="14"/>
     </row>
     <row r="505" spans="1:7">
-      <c r="A505" s="1"/>
-      <c r="B505" s="1"/>
-      <c r="C505" s="6"/>
-      <c r="D505" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="E505" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F505" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G505" s="3" t="s">
-        <v>21</v>
-      </c>
+      <c r="A505" s="14"/>
+      <c r="B505" s="14"/>
+      <c r="C505" s="14"/>
+      <c r="D505" s="36"/>
+      <c r="E505" s="3"/>
+      <c r="F505" s="13"/>
+      <c r="G505" s="14"/>
     </row>
     <row r="506" spans="1:7">
-      <c r="A506" s="1"/>
-      <c r="B506" s="1"/>
-      <c r="C506" s="6"/>
-      <c r="D506" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="E506" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F506" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G506" s="3" t="s">
-        <v>24</v>
-      </c>
+      <c r="A506" s="14"/>
+      <c r="B506" s="14"/>
+      <c r="C506" s="14"/>
+      <c r="D506" s="36"/>
+      <c r="E506" s="3"/>
+      <c r="F506" s="13"/>
+      <c r="G506" s="14"/>
     </row>
     <row r="507" spans="1:7">
-      <c r="A507" s="1"/>
-      <c r="B507" s="1"/>
-      <c r="C507" s="6"/>
-      <c r="D507" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E507" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F507" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G507" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="A507" s="14"/>
+      <c r="B507" s="14"/>
+      <c r="C507" s="14"/>
+      <c r="D507" s="36"/>
+      <c r="E507" s="3"/>
+      <c r="F507" s="13"/>
+      <c r="G507" s="14"/>
     </row>
     <row r="508" spans="1:7">
-      <c r="A508" s="1"/>
-      <c r="B508" s="1"/>
-      <c r="C508" s="6"/>
-      <c r="D508" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E508" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F508" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G508" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="A508" s="14"/>
+      <c r="B508" s="14"/>
+      <c r="C508" s="14"/>
+      <c r="D508" s="36"/>
+      <c r="E508" s="3"/>
+      <c r="F508" s="13"/>
+      <c r="G508" s="14"/>
     </row>
     <row r="509" spans="1:7">
-      <c r="A509" s="1"/>
-      <c r="B509" s="1"/>
-      <c r="C509" s="1"/>
-      <c r="D509" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E509" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F509" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G509" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="510" spans="1:7" ht="26">
-      <c r="A510" s="1"/>
-      <c r="B510" s="1"/>
-      <c r="C510" s="7"/>
-      <c r="D510" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E510" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F510" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G510" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="511" spans="1:7">
-      <c r="A511" s="12"/>
-      <c r="B511" s="12"/>
-      <c r="C511" s="12"/>
-      <c r="D511" s="149" t="s">
-        <v>35</v>
-      </c>
-      <c r="E511" s="150" t="s">
-        <v>4</v>
-      </c>
-      <c r="F511" s="151" t="s">
-        <v>36</v>
-      </c>
-      <c r="G511" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="512" spans="1:7">
-      <c r="A512" s="12"/>
-      <c r="B512" s="12"/>
-      <c r="C512" s="12"/>
-      <c r="D512" s="149"/>
-      <c r="E512" s="150"/>
-      <c r="F512" s="151"/>
-      <c r="G512" s="3" t="s">
-        <v>38</v>
-      </c>
+      <c r="A509" s="14"/>
+      <c r="B509" s="14"/>
+      <c r="C509" s="14"/>
+      <c r="D509" s="36"/>
+      <c r="E509" s="3"/>
+      <c r="F509" s="13"/>
+      <c r="G509" s="14"/>
+    </row>
+    <row r="510" spans="1:7">
+      <c r="A510" s="14"/>
+      <c r="B510" s="14"/>
+      <c r="C510" s="14"/>
+      <c r="D510" s="36"/>
+      <c r="E510" s="3"/>
+      <c r="F510" s="13"/>
+      <c r="G510" s="14"/>
+    </row>
+    <row r="511" spans="1:7" ht="15.5">
+      <c r="A511" s="1"/>
+      <c r="B511" s="1"/>
+      <c r="C511" s="1"/>
+      <c r="D511" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E511" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F511" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G511" s="5"/>
+    </row>
+    <row r="512" spans="1:7" ht="15.5">
+      <c r="A512" s="1"/>
+      <c r="B512" s="1"/>
+      <c r="C512" s="1"/>
+      <c r="D512" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E512" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F512" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G512" s="5"/>
+    </row>
+    <row r="513" spans="1:7">
+      <c r="A513" s="14"/>
+      <c r="B513" s="14"/>
+      <c r="C513" s="14"/>
+      <c r="D513" s="15"/>
+      <c r="E513" s="3"/>
+      <c r="F513" s="14"/>
+      <c r="G513" s="14"/>
     </row>
     <row r="514" spans="1:7">
-      <c r="A514" s="1"/>
-      <c r="B514" s="1"/>
-      <c r="C514" s="1"/>
-      <c r="D514" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E514" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F514" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G514" s="3">
-        <v>20</v>
-      </c>
+      <c r="A514" s="14"/>
+      <c r="B514" s="14"/>
+      <c r="C514" s="14"/>
+      <c r="D514" s="15"/>
+      <c r="E514" s="3"/>
+      <c r="F514" s="14"/>
+      <c r="G514" s="14"/>
     </row>
     <row r="515" spans="1:7">
       <c r="A515" s="1"/>
       <c r="B515" s="1"/>
       <c r="C515" s="1"/>
-      <c r="D515" s="152" t="s">
-        <v>42</v>
-      </c>
-      <c r="E515" s="150" t="s">
-        <v>4</v>
-      </c>
-      <c r="F515" s="151" t="s">
-        <v>43</v>
-      </c>
-      <c r="G515" s="3">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="516" spans="1:7">
+      <c r="D515" s="1"/>
+      <c r="E515" s="3"/>
+      <c r="F515" s="4"/>
+      <c r="G515" s="3"/>
+    </row>
+    <row r="516" spans="1:7" ht="15.5">
       <c r="A516" s="1"/>
       <c r="B516" s="1"/>
       <c r="C516" s="1"/>
-      <c r="D516" s="152"/>
-      <c r="E516" s="150"/>
-      <c r="F516" s="151"/>
-      <c r="G516" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="517" spans="1:7">
-      <c r="A517" s="12"/>
-      <c r="B517" s="12"/>
-      <c r="C517" s="12"/>
-      <c r="D517" s="149" t="s">
-        <v>45</v>
-      </c>
-      <c r="E517" s="150" t="s">
-        <v>4</v>
-      </c>
-      <c r="F517" s="151" t="s">
-        <v>46</v>
-      </c>
-      <c r="G517" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="518" spans="1:7">
-      <c r="A518" s="12"/>
-      <c r="B518" s="12"/>
-      <c r="C518" s="12"/>
-      <c r="D518" s="149"/>
-      <c r="E518" s="150"/>
-      <c r="F518" s="151"/>
-      <c r="G518" s="3" t="s">
-        <v>48</v>
+      <c r="D516" s="13"/>
+      <c r="E516" s="3"/>
+      <c r="F516" s="4"/>
+      <c r="G516" s="5"/>
+    </row>
+    <row r="517" spans="1:7" ht="15.5">
+      <c r="A517" s="1"/>
+      <c r="B517" s="1"/>
+      <c r="C517" s="1"/>
+      <c r="D517" s="13"/>
+      <c r="E517" s="3"/>
+      <c r="F517" s="4"/>
+      <c r="G517" s="5"/>
+    </row>
+    <row r="518" spans="1:7" ht="15.5">
+      <c r="A518" s="1"/>
+      <c r="B518" s="1"/>
+      <c r="C518" s="1"/>
+      <c r="D518" s="13"/>
+      <c r="E518" s="3"/>
+      <c r="F518" s="4"/>
+      <c r="G518" s="5"/>
+    </row>
+    <row r="519" spans="1:7">
+      <c r="A519" s="1"/>
+      <c r="B519" s="1"/>
+      <c r="C519" s="6"/>
+      <c r="D519" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E519" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F519" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G519" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="520" spans="1:7">
       <c r="A520" s="1"/>
       <c r="B520" s="1"/>
-      <c r="C520" s="1"/>
-      <c r="D520" s="1" t="s">
-        <v>50</v>
+      <c r="C520" s="6"/>
+      <c r="D520" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="E520" s="3" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F520" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G520" s="3">
-        <v>80</v>
+        <v>23</v>
+      </c>
+      <c r="G520" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="521" spans="1:7">
       <c r="A521" s="1"/>
       <c r="B521" s="1"/>
-      <c r="C521" s="1"/>
-      <c r="D521" s="152" t="s">
-        <v>52</v>
-      </c>
-      <c r="E521" s="150" t="s">
-        <v>2</v>
-      </c>
-      <c r="F521" s="151" t="s">
-        <v>53</v>
-      </c>
-      <c r="G521" s="3">
-        <v>40</v>
+      <c r="C521" s="6"/>
+      <c r="D521" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E521" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F521" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G521" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="522" spans="1:7">
       <c r="A522" s="1"/>
       <c r="B522" s="1"/>
-      <c r="C522" s="1"/>
-      <c r="D522" s="152"/>
-      <c r="E522" s="150"/>
-      <c r="F522" s="151"/>
+      <c r="C522" s="6"/>
+      <c r="D522" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E522" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F522" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="G522" s="3" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
     </row>
     <row r="523" spans="1:7">
       <c r="A523" s="1"/>
       <c r="B523" s="1"/>
       <c r="C523" s="1"/>
-      <c r="D523" s="149" t="s">
-        <v>54</v>
-      </c>
-      <c r="E523" s="150" t="s">
-        <v>4</v>
-      </c>
-      <c r="F523" s="151" t="s">
-        <v>55</v>
-      </c>
-      <c r="G523" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="524" spans="1:7">
+      <c r="D523" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E523" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F523" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G523" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="524" spans="1:7" ht="26">
       <c r="A524" s="1"/>
       <c r="B524" s="1"/>
-      <c r="C524" s="1"/>
-      <c r="D524" s="149"/>
-      <c r="E524" s="150"/>
-      <c r="F524" s="151"/>
-      <c r="G524" s="3" t="s">
-        <v>57</v>
+      <c r="C524" s="7"/>
+      <c r="D524" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E524" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F524" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G524" s="3">
+        <v>10</v>
       </c>
     </row>
     <row r="525" spans="1:7">
-      <c r="A525" s="1"/>
-      <c r="B525" s="1"/>
-      <c r="C525" s="1"/>
-      <c r="D525" s="149" t="s">
-        <v>58</v>
+      <c r="A525" s="12"/>
+      <c r="B525" s="12"/>
+      <c r="C525" s="12"/>
+      <c r="D525" s="152" t="s">
+        <v>35</v>
       </c>
       <c r="E525" s="150" t="s">
         <v>4</v>
       </c>
       <c r="F525" s="151" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="G525" s="3" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
     </row>
     <row r="526" spans="1:7">
-      <c r="A526" s="1"/>
-      <c r="B526" s="1"/>
-      <c r="C526" s="1"/>
-      <c r="D526" s="149"/>
+      <c r="A526" s="12"/>
+      <c r="B526" s="12"/>
+      <c r="C526" s="12"/>
+      <c r="D526" s="152"/>
       <c r="E526" s="150"/>
       <c r="F526" s="151"/>
       <c r="G526" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="527" spans="1:7">
-      <c r="A527" s="1"/>
-      <c r="B527" s="1"/>
-      <c r="C527" s="1"/>
-      <c r="D527" s="149" t="s">
-        <v>62</v>
-      </c>
-      <c r="E527" s="150" t="s">
-        <v>4</v>
-      </c>
-      <c r="F527" s="151" t="s">
-        <v>63</v>
-      </c>
-      <c r="G527" s="3" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
     </row>
     <row r="528" spans="1:7">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="1"/>
-      <c r="D528" s="149"/>
-      <c r="E528" s="150"/>
-      <c r="F528" s="151"/>
-      <c r="G528" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="529" spans="1:7" ht="51">
+      <c r="D528" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E528" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F528" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G528" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="529" spans="1:7">
       <c r="A529" s="1"/>
       <c r="B529" s="1"/>
       <c r="C529" s="1"/>
-      <c r="D529" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E529" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F529" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="G529" s="5"/>
+      <c r="D529" s="149" t="s">
+        <v>42</v>
+      </c>
+      <c r="E529" s="150" t="s">
+        <v>4</v>
+      </c>
+      <c r="F529" s="151" t="s">
+        <v>43</v>
+      </c>
+      <c r="G529" s="3">
+        <v>40</v>
+      </c>
     </row>
     <row r="530" spans="1:7">
       <c r="A530" s="1"/>
       <c r="B530" s="1"/>
       <c r="C530" s="1"/>
-      <c r="D530" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E530" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F530" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G530" s="3">
-        <v>100</v>
+      <c r="D530" s="149"/>
+      <c r="E530" s="150"/>
+      <c r="F530" s="151"/>
+      <c r="G530" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="531" spans="1:7">
-      <c r="A531" s="1"/>
-      <c r="B531" s="1"/>
-      <c r="C531" s="1"/>
-      <c r="D531" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E531" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F531" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G531" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="532" spans="1:7" ht="26">
-      <c r="A532" s="1"/>
-      <c r="B532" s="1"/>
-      <c r="C532" s="1"/>
-      <c r="D532" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E532" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F532" s="4" t="s">
-        <v>84</v>
-      </c>
+      <c r="A531" s="12"/>
+      <c r="B531" s="12"/>
+      <c r="C531" s="12"/>
+      <c r="D531" s="152" t="s">
+        <v>45</v>
+      </c>
+      <c r="E531" s="150" t="s">
+        <v>4</v>
+      </c>
+      <c r="F531" s="151" t="s">
+        <v>46</v>
+      </c>
+      <c r="G531" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="532" spans="1:7">
+      <c r="A532" s="12"/>
+      <c r="B532" s="12"/>
+      <c r="C532" s="12"/>
+      <c r="D532" s="152"/>
+      <c r="E532" s="150"/>
+      <c r="F532" s="151"/>
       <c r="G532" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="533" spans="1:7">
-      <c r="A533" s="1"/>
-      <c r="B533" s="1"/>
-      <c r="C533" s="1"/>
-      <c r="D533" s="152" t="s">
-        <v>86</v>
-      </c>
-      <c r="E533" s="150" t="s">
-        <v>4</v>
-      </c>
-      <c r="F533" s="151" t="s">
-        <v>87</v>
-      </c>
-      <c r="G533" s="3" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
     </row>
     <row r="534" spans="1:7">
       <c r="A534" s="1"/>
       <c r="B534" s="1"/>
       <c r="C534" s="1"/>
-      <c r="D534" s="152"/>
-      <c r="E534" s="150"/>
-      <c r="F534" s="151"/>
-      <c r="G534" s="3" t="s">
-        <v>89</v>
+      <c r="D534" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E534" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F534" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G534" s="3">
+        <v>80</v>
       </c>
     </row>
     <row r="535" spans="1:7">
       <c r="A535" s="1"/>
       <c r="B535" s="1"/>
       <c r="C535" s="1"/>
-      <c r="D535" s="152"/>
-      <c r="E535" s="150"/>
-      <c r="F535" s="151"/>
-      <c r="G535" s="3" t="s">
-        <v>90</v>
+      <c r="D535" s="149" t="s">
+        <v>52</v>
+      </c>
+      <c r="E535" s="150" t="s">
+        <v>2</v>
+      </c>
+      <c r="F535" s="151" t="s">
+        <v>53</v>
+      </c>
+      <c r="G535" s="3">
+        <v>40</v>
       </c>
     </row>
     <row r="536" spans="1:7">
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
       <c r="C536" s="1"/>
-      <c r="D536" s="152" t="s">
-        <v>91</v>
-      </c>
-      <c r="E536" s="150" t="s">
-        <v>4</v>
-      </c>
-      <c r="F536" s="151" t="s">
-        <v>92</v>
-      </c>
+      <c r="D536" s="149"/>
+      <c r="E536" s="150"/>
+      <c r="F536" s="151"/>
       <c r="G536" s="3" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
     </row>
     <row r="537" spans="1:7">
       <c r="A537" s="1"/>
       <c r="B537" s="1"/>
       <c r="C537" s="1"/>
-      <c r="D537" s="152"/>
-      <c r="E537" s="150"/>
-      <c r="F537" s="151"/>
+      <c r="D537" s="152" t="s">
+        <v>54</v>
+      </c>
+      <c r="E537" s="150" t="s">
+        <v>4</v>
+      </c>
+      <c r="F537" s="151" t="s">
+        <v>55</v>
+      </c>
       <c r="G537" s="3" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
     </row>
     <row r="538" spans="1:7">
@@ -42147,177 +42216,236 @@
       <c r="E538" s="150"/>
       <c r="F538" s="151"/>
       <c r="G538" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="539" spans="1:7" ht="15.5">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="539" spans="1:7">
       <c r="A539" s="1"/>
       <c r="B539" s="1"/>
       <c r="C539" s="1"/>
-      <c r="D539" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E539" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F539" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G539" s="5"/>
-    </row>
-    <row r="540" spans="1:7" ht="15.5">
+      <c r="D539" s="152" t="s">
+        <v>58</v>
+      </c>
+      <c r="E539" s="150" t="s">
+        <v>4</v>
+      </c>
+      <c r="F539" s="151" t="s">
+        <v>59</v>
+      </c>
+      <c r="G539" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="540" spans="1:7">
       <c r="A540" s="1"/>
       <c r="B540" s="1"/>
       <c r="C540" s="1"/>
-      <c r="D540" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E540" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F540" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G540" s="5"/>
-    </row>
-    <row r="541" spans="1:7" ht="15.5">
+      <c r="D540" s="152"/>
+      <c r="E540" s="150"/>
+      <c r="F540" s="151"/>
+      <c r="G540" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="541" spans="1:7">
       <c r="A541" s="1"/>
       <c r="B541" s="1"/>
       <c r="C541" s="1"/>
-      <c r="D541" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E541" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F541" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="G541" s="5"/>
-    </row>
-    <row r="542" spans="1:7" ht="15.5">
+      <c r="D541" s="152" t="s">
+        <v>62</v>
+      </c>
+      <c r="E541" s="150" t="s">
+        <v>4</v>
+      </c>
+      <c r="F541" s="151" t="s">
+        <v>63</v>
+      </c>
+      <c r="G541" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="542" spans="1:7">
       <c r="A542" s="1"/>
       <c r="B542" s="1"/>
       <c r="C542" s="1"/>
-      <c r="D542" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E542" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F542" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="G542" s="5"/>
-    </row>
-    <row r="543" spans="1:7" ht="15.5">
+      <c r="D542" s="152"/>
+      <c r="E542" s="150"/>
+      <c r="F542" s="151"/>
+      <c r="G542" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="543" spans="1:7" ht="51">
       <c r="A543" s="1"/>
       <c r="B543" s="1"/>
       <c r="C543" s="1"/>
       <c r="D543" s="1" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="E543" s="3" t="s">
-        <v>102</v>
+        <v>4</v>
       </c>
       <c r="F543" s="4" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="G543" s="5"/>
     </row>
-    <row r="544" spans="1:7" ht="15.5">
+    <row r="544" spans="1:7">
       <c r="A544" s="1"/>
       <c r="B544" s="1"/>
       <c r="C544" s="1"/>
       <c r="D544" s="1" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="E544" s="3" t="s">
-        <v>102</v>
+        <v>2</v>
       </c>
       <c r="F544" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="G544" s="5"/>
-    </row>
-    <row r="545" spans="1:7" ht="15.5">
+        <v>81</v>
+      </c>
+      <c r="G544" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="545" spans="1:7">
       <c r="A545" s="1"/>
       <c r="B545" s="1"/>
       <c r="C545" s="1"/>
       <c r="D545" s="1" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="E545" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F545" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="G545" s="5"/>
-    </row>
-    <row r="546" spans="1:7" ht="15.5">
+        <v>81</v>
+      </c>
+      <c r="G545" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="546" spans="1:7" ht="26">
       <c r="A546" s="1"/>
       <c r="B546" s="1"/>
       <c r="C546" s="1"/>
       <c r="D546" s="1" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="E546" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F546" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="G546" s="5"/>
+        <v>84</v>
+      </c>
+      <c r="G546" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="547" spans="1:7">
+      <c r="A547" s="1"/>
+      <c r="B547" s="1"/>
+      <c r="C547" s="1"/>
+      <c r="D547" s="149" t="s">
+        <v>86</v>
+      </c>
+      <c r="E547" s="150" t="s">
+        <v>4</v>
+      </c>
+      <c r="F547" s="151" t="s">
+        <v>87</v>
+      </c>
+      <c r="G547" s="3" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="548" spans="1:7">
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
       <c r="C548" s="1"/>
-      <c r="D548" s="1"/>
-      <c r="E548" s="3"/>
-      <c r="F548" s="4"/>
-      <c r="G548" s="3"/>
+      <c r="D548" s="149"/>
+      <c r="E548" s="150"/>
+      <c r="F548" s="151"/>
+      <c r="G548" s="3" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="549" spans="1:7">
       <c r="A549" s="1"/>
       <c r="B549" s="1"/>
       <c r="C549" s="1"/>
-      <c r="D549" s="1"/>
-      <c r="E549" s="3"/>
-      <c r="F549" s="4"/>
-      <c r="G549" s="3"/>
+      <c r="D549" s="149"/>
+      <c r="E549" s="150"/>
+      <c r="F549" s="151"/>
+      <c r="G549" s="3" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="550" spans="1:7">
       <c r="A550" s="1"/>
       <c r="B550" s="1"/>
       <c r="C550" s="1"/>
-      <c r="D550" s="1"/>
-      <c r="E550" s="3"/>
-      <c r="F550" s="4"/>
-      <c r="G550" s="3"/>
+      <c r="D550" s="149" t="s">
+        <v>91</v>
+      </c>
+      <c r="E550" s="150" t="s">
+        <v>4</v>
+      </c>
+      <c r="F550" s="151" t="s">
+        <v>92</v>
+      </c>
+      <c r="G550" s="3" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="551" spans="1:7">
       <c r="A551" s="1"/>
       <c r="B551" s="1"/>
       <c r="C551" s="1"/>
-      <c r="D551" s="1"/>
-      <c r="E551" s="3"/>
-      <c r="F551" s="4"/>
-      <c r="G551" s="3"/>
+      <c r="D551" s="149"/>
+      <c r="E551" s="150"/>
+      <c r="F551" s="151"/>
+      <c r="G551" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="552" spans="1:7">
+      <c r="A552" s="1"/>
+      <c r="B552" s="1"/>
+      <c r="C552" s="1"/>
+      <c r="D552" s="149"/>
+      <c r="E552" s="150"/>
+      <c r="F552" s="151"/>
+      <c r="G552" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="553" spans="1:7" ht="15.5">
+      <c r="A553" s="1"/>
+      <c r="B553" s="1"/>
+      <c r="C553" s="1"/>
+      <c r="D553" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E553" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F553" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G553" s="5"/>
     </row>
     <row r="554" spans="1:7" ht="15.5">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="1"/>
       <c r="D554" s="1" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="E554" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F554" s="4" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G554" s="5"/>
     </row>
@@ -42326,13 +42454,13 @@
       <c r="B555" s="1"/>
       <c r="C555" s="1"/>
       <c r="D555" s="1" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="E555" s="3" t="s">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="F555" s="4" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="G555" s="5"/>
     </row>
@@ -42341,28 +42469,58 @@
       <c r="B556" s="1"/>
       <c r="C556" s="1"/>
       <c r="D556" s="1" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="E556" s="3" t="s">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="F556" s="4" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="G556" s="5"/>
+    </row>
+    <row r="557" spans="1:7" ht="15.5">
+      <c r="A557" s="1"/>
+      <c r="B557" s="1"/>
+      <c r="C557" s="1"/>
+      <c r="D557" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E557" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F557" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G557" s="5"/>
+    </row>
+    <row r="558" spans="1:7" ht="15.5">
+      <c r="A558" s="1"/>
+      <c r="B558" s="1"/>
+      <c r="C558" s="1"/>
+      <c r="D558" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E558" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F558" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G558" s="5"/>
     </row>
     <row r="559" spans="1:7" ht="15.5">
       <c r="A559" s="1"/>
       <c r="B559" s="1"/>
       <c r="C559" s="1"/>
       <c r="D559" s="1" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="E559" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F559" s="4" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="G559" s="5"/>
     </row>
@@ -42371,109 +42529,64 @@
       <c r="B560" s="1"/>
       <c r="C560" s="1"/>
       <c r="D560" s="1" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="E560" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F560" s="4" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="G560" s="5"/>
     </row>
-    <row r="561" spans="1:7" ht="15.5">
-      <c r="A561" s="1"/>
-      <c r="B561" s="1"/>
-      <c r="C561" s="1"/>
-      <c r="D561" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E561" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F561" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="G561" s="5"/>
+    <row r="562" spans="1:7">
+      <c r="A562" s="1"/>
+      <c r="B562" s="1"/>
+      <c r="C562" s="1"/>
+      <c r="D562" s="1"/>
+      <c r="E562" s="3"/>
+      <c r="F562" s="4"/>
+      <c r="G562" s="3"/>
     </row>
     <row r="563" spans="1:7">
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
-      <c r="D563" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="E563" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F563" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="G563" s="3" t="s">
-        <v>126</v>
-      </c>
+      <c r="D563" s="1"/>
+      <c r="E563" s="3"/>
+      <c r="F563" s="4"/>
+      <c r="G563" s="3"/>
+    </row>
+    <row r="564" spans="1:7">
+      <c r="A564" s="1"/>
+      <c r="B564" s="1"/>
+      <c r="C564" s="1"/>
+      <c r="D564" s="1"/>
+      <c r="E564" s="3"/>
+      <c r="F564" s="4"/>
+      <c r="G564" s="3"/>
     </row>
     <row r="565" spans="1:7">
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
-      <c r="D565" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E565" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F565" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="G565" s="3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="566" spans="1:7">
-      <c r="A566" s="1"/>
-      <c r="B566" s="1"/>
-      <c r="C566" s="1"/>
-      <c r="D566" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="E566" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F566" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="G566" s="3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="567" spans="1:7" ht="15.5">
-      <c r="A567" s="1"/>
-      <c r="B567" s="1"/>
-      <c r="C567" s="1"/>
-      <c r="D567" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="E567" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F567" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="G567" s="5"/>
+      <c r="D565" s="1"/>
+      <c r="E565" s="3"/>
+      <c r="F565" s="4"/>
+      <c r="G565" s="3"/>
     </row>
     <row r="568" spans="1:7" ht="15.5">
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
       <c r="C568" s="1"/>
       <c r="D568" s="1" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="E568" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F568" s="4" t="s">
-        <v>145</v>
+        <v>111</v>
       </c>
       <c r="G568" s="5"/>
     </row>
@@ -42481,122 +42594,278 @@
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
       <c r="C569" s="1"/>
-      <c r="D569" s="28"/>
-      <c r="E569" s="3"/>
-      <c r="F569" s="4"/>
+      <c r="D569" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E569" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F569" s="4" t="s">
+        <v>113</v>
+      </c>
       <c r="G569" s="5"/>
     </row>
-    <row r="570" spans="1:7">
-      <c r="A570" s="27"/>
-      <c r="B570" s="27"/>
-      <c r="C570" s="27"/>
-      <c r="D570" s="28"/>
-      <c r="E570" s="3"/>
+    <row r="570" spans="1:7" ht="15.5">
+      <c r="A570" s="1"/>
+      <c r="B570" s="1"/>
+      <c r="C570" s="1"/>
+      <c r="D570" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E570" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="F570" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="G570" s="3" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="578" spans="1:6">
-      <c r="A578" s="1"/>
-      <c r="B578" s="1"/>
-      <c r="C578" s="1"/>
-      <c r="D578" s="67" t="s">
-        <v>279</v>
-      </c>
-      <c r="E578" s="19"/>
-      <c r="F578" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="579" spans="1:6">
+        <v>115</v>
+      </c>
+      <c r="G570" s="5"/>
+    </row>
+    <row r="573" spans="1:7" ht="15.5">
+      <c r="A573" s="1"/>
+      <c r="B573" s="1"/>
+      <c r="C573" s="1"/>
+      <c r="D573" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E573" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F573" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="G573" s="5"/>
+    </row>
+    <row r="574" spans="1:7" ht="15.5">
+      <c r="A574" s="1"/>
+      <c r="B574" s="1"/>
+      <c r="C574" s="1"/>
+      <c r="D574" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E574" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F574" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="G574" s="5"/>
+    </row>
+    <row r="575" spans="1:7" ht="15.5">
+      <c r="A575" s="1"/>
+      <c r="B575" s="1"/>
+      <c r="C575" s="1"/>
+      <c r="D575" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E575" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F575" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G575" s="5"/>
+    </row>
+    <row r="577" spans="1:7">
+      <c r="A577" s="1"/>
+      <c r="B577" s="1"/>
+      <c r="C577" s="1"/>
+      <c r="D577" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E577" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F577" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G577" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="579" spans="1:7">
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
-      <c r="D579" s="67" t="s">
-        <v>278</v>
-      </c>
-      <c r="E579" s="19"/>
-      <c r="F579" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="580" spans="1:6">
+      <c r="D579" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E579" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F579" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="G579" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="580" spans="1:7">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
-      <c r="D580" s="67" t="s">
-        <v>592</v>
-      </c>
-      <c r="E580" s="19"/>
-      <c r="F580" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="581" spans="1:6">
+      <c r="D580" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E580" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F580" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G580" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="581" spans="1:7" ht="15.5">
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
-      <c r="D581" s="67" t="s">
-        <v>593</v>
-      </c>
-      <c r="E581" s="19"/>
-      <c r="F581" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="582" spans="1:6">
+      <c r="D581" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E581" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F581" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="G581" s="5"/>
+    </row>
+    <row r="582" spans="1:7" ht="15.5">
       <c r="A582" s="1"/>
       <c r="B582" s="1"/>
       <c r="C582" s="1"/>
-      <c r="D582" s="67" t="s">
-        <v>842</v>
-      </c>
-      <c r="E582" s="19"/>
-    </row>
-    <row r="583" spans="1:6">
+      <c r="D582" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E582" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F582" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G582" s="5"/>
+    </row>
+    <row r="583" spans="1:7" ht="15.5">
       <c r="A583" s="1"/>
       <c r="B583" s="1"/>
       <c r="C583" s="1"/>
-      <c r="D583" s="67" t="s">
+      <c r="D583" s="28"/>
+      <c r="E583" s="3"/>
+      <c r="F583" s="4"/>
+      <c r="G583" s="5"/>
+    </row>
+    <row r="584" spans="1:7">
+      <c r="A584" s="27"/>
+      <c r="B584" s="27"/>
+      <c r="C584" s="27"/>
+      <c r="D584" s="28"/>
+      <c r="E584" s="3"/>
+      <c r="F584" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G584" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="592" spans="1:7">
+      <c r="A592" s="1"/>
+      <c r="B592" s="1"/>
+      <c r="C592" s="1"/>
+      <c r="D592" s="67" t="s">
+        <v>279</v>
+      </c>
+      <c r="E592" s="19"/>
+      <c r="F592" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="593" spans="1:6">
+      <c r="A593" s="1"/>
+      <c r="B593" s="1"/>
+      <c r="C593" s="1"/>
+      <c r="D593" s="67" t="s">
+        <v>278</v>
+      </c>
+      <c r="E593" s="19"/>
+      <c r="F593" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="594" spans="1:6">
+      <c r="A594" s="1"/>
+      <c r="B594" s="1"/>
+      <c r="C594" s="1"/>
+      <c r="D594" s="67" t="s">
+        <v>592</v>
+      </c>
+      <c r="E594" s="19"/>
+      <c r="F594" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="595" spans="1:6">
+      <c r="A595" s="1"/>
+      <c r="B595" s="1"/>
+      <c r="C595" s="1"/>
+      <c r="D595" s="67" t="s">
+        <v>593</v>
+      </c>
+      <c r="E595" s="19"/>
+      <c r="F595" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="596" spans="1:6">
+      <c r="A596" s="1"/>
+      <c r="B596" s="1"/>
+      <c r="C596" s="1"/>
+      <c r="D596" s="67" t="s">
+        <v>842</v>
+      </c>
+      <c r="E596" s="19"/>
+    </row>
+    <row r="597" spans="1:6">
+      <c r="A597" s="1"/>
+      <c r="B597" s="1"/>
+      <c r="C597" s="1"/>
+      <c r="D597" s="67" t="s">
         <v>847</v>
       </c>
-      <c r="E583" s="19"/>
-      <c r="F583" s="48" t="s">
+      <c r="E597" s="19"/>
+      <c r="F597" s="48" t="s">
         <v>611</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D536:D538"/>
-    <mergeCell ref="E536:E538"/>
-    <mergeCell ref="F536:F538"/>
-    <mergeCell ref="D527:D528"/>
-    <mergeCell ref="E527:E528"/>
-    <mergeCell ref="F527:F528"/>
-    <mergeCell ref="D533:D535"/>
-    <mergeCell ref="E533:E535"/>
-    <mergeCell ref="F533:F535"/>
-    <mergeCell ref="D523:D524"/>
-    <mergeCell ref="E523:E524"/>
-    <mergeCell ref="F523:F524"/>
     <mergeCell ref="D525:D526"/>
     <mergeCell ref="E525:E526"/>
     <mergeCell ref="F525:F526"/>
-    <mergeCell ref="D517:D518"/>
-    <mergeCell ref="E517:E518"/>
-    <mergeCell ref="F517:F518"/>
-    <mergeCell ref="D521:D522"/>
-    <mergeCell ref="E521:E522"/>
-    <mergeCell ref="F521:F522"/>
-    <mergeCell ref="D511:D512"/>
-    <mergeCell ref="E511:E512"/>
-    <mergeCell ref="F511:F512"/>
-    <mergeCell ref="D515:D516"/>
-    <mergeCell ref="E515:E516"/>
-    <mergeCell ref="F515:F516"/>
+    <mergeCell ref="D529:D530"/>
+    <mergeCell ref="E529:E530"/>
+    <mergeCell ref="F529:F530"/>
+    <mergeCell ref="D531:D532"/>
+    <mergeCell ref="E531:E532"/>
+    <mergeCell ref="F531:F532"/>
+    <mergeCell ref="D535:D536"/>
+    <mergeCell ref="E535:E536"/>
+    <mergeCell ref="F535:F536"/>
+    <mergeCell ref="D537:D538"/>
+    <mergeCell ref="E537:E538"/>
+    <mergeCell ref="F537:F538"/>
+    <mergeCell ref="D539:D540"/>
+    <mergeCell ref="E539:E540"/>
+    <mergeCell ref="F539:F540"/>
+    <mergeCell ref="D550:D552"/>
+    <mergeCell ref="E550:E552"/>
+    <mergeCell ref="F550:F552"/>
+    <mergeCell ref="D541:D542"/>
+    <mergeCell ref="E541:E542"/>
+    <mergeCell ref="F541:F542"/>
+    <mergeCell ref="D547:D549"/>
+    <mergeCell ref="E547:E549"/>
+    <mergeCell ref="F547:F549"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1" display="Abbreviation of the journal name. We use WoS abbreviations that can be found here: https://images.webofknowledge.com/images/help/WOS/A_abrvjt.html" xr:uid="{6BB52E4D-01E2-44A6-B6CC-352383FA2940}"/>
@@ -42608,6 +42877,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4e0e0d96de7fb32b1678b66c28514d8e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" xmlns:ns3="432dd258-9dce-4cb3-b611-c68c0fbce7f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac451aab8c96dec805c937cbafca7133" ns2:_="" ns3:_="">
     <xsd:import namespace="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
@@ -42808,27 +43097,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0C90B0A-DBBE-4147-B2EE-79946A8DC171}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63F80AE0-5CF8-441A-8E3E-6D76A3390D5E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
+    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC19592A-9F30-4B32-9428-1D9634B8A0D4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -42845,23 +43133,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63F80AE0-5CF8-441A-8E3E-6D76A3390D5E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
-    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0C90B0A-DBBE-4147-B2EE-79946A8DC171}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
+++ b/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Evidence_Hub/02.FOMD/02.metadata_structure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2766" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4133BF4-8489-4D80-95EF-A6D1878142A5}"/>
+  <xr:revisionPtr revIDLastSave="2773" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FE22A88-44DF-4B2A-8E0D-C01825CAFAFC}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{FAB1A633-BA4D-4813-8605-DC3F4755D7C7}"/>
   </bookViews>
@@ -307,7 +307,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6406" uniqueCount="1577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6409" uniqueCount="1577">
   <si>
     <t>Example</t>
   </si>
@@ -10864,7 +10864,7 @@
     <t>Estimated sample size for the treatment system, estimated only when there was no reported sample size</t>
   </si>
   <si>
-    <t>vi</t>
+    <t>Effect size type: Log Response Ratio or Standardized mean difference</t>
   </si>
 </sst>
 </file>
@@ -12104,13 +12104,13 @@
     <xf numFmtId="0" fontId="15" fillId="61" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="62" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="63" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="63" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -31204,13 +31204,13 @@
       <c r="L542" s="12"/>
       <c r="M542" s="12"/>
       <c r="N542" s="12"/>
-      <c r="O542" s="152" t="s">
+      <c r="O542" s="150" t="s">
         <v>35</v>
       </c>
-      <c r="P542" s="150" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q542" s="151" t="s">
+      <c r="P542" s="151" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q542" s="152" t="s">
         <v>36</v>
       </c>
       <c r="R542" s="3" t="s">
@@ -31232,9 +31232,9 @@
       <c r="L543" s="12"/>
       <c r="M543" s="12"/>
       <c r="N543" s="12"/>
-      <c r="O543" s="152"/>
-      <c r="P543" s="150"/>
-      <c r="Q543" s="151"/>
+      <c r="O543" s="150"/>
+      <c r="P543" s="151"/>
+      <c r="Q543" s="152"/>
       <c r="R543" s="3" t="s">
         <v>38</v>
       </c>
@@ -31282,13 +31282,13 @@
       <c r="L546" s="1"/>
       <c r="M546" s="1"/>
       <c r="N546" s="1"/>
-      <c r="O546" s="149" t="s">
+      <c r="O546" s="153" t="s">
         <v>42</v>
       </c>
-      <c r="P546" s="150" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q546" s="151" t="s">
+      <c r="P546" s="151" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q546" s="152" t="s">
         <v>43</v>
       </c>
       <c r="R546" s="3">
@@ -31310,9 +31310,9 @@
       <c r="L547" s="1"/>
       <c r="M547" s="1"/>
       <c r="N547" s="1"/>
-      <c r="O547" s="149"/>
-      <c r="P547" s="150"/>
-      <c r="Q547" s="151"/>
+      <c r="O547" s="153"/>
+      <c r="P547" s="151"/>
+      <c r="Q547" s="152"/>
       <c r="R547" s="3" t="s">
         <v>44</v>
       </c>
@@ -31332,13 +31332,13 @@
       <c r="L548" s="12"/>
       <c r="M548" s="12"/>
       <c r="N548" s="12"/>
-      <c r="O548" s="152" t="s">
+      <c r="O548" s="150" t="s">
         <v>45</v>
       </c>
-      <c r="P548" s="150" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q548" s="151" t="s">
+      <c r="P548" s="151" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q548" s="152" t="s">
         <v>46</v>
       </c>
       <c r="R548" s="3" t="s">
@@ -31360,9 +31360,9 @@
       <c r="L549" s="12"/>
       <c r="M549" s="12"/>
       <c r="N549" s="12"/>
-      <c r="O549" s="152"/>
-      <c r="P549" s="150"/>
-      <c r="Q549" s="151"/>
+      <c r="O549" s="150"/>
+      <c r="P549" s="151"/>
+      <c r="Q549" s="152"/>
       <c r="R549" s="3" t="s">
         <v>48</v>
       </c>
@@ -31410,13 +31410,13 @@
       <c r="L552" s="1"/>
       <c r="M552" s="1"/>
       <c r="N552" s="1"/>
-      <c r="O552" s="149" t="s">
+      <c r="O552" s="153" t="s">
         <v>52</v>
       </c>
-      <c r="P552" s="150" t="s">
+      <c r="P552" s="151" t="s">
         <v>2</v>
       </c>
-      <c r="Q552" s="151" t="s">
+      <c r="Q552" s="152" t="s">
         <v>53</v>
       </c>
       <c r="R552" s="3">
@@ -31438,9 +31438,9 @@
       <c r="L553" s="1"/>
       <c r="M553" s="1"/>
       <c r="N553" s="1"/>
-      <c r="O553" s="149"/>
-      <c r="P553" s="150"/>
-      <c r="Q553" s="151"/>
+      <c r="O553" s="153"/>
+      <c r="P553" s="151"/>
+      <c r="Q553" s="152"/>
       <c r="R553" s="3" t="s">
         <v>44</v>
       </c>
@@ -31460,13 +31460,13 @@
       <c r="L554" s="1"/>
       <c r="M554" s="1"/>
       <c r="N554" s="1"/>
-      <c r="O554" s="152" t="s">
+      <c r="O554" s="150" t="s">
         <v>54</v>
       </c>
-      <c r="P554" s="150" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q554" s="151" t="s">
+      <c r="P554" s="151" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q554" s="152" t="s">
         <v>55</v>
       </c>
       <c r="R554" s="3" t="s">
@@ -31488,9 +31488,9 @@
       <c r="L555" s="1"/>
       <c r="M555" s="1"/>
       <c r="N555" s="1"/>
-      <c r="O555" s="152"/>
-      <c r="P555" s="150"/>
-      <c r="Q555" s="151"/>
+      <c r="O555" s="150"/>
+      <c r="P555" s="151"/>
+      <c r="Q555" s="152"/>
       <c r="R555" s="3" t="s">
         <v>57</v>
       </c>
@@ -31510,13 +31510,13 @@
       <c r="L556" s="1"/>
       <c r="M556" s="1"/>
       <c r="N556" s="1"/>
-      <c r="O556" s="152" t="s">
+      <c r="O556" s="150" t="s">
         <v>58</v>
       </c>
-      <c r="P556" s="150" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q556" s="151" t="s">
+      <c r="P556" s="151" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q556" s="152" t="s">
         <v>59</v>
       </c>
       <c r="R556" s="3" t="s">
@@ -31538,9 +31538,9 @@
       <c r="L557" s="1"/>
       <c r="M557" s="1"/>
       <c r="N557" s="1"/>
-      <c r="O557" s="152"/>
-      <c r="P557" s="150"/>
-      <c r="Q557" s="151"/>
+      <c r="O557" s="150"/>
+      <c r="P557" s="151"/>
+      <c r="Q557" s="152"/>
       <c r="R557" s="3" t="s">
         <v>61</v>
       </c>
@@ -31560,13 +31560,13 @@
       <c r="L558" s="1"/>
       <c r="M558" s="1"/>
       <c r="N558" s="1"/>
-      <c r="O558" s="152" t="s">
+      <c r="O558" s="150" t="s">
         <v>62</v>
       </c>
-      <c r="P558" s="150" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q558" s="151" t="s">
+      <c r="P558" s="151" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q558" s="152" t="s">
         <v>63</v>
       </c>
       <c r="R558" s="3" t="s">
@@ -31588,9 +31588,9 @@
       <c r="L559" s="1"/>
       <c r="M559" s="1"/>
       <c r="N559" s="1"/>
-      <c r="O559" s="152"/>
-      <c r="P559" s="150"/>
-      <c r="Q559" s="151"/>
+      <c r="O559" s="150"/>
+      <c r="P559" s="151"/>
+      <c r="Q559" s="152"/>
       <c r="R559" s="3" t="s">
         <v>65</v>
       </c>
@@ -31720,13 +31720,13 @@
       <c r="L564" s="1"/>
       <c r="M564" s="1"/>
       <c r="N564" s="1"/>
-      <c r="O564" s="149" t="s">
+      <c r="O564" s="153" t="s">
         <v>86</v>
       </c>
-      <c r="P564" s="150" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q564" s="151" t="s">
+      <c r="P564" s="151" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q564" s="152" t="s">
         <v>87</v>
       </c>
       <c r="R564" s="3" t="s">
@@ -31748,9 +31748,9 @@
       <c r="L565" s="1"/>
       <c r="M565" s="1"/>
       <c r="N565" s="1"/>
-      <c r="O565" s="149"/>
-      <c r="P565" s="150"/>
-      <c r="Q565" s="151"/>
+      <c r="O565" s="153"/>
+      <c r="P565" s="151"/>
+      <c r="Q565" s="152"/>
       <c r="R565" s="3" t="s">
         <v>89</v>
       </c>
@@ -31770,9 +31770,9 @@
       <c r="L566" s="1"/>
       <c r="M566" s="1"/>
       <c r="N566" s="1"/>
-      <c r="O566" s="149"/>
-      <c r="P566" s="150"/>
-      <c r="Q566" s="151"/>
+      <c r="O566" s="153"/>
+      <c r="P566" s="151"/>
+      <c r="Q566" s="152"/>
       <c r="R566" s="3" t="s">
         <v>90</v>
       </c>
@@ -31792,13 +31792,13 @@
       <c r="L567" s="1"/>
       <c r="M567" s="1"/>
       <c r="N567" s="1"/>
-      <c r="O567" s="149" t="s">
+      <c r="O567" s="153" t="s">
         <v>91</v>
       </c>
-      <c r="P567" s="150" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q567" s="151" t="s">
+      <c r="P567" s="151" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q567" s="152" t="s">
         <v>92</v>
       </c>
       <c r="R567" s="3" t="s">
@@ -31820,9 +31820,9 @@
       <c r="L568" s="1"/>
       <c r="M568" s="1"/>
       <c r="N568" s="1"/>
-      <c r="O568" s="149"/>
-      <c r="P568" s="150"/>
-      <c r="Q568" s="151"/>
+      <c r="O568" s="153"/>
+      <c r="P568" s="151"/>
+      <c r="Q568" s="152"/>
       <c r="R568" s="3" t="s">
         <v>89</v>
       </c>
@@ -31842,9 +31842,9 @@
       <c r="L569" s="1"/>
       <c r="M569" s="1"/>
       <c r="N569" s="1"/>
-      <c r="O569" s="149"/>
-      <c r="P569" s="150"/>
-      <c r="Q569" s="151"/>
+      <c r="O569" s="153"/>
+      <c r="P569" s="151"/>
+      <c r="Q569" s="152"/>
       <c r="R569" s="3" t="s">
         <v>90</v>
       </c>
@@ -32611,6 +32611,24 @@
   </sheetData>
   <autoFilter ref="A1:S319" xr:uid="{82619C4B-D6B1-486E-87C6-D2252668E253}"/>
   <mergeCells count="27">
+    <mergeCell ref="O542:O543"/>
+    <mergeCell ref="P542:P543"/>
+    <mergeCell ref="Q542:Q543"/>
+    <mergeCell ref="O546:O547"/>
+    <mergeCell ref="P546:P547"/>
+    <mergeCell ref="Q546:Q547"/>
+    <mergeCell ref="O556:O557"/>
+    <mergeCell ref="P556:P557"/>
+    <mergeCell ref="Q556:Q557"/>
+    <mergeCell ref="O558:O559"/>
+    <mergeCell ref="P558:P559"/>
+    <mergeCell ref="Q558:Q559"/>
+    <mergeCell ref="O564:O566"/>
+    <mergeCell ref="P564:P566"/>
+    <mergeCell ref="Q564:Q566"/>
+    <mergeCell ref="O567:O569"/>
+    <mergeCell ref="P567:P569"/>
+    <mergeCell ref="Q567:Q569"/>
     <mergeCell ref="O554:O555"/>
     <mergeCell ref="P554:P555"/>
     <mergeCell ref="Q554:Q555"/>
@@ -32620,24 +32638,6 @@
     <mergeCell ref="P552:P553"/>
     <mergeCell ref="Q552:Q553"/>
     <mergeCell ref="O548:O549"/>
-    <mergeCell ref="O564:O566"/>
-    <mergeCell ref="P564:P566"/>
-    <mergeCell ref="Q564:Q566"/>
-    <mergeCell ref="O567:O569"/>
-    <mergeCell ref="P567:P569"/>
-    <mergeCell ref="Q567:Q569"/>
-    <mergeCell ref="O556:O557"/>
-    <mergeCell ref="P556:P557"/>
-    <mergeCell ref="Q556:Q557"/>
-    <mergeCell ref="O558:O559"/>
-    <mergeCell ref="P558:P559"/>
-    <mergeCell ref="Q558:Q559"/>
-    <mergeCell ref="O542:O543"/>
-    <mergeCell ref="P542:P543"/>
-    <mergeCell ref="Q542:Q543"/>
-    <mergeCell ref="O546:O547"/>
-    <mergeCell ref="P546:P547"/>
-    <mergeCell ref="Q546:Q547"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="Q7" r:id="rId1" display="Abbreviation of the journal name. We use WoS abbreviations that can be found here: https://images.webofknowledge.com/images/help/WOS/A_abrvjt.html" xr:uid="{B4DADD6B-F846-45B3-933B-5F25CC9FEF24}"/>
@@ -32657,7 +32657,7 @@
     <col min="3" max="3" width="20.54296875" customWidth="1"/>
     <col min="4" max="4" width="36.453125" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="121.81640625" style="10" customWidth="1"/>
+    <col min="6" max="6" width="87" style="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -38288,10 +38288,10 @@
     <row r="289" spans="1:7">
       <c r="A289" s="14"/>
       <c r="B289" s="14"/>
-      <c r="C289" s="153" t="s">
+      <c r="C289" s="149" t="s">
         <v>1555</v>
       </c>
-      <c r="D289" s="153" t="s">
+      <c r="D289" s="149" t="s">
         <v>1564</v>
       </c>
       <c r="E289" s="3"/>
@@ -38303,10 +38303,10 @@
     <row r="290" spans="1:7">
       <c r="A290" s="14"/>
       <c r="B290" s="14"/>
-      <c r="C290" s="153" t="s">
+      <c r="C290" s="149" t="s">
         <v>1555</v>
       </c>
-      <c r="D290" s="153" t="s">
+      <c r="D290" s="149" t="s">
         <v>1565</v>
       </c>
       <c r="E290" s="3"/>
@@ -38318,10 +38318,10 @@
     <row r="291" spans="1:7">
       <c r="A291" s="14"/>
       <c r="B291" s="14"/>
-      <c r="C291" s="153" t="s">
+      <c r="C291" s="149" t="s">
         <v>1555</v>
       </c>
-      <c r="D291" s="153" t="s">
+      <c r="D291" s="149" t="s">
         <v>1566</v>
       </c>
       <c r="E291" s="3"/>
@@ -38333,10 +38333,10 @@
     <row r="292" spans="1:7">
       <c r="A292" s="14"/>
       <c r="B292" s="14"/>
-      <c r="C292" s="153" t="s">
+      <c r="C292" s="149" t="s">
         <v>1555</v>
       </c>
-      <c r="D292" s="153" t="s">
+      <c r="D292" s="149" t="s">
         <v>1567</v>
       </c>
       <c r="E292" s="3"/>
@@ -38348,10 +38348,10 @@
     <row r="293" spans="1:7">
       <c r="A293" s="14"/>
       <c r="B293" s="14"/>
-      <c r="C293" s="153" t="s">
+      <c r="C293" s="149" t="s">
         <v>1555</v>
       </c>
-      <c r="D293" s="153" t="s">
+      <c r="D293" s="149" t="s">
         <v>1568</v>
       </c>
       <c r="E293" s="3"/>
@@ -38363,10 +38363,10 @@
     <row r="294" spans="1:7">
       <c r="A294" s="14"/>
       <c r="B294" s="14"/>
-      <c r="C294" s="153" t="s">
+      <c r="C294" s="149" t="s">
         <v>1555</v>
       </c>
-      <c r="D294" s="153" t="s">
+      <c r="D294" s="149" t="s">
         <v>1569</v>
       </c>
       <c r="E294" s="3"/>
@@ -38378,10 +38378,10 @@
     <row r="295" spans="1:7">
       <c r="A295" s="14"/>
       <c r="B295" s="14"/>
-      <c r="C295" s="153" t="s">
+      <c r="C295" s="149" t="s">
         <v>1555</v>
       </c>
-      <c r="D295" s="153" t="s">
+      <c r="D295" s="149" t="s">
         <v>1563</v>
       </c>
       <c r="E295" s="3"/>
@@ -38393,10 +38393,10 @@
     <row r="296" spans="1:7">
       <c r="A296" s="14"/>
       <c r="B296" s="14"/>
-      <c r="C296" s="153" t="s">
+      <c r="C296" s="149" t="s">
         <v>1555</v>
       </c>
-      <c r="D296" s="153" t="s">
+      <c r="D296" s="149" t="s">
         <v>1562</v>
       </c>
       <c r="E296" s="3"/>
@@ -38408,10 +38408,10 @@
     <row r="297" spans="1:7">
       <c r="A297" s="14"/>
       <c r="B297" s="14"/>
-      <c r="C297" s="153" t="s">
+      <c r="C297" s="149" t="s">
         <v>1555</v>
       </c>
-      <c r="D297" s="153" t="s">
+      <c r="D297" s="149" t="s">
         <v>1559</v>
       </c>
       <c r="E297" s="3"/>
@@ -38423,10 +38423,10 @@
     <row r="298" spans="1:7">
       <c r="A298" s="14"/>
       <c r="B298" s="14"/>
-      <c r="C298" s="153" t="s">
+      <c r="C298" s="149" t="s">
         <v>1555</v>
       </c>
-      <c r="D298" s="153" t="s">
+      <c r="D298" s="149" t="s">
         <v>1560</v>
       </c>
       <c r="E298" s="3"/>
@@ -38438,10 +38438,10 @@
     <row r="299" spans="1:7">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
-      <c r="C299" s="153" t="s">
+      <c r="C299" s="149" t="s">
         <v>1555</v>
       </c>
-      <c r="D299" s="153" t="s">
+      <c r="D299" s="149" t="s">
         <v>1554</v>
       </c>
       <c r="F299" s="10" t="s">
@@ -38451,31 +38451,34 @@
     <row r="300" spans="1:7">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
-      <c r="C300" s="153" t="s">
+      <c r="C300" s="149" t="s">
         <v>1555</v>
       </c>
-      <c r="D300" s="153" t="s">
+      <c r="D300" s="149" t="s">
         <v>651</v>
+      </c>
+      <c r="F300" s="10" t="s">
+        <v>1576</v>
       </c>
     </row>
     <row r="301" spans="1:7">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
-      <c r="C301" s="153" t="s">
+      <c r="C301" s="149" t="s">
         <v>1555</v>
       </c>
-      <c r="D301" s="153" t="s">
-        <v>116</v>
+      <c r="D301" s="149" t="s">
+        <v>840</v>
       </c>
     </row>
     <row r="302" spans="1:7">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
-      <c r="C302" s="153" t="s">
+      <c r="C302" s="149" t="s">
         <v>1555</v>
       </c>
-      <c r="D302" s="153" t="s">
-        <v>1576</v>
+      <c r="D302" s="149" t="s">
+        <v>841</v>
       </c>
     </row>
     <row r="303" spans="1:7">
@@ -38488,6 +38491,12 @@
     </row>
     <row r="307" spans="3:7">
       <c r="C307" s="29" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D307" s="29" t="s">
+        <v>1029</v>
+      </c>
+      <c r="E307" s="29" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -42049,13 +42058,13 @@
       <c r="A525" s="12"/>
       <c r="B525" s="12"/>
       <c r="C525" s="12"/>
-      <c r="D525" s="152" t="s">
+      <c r="D525" s="150" t="s">
         <v>35</v>
       </c>
-      <c r="E525" s="150" t="s">
-        <v>4</v>
-      </c>
-      <c r="F525" s="151" t="s">
+      <c r="E525" s="151" t="s">
+        <v>4</v>
+      </c>
+      <c r="F525" s="152" t="s">
         <v>36</v>
       </c>
       <c r="G525" s="3" t="s">
@@ -42066,9 +42075,9 @@
       <c r="A526" s="12"/>
       <c r="B526" s="12"/>
       <c r="C526" s="12"/>
-      <c r="D526" s="152"/>
-      <c r="E526" s="150"/>
-      <c r="F526" s="151"/>
+      <c r="D526" s="150"/>
+      <c r="E526" s="151"/>
+      <c r="F526" s="152"/>
       <c r="G526" s="3" t="s">
         <v>38</v>
       </c>
@@ -42094,13 +42103,13 @@
       <c r="A529" s="1"/>
       <c r="B529" s="1"/>
       <c r="C529" s="1"/>
-      <c r="D529" s="149" t="s">
+      <c r="D529" s="153" t="s">
         <v>42</v>
       </c>
-      <c r="E529" s="150" t="s">
-        <v>4</v>
-      </c>
-      <c r="F529" s="151" t="s">
+      <c r="E529" s="151" t="s">
+        <v>4</v>
+      </c>
+      <c r="F529" s="152" t="s">
         <v>43</v>
       </c>
       <c r="G529" s="3">
@@ -42111,9 +42120,9 @@
       <c r="A530" s="1"/>
       <c r="B530" s="1"/>
       <c r="C530" s="1"/>
-      <c r="D530" s="149"/>
-      <c r="E530" s="150"/>
-      <c r="F530" s="151"/>
+      <c r="D530" s="153"/>
+      <c r="E530" s="151"/>
+      <c r="F530" s="152"/>
       <c r="G530" s="3" t="s">
         <v>44</v>
       </c>
@@ -42122,13 +42131,13 @@
       <c r="A531" s="12"/>
       <c r="B531" s="12"/>
       <c r="C531" s="12"/>
-      <c r="D531" s="152" t="s">
+      <c r="D531" s="150" t="s">
         <v>45</v>
       </c>
-      <c r="E531" s="150" t="s">
-        <v>4</v>
-      </c>
-      <c r="F531" s="151" t="s">
+      <c r="E531" s="151" t="s">
+        <v>4</v>
+      </c>
+      <c r="F531" s="152" t="s">
         <v>46</v>
       </c>
       <c r="G531" s="3" t="s">
@@ -42139,9 +42148,9 @@
       <c r="A532" s="12"/>
       <c r="B532" s="12"/>
       <c r="C532" s="12"/>
-      <c r="D532" s="152"/>
-      <c r="E532" s="150"/>
-      <c r="F532" s="151"/>
+      <c r="D532" s="150"/>
+      <c r="E532" s="151"/>
+      <c r="F532" s="152"/>
       <c r="G532" s="3" t="s">
         <v>48</v>
       </c>
@@ -42167,13 +42176,13 @@
       <c r="A535" s="1"/>
       <c r="B535" s="1"/>
       <c r="C535" s="1"/>
-      <c r="D535" s="149" t="s">
+      <c r="D535" s="153" t="s">
         <v>52</v>
       </c>
-      <c r="E535" s="150" t="s">
+      <c r="E535" s="151" t="s">
         <v>2</v>
       </c>
-      <c r="F535" s="151" t="s">
+      <c r="F535" s="152" t="s">
         <v>53</v>
       </c>
       <c r="G535" s="3">
@@ -42184,9 +42193,9 @@
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
       <c r="C536" s="1"/>
-      <c r="D536" s="149"/>
-      <c r="E536" s="150"/>
-      <c r="F536" s="151"/>
+      <c r="D536" s="153"/>
+      <c r="E536" s="151"/>
+      <c r="F536" s="152"/>
       <c r="G536" s="3" t="s">
         <v>44</v>
       </c>
@@ -42195,13 +42204,13 @@
       <c r="A537" s="1"/>
       <c r="B537" s="1"/>
       <c r="C537" s="1"/>
-      <c r="D537" s="152" t="s">
+      <c r="D537" s="150" t="s">
         <v>54</v>
       </c>
-      <c r="E537" s="150" t="s">
-        <v>4</v>
-      </c>
-      <c r="F537" s="151" t="s">
+      <c r="E537" s="151" t="s">
+        <v>4</v>
+      </c>
+      <c r="F537" s="152" t="s">
         <v>55</v>
       </c>
       <c r="G537" s="3" t="s">
@@ -42212,9 +42221,9 @@
       <c r="A538" s="1"/>
       <c r="B538" s="1"/>
       <c r="C538" s="1"/>
-      <c r="D538" s="152"/>
-      <c r="E538" s="150"/>
-      <c r="F538" s="151"/>
+      <c r="D538" s="150"/>
+      <c r="E538" s="151"/>
+      <c r="F538" s="152"/>
       <c r="G538" s="3" t="s">
         <v>57</v>
       </c>
@@ -42223,13 +42232,13 @@
       <c r="A539" s="1"/>
       <c r="B539" s="1"/>
       <c r="C539" s="1"/>
-      <c r="D539" s="152" t="s">
+      <c r="D539" s="150" t="s">
         <v>58</v>
       </c>
-      <c r="E539" s="150" t="s">
-        <v>4</v>
-      </c>
-      <c r="F539" s="151" t="s">
+      <c r="E539" s="151" t="s">
+        <v>4</v>
+      </c>
+      <c r="F539" s="152" t="s">
         <v>59</v>
       </c>
       <c r="G539" s="3" t="s">
@@ -42240,9 +42249,9 @@
       <c r="A540" s="1"/>
       <c r="B540" s="1"/>
       <c r="C540" s="1"/>
-      <c r="D540" s="152"/>
-      <c r="E540" s="150"/>
-      <c r="F540" s="151"/>
+      <c r="D540" s="150"/>
+      <c r="E540" s="151"/>
+      <c r="F540" s="152"/>
       <c r="G540" s="3" t="s">
         <v>61</v>
       </c>
@@ -42251,13 +42260,13 @@
       <c r="A541" s="1"/>
       <c r="B541" s="1"/>
       <c r="C541" s="1"/>
-      <c r="D541" s="152" t="s">
+      <c r="D541" s="150" t="s">
         <v>62</v>
       </c>
-      <c r="E541" s="150" t="s">
-        <v>4</v>
-      </c>
-      <c r="F541" s="151" t="s">
+      <c r="E541" s="151" t="s">
+        <v>4</v>
+      </c>
+      <c r="F541" s="152" t="s">
         <v>63</v>
       </c>
       <c r="G541" s="3" t="s">
@@ -42268,9 +42277,9 @@
       <c r="A542" s="1"/>
       <c r="B542" s="1"/>
       <c r="C542" s="1"/>
-      <c r="D542" s="152"/>
-      <c r="E542" s="150"/>
-      <c r="F542" s="151"/>
+      <c r="D542" s="150"/>
+      <c r="E542" s="151"/>
+      <c r="F542" s="152"/>
       <c r="G542" s="3" t="s">
         <v>65</v>
       </c>
@@ -42345,13 +42354,13 @@
       <c r="A547" s="1"/>
       <c r="B547" s="1"/>
       <c r="C547" s="1"/>
-      <c r="D547" s="149" t="s">
+      <c r="D547" s="153" t="s">
         <v>86</v>
       </c>
-      <c r="E547" s="150" t="s">
-        <v>4</v>
-      </c>
-      <c r="F547" s="151" t="s">
+      <c r="E547" s="151" t="s">
+        <v>4</v>
+      </c>
+      <c r="F547" s="152" t="s">
         <v>87</v>
       </c>
       <c r="G547" s="3" t="s">
@@ -42362,9 +42371,9 @@
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
       <c r="C548" s="1"/>
-      <c r="D548" s="149"/>
-      <c r="E548" s="150"/>
-      <c r="F548" s="151"/>
+      <c r="D548" s="153"/>
+      <c r="E548" s="151"/>
+      <c r="F548" s="152"/>
       <c r="G548" s="3" t="s">
         <v>89</v>
       </c>
@@ -42373,9 +42382,9 @@
       <c r="A549" s="1"/>
       <c r="B549" s="1"/>
       <c r="C549" s="1"/>
-      <c r="D549" s="149"/>
-      <c r="E549" s="150"/>
-      <c r="F549" s="151"/>
+      <c r="D549" s="153"/>
+      <c r="E549" s="151"/>
+      <c r="F549" s="152"/>
       <c r="G549" s="3" t="s">
         <v>90</v>
       </c>
@@ -42384,13 +42393,13 @@
       <c r="A550" s="1"/>
       <c r="B550" s="1"/>
       <c r="C550" s="1"/>
-      <c r="D550" s="149" t="s">
+      <c r="D550" s="153" t="s">
         <v>91</v>
       </c>
-      <c r="E550" s="150" t="s">
-        <v>4</v>
-      </c>
-      <c r="F550" s="151" t="s">
+      <c r="E550" s="151" t="s">
+        <v>4</v>
+      </c>
+      <c r="F550" s="152" t="s">
         <v>92</v>
       </c>
       <c r="G550" s="3" t="s">
@@ -42401,9 +42410,9 @@
       <c r="A551" s="1"/>
       <c r="B551" s="1"/>
       <c r="C551" s="1"/>
-      <c r="D551" s="149"/>
-      <c r="E551" s="150"/>
-      <c r="F551" s="151"/>
+      <c r="D551" s="153"/>
+      <c r="E551" s="151"/>
+      <c r="F551" s="152"/>
       <c r="G551" s="3" t="s">
         <v>89</v>
       </c>
@@ -42412,9 +42421,9 @@
       <c r="A552" s="1"/>
       <c r="B552" s="1"/>
       <c r="C552" s="1"/>
-      <c r="D552" s="149"/>
-      <c r="E552" s="150"/>
-      <c r="F552" s="151"/>
+      <c r="D552" s="153"/>
+      <c r="E552" s="151"/>
+      <c r="F552" s="152"/>
       <c r="G552" s="3" t="s">
         <v>90</v>
       </c>
@@ -42839,24 +42848,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D525:D526"/>
-    <mergeCell ref="E525:E526"/>
-    <mergeCell ref="F525:F526"/>
-    <mergeCell ref="D529:D530"/>
-    <mergeCell ref="E529:E530"/>
-    <mergeCell ref="F529:F530"/>
-    <mergeCell ref="D531:D532"/>
-    <mergeCell ref="E531:E532"/>
-    <mergeCell ref="F531:F532"/>
-    <mergeCell ref="D535:D536"/>
-    <mergeCell ref="E535:E536"/>
-    <mergeCell ref="F535:F536"/>
-    <mergeCell ref="D537:D538"/>
-    <mergeCell ref="E537:E538"/>
-    <mergeCell ref="F537:F538"/>
-    <mergeCell ref="D539:D540"/>
-    <mergeCell ref="E539:E540"/>
-    <mergeCell ref="F539:F540"/>
     <mergeCell ref="D550:D552"/>
     <mergeCell ref="E550:E552"/>
     <mergeCell ref="F550:F552"/>
@@ -42866,6 +42857,24 @@
     <mergeCell ref="D547:D549"/>
     <mergeCell ref="E547:E549"/>
     <mergeCell ref="F547:F549"/>
+    <mergeCell ref="D537:D538"/>
+    <mergeCell ref="E537:E538"/>
+    <mergeCell ref="F537:F538"/>
+    <mergeCell ref="D539:D540"/>
+    <mergeCell ref="E539:E540"/>
+    <mergeCell ref="F539:F540"/>
+    <mergeCell ref="D531:D532"/>
+    <mergeCell ref="E531:E532"/>
+    <mergeCell ref="F531:F532"/>
+    <mergeCell ref="D535:D536"/>
+    <mergeCell ref="E535:E536"/>
+    <mergeCell ref="F535:F536"/>
+    <mergeCell ref="D525:D526"/>
+    <mergeCell ref="E525:E526"/>
+    <mergeCell ref="F525:F526"/>
+    <mergeCell ref="D529:D530"/>
+    <mergeCell ref="E529:E530"/>
+    <mergeCell ref="F529:F530"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1" display="Abbreviation of the journal name. We use WoS abbreviations that can be found here: https://images.webofknowledge.com/images/help/WOS/A_abrvjt.html" xr:uid="{6BB52E4D-01E2-44A6-B6CC-352383FA2940}"/>
@@ -42877,26 +42886,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4e0e0d96de7fb32b1678b66c28514d8e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" xmlns:ns3="432dd258-9dce-4cb3-b611-c68c0fbce7f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac451aab8c96dec805c937cbafca7133" ns2:_="" ns3:_="">
     <xsd:import namespace="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
@@ -43097,10 +43086,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0C90B0A-DBBE-4147-B2EE-79946A8DC171}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC19592A-9F30-4B32-9428-1D9634B8A0D4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
+    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -43117,20 +43137,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC19592A-9F30-4B32-9428-1D9634B8A0D4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0C90B0A-DBBE-4147-B2EE-79946A8DC171}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
-    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
+++ b/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="3044" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE7C217D-E428-40D6-8FB6-826D5C0759D2}"/>
   <bookViews>
-    <workbookView xWindow="-57710" yWindow="-110" windowWidth="29020" windowHeight="15700" xr2:uid="{FAB1A633-BA4D-4813-8605-DC3F4755D7C7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{FAB1A633-BA4D-4813-8605-DC3F4755D7C7}"/>
   </bookViews>
   <sheets>
     <sheet name="10_FOMD_metadata_synthesis" sheetId="1" r:id="rId1"/>
@@ -33072,6 +33072,24 @@
   </sheetData>
   <autoFilter ref="A1:S321" xr:uid="{82619C4B-D6B1-486E-87C6-D2252668E253}"/>
   <mergeCells count="27">
+    <mergeCell ref="O544:O545"/>
+    <mergeCell ref="P544:P545"/>
+    <mergeCell ref="Q544:Q545"/>
+    <mergeCell ref="O548:O549"/>
+    <mergeCell ref="P548:P549"/>
+    <mergeCell ref="Q548:Q549"/>
+    <mergeCell ref="O558:O559"/>
+    <mergeCell ref="P558:P559"/>
+    <mergeCell ref="Q558:Q559"/>
+    <mergeCell ref="O560:O561"/>
+    <mergeCell ref="P560:P561"/>
+    <mergeCell ref="Q560:Q561"/>
+    <mergeCell ref="O566:O568"/>
+    <mergeCell ref="P566:P568"/>
+    <mergeCell ref="Q566:Q568"/>
+    <mergeCell ref="O569:O571"/>
+    <mergeCell ref="P569:P571"/>
+    <mergeCell ref="Q569:Q571"/>
     <mergeCell ref="O556:O557"/>
     <mergeCell ref="P556:P557"/>
     <mergeCell ref="Q556:Q557"/>
@@ -33081,24 +33099,6 @@
     <mergeCell ref="P554:P555"/>
     <mergeCell ref="Q554:Q555"/>
     <mergeCell ref="O550:O551"/>
-    <mergeCell ref="O566:O568"/>
-    <mergeCell ref="P566:P568"/>
-    <mergeCell ref="Q566:Q568"/>
-    <mergeCell ref="O569:O571"/>
-    <mergeCell ref="P569:P571"/>
-    <mergeCell ref="Q569:Q571"/>
-    <mergeCell ref="O558:O559"/>
-    <mergeCell ref="P558:P559"/>
-    <mergeCell ref="Q558:Q559"/>
-    <mergeCell ref="O560:O561"/>
-    <mergeCell ref="P560:P561"/>
-    <mergeCell ref="Q560:Q561"/>
-    <mergeCell ref="O544:O545"/>
-    <mergeCell ref="P544:P545"/>
-    <mergeCell ref="Q544:Q545"/>
-    <mergeCell ref="O548:O549"/>
-    <mergeCell ref="P548:P549"/>
-    <mergeCell ref="Q548:Q549"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="Q7" r:id="rId1" display="Abbreviation of the journal name. We use WoS abbreviations that can be found here: https://images.webofknowledge.com/images/help/WOS/A_abrvjt.html" xr:uid="{B4DADD6B-F846-45B3-933B-5F25CC9FEF24}"/>
@@ -43675,24 +43675,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D553:D554"/>
-    <mergeCell ref="E553:E554"/>
-    <mergeCell ref="F553:F554"/>
-    <mergeCell ref="D557:D558"/>
-    <mergeCell ref="E557:E558"/>
-    <mergeCell ref="F557:F558"/>
-    <mergeCell ref="D559:D560"/>
-    <mergeCell ref="E559:E560"/>
-    <mergeCell ref="F559:F560"/>
-    <mergeCell ref="D563:D564"/>
-    <mergeCell ref="E563:E564"/>
-    <mergeCell ref="F563:F564"/>
-    <mergeCell ref="D565:D566"/>
-    <mergeCell ref="E565:E566"/>
-    <mergeCell ref="F565:F566"/>
-    <mergeCell ref="D567:D568"/>
-    <mergeCell ref="E567:E568"/>
-    <mergeCell ref="F567:F568"/>
     <mergeCell ref="D578:D580"/>
     <mergeCell ref="E578:E580"/>
     <mergeCell ref="F578:F580"/>
@@ -43702,6 +43684,24 @@
     <mergeCell ref="D575:D577"/>
     <mergeCell ref="E575:E577"/>
     <mergeCell ref="F575:F577"/>
+    <mergeCell ref="D565:D566"/>
+    <mergeCell ref="E565:E566"/>
+    <mergeCell ref="F565:F566"/>
+    <mergeCell ref="D567:D568"/>
+    <mergeCell ref="E567:E568"/>
+    <mergeCell ref="F567:F568"/>
+    <mergeCell ref="D559:D560"/>
+    <mergeCell ref="E559:E560"/>
+    <mergeCell ref="F559:F560"/>
+    <mergeCell ref="D563:D564"/>
+    <mergeCell ref="E563:E564"/>
+    <mergeCell ref="F563:F564"/>
+    <mergeCell ref="D553:D554"/>
+    <mergeCell ref="E553:E554"/>
+    <mergeCell ref="F553:F554"/>
+    <mergeCell ref="D557:D558"/>
+    <mergeCell ref="E557:E558"/>
+    <mergeCell ref="F557:F558"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1" display="Abbreviation of the journal name. We use WoS abbreviations that can be found here: https://images.webofknowledge.com/images/help/WOS/A_abrvjt.html" xr:uid="{6BB52E4D-01E2-44A6-B6CC-352383FA2940}"/>
@@ -43713,6 +43713,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4e0e0d96de7fb32b1678b66c28514d8e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" xmlns:ns3="432dd258-9dce-4cb3-b611-c68c0fbce7f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac451aab8c96dec805c937cbafca7133" ns2:_="" ns3:_="">
     <xsd:import namespace="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
@@ -43913,27 +43933,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63F80AE0-5CF8-441A-8E3E-6D76A3390D5E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
+    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0C90B0A-DBBE-4147-B2EE-79946A8DC171}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC19592A-9F30-4B32-9428-1D9634B8A0D4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -43950,23 +43969,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0C90B0A-DBBE-4147-B2EE-79946A8DC171}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63F80AE0-5CF8-441A-8E3E-6D76A3390D5E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
-    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
+++ b/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Evidence_Hub/02.FOMD/02.metadata_structure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3044" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE7C217D-E428-40D6-8FB6-826D5C0759D2}"/>
+  <xr:revisionPtr revIDLastSave="3050" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{178109FE-65A5-42B3-8323-F656C62B27EA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{FAB1A633-BA4D-4813-8605-DC3F4755D7C7}"/>
   </bookViews>
@@ -334,7 +334,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6521" uniqueCount="1648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6521" uniqueCount="1652">
   <si>
     <t>Example</t>
   </si>
@@ -11105,6 +11105,18 @@
   </si>
   <si>
     <t>out_comparison_id</t>
+  </si>
+  <si>
+    <t>pler_calc</t>
+  </si>
+  <si>
+    <t>pler_sd_calc</t>
+  </si>
+  <si>
+    <t>ler_calc</t>
+  </si>
+  <si>
+    <t>ler_sd_calc</t>
   </si>
 </sst>
 </file>
@@ -12363,12 +12375,12 @@
     <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="63" fillId="63" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -31665,7 +31677,7 @@
       <c r="L544" s="12"/>
       <c r="M544" s="12"/>
       <c r="N544" s="12"/>
-      <c r="O544" s="156" t="s">
+      <c r="O544" s="159" t="s">
         <v>35</v>
       </c>
       <c r="P544" s="157" t="s">
@@ -31693,7 +31705,7 @@
       <c r="L545" s="12"/>
       <c r="M545" s="12"/>
       <c r="N545" s="12"/>
-      <c r="O545" s="156"/>
+      <c r="O545" s="159"/>
       <c r="P545" s="157"/>
       <c r="Q545" s="158"/>
       <c r="R545" s="3" t="s">
@@ -31743,7 +31755,7 @@
       <c r="L548" s="1"/>
       <c r="M548" s="1"/>
       <c r="N548" s="1"/>
-      <c r="O548" s="159" t="s">
+      <c r="O548" s="156" t="s">
         <v>42</v>
       </c>
       <c r="P548" s="157" t="s">
@@ -31771,7 +31783,7 @@
       <c r="L549" s="1"/>
       <c r="M549" s="1"/>
       <c r="N549" s="1"/>
-      <c r="O549" s="159"/>
+      <c r="O549" s="156"/>
       <c r="P549" s="157"/>
       <c r="Q549" s="158"/>
       <c r="R549" s="3" t="s">
@@ -31793,7 +31805,7 @@
       <c r="L550" s="12"/>
       <c r="M550" s="12"/>
       <c r="N550" s="12"/>
-      <c r="O550" s="156" t="s">
+      <c r="O550" s="159" t="s">
         <v>45</v>
       </c>
       <c r="P550" s="157" t="s">
@@ -31821,7 +31833,7 @@
       <c r="L551" s="12"/>
       <c r="M551" s="12"/>
       <c r="N551" s="12"/>
-      <c r="O551" s="156"/>
+      <c r="O551" s="159"/>
       <c r="P551" s="157"/>
       <c r="Q551" s="158"/>
       <c r="R551" s="3" t="s">
@@ -31871,7 +31883,7 @@
       <c r="L554" s="1"/>
       <c r="M554" s="1"/>
       <c r="N554" s="1"/>
-      <c r="O554" s="159" t="s">
+      <c r="O554" s="156" t="s">
         <v>52</v>
       </c>
       <c r="P554" s="157" t="s">
@@ -31899,7 +31911,7 @@
       <c r="L555" s="1"/>
       <c r="M555" s="1"/>
       <c r="N555" s="1"/>
-      <c r="O555" s="159"/>
+      <c r="O555" s="156"/>
       <c r="P555" s="157"/>
       <c r="Q555" s="158"/>
       <c r="R555" s="3" t="s">
@@ -31921,7 +31933,7 @@
       <c r="L556" s="1"/>
       <c r="M556" s="1"/>
       <c r="N556" s="1"/>
-      <c r="O556" s="156" t="s">
+      <c r="O556" s="159" t="s">
         <v>54</v>
       </c>
       <c r="P556" s="157" t="s">
@@ -31949,7 +31961,7 @@
       <c r="L557" s="1"/>
       <c r="M557" s="1"/>
       <c r="N557" s="1"/>
-      <c r="O557" s="156"/>
+      <c r="O557" s="159"/>
       <c r="P557" s="157"/>
       <c r="Q557" s="158"/>
       <c r="R557" s="3" t="s">
@@ -31971,7 +31983,7 @@
       <c r="L558" s="1"/>
       <c r="M558" s="1"/>
       <c r="N558" s="1"/>
-      <c r="O558" s="156" t="s">
+      <c r="O558" s="159" t="s">
         <v>58</v>
       </c>
       <c r="P558" s="157" t="s">
@@ -31999,7 +32011,7 @@
       <c r="L559" s="1"/>
       <c r="M559" s="1"/>
       <c r="N559" s="1"/>
-      <c r="O559" s="156"/>
+      <c r="O559" s="159"/>
       <c r="P559" s="157"/>
       <c r="Q559" s="158"/>
       <c r="R559" s="3" t="s">
@@ -32021,7 +32033,7 @@
       <c r="L560" s="1"/>
       <c r="M560" s="1"/>
       <c r="N560" s="1"/>
-      <c r="O560" s="156" t="s">
+      <c r="O560" s="159" t="s">
         <v>62</v>
       </c>
       <c r="P560" s="157" t="s">
@@ -32049,7 +32061,7 @@
       <c r="L561" s="1"/>
       <c r="M561" s="1"/>
       <c r="N561" s="1"/>
-      <c r="O561" s="156"/>
+      <c r="O561" s="159"/>
       <c r="P561" s="157"/>
       <c r="Q561" s="158"/>
       <c r="R561" s="3" t="s">
@@ -32181,7 +32193,7 @@
       <c r="L566" s="1"/>
       <c r="M566" s="1"/>
       <c r="N566" s="1"/>
-      <c r="O566" s="159" t="s">
+      <c r="O566" s="156" t="s">
         <v>86</v>
       </c>
       <c r="P566" s="157" t="s">
@@ -32209,7 +32221,7 @@
       <c r="L567" s="1"/>
       <c r="M567" s="1"/>
       <c r="N567" s="1"/>
-      <c r="O567" s="159"/>
+      <c r="O567" s="156"/>
       <c r="P567" s="157"/>
       <c r="Q567" s="158"/>
       <c r="R567" s="3" t="s">
@@ -32231,7 +32243,7 @@
       <c r="L568" s="1"/>
       <c r="M568" s="1"/>
       <c r="N568" s="1"/>
-      <c r="O568" s="159"/>
+      <c r="O568" s="156"/>
       <c r="P568" s="157"/>
       <c r="Q568" s="158"/>
       <c r="R568" s="3" t="s">
@@ -32253,7 +32265,7 @@
       <c r="L569" s="1"/>
       <c r="M569" s="1"/>
       <c r="N569" s="1"/>
-      <c r="O569" s="159" t="s">
+      <c r="O569" s="156" t="s">
         <v>91</v>
       </c>
       <c r="P569" s="157" t="s">
@@ -32281,7 +32293,7 @@
       <c r="L570" s="1"/>
       <c r="M570" s="1"/>
       <c r="N570" s="1"/>
-      <c r="O570" s="159"/>
+      <c r="O570" s="156"/>
       <c r="P570" s="157"/>
       <c r="Q570" s="158"/>
       <c r="R570" s="3" t="s">
@@ -32303,7 +32315,7 @@
       <c r="L571" s="1"/>
       <c r="M571" s="1"/>
       <c r="N571" s="1"/>
-      <c r="O571" s="159"/>
+      <c r="O571" s="156"/>
       <c r="P571" s="157"/>
       <c r="Q571" s="158"/>
       <c r="R571" s="3" t="s">
@@ -33072,24 +33084,6 @@
   </sheetData>
   <autoFilter ref="A1:S321" xr:uid="{82619C4B-D6B1-486E-87C6-D2252668E253}"/>
   <mergeCells count="27">
-    <mergeCell ref="O544:O545"/>
-    <mergeCell ref="P544:P545"/>
-    <mergeCell ref="Q544:Q545"/>
-    <mergeCell ref="O548:O549"/>
-    <mergeCell ref="P548:P549"/>
-    <mergeCell ref="Q548:Q549"/>
-    <mergeCell ref="O558:O559"/>
-    <mergeCell ref="P558:P559"/>
-    <mergeCell ref="Q558:Q559"/>
-    <mergeCell ref="O560:O561"/>
-    <mergeCell ref="P560:P561"/>
-    <mergeCell ref="Q560:Q561"/>
-    <mergeCell ref="O566:O568"/>
-    <mergeCell ref="P566:P568"/>
-    <mergeCell ref="Q566:Q568"/>
-    <mergeCell ref="O569:O571"/>
-    <mergeCell ref="P569:P571"/>
-    <mergeCell ref="Q569:Q571"/>
     <mergeCell ref="O556:O557"/>
     <mergeCell ref="P556:P557"/>
     <mergeCell ref="Q556:Q557"/>
@@ -33099,6 +33093,24 @@
     <mergeCell ref="P554:P555"/>
     <mergeCell ref="Q554:Q555"/>
     <mergeCell ref="O550:O551"/>
+    <mergeCell ref="O566:O568"/>
+    <mergeCell ref="P566:P568"/>
+    <mergeCell ref="Q566:Q568"/>
+    <mergeCell ref="O569:O571"/>
+    <mergeCell ref="P569:P571"/>
+    <mergeCell ref="Q569:Q571"/>
+    <mergeCell ref="O558:O559"/>
+    <mergeCell ref="P558:P559"/>
+    <mergeCell ref="Q558:Q559"/>
+    <mergeCell ref="O560:O561"/>
+    <mergeCell ref="P560:P561"/>
+    <mergeCell ref="Q560:Q561"/>
+    <mergeCell ref="O544:O545"/>
+    <mergeCell ref="P544:P545"/>
+    <mergeCell ref="Q544:Q545"/>
+    <mergeCell ref="O548:O549"/>
+    <mergeCell ref="P548:P549"/>
+    <mergeCell ref="Q548:Q549"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="Q7" r:id="rId1" display="Abbreviation of the journal name. We use WoS abbreviations that can be found here: https://images.webofknowledge.com/images/help/WOS/A_abrvjt.html" xr:uid="{B4DADD6B-F846-45B3-933B-5F25CC9FEF24}"/>
@@ -39194,7 +39206,7 @@
         <v>1630</v>
       </c>
       <c r="D321" s="152" t="s">
-        <v>1637</v>
+        <v>1648</v>
       </c>
       <c r="E321" s="3" t="s">
         <v>2</v>
@@ -39207,7 +39219,7 @@
         <v>1630</v>
       </c>
       <c r="D322" s="152" t="s">
-        <v>1638</v>
+        <v>1649</v>
       </c>
       <c r="E322" s="3" t="s">
         <v>2</v>
@@ -39218,7 +39230,7 @@
         <v>1630</v>
       </c>
       <c r="D323" s="152" t="s">
-        <v>1639</v>
+        <v>1650</v>
       </c>
       <c r="E323" s="3" t="s">
         <v>2</v>
@@ -39229,7 +39241,7 @@
         <v>1630</v>
       </c>
       <c r="D324" s="152" t="s">
-        <v>1640</v>
+        <v>1651</v>
       </c>
       <c r="E324" s="3" t="s">
         <v>2</v>
@@ -42885,7 +42897,7 @@
       <c r="A553" s="12"/>
       <c r="B553" s="12"/>
       <c r="C553" s="12"/>
-      <c r="D553" s="156" t="s">
+      <c r="D553" s="159" t="s">
         <v>35</v>
       </c>
       <c r="E553" s="157" t="s">
@@ -42902,7 +42914,7 @@
       <c r="A554" s="12"/>
       <c r="B554" s="12"/>
       <c r="C554" s="12"/>
-      <c r="D554" s="156"/>
+      <c r="D554" s="159"/>
       <c r="E554" s="157"/>
       <c r="F554" s="158"/>
       <c r="G554" s="3" t="s">
@@ -42930,7 +42942,7 @@
       <c r="A557" s="1"/>
       <c r="B557" s="1"/>
       <c r="C557" s="1"/>
-      <c r="D557" s="159" t="s">
+      <c r="D557" s="156" t="s">
         <v>42</v>
       </c>
       <c r="E557" s="157" t="s">
@@ -42947,7 +42959,7 @@
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
       <c r="C558" s="1"/>
-      <c r="D558" s="159"/>
+      <c r="D558" s="156"/>
       <c r="E558" s="157"/>
       <c r="F558" s="158"/>
       <c r="G558" s="3" t="s">
@@ -42958,7 +42970,7 @@
       <c r="A559" s="12"/>
       <c r="B559" s="12"/>
       <c r="C559" s="12"/>
-      <c r="D559" s="156" t="s">
+      <c r="D559" s="159" t="s">
         <v>45</v>
       </c>
       <c r="E559" s="157" t="s">
@@ -42975,7 +42987,7 @@
       <c r="A560" s="12"/>
       <c r="B560" s="12"/>
       <c r="C560" s="12"/>
-      <c r="D560" s="156"/>
+      <c r="D560" s="159"/>
       <c r="E560" s="157"/>
       <c r="F560" s="158"/>
       <c r="G560" s="3" t="s">
@@ -43003,7 +43015,7 @@
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
-      <c r="D563" s="159" t="s">
+      <c r="D563" s="156" t="s">
         <v>52</v>
       </c>
       <c r="E563" s="157" t="s">
@@ -43020,7 +43032,7 @@
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
-      <c r="D564" s="159"/>
+      <c r="D564" s="156"/>
       <c r="E564" s="157"/>
       <c r="F564" s="158"/>
       <c r="G564" s="3" t="s">
@@ -43031,7 +43043,7 @@
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
-      <c r="D565" s="156" t="s">
+      <c r="D565" s="159" t="s">
         <v>54</v>
       </c>
       <c r="E565" s="157" t="s">
@@ -43048,7 +43060,7 @@
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
-      <c r="D566" s="156"/>
+      <c r="D566" s="159"/>
       <c r="E566" s="157"/>
       <c r="F566" s="158"/>
       <c r="G566" s="3" t="s">
@@ -43059,7 +43071,7 @@
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
       <c r="C567" s="1"/>
-      <c r="D567" s="156" t="s">
+      <c r="D567" s="159" t="s">
         <v>58</v>
       </c>
       <c r="E567" s="157" t="s">
@@ -43076,7 +43088,7 @@
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
       <c r="C568" s="1"/>
-      <c r="D568" s="156"/>
+      <c r="D568" s="159"/>
       <c r="E568" s="157"/>
       <c r="F568" s="158"/>
       <c r="G568" s="3" t="s">
@@ -43087,7 +43099,7 @@
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
       <c r="C569" s="1"/>
-      <c r="D569" s="156" t="s">
+      <c r="D569" s="159" t="s">
         <v>62</v>
       </c>
       <c r="E569" s="157" t="s">
@@ -43104,7 +43116,7 @@
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
       <c r="C570" s="1"/>
-      <c r="D570" s="156"/>
+      <c r="D570" s="159"/>
       <c r="E570" s="157"/>
       <c r="F570" s="158"/>
       <c r="G570" s="3" t="s">
@@ -43181,7 +43193,7 @@
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
       <c r="C575" s="1"/>
-      <c r="D575" s="159" t="s">
+      <c r="D575" s="156" t="s">
         <v>86</v>
       </c>
       <c r="E575" s="157" t="s">
@@ -43198,7 +43210,7 @@
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
-      <c r="D576" s="159"/>
+      <c r="D576" s="156"/>
       <c r="E576" s="157"/>
       <c r="F576" s="158"/>
       <c r="G576" s="3" t="s">
@@ -43209,7 +43221,7 @@
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
       <c r="C577" s="1"/>
-      <c r="D577" s="159"/>
+      <c r="D577" s="156"/>
       <c r="E577" s="157"/>
       <c r="F577" s="158"/>
       <c r="G577" s="3" t="s">
@@ -43220,7 +43232,7 @@
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
-      <c r="D578" s="159" t="s">
+      <c r="D578" s="156" t="s">
         <v>91</v>
       </c>
       <c r="E578" s="157" t="s">
@@ -43237,7 +43249,7 @@
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
-      <c r="D579" s="159"/>
+      <c r="D579" s="156"/>
       <c r="E579" s="157"/>
       <c r="F579" s="158"/>
       <c r="G579" s="3" t="s">
@@ -43248,7 +43260,7 @@
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
-      <c r="D580" s="159"/>
+      <c r="D580" s="156"/>
       <c r="E580" s="157"/>
       <c r="F580" s="158"/>
       <c r="G580" s="3" t="s">
@@ -43675,6 +43687,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D553:D554"/>
+    <mergeCell ref="E553:E554"/>
+    <mergeCell ref="F553:F554"/>
+    <mergeCell ref="D557:D558"/>
+    <mergeCell ref="E557:E558"/>
+    <mergeCell ref="F557:F558"/>
+    <mergeCell ref="D559:D560"/>
+    <mergeCell ref="E559:E560"/>
+    <mergeCell ref="F559:F560"/>
+    <mergeCell ref="D563:D564"/>
+    <mergeCell ref="E563:E564"/>
+    <mergeCell ref="F563:F564"/>
+    <mergeCell ref="D565:D566"/>
+    <mergeCell ref="E565:E566"/>
+    <mergeCell ref="F565:F566"/>
+    <mergeCell ref="D567:D568"/>
+    <mergeCell ref="E567:E568"/>
+    <mergeCell ref="F567:F568"/>
     <mergeCell ref="D578:D580"/>
     <mergeCell ref="E578:E580"/>
     <mergeCell ref="F578:F580"/>
@@ -43684,24 +43714,6 @@
     <mergeCell ref="D575:D577"/>
     <mergeCell ref="E575:E577"/>
     <mergeCell ref="F575:F577"/>
-    <mergeCell ref="D565:D566"/>
-    <mergeCell ref="E565:E566"/>
-    <mergeCell ref="F565:F566"/>
-    <mergeCell ref="D567:D568"/>
-    <mergeCell ref="E567:E568"/>
-    <mergeCell ref="F567:F568"/>
-    <mergeCell ref="D559:D560"/>
-    <mergeCell ref="E559:E560"/>
-    <mergeCell ref="F559:F560"/>
-    <mergeCell ref="D563:D564"/>
-    <mergeCell ref="E563:E564"/>
-    <mergeCell ref="F563:F564"/>
-    <mergeCell ref="D553:D554"/>
-    <mergeCell ref="E553:E554"/>
-    <mergeCell ref="F553:F554"/>
-    <mergeCell ref="D557:D558"/>
-    <mergeCell ref="E557:E558"/>
-    <mergeCell ref="F557:F558"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1" display="Abbreviation of the journal name. We use WoS abbreviations that can be found here: https://images.webofknowledge.com/images/help/WOS/A_abrvjt.html" xr:uid="{6BB52E4D-01E2-44A6-B6CC-352383FA2940}"/>
@@ -43713,26 +43725,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4e0e0d96de7fb32b1678b66c28514d8e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" xmlns:ns3="432dd258-9dce-4cb3-b611-c68c0fbce7f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac451aab8c96dec805c937cbafca7133" ns2:_="" ns3:_="">
     <xsd:import namespace="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
@@ -43933,26 +43925,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63F80AE0-5CF8-441A-8E3E-6D76A3390D5E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
-    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0C90B0A-DBBE-4147-B2EE-79946A8DC171}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC19592A-9F30-4B32-9428-1D9634B8A0D4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -43969,4 +43962,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0C90B0A-DBBE-4147-B2EE-79946A8DC171}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63F80AE0-5CF8-441A-8E3E-6D76A3390D5E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
+    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
+++ b/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Evidence_Hub/02.FOMD/02.metadata_structure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3050" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{178109FE-65A5-42B3-8323-F656C62B27EA}"/>
+  <xr:revisionPtr revIDLastSave="3057" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28C25BDE-0F87-423D-B6C7-5ED6DE029526}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{FAB1A633-BA4D-4813-8605-DC3F4755D7C7}"/>
+    <workbookView xWindow="-57710" yWindow="-110" windowWidth="29020" windowHeight="15700" activeTab="2" xr2:uid="{FAB1A633-BA4D-4813-8605-DC3F4755D7C7}"/>
   </bookViews>
   <sheets>
     <sheet name="10_FOMD_metadata_synthesis" sheetId="1" r:id="rId1"/>
@@ -12375,12 +12375,12 @@
     <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="63" fillId="63" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -31677,7 +31677,7 @@
       <c r="L544" s="12"/>
       <c r="M544" s="12"/>
       <c r="N544" s="12"/>
-      <c r="O544" s="159" t="s">
+      <c r="O544" s="156" t="s">
         <v>35</v>
       </c>
       <c r="P544" s="157" t="s">
@@ -31705,7 +31705,7 @@
       <c r="L545" s="12"/>
       <c r="M545" s="12"/>
       <c r="N545" s="12"/>
-      <c r="O545" s="159"/>
+      <c r="O545" s="156"/>
       <c r="P545" s="157"/>
       <c r="Q545" s="158"/>
       <c r="R545" s="3" t="s">
@@ -31755,7 +31755,7 @@
       <c r="L548" s="1"/>
       <c r="M548" s="1"/>
       <c r="N548" s="1"/>
-      <c r="O548" s="156" t="s">
+      <c r="O548" s="159" t="s">
         <v>42</v>
       </c>
       <c r="P548" s="157" t="s">
@@ -31783,7 +31783,7 @@
       <c r="L549" s="1"/>
       <c r="M549" s="1"/>
       <c r="N549" s="1"/>
-      <c r="O549" s="156"/>
+      <c r="O549" s="159"/>
       <c r="P549" s="157"/>
       <c r="Q549" s="158"/>
       <c r="R549" s="3" t="s">
@@ -31805,7 +31805,7 @@
       <c r="L550" s="12"/>
       <c r="M550" s="12"/>
       <c r="N550" s="12"/>
-      <c r="O550" s="159" t="s">
+      <c r="O550" s="156" t="s">
         <v>45</v>
       </c>
       <c r="P550" s="157" t="s">
@@ -31833,7 +31833,7 @@
       <c r="L551" s="12"/>
       <c r="M551" s="12"/>
       <c r="N551" s="12"/>
-      <c r="O551" s="159"/>
+      <c r="O551" s="156"/>
       <c r="P551" s="157"/>
       <c r="Q551" s="158"/>
       <c r="R551" s="3" t="s">
@@ -31883,7 +31883,7 @@
       <c r="L554" s="1"/>
       <c r="M554" s="1"/>
       <c r="N554" s="1"/>
-      <c r="O554" s="156" t="s">
+      <c r="O554" s="159" t="s">
         <v>52</v>
       </c>
       <c r="P554" s="157" t="s">
@@ -31911,7 +31911,7 @@
       <c r="L555" s="1"/>
       <c r="M555" s="1"/>
       <c r="N555" s="1"/>
-      <c r="O555" s="156"/>
+      <c r="O555" s="159"/>
       <c r="P555" s="157"/>
       <c r="Q555" s="158"/>
       <c r="R555" s="3" t="s">
@@ -31933,7 +31933,7 @@
       <c r="L556" s="1"/>
       <c r="M556" s="1"/>
       <c r="N556" s="1"/>
-      <c r="O556" s="159" t="s">
+      <c r="O556" s="156" t="s">
         <v>54</v>
       </c>
       <c r="P556" s="157" t="s">
@@ -31961,7 +31961,7 @@
       <c r="L557" s="1"/>
       <c r="M557" s="1"/>
       <c r="N557" s="1"/>
-      <c r="O557" s="159"/>
+      <c r="O557" s="156"/>
       <c r="P557" s="157"/>
       <c r="Q557" s="158"/>
       <c r="R557" s="3" t="s">
@@ -31983,7 +31983,7 @@
       <c r="L558" s="1"/>
       <c r="M558" s="1"/>
       <c r="N558" s="1"/>
-      <c r="O558" s="159" t="s">
+      <c r="O558" s="156" t="s">
         <v>58</v>
       </c>
       <c r="P558" s="157" t="s">
@@ -32011,7 +32011,7 @@
       <c r="L559" s="1"/>
       <c r="M559" s="1"/>
       <c r="N559" s="1"/>
-      <c r="O559" s="159"/>
+      <c r="O559" s="156"/>
       <c r="P559" s="157"/>
       <c r="Q559" s="158"/>
       <c r="R559" s="3" t="s">
@@ -32033,7 +32033,7 @@
       <c r="L560" s="1"/>
       <c r="M560" s="1"/>
       <c r="N560" s="1"/>
-      <c r="O560" s="159" t="s">
+      <c r="O560" s="156" t="s">
         <v>62</v>
       </c>
       <c r="P560" s="157" t="s">
@@ -32061,7 +32061,7 @@
       <c r="L561" s="1"/>
       <c r="M561" s="1"/>
       <c r="N561" s="1"/>
-      <c r="O561" s="159"/>
+      <c r="O561" s="156"/>
       <c r="P561" s="157"/>
       <c r="Q561" s="158"/>
       <c r="R561" s="3" t="s">
@@ -32193,7 +32193,7 @@
       <c r="L566" s="1"/>
       <c r="M566" s="1"/>
       <c r="N566" s="1"/>
-      <c r="O566" s="156" t="s">
+      <c r="O566" s="159" t="s">
         <v>86</v>
       </c>
       <c r="P566" s="157" t="s">
@@ -32221,7 +32221,7 @@
       <c r="L567" s="1"/>
       <c r="M567" s="1"/>
       <c r="N567" s="1"/>
-      <c r="O567" s="156"/>
+      <c r="O567" s="159"/>
       <c r="P567" s="157"/>
       <c r="Q567" s="158"/>
       <c r="R567" s="3" t="s">
@@ -32243,7 +32243,7 @@
       <c r="L568" s="1"/>
       <c r="M568" s="1"/>
       <c r="N568" s="1"/>
-      <c r="O568" s="156"/>
+      <c r="O568" s="159"/>
       <c r="P568" s="157"/>
       <c r="Q568" s="158"/>
       <c r="R568" s="3" t="s">
@@ -32265,7 +32265,7 @@
       <c r="L569" s="1"/>
       <c r="M569" s="1"/>
       <c r="N569" s="1"/>
-      <c r="O569" s="156" t="s">
+      <c r="O569" s="159" t="s">
         <v>91</v>
       </c>
       <c r="P569" s="157" t="s">
@@ -32293,7 +32293,7 @@
       <c r="L570" s="1"/>
       <c r="M570" s="1"/>
       <c r="N570" s="1"/>
-      <c r="O570" s="156"/>
+      <c r="O570" s="159"/>
       <c r="P570" s="157"/>
       <c r="Q570" s="158"/>
       <c r="R570" s="3" t="s">
@@ -32315,7 +32315,7 @@
       <c r="L571" s="1"/>
       <c r="M571" s="1"/>
       <c r="N571" s="1"/>
-      <c r="O571" s="156"/>
+      <c r="O571" s="159"/>
       <c r="P571" s="157"/>
       <c r="Q571" s="158"/>
       <c r="R571" s="3" t="s">
@@ -33084,6 +33084,24 @@
   </sheetData>
   <autoFilter ref="A1:S321" xr:uid="{82619C4B-D6B1-486E-87C6-D2252668E253}"/>
   <mergeCells count="27">
+    <mergeCell ref="O544:O545"/>
+    <mergeCell ref="P544:P545"/>
+    <mergeCell ref="Q544:Q545"/>
+    <mergeCell ref="O548:O549"/>
+    <mergeCell ref="P548:P549"/>
+    <mergeCell ref="Q548:Q549"/>
+    <mergeCell ref="O558:O559"/>
+    <mergeCell ref="P558:P559"/>
+    <mergeCell ref="Q558:Q559"/>
+    <mergeCell ref="O560:O561"/>
+    <mergeCell ref="P560:P561"/>
+    <mergeCell ref="Q560:Q561"/>
+    <mergeCell ref="O566:O568"/>
+    <mergeCell ref="P566:P568"/>
+    <mergeCell ref="Q566:Q568"/>
+    <mergeCell ref="O569:O571"/>
+    <mergeCell ref="P569:P571"/>
+    <mergeCell ref="Q569:Q571"/>
     <mergeCell ref="O556:O557"/>
     <mergeCell ref="P556:P557"/>
     <mergeCell ref="Q556:Q557"/>
@@ -33093,24 +33111,6 @@
     <mergeCell ref="P554:P555"/>
     <mergeCell ref="Q554:Q555"/>
     <mergeCell ref="O550:O551"/>
-    <mergeCell ref="O566:O568"/>
-    <mergeCell ref="P566:P568"/>
-    <mergeCell ref="Q566:Q568"/>
-    <mergeCell ref="O569:O571"/>
-    <mergeCell ref="P569:P571"/>
-    <mergeCell ref="Q569:Q571"/>
-    <mergeCell ref="O558:O559"/>
-    <mergeCell ref="P558:P559"/>
-    <mergeCell ref="Q558:Q559"/>
-    <mergeCell ref="O560:O561"/>
-    <mergeCell ref="P560:P561"/>
-    <mergeCell ref="Q560:Q561"/>
-    <mergeCell ref="O544:O545"/>
-    <mergeCell ref="P544:P545"/>
-    <mergeCell ref="Q544:Q545"/>
-    <mergeCell ref="O548:O549"/>
-    <mergeCell ref="P548:P549"/>
-    <mergeCell ref="Q548:Q549"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="Q7" r:id="rId1" display="Abbreviation of the journal name. We use WoS abbreviations that can be found here: https://images.webofknowledge.com/images/help/WOS/A_abrvjt.html" xr:uid="{B4DADD6B-F846-45B3-933B-5F25CC9FEF24}"/>
@@ -33368,7 +33368,7 @@
       </c>
       <c r="G11" s="3"/>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" ht="14" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="114" t="s">
         <v>974</v>
@@ -33377,13 +33377,13 @@
         <v>616</v>
       </c>
       <c r="D12" s="115" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F12" s="116" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G12" s="3"/>
     </row>
@@ -33396,13 +33396,13 @@
         <v>616</v>
       </c>
       <c r="D13" s="115" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F13" s="116" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G13" s="3"/>
     </row>
@@ -33567,13 +33567,13 @@
         <v>616</v>
       </c>
       <c r="D22" s="115" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="E22" s="92" t="s">
         <v>4</v>
       </c>
       <c r="F22" s="116" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G22" s="92"/>
     </row>
@@ -33586,13 +33586,13 @@
         <v>616</v>
       </c>
       <c r="D23" s="115" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="E23" s="92" t="s">
         <v>4</v>
       </c>
       <c r="F23" s="116" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G23" s="92"/>
     </row>
@@ -42897,7 +42897,7 @@
       <c r="A553" s="12"/>
       <c r="B553" s="12"/>
       <c r="C553" s="12"/>
-      <c r="D553" s="159" t="s">
+      <c r="D553" s="156" t="s">
         <v>35</v>
       </c>
       <c r="E553" s="157" t="s">
@@ -42914,7 +42914,7 @@
       <c r="A554" s="12"/>
       <c r="B554" s="12"/>
       <c r="C554" s="12"/>
-      <c r="D554" s="159"/>
+      <c r="D554" s="156"/>
       <c r="E554" s="157"/>
       <c r="F554" s="158"/>
       <c r="G554" s="3" t="s">
@@ -42942,7 +42942,7 @@
       <c r="A557" s="1"/>
       <c r="B557" s="1"/>
       <c r="C557" s="1"/>
-      <c r="D557" s="156" t="s">
+      <c r="D557" s="159" t="s">
         <v>42</v>
       </c>
       <c r="E557" s="157" t="s">
@@ -42959,7 +42959,7 @@
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
       <c r="C558" s="1"/>
-      <c r="D558" s="156"/>
+      <c r="D558" s="159"/>
       <c r="E558" s="157"/>
       <c r="F558" s="158"/>
       <c r="G558" s="3" t="s">
@@ -42970,7 +42970,7 @@
       <c r="A559" s="12"/>
       <c r="B559" s="12"/>
       <c r="C559" s="12"/>
-      <c r="D559" s="159" t="s">
+      <c r="D559" s="156" t="s">
         <v>45</v>
       </c>
       <c r="E559" s="157" t="s">
@@ -42987,7 +42987,7 @@
       <c r="A560" s="12"/>
       <c r="B560" s="12"/>
       <c r="C560" s="12"/>
-      <c r="D560" s="159"/>
+      <c r="D560" s="156"/>
       <c r="E560" s="157"/>
       <c r="F560" s="158"/>
       <c r="G560" s="3" t="s">
@@ -43015,7 +43015,7 @@
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
-      <c r="D563" s="156" t="s">
+      <c r="D563" s="159" t="s">
         <v>52</v>
       </c>
       <c r="E563" s="157" t="s">
@@ -43032,7 +43032,7 @@
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
-      <c r="D564" s="156"/>
+      <c r="D564" s="159"/>
       <c r="E564" s="157"/>
       <c r="F564" s="158"/>
       <c r="G564" s="3" t="s">
@@ -43043,7 +43043,7 @@
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
-      <c r="D565" s="159" t="s">
+      <c r="D565" s="156" t="s">
         <v>54</v>
       </c>
       <c r="E565" s="157" t="s">
@@ -43060,7 +43060,7 @@
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
-      <c r="D566" s="159"/>
+      <c r="D566" s="156"/>
       <c r="E566" s="157"/>
       <c r="F566" s="158"/>
       <c r="G566" s="3" t="s">
@@ -43071,7 +43071,7 @@
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
       <c r="C567" s="1"/>
-      <c r="D567" s="159" t="s">
+      <c r="D567" s="156" t="s">
         <v>58</v>
       </c>
       <c r="E567" s="157" t="s">
@@ -43088,7 +43088,7 @@
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
       <c r="C568" s="1"/>
-      <c r="D568" s="159"/>
+      <c r="D568" s="156"/>
       <c r="E568" s="157"/>
       <c r="F568" s="158"/>
       <c r="G568" s="3" t="s">
@@ -43099,7 +43099,7 @@
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
       <c r="C569" s="1"/>
-      <c r="D569" s="159" t="s">
+      <c r="D569" s="156" t="s">
         <v>62</v>
       </c>
       <c r="E569" s="157" t="s">
@@ -43116,7 +43116,7 @@
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
       <c r="C570" s="1"/>
-      <c r="D570" s="159"/>
+      <c r="D570" s="156"/>
       <c r="E570" s="157"/>
       <c r="F570" s="158"/>
       <c r="G570" s="3" t="s">
@@ -43193,7 +43193,7 @@
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
       <c r="C575" s="1"/>
-      <c r="D575" s="156" t="s">
+      <c r="D575" s="159" t="s">
         <v>86</v>
       </c>
       <c r="E575" s="157" t="s">
@@ -43210,7 +43210,7 @@
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
-      <c r="D576" s="156"/>
+      <c r="D576" s="159"/>
       <c r="E576" s="157"/>
       <c r="F576" s="158"/>
       <c r="G576" s="3" t="s">
@@ -43221,7 +43221,7 @@
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
       <c r="C577" s="1"/>
-      <c r="D577" s="156"/>
+      <c r="D577" s="159"/>
       <c r="E577" s="157"/>
       <c r="F577" s="158"/>
       <c r="G577" s="3" t="s">
@@ -43232,7 +43232,7 @@
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
-      <c r="D578" s="156" t="s">
+      <c r="D578" s="159" t="s">
         <v>91</v>
       </c>
       <c r="E578" s="157" t="s">
@@ -43249,7 +43249,7 @@
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
-      <c r="D579" s="156"/>
+      <c r="D579" s="159"/>
       <c r="E579" s="157"/>
       <c r="F579" s="158"/>
       <c r="G579" s="3" t="s">
@@ -43260,7 +43260,7 @@
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
-      <c r="D580" s="156"/>
+      <c r="D580" s="159"/>
       <c r="E580" s="157"/>
       <c r="F580" s="158"/>
       <c r="G580" s="3" t="s">
@@ -43687,24 +43687,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D553:D554"/>
-    <mergeCell ref="E553:E554"/>
-    <mergeCell ref="F553:F554"/>
-    <mergeCell ref="D557:D558"/>
-    <mergeCell ref="E557:E558"/>
-    <mergeCell ref="F557:F558"/>
-    <mergeCell ref="D559:D560"/>
-    <mergeCell ref="E559:E560"/>
-    <mergeCell ref="F559:F560"/>
-    <mergeCell ref="D563:D564"/>
-    <mergeCell ref="E563:E564"/>
-    <mergeCell ref="F563:F564"/>
-    <mergeCell ref="D565:D566"/>
-    <mergeCell ref="E565:E566"/>
-    <mergeCell ref="F565:F566"/>
-    <mergeCell ref="D567:D568"/>
-    <mergeCell ref="E567:E568"/>
-    <mergeCell ref="F567:F568"/>
     <mergeCell ref="D578:D580"/>
     <mergeCell ref="E578:E580"/>
     <mergeCell ref="F578:F580"/>
@@ -43714,6 +43696,24 @@
     <mergeCell ref="D575:D577"/>
     <mergeCell ref="E575:E577"/>
     <mergeCell ref="F575:F577"/>
+    <mergeCell ref="D565:D566"/>
+    <mergeCell ref="E565:E566"/>
+    <mergeCell ref="F565:F566"/>
+    <mergeCell ref="D567:D568"/>
+    <mergeCell ref="E567:E568"/>
+    <mergeCell ref="F567:F568"/>
+    <mergeCell ref="D559:D560"/>
+    <mergeCell ref="E559:E560"/>
+    <mergeCell ref="F559:F560"/>
+    <mergeCell ref="D563:D564"/>
+    <mergeCell ref="E563:E564"/>
+    <mergeCell ref="F563:F564"/>
+    <mergeCell ref="D553:D554"/>
+    <mergeCell ref="E553:E554"/>
+    <mergeCell ref="F553:F554"/>
+    <mergeCell ref="D557:D558"/>
+    <mergeCell ref="E557:E558"/>
+    <mergeCell ref="F557:F558"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1" display="Abbreviation of the journal name. We use WoS abbreviations that can be found here: https://images.webofknowledge.com/images/help/WOS/A_abrvjt.html" xr:uid="{6BB52E4D-01E2-44A6-B6CC-352383FA2940}"/>
@@ -43725,6 +43725,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4e0e0d96de7fb32b1678b66c28514d8e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" xmlns:ns3="432dd258-9dce-4cb3-b611-c68c0fbce7f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac451aab8c96dec805c937cbafca7133" ns2:_="" ns3:_="">
     <xsd:import namespace="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
@@ -43925,27 +43945,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63F80AE0-5CF8-441A-8E3E-6D76A3390D5E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
+    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0C90B0A-DBBE-4147-B2EE-79946A8DC171}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC19592A-9F30-4B32-9428-1D9634B8A0D4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -43962,23 +43981,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0C90B0A-DBBE-4147-B2EE-79946A8DC171}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63F80AE0-5CF8-441A-8E3E-6D76A3390D5E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
-    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
+++ b/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="3057" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28C25BDE-0F87-423D-B6C7-5ED6DE029526}"/>
   <bookViews>
-    <workbookView xWindow="-57710" yWindow="-110" windowWidth="29020" windowHeight="15700" activeTab="2" xr2:uid="{FAB1A633-BA4D-4813-8605-DC3F4755D7C7}"/>
+    <workbookView xWindow="57490" yWindow="-110" windowWidth="29020" windowHeight="15700" activeTab="2" xr2:uid="{FAB1A633-BA4D-4813-8605-DC3F4755D7C7}"/>
   </bookViews>
   <sheets>
     <sheet name="10_FOMD_metadata_synthesis" sheetId="1" r:id="rId1"/>
@@ -12375,12 +12375,12 @@
     <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="63" fillId="63" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -31677,7 +31677,7 @@
       <c r="L544" s="12"/>
       <c r="M544" s="12"/>
       <c r="N544" s="12"/>
-      <c r="O544" s="156" t="s">
+      <c r="O544" s="159" t="s">
         <v>35</v>
       </c>
       <c r="P544" s="157" t="s">
@@ -31705,7 +31705,7 @@
       <c r="L545" s="12"/>
       <c r="M545" s="12"/>
       <c r="N545" s="12"/>
-      <c r="O545" s="156"/>
+      <c r="O545" s="159"/>
       <c r="P545" s="157"/>
       <c r="Q545" s="158"/>
       <c r="R545" s="3" t="s">
@@ -31755,7 +31755,7 @@
       <c r="L548" s="1"/>
       <c r="M548" s="1"/>
       <c r="N548" s="1"/>
-      <c r="O548" s="159" t="s">
+      <c r="O548" s="156" t="s">
         <v>42</v>
       </c>
       <c r="P548" s="157" t="s">
@@ -31783,7 +31783,7 @@
       <c r="L549" s="1"/>
       <c r="M549" s="1"/>
       <c r="N549" s="1"/>
-      <c r="O549" s="159"/>
+      <c r="O549" s="156"/>
       <c r="P549" s="157"/>
       <c r="Q549" s="158"/>
       <c r="R549" s="3" t="s">
@@ -31805,7 +31805,7 @@
       <c r="L550" s="12"/>
       <c r="M550" s="12"/>
       <c r="N550" s="12"/>
-      <c r="O550" s="156" t="s">
+      <c r="O550" s="159" t="s">
         <v>45</v>
       </c>
       <c r="P550" s="157" t="s">
@@ -31833,7 +31833,7 @@
       <c r="L551" s="12"/>
       <c r="M551" s="12"/>
       <c r="N551" s="12"/>
-      <c r="O551" s="156"/>
+      <c r="O551" s="159"/>
       <c r="P551" s="157"/>
       <c r="Q551" s="158"/>
       <c r="R551" s="3" t="s">
@@ -31883,7 +31883,7 @@
       <c r="L554" s="1"/>
       <c r="M554" s="1"/>
       <c r="N554" s="1"/>
-      <c r="O554" s="159" t="s">
+      <c r="O554" s="156" t="s">
         <v>52</v>
       </c>
       <c r="P554" s="157" t="s">
@@ -31911,7 +31911,7 @@
       <c r="L555" s="1"/>
       <c r="M555" s="1"/>
       <c r="N555" s="1"/>
-      <c r="O555" s="159"/>
+      <c r="O555" s="156"/>
       <c r="P555" s="157"/>
       <c r="Q555" s="158"/>
       <c r="R555" s="3" t="s">
@@ -31933,7 +31933,7 @@
       <c r="L556" s="1"/>
       <c r="M556" s="1"/>
       <c r="N556" s="1"/>
-      <c r="O556" s="156" t="s">
+      <c r="O556" s="159" t="s">
         <v>54</v>
       </c>
       <c r="P556" s="157" t="s">
@@ -31961,7 +31961,7 @@
       <c r="L557" s="1"/>
       <c r="M557" s="1"/>
       <c r="N557" s="1"/>
-      <c r="O557" s="156"/>
+      <c r="O557" s="159"/>
       <c r="P557" s="157"/>
       <c r="Q557" s="158"/>
       <c r="R557" s="3" t="s">
@@ -31983,7 +31983,7 @@
       <c r="L558" s="1"/>
       <c r="M558" s="1"/>
       <c r="N558" s="1"/>
-      <c r="O558" s="156" t="s">
+      <c r="O558" s="159" t="s">
         <v>58</v>
       </c>
       <c r="P558" s="157" t="s">
@@ -32011,7 +32011,7 @@
       <c r="L559" s="1"/>
       <c r="M559" s="1"/>
       <c r="N559" s="1"/>
-      <c r="O559" s="156"/>
+      <c r="O559" s="159"/>
       <c r="P559" s="157"/>
       <c r="Q559" s="158"/>
       <c r="R559" s="3" t="s">
@@ -32033,7 +32033,7 @@
       <c r="L560" s="1"/>
       <c r="M560" s="1"/>
       <c r="N560" s="1"/>
-      <c r="O560" s="156" t="s">
+      <c r="O560" s="159" t="s">
         <v>62</v>
       </c>
       <c r="P560" s="157" t="s">
@@ -32061,7 +32061,7 @@
       <c r="L561" s="1"/>
       <c r="M561" s="1"/>
       <c r="N561" s="1"/>
-      <c r="O561" s="156"/>
+      <c r="O561" s="159"/>
       <c r="P561" s="157"/>
       <c r="Q561" s="158"/>
       <c r="R561" s="3" t="s">
@@ -32193,7 +32193,7 @@
       <c r="L566" s="1"/>
       <c r="M566" s="1"/>
       <c r="N566" s="1"/>
-      <c r="O566" s="159" t="s">
+      <c r="O566" s="156" t="s">
         <v>86</v>
       </c>
       <c r="P566" s="157" t="s">
@@ -32221,7 +32221,7 @@
       <c r="L567" s="1"/>
       <c r="M567" s="1"/>
       <c r="N567" s="1"/>
-      <c r="O567" s="159"/>
+      <c r="O567" s="156"/>
       <c r="P567" s="157"/>
       <c r="Q567" s="158"/>
       <c r="R567" s="3" t="s">
@@ -32243,7 +32243,7 @@
       <c r="L568" s="1"/>
       <c r="M568" s="1"/>
       <c r="N568" s="1"/>
-      <c r="O568" s="159"/>
+      <c r="O568" s="156"/>
       <c r="P568" s="157"/>
       <c r="Q568" s="158"/>
       <c r="R568" s="3" t="s">
@@ -32265,7 +32265,7 @@
       <c r="L569" s="1"/>
       <c r="M569" s="1"/>
       <c r="N569" s="1"/>
-      <c r="O569" s="159" t="s">
+      <c r="O569" s="156" t="s">
         <v>91</v>
       </c>
       <c r="P569" s="157" t="s">
@@ -32293,7 +32293,7 @@
       <c r="L570" s="1"/>
       <c r="M570" s="1"/>
       <c r="N570" s="1"/>
-      <c r="O570" s="159"/>
+      <c r="O570" s="156"/>
       <c r="P570" s="157"/>
       <c r="Q570" s="158"/>
       <c r="R570" s="3" t="s">
@@ -32315,7 +32315,7 @@
       <c r="L571" s="1"/>
       <c r="M571" s="1"/>
       <c r="N571" s="1"/>
-      <c r="O571" s="159"/>
+      <c r="O571" s="156"/>
       <c r="P571" s="157"/>
       <c r="Q571" s="158"/>
       <c r="R571" s="3" t="s">
@@ -33084,24 +33084,6 @@
   </sheetData>
   <autoFilter ref="A1:S321" xr:uid="{82619C4B-D6B1-486E-87C6-D2252668E253}"/>
   <mergeCells count="27">
-    <mergeCell ref="O544:O545"/>
-    <mergeCell ref="P544:P545"/>
-    <mergeCell ref="Q544:Q545"/>
-    <mergeCell ref="O548:O549"/>
-    <mergeCell ref="P548:P549"/>
-    <mergeCell ref="Q548:Q549"/>
-    <mergeCell ref="O558:O559"/>
-    <mergeCell ref="P558:P559"/>
-    <mergeCell ref="Q558:Q559"/>
-    <mergeCell ref="O560:O561"/>
-    <mergeCell ref="P560:P561"/>
-    <mergeCell ref="Q560:Q561"/>
-    <mergeCell ref="O566:O568"/>
-    <mergeCell ref="P566:P568"/>
-    <mergeCell ref="Q566:Q568"/>
-    <mergeCell ref="O569:O571"/>
-    <mergeCell ref="P569:P571"/>
-    <mergeCell ref="Q569:Q571"/>
     <mergeCell ref="O556:O557"/>
     <mergeCell ref="P556:P557"/>
     <mergeCell ref="Q556:Q557"/>
@@ -33111,6 +33093,24 @@
     <mergeCell ref="P554:P555"/>
     <mergeCell ref="Q554:Q555"/>
     <mergeCell ref="O550:O551"/>
+    <mergeCell ref="O566:O568"/>
+    <mergeCell ref="P566:P568"/>
+    <mergeCell ref="Q566:Q568"/>
+    <mergeCell ref="O569:O571"/>
+    <mergeCell ref="P569:P571"/>
+    <mergeCell ref="Q569:Q571"/>
+    <mergeCell ref="O558:O559"/>
+    <mergeCell ref="P558:P559"/>
+    <mergeCell ref="Q558:Q559"/>
+    <mergeCell ref="O560:O561"/>
+    <mergeCell ref="P560:P561"/>
+    <mergeCell ref="Q560:Q561"/>
+    <mergeCell ref="O544:O545"/>
+    <mergeCell ref="P544:P545"/>
+    <mergeCell ref="Q544:Q545"/>
+    <mergeCell ref="O548:O549"/>
+    <mergeCell ref="P548:P549"/>
+    <mergeCell ref="Q548:Q549"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="Q7" r:id="rId1" display="Abbreviation of the journal name. We use WoS abbreviations that can be found here: https://images.webofknowledge.com/images/help/WOS/A_abrvjt.html" xr:uid="{B4DADD6B-F846-45B3-933B-5F25CC9FEF24}"/>
@@ -42897,7 +42897,7 @@
       <c r="A553" s="12"/>
       <c r="B553" s="12"/>
       <c r="C553" s="12"/>
-      <c r="D553" s="156" t="s">
+      <c r="D553" s="159" t="s">
         <v>35</v>
       </c>
       <c r="E553" s="157" t="s">
@@ -42914,7 +42914,7 @@
       <c r="A554" s="12"/>
       <c r="B554" s="12"/>
       <c r="C554" s="12"/>
-      <c r="D554" s="156"/>
+      <c r="D554" s="159"/>
       <c r="E554" s="157"/>
       <c r="F554" s="158"/>
       <c r="G554" s="3" t="s">
@@ -42942,7 +42942,7 @@
       <c r="A557" s="1"/>
       <c r="B557" s="1"/>
       <c r="C557" s="1"/>
-      <c r="D557" s="159" t="s">
+      <c r="D557" s="156" t="s">
         <v>42</v>
       </c>
       <c r="E557" s="157" t="s">
@@ -42959,7 +42959,7 @@
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
       <c r="C558" s="1"/>
-      <c r="D558" s="159"/>
+      <c r="D558" s="156"/>
       <c r="E558" s="157"/>
       <c r="F558" s="158"/>
       <c r="G558" s="3" t="s">
@@ -42970,7 +42970,7 @@
       <c r="A559" s="12"/>
       <c r="B559" s="12"/>
       <c r="C559" s="12"/>
-      <c r="D559" s="156" t="s">
+      <c r="D559" s="159" t="s">
         <v>45</v>
       </c>
       <c r="E559" s="157" t="s">
@@ -42987,7 +42987,7 @@
       <c r="A560" s="12"/>
       <c r="B560" s="12"/>
       <c r="C560" s="12"/>
-      <c r="D560" s="156"/>
+      <c r="D560" s="159"/>
       <c r="E560" s="157"/>
       <c r="F560" s="158"/>
       <c r="G560" s="3" t="s">
@@ -43015,7 +43015,7 @@
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
-      <c r="D563" s="159" t="s">
+      <c r="D563" s="156" t="s">
         <v>52</v>
       </c>
       <c r="E563" s="157" t="s">
@@ -43032,7 +43032,7 @@
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
-      <c r="D564" s="159"/>
+      <c r="D564" s="156"/>
       <c r="E564" s="157"/>
       <c r="F564" s="158"/>
       <c r="G564" s="3" t="s">
@@ -43043,7 +43043,7 @@
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
-      <c r="D565" s="156" t="s">
+      <c r="D565" s="159" t="s">
         <v>54</v>
       </c>
       <c r="E565" s="157" t="s">
@@ -43060,7 +43060,7 @@
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
-      <c r="D566" s="156"/>
+      <c r="D566" s="159"/>
       <c r="E566" s="157"/>
       <c r="F566" s="158"/>
       <c r="G566" s="3" t="s">
@@ -43071,7 +43071,7 @@
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
       <c r="C567" s="1"/>
-      <c r="D567" s="156" t="s">
+      <c r="D567" s="159" t="s">
         <v>58</v>
       </c>
       <c r="E567" s="157" t="s">
@@ -43088,7 +43088,7 @@
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
       <c r="C568" s="1"/>
-      <c r="D568" s="156"/>
+      <c r="D568" s="159"/>
       <c r="E568" s="157"/>
       <c r="F568" s="158"/>
       <c r="G568" s="3" t="s">
@@ -43099,7 +43099,7 @@
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
       <c r="C569" s="1"/>
-      <c r="D569" s="156" t="s">
+      <c r="D569" s="159" t="s">
         <v>62</v>
       </c>
       <c r="E569" s="157" t="s">
@@ -43116,7 +43116,7 @@
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
       <c r="C570" s="1"/>
-      <c r="D570" s="156"/>
+      <c r="D570" s="159"/>
       <c r="E570" s="157"/>
       <c r="F570" s="158"/>
       <c r="G570" s="3" t="s">
@@ -43193,7 +43193,7 @@
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
       <c r="C575" s="1"/>
-      <c r="D575" s="159" t="s">
+      <c r="D575" s="156" t="s">
         <v>86</v>
       </c>
       <c r="E575" s="157" t="s">
@@ -43210,7 +43210,7 @@
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
-      <c r="D576" s="159"/>
+      <c r="D576" s="156"/>
       <c r="E576" s="157"/>
       <c r="F576" s="158"/>
       <c r="G576" s="3" t="s">
@@ -43221,7 +43221,7 @@
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
       <c r="C577" s="1"/>
-      <c r="D577" s="159"/>
+      <c r="D577" s="156"/>
       <c r="E577" s="157"/>
       <c r="F577" s="158"/>
       <c r="G577" s="3" t="s">
@@ -43232,7 +43232,7 @@
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
-      <c r="D578" s="159" t="s">
+      <c r="D578" s="156" t="s">
         <v>91</v>
       </c>
       <c r="E578" s="157" t="s">
@@ -43249,7 +43249,7 @@
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
-      <c r="D579" s="159"/>
+      <c r="D579" s="156"/>
       <c r="E579" s="157"/>
       <c r="F579" s="158"/>
       <c r="G579" s="3" t="s">
@@ -43260,7 +43260,7 @@
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
-      <c r="D580" s="159"/>
+      <c r="D580" s="156"/>
       <c r="E580" s="157"/>
       <c r="F580" s="158"/>
       <c r="G580" s="3" t="s">
@@ -43687,6 +43687,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D553:D554"/>
+    <mergeCell ref="E553:E554"/>
+    <mergeCell ref="F553:F554"/>
+    <mergeCell ref="D557:D558"/>
+    <mergeCell ref="E557:E558"/>
+    <mergeCell ref="F557:F558"/>
+    <mergeCell ref="D559:D560"/>
+    <mergeCell ref="E559:E560"/>
+    <mergeCell ref="F559:F560"/>
+    <mergeCell ref="D563:D564"/>
+    <mergeCell ref="E563:E564"/>
+    <mergeCell ref="F563:F564"/>
+    <mergeCell ref="D565:D566"/>
+    <mergeCell ref="E565:E566"/>
+    <mergeCell ref="F565:F566"/>
+    <mergeCell ref="D567:D568"/>
+    <mergeCell ref="E567:E568"/>
+    <mergeCell ref="F567:F568"/>
     <mergeCell ref="D578:D580"/>
     <mergeCell ref="E578:E580"/>
     <mergeCell ref="F578:F580"/>
@@ -43696,24 +43714,6 @@
     <mergeCell ref="D575:D577"/>
     <mergeCell ref="E575:E577"/>
     <mergeCell ref="F575:F577"/>
-    <mergeCell ref="D565:D566"/>
-    <mergeCell ref="E565:E566"/>
-    <mergeCell ref="F565:F566"/>
-    <mergeCell ref="D567:D568"/>
-    <mergeCell ref="E567:E568"/>
-    <mergeCell ref="F567:F568"/>
-    <mergeCell ref="D559:D560"/>
-    <mergeCell ref="E559:E560"/>
-    <mergeCell ref="F559:F560"/>
-    <mergeCell ref="D563:D564"/>
-    <mergeCell ref="E563:E564"/>
-    <mergeCell ref="F563:F564"/>
-    <mergeCell ref="D553:D554"/>
-    <mergeCell ref="E553:E554"/>
-    <mergeCell ref="F553:F554"/>
-    <mergeCell ref="D557:D558"/>
-    <mergeCell ref="E557:E558"/>
-    <mergeCell ref="F557:F558"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1" display="Abbreviation of the journal name. We use WoS abbreviations that can be found here: https://images.webofknowledge.com/images/help/WOS/A_abrvjt.html" xr:uid="{6BB52E4D-01E2-44A6-B6CC-352383FA2940}"/>
@@ -43725,26 +43725,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4e0e0d96de7fb32b1678b66c28514d8e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" xmlns:ns3="432dd258-9dce-4cb3-b611-c68c0fbce7f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac451aab8c96dec805c937cbafca7133" ns2:_="" ns3:_="">
     <xsd:import namespace="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
@@ -43945,26 +43925,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63F80AE0-5CF8-441A-8E3E-6D76A3390D5E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
-    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0C90B0A-DBBE-4147-B2EE-79946A8DC171}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC19592A-9F30-4B32-9428-1D9634B8A0D4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -43981,4 +43962,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0C90B0A-DBBE-4147-B2EE-79946A8DC171}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63F80AE0-5CF8-441A-8E3E-6D76A3390D5E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
+    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
+++ b/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Evidence_Hub/02.FOMD/02.metadata_structure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3057" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28C25BDE-0F87-423D-B6C7-5ED6DE029526}"/>
+  <xr:revisionPtr revIDLastSave="3077" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E8218A6-A563-4D3D-A425-2A9DFD55F8A1}"/>
   <bookViews>
     <workbookView xWindow="57490" yWindow="-110" windowWidth="29020" windowHeight="15700" activeTab="2" xr2:uid="{FAB1A633-BA4D-4813-8605-DC3F4755D7C7}"/>
   </bookViews>
@@ -269,7 +269,7 @@
     Should be the same for C and T, to check!</t>
       </text>
     </comment>
-    <comment ref="F381" authorId="1" shapeId="0" xr:uid="{05ADAAF8-AA23-445C-819C-71D52878014A}">
+    <comment ref="F382" authorId="1" shapeId="0" xr:uid="{05ADAAF8-AA23-445C-819C-71D52878014A}">
       <text>
         <r>
           <rPr>
@@ -283,7 +283,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F386" authorId="1" shapeId="0" xr:uid="{75001466-4C34-4F54-9B7C-4BBE6FBB3311}">
+    <comment ref="F387" authorId="1" shapeId="0" xr:uid="{75001466-4C34-4F54-9B7C-4BBE6FBB3311}">
       <text>
         <r>
           <rPr>
@@ -297,7 +297,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F499" authorId="7" shapeId="0" xr:uid="{CE5CE24D-637F-4D3D-9BD9-7662441D05AB}">
+    <comment ref="F500" authorId="7" shapeId="0" xr:uid="{CE5CE24D-637F-4D3D-9BD9-7662441D05AB}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -305,7 +305,7 @@
     Not sure what is this</t>
       </text>
     </comment>
-    <comment ref="F502" authorId="8" shapeId="0" xr:uid="{C0FFB8F0-4213-4080-AB70-B8075981D569}">
+    <comment ref="F503" authorId="8" shapeId="0" xr:uid="{C0FFB8F0-4213-4080-AB70-B8075981D569}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -313,7 +313,7 @@
     Not sure what is this</t>
       </text>
     </comment>
-    <comment ref="F505" authorId="9" shapeId="0" xr:uid="{63BE61FA-9CD1-49AD-95A7-6F9953D136F9}">
+    <comment ref="F506" authorId="9" shapeId="0" xr:uid="{63BE61FA-9CD1-49AD-95A7-6F9953D136F9}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -321,7 +321,7 @@
     Not sure what is this</t>
       </text>
     </comment>
-    <comment ref="F508" authorId="10" shapeId="0" xr:uid="{41477B88-7470-4A29-8291-5BA04E3F99E0}">
+    <comment ref="F509" authorId="10" shapeId="0" xr:uid="{41477B88-7470-4A29-8291-5BA04E3F99E0}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -334,7 +334,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6521" uniqueCount="1652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6533" uniqueCount="1655">
   <si>
     <t>Example</t>
   </si>
@@ -11107,16 +11107,25 @@
     <t>out_comparison_id</t>
   </si>
   <si>
-    <t>pler_calc</t>
-  </si>
-  <si>
-    <t>pler_sd_calc</t>
-  </si>
-  <si>
-    <t>ler_calc</t>
-  </si>
-  <si>
     <t>ler_sd_calc</t>
+  </si>
+  <si>
+    <t>pler_var_calc</t>
+  </si>
+  <si>
+    <t>ler_value_calc</t>
+  </si>
+  <si>
+    <t>ler_effect_size_yi</t>
+  </si>
+  <si>
+    <t>ler_effect_size_vi</t>
+  </si>
+  <si>
+    <t>ler_effect_size_type</t>
+  </si>
+  <si>
+    <t>ler_product</t>
   </si>
 </sst>
 </file>
@@ -13270,16 +13279,16 @@
   <threadedComment ref="D272" dT="2026-07-31T15:25:48.37" personId="{8754E5AB-4123-45AF-A584-AD9CD6F7A032}" id="{EAB21104-13DB-406F-AB06-2D8E16F65555}">
     <text>Should be the same for C and T, to check!</text>
   </threadedComment>
-  <threadedComment ref="F499" dT="2026-02-20T20:50:13.23" personId="{8754E5AB-4123-45AF-A584-AD9CD6F7A032}" id="{CE5CE24D-637F-4D3D-9BD9-7662441D05AB}">
+  <threadedComment ref="F500" dT="2026-02-20T20:50:13.23" personId="{8754E5AB-4123-45AF-A584-AD9CD6F7A032}" id="{CE5CE24D-637F-4D3D-9BD9-7662441D05AB}">
     <text>Not sure what is this</text>
   </threadedComment>
-  <threadedComment ref="F502" dT="2026-02-20T20:50:13.23" personId="{8754E5AB-4123-45AF-A584-AD9CD6F7A032}" id="{C0FFB8F0-4213-4080-AB70-B8075981D569}">
+  <threadedComment ref="F503" dT="2026-02-20T20:50:13.23" personId="{8754E5AB-4123-45AF-A584-AD9CD6F7A032}" id="{C0FFB8F0-4213-4080-AB70-B8075981D569}">
     <text>Not sure what is this</text>
   </threadedComment>
-  <threadedComment ref="F505" dT="2026-02-20T20:51:05.06" personId="{8754E5AB-4123-45AF-A584-AD9CD6F7A032}" id="{63BE61FA-9CD1-49AD-95A7-6F9953D136F9}">
+  <threadedComment ref="F506" dT="2026-02-20T20:51:05.06" personId="{8754E5AB-4123-45AF-A584-AD9CD6F7A032}" id="{63BE61FA-9CD1-49AD-95A7-6F9953D136F9}">
     <text>Not sure what is this</text>
   </threadedComment>
-  <threadedComment ref="F508" dT="2026-02-20T20:51:05.06" personId="{8754E5AB-4123-45AF-A584-AD9CD6F7A032}" id="{41477B88-7470-4A29-8291-5BA04E3F99E0}">
+  <threadedComment ref="F509" dT="2026-02-20T20:51:05.06" personId="{8754E5AB-4123-45AF-A584-AD9CD6F7A032}" id="{41477B88-7470-4A29-8291-5BA04E3F99E0}">
     <text>Not sure what is this</text>
   </threadedComment>
 </ThreadedComments>
@@ -33123,7 +33132,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14A586C8-08A0-4640-80FB-651A99A88EA6}">
-  <dimension ref="A1:H625"/>
+  <dimension ref="A1:H626"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="2" width="32.81640625" customWidth="1"/>
@@ -39206,7 +39215,7 @@
         <v>1630</v>
       </c>
       <c r="D321" s="152" t="s">
-        <v>1648</v>
+        <v>1637</v>
       </c>
       <c r="E321" s="3" t="s">
         <v>2</v>
@@ -39241,31 +39250,55 @@
         <v>1630</v>
       </c>
       <c r="D324" s="152" t="s">
-        <v>1651</v>
+        <v>1648</v>
       </c>
       <c r="E324" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="325" spans="1:7">
-      <c r="C325" s="153"/>
-      <c r="D325" s="154"/>
-      <c r="E325" s="3"/>
+      <c r="C325" s="84" t="s">
+        <v>1630</v>
+      </c>
+      <c r="D325" s="154" t="s">
+        <v>1654</v>
+      </c>
+      <c r="E325" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="326" spans="1:7">
-      <c r="C326" s="153"/>
-      <c r="D326" s="154"/>
-      <c r="E326" s="3"/>
+      <c r="C326" s="137" t="s">
+        <v>1552</v>
+      </c>
+      <c r="D326" s="154" t="s">
+        <v>1653</v>
+      </c>
+      <c r="E326" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="327" spans="1:7">
-      <c r="C327" s="153"/>
-      <c r="D327" s="154"/>
-      <c r="E327" s="3"/>
+      <c r="C327" s="84" t="s">
+        <v>1630</v>
+      </c>
+      <c r="D327" s="154" t="s">
+        <v>1651</v>
+      </c>
+      <c r="E327" s="3" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="328" spans="1:7">
-      <c r="C328" s="153"/>
-      <c r="D328" s="154"/>
-      <c r="E328" s="3"/>
+      <c r="C328" s="84" t="s">
+        <v>1630</v>
+      </c>
+      <c r="D328" s="154" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E328" s="3" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="329" spans="1:7">
       <c r="C329" s="153"/>
@@ -39273,46 +39306,38 @@
       <c r="E329" s="3"/>
     </row>
     <row r="330" spans="1:7">
-      <c r="C330" s="29" t="s">
+      <c r="C330" s="153"/>
+      <c r="D330" s="154"/>
+      <c r="E330" s="3"/>
+    </row>
+    <row r="331" spans="1:7">
+      <c r="C331" s="29" t="s">
         <v>1027</v>
       </c>
-      <c r="D330" s="29" t="s">
+      <c r="D331" s="29" t="s">
         <v>1027</v>
       </c>
-      <c r="E330" s="29" t="s">
+      <c r="E331" s="29" t="s">
         <v>1027</v>
-      </c>
-    </row>
-    <row r="331" spans="1:7">
-      <c r="C331" s="14" t="s">
-        <v>765</v>
-      </c>
-      <c r="D331" t="s">
-        <v>1618</v>
-      </c>
-      <c r="E331" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="332" spans="1:7">
       <c r="C332" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D332" s="59" t="s">
-        <v>1592</v>
-      </c>
-      <c r="E332" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F332" s="3"/>
-      <c r="G332" s="3"/>
+      <c r="D332" t="s">
+        <v>1618</v>
+      </c>
+      <c r="E332" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="333" spans="1:7">
       <c r="C333" s="14" t="s">
         <v>765</v>
       </c>
       <c r="D333" s="59" t="s">
-        <v>1596</v>
+        <v>1592</v>
       </c>
       <c r="E333" s="3" t="s">
         <v>2</v>
@@ -39324,11 +39349,11 @@
       <c r="C334" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D334" t="s">
-        <v>1619</v>
-      </c>
-      <c r="E334" t="s">
-        <v>4</v>
+      <c r="D334" s="59" t="s">
+        <v>1596</v>
+      </c>
+      <c r="E334" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="F334" s="3"/>
       <c r="G334" s="3"/>
@@ -39337,11 +39362,11 @@
       <c r="C335" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D335" s="59" t="s">
-        <v>1593</v>
-      </c>
-      <c r="E335" s="3" t="s">
-        <v>2</v>
+      <c r="D335" t="s">
+        <v>1619</v>
+      </c>
+      <c r="E335" t="s">
+        <v>4</v>
       </c>
       <c r="F335" s="3"/>
       <c r="G335" s="3"/>
@@ -39351,7 +39376,7 @@
         <v>765</v>
       </c>
       <c r="D336" s="59" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="E336" s="3" t="s">
         <v>2</v>
@@ -39363,11 +39388,11 @@
       <c r="C337" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D337" t="s">
-        <v>1620</v>
-      </c>
-      <c r="E337" t="s">
-        <v>4</v>
+      <c r="D337" s="59" t="s">
+        <v>1595</v>
+      </c>
+      <c r="E337" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="F337" s="3"/>
       <c r="G337" s="3"/>
@@ -39376,11 +39401,11 @@
       <c r="C338" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D338" s="59" t="s">
-        <v>1594</v>
-      </c>
-      <c r="E338" s="3" t="s">
-        <v>2</v>
+      <c r="D338" t="s">
+        <v>1620</v>
+      </c>
+      <c r="E338" t="s">
+        <v>4</v>
       </c>
       <c r="F338" s="3"/>
       <c r="G338" s="3"/>
@@ -39390,7 +39415,7 @@
         <v>765</v>
       </c>
       <c r="D339" s="59" t="s">
-        <v>1597</v>
+        <v>1594</v>
       </c>
       <c r="E339" s="3" t="s">
         <v>2</v>
@@ -39402,10 +39427,12 @@
       <c r="C340" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D340" t="s">
-        <v>1625</v>
-      </c>
-      <c r="E340" s="3"/>
+      <c r="D340" s="59" t="s">
+        <v>1597</v>
+      </c>
+      <c r="E340" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="F340" s="3"/>
       <c r="G340" s="3"/>
     </row>
@@ -39413,12 +39440,10 @@
       <c r="C341" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D341" s="59" t="s">
-        <v>1598</v>
-      </c>
-      <c r="E341" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="D341" t="s">
+        <v>1625</v>
+      </c>
+      <c r="E341" s="3"/>
       <c r="F341" s="3"/>
       <c r="G341" s="3"/>
     </row>
@@ -39427,7 +39452,7 @@
         <v>765</v>
       </c>
       <c r="D342" s="59" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="E342" s="3" t="s">
         <v>2</v>
@@ -39440,7 +39465,7 @@
         <v>765</v>
       </c>
       <c r="D343" s="59" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="E343" s="3" t="s">
         <v>2</v>
@@ -39453,7 +39478,7 @@
         <v>765</v>
       </c>
       <c r="D344" s="59" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="E344" s="3" t="s">
         <v>2</v>
@@ -39466,7 +39491,7 @@
         <v>765</v>
       </c>
       <c r="D345" s="59" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="E345" s="3" t="s">
         <v>2</v>
@@ -39479,7 +39504,7 @@
         <v>765</v>
       </c>
       <c r="D346" s="59" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="E346" s="3" t="s">
         <v>2</v>
@@ -39492,7 +39517,7 @@
         <v>765</v>
       </c>
       <c r="D347" s="59" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="E347" s="3" t="s">
         <v>2</v>
@@ -39505,7 +39530,7 @@
         <v>765</v>
       </c>
       <c r="D348" s="59" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="E348" s="3" t="s">
         <v>2</v>
@@ -39518,7 +39543,7 @@
         <v>765</v>
       </c>
       <c r="D349" s="59" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="E349" s="3" t="s">
         <v>2</v>
@@ -39531,7 +39556,7 @@
         <v>765</v>
       </c>
       <c r="D350" s="59" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="E350" s="3" t="s">
         <v>2</v>
@@ -39544,7 +39569,7 @@
         <v>765</v>
       </c>
       <c r="D351" s="59" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="E351" s="3" t="s">
         <v>2</v>
@@ -39557,7 +39582,7 @@
         <v>765</v>
       </c>
       <c r="D352" s="59" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="E352" s="3" t="s">
         <v>2</v>
@@ -39570,7 +39595,7 @@
         <v>765</v>
       </c>
       <c r="D353" s="59" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="E353" s="3" t="s">
         <v>2</v>
@@ -39583,7 +39608,7 @@
         <v>765</v>
       </c>
       <c r="D354" s="59" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="E354" s="3" t="s">
         <v>2</v>
@@ -39592,9 +39617,15 @@
       <c r="G354" s="3"/>
     </row>
     <row r="355" spans="1:7">
-      <c r="C355" s="14"/>
-      <c r="D355" s="59"/>
-      <c r="E355" s="3"/>
+      <c r="C355" s="14" t="s">
+        <v>765</v>
+      </c>
+      <c r="D355" s="59" t="s">
+        <v>1611</v>
+      </c>
+      <c r="E355" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="F355" s="3"/>
       <c r="G355" s="3"/>
     </row>
@@ -39620,21 +39651,11 @@
       <c r="G358" s="3"/>
     </row>
     <row r="359" spans="1:7">
-      <c r="A359" s="14"/>
-      <c r="B359" s="14"/>
-      <c r="C359" s="14" t="s">
-        <v>765</v>
-      </c>
-      <c r="D359" s="36" t="s">
-        <v>644</v>
-      </c>
-      <c r="E359" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F359" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="G359" s="14"/>
+      <c r="C359" s="14"/>
+      <c r="D359" s="59"/>
+      <c r="E359" s="3"/>
+      <c r="F359" s="3"/>
+      <c r="G359" s="3"/>
     </row>
     <row r="360" spans="1:7">
       <c r="A360" s="14"/>
@@ -39643,7 +39664,7 @@
         <v>765</v>
       </c>
       <c r="D360" s="36" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E360" s="1" t="s">
         <v>4</v>
@@ -39660,7 +39681,7 @@
         <v>765</v>
       </c>
       <c r="D361" s="36" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E361" s="1" t="s">
         <v>4</v>
@@ -39677,7 +39698,7 @@
         <v>765</v>
       </c>
       <c r="D362" s="36" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E362" s="1" t="s">
         <v>4</v>
@@ -39693,14 +39714,14 @@
       <c r="C363" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D363" s="16" t="s">
-        <v>1621</v>
-      </c>
-      <c r="E363" s="3" t="s">
+      <c r="D363" s="36" t="s">
+        <v>647</v>
+      </c>
+      <c r="E363" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F363" s="3" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="G363" s="14"/>
     </row>
@@ -39711,13 +39732,13 @@
         <v>765</v>
       </c>
       <c r="D364" s="16" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="E364" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F364" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G364" s="14"/>
     </row>
@@ -39728,13 +39749,13 @@
         <v>765</v>
       </c>
       <c r="D365" s="16" t="s">
-        <v>661</v>
+        <v>1622</v>
       </c>
       <c r="E365" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F365" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G365" s="14"/>
     </row>
@@ -39745,13 +39766,13 @@
         <v>765</v>
       </c>
       <c r="D366" s="16" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="E366" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F366" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G366" s="14"/>
     </row>
@@ -39762,13 +39783,13 @@
         <v>765</v>
       </c>
       <c r="D367" s="16" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="E367" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F367" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G367" s="14"/>
     </row>
@@ -39779,13 +39800,13 @@
         <v>765</v>
       </c>
       <c r="D368" s="16" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="E368" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F368" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G368" s="14"/>
     </row>
@@ -39796,13 +39817,13 @@
         <v>765</v>
       </c>
       <c r="D369" s="16" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="E369" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F369" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G369" s="14"/>
     </row>
@@ -39813,13 +39834,13 @@
         <v>765</v>
       </c>
       <c r="D370" s="16" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="E370" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F370" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G370" s="14"/>
     </row>
@@ -39830,13 +39851,13 @@
         <v>765</v>
       </c>
       <c r="D371" s="16" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E371" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F371" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G371" s="14"/>
     </row>
@@ -39847,13 +39868,13 @@
         <v>765</v>
       </c>
       <c r="D372" s="16" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="E372" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F372" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G372" s="14"/>
     </row>
@@ -39864,13 +39885,13 @@
         <v>765</v>
       </c>
       <c r="D373" s="16" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="E373" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F373" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G373" s="14"/>
     </row>
@@ -39881,13 +39902,13 @@
         <v>765</v>
       </c>
       <c r="D374" s="16" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="E374" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F374" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G374" s="14"/>
     </row>
@@ -39897,14 +39918,14 @@
       <c r="C375" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D375" s="34" t="s">
-        <v>671</v>
+      <c r="D375" s="16" t="s">
+        <v>670</v>
       </c>
       <c r="E375" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F375" s="3" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="G375" s="14"/>
     </row>
@@ -39915,13 +39936,13 @@
         <v>765</v>
       </c>
       <c r="D376" s="34" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E376" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F376" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G376" s="14"/>
     </row>
@@ -39932,13 +39953,13 @@
         <v>765</v>
       </c>
       <c r="D377" s="34" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="E377" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F377" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="G377" s="14"/>
     </row>
@@ -39949,13 +39970,13 @@
         <v>765</v>
       </c>
       <c r="D378" s="34" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="E378" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F378" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G378" s="14"/>
     </row>
@@ -39965,18 +39986,16 @@
       <c r="C379" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D379" s="20" t="s">
-        <v>675</v>
+      <c r="D379" s="34" t="s">
+        <v>674</v>
       </c>
       <c r="E379" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F379" t="s">
-        <v>325</v>
-      </c>
-      <c r="G379" s="31" t="s">
-        <v>326</v>
-      </c>
+      <c r="F379" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="G379" s="14"/>
     </row>
     <row r="380" spans="1:7">
       <c r="A380" s="14"/>
@@ -39985,16 +40004,16 @@
         <v>765</v>
       </c>
       <c r="D380" s="20" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E380" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F380" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G380" s="31" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="381" spans="1:7">
@@ -40004,16 +40023,16 @@
         <v>765</v>
       </c>
       <c r="D381" s="20" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="E381" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F381" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G381" s="31" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="382" spans="1:7">
@@ -40023,54 +40042,54 @@
         <v>765</v>
       </c>
       <c r="D382" s="20" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="E382" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F382" t="s">
-        <v>331</v>
-      </c>
-      <c r="G382" s="31">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="383" spans="1:7" ht="15.5">
+        <v>329</v>
+      </c>
+      <c r="G382" s="31" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="383" spans="1:7">
       <c r="A383" s="14"/>
       <c r="B383" s="14"/>
       <c r="C383" s="14" t="s">
         <v>765</v>
       </c>
       <c r="D383" s="20" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E383" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F383" t="s">
-        <v>332</v>
-      </c>
-      <c r="G383" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="384" spans="1:7">
+        <v>331</v>
+      </c>
+      <c r="G383" s="31">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="384" spans="1:7" ht="15.5">
       <c r="A384" s="14"/>
       <c r="B384" s="14"/>
       <c r="C384" s="14" t="s">
         <v>765</v>
       </c>
       <c r="D384" s="20" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E384" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F384" t="s">
-        <v>325</v>
-      </c>
-      <c r="G384" s="31" t="s">
-        <v>326</v>
+        <v>332</v>
+      </c>
+      <c r="G384" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="385" spans="1:7">
@@ -40080,16 +40099,16 @@
         <v>765</v>
       </c>
       <c r="D385" s="20" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E385" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F385" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G385" s="31" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="386" spans="1:7">
@@ -40099,16 +40118,16 @@
         <v>765</v>
       </c>
       <c r="D386" s="20" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="E386" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F386" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G386" s="31" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="387" spans="1:7">
@@ -40118,88 +40137,88 @@
         <v>765</v>
       </c>
       <c r="D387" s="20" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E387" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F387" t="s">
-        <v>331</v>
-      </c>
-      <c r="G387" s="31">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="388" spans="1:7" ht="15.5">
+        <v>329</v>
+      </c>
+      <c r="G387" s="31" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="388" spans="1:7">
       <c r="A388" s="14"/>
       <c r="B388" s="14"/>
       <c r="C388" s="14" t="s">
         <v>765</v>
       </c>
       <c r="D388" s="20" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="E388" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F388" t="s">
-        <v>332</v>
-      </c>
-      <c r="G388" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="389" spans="1:7">
+        <v>331</v>
+      </c>
+      <c r="G388" s="31">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="389" spans="1:7" ht="15.5">
       <c r="A389" s="14"/>
       <c r="B389" s="14"/>
       <c r="C389" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D389" s="24" t="s">
-        <v>685</v>
+      <c r="D389" s="20" t="s">
+        <v>684</v>
       </c>
       <c r="E389" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F389" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="390" spans="1:7" ht="15.5">
+        <v>332</v>
+      </c>
+      <c r="G389" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="390" spans="1:7">
       <c r="A390" s="14"/>
       <c r="B390" s="14"/>
       <c r="C390" s="14" t="s">
         <v>765</v>
       </c>
       <c r="D390" s="24" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E390" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F390" t="s">
-        <v>344</v>
-      </c>
-      <c r="G390" s="5"/>
-    </row>
-    <row r="391" spans="1:7">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="391" spans="1:7" ht="15.5">
       <c r="A391" s="14"/>
       <c r="B391" s="14"/>
       <c r="C391" s="14" t="s">
         <v>765</v>
       </c>
       <c r="D391" s="24" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E391" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F391" t="s">
-        <v>603</v>
-      </c>
-      <c r="G391" s="31" t="s">
-        <v>346</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="G391" s="5"/>
     </row>
     <row r="392" spans="1:7">
       <c r="A392" s="14"/>
@@ -40208,50 +40227,50 @@
         <v>765</v>
       </c>
       <c r="D392" s="24" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E392" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F392" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="393" spans="1:7" ht="15.5">
+        <v>603</v>
+      </c>
+      <c r="G392" s="31" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="393" spans="1:7">
       <c r="A393" s="14"/>
       <c r="B393" s="14"/>
       <c r="C393" s="14" t="s">
         <v>765</v>
       </c>
       <c r="D393" s="24" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E393" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F393" t="s">
-        <v>344</v>
-      </c>
-      <c r="G393" s="5"/>
-    </row>
-    <row r="394" spans="1:7">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="394" spans="1:7" ht="15.5">
       <c r="A394" s="14"/>
       <c r="B394" s="14"/>
       <c r="C394" s="14" t="s">
         <v>765</v>
       </c>
       <c r="D394" s="24" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="E394" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F394" t="s">
-        <v>603</v>
-      </c>
-      <c r="G394" s="31" t="s">
-        <v>346</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="G394" s="5"/>
     </row>
     <row r="395" spans="1:7">
       <c r="A395" s="14"/>
@@ -40259,17 +40278,17 @@
       <c r="C395" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D395" s="23" t="s">
-        <v>691</v>
+      <c r="D395" s="24" t="s">
+        <v>690</v>
       </c>
       <c r="E395" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F395" t="s">
-        <v>350</v>
+        <v>603</v>
       </c>
       <c r="G395" s="31" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
     </row>
     <row r="396" spans="1:7">
@@ -40279,53 +40298,53 @@
         <v>765</v>
       </c>
       <c r="D396" s="23" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E396" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F396" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G396" s="31" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="397" spans="1:7" ht="15.5">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="397" spans="1:7">
       <c r="A397" s="14"/>
       <c r="B397" s="14"/>
       <c r="C397" s="14" t="s">
         <v>765</v>
       </c>
       <c r="D397" s="23" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E397" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F397" t="s">
-        <v>355</v>
-      </c>
-      <c r="G397" s="5"/>
-    </row>
-    <row r="398" spans="1:7">
+        <v>351</v>
+      </c>
+      <c r="G397" s="31" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="398" spans="1:7" ht="15.5">
       <c r="A398" s="14"/>
       <c r="B398" s="14"/>
       <c r="C398" s="14" t="s">
         <v>765</v>
       </c>
       <c r="D398" s="23" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E398" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F398" t="s">
-        <v>356</v>
-      </c>
-      <c r="G398" s="31" t="s">
-        <v>357</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="G398" s="5"/>
     </row>
     <row r="399" spans="1:7">
       <c r="A399" s="14"/>
@@ -40334,16 +40353,16 @@
         <v>765</v>
       </c>
       <c r="D399" s="23" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E399" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F399" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="G399" s="31" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="400" spans="1:7">
@@ -40353,53 +40372,53 @@
         <v>765</v>
       </c>
       <c r="D400" s="23" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="E400" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F400" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G400" s="31" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="401" spans="1:7" ht="15.5">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="401" spans="1:7">
       <c r="A401" s="14"/>
       <c r="B401" s="14"/>
       <c r="C401" s="14" t="s">
         <v>765</v>
       </c>
       <c r="D401" s="23" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E401" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F401" t="s">
-        <v>355</v>
-      </c>
-      <c r="G401" s="5"/>
-    </row>
-    <row r="402" spans="1:7" ht="15" thickBot="1">
+        <v>351</v>
+      </c>
+      <c r="G401" s="31" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="402" spans="1:7" ht="15.5">
       <c r="A402" s="14"/>
       <c r="B402" s="14"/>
       <c r="C402" s="14" t="s">
         <v>765</v>
       </c>
       <c r="D402" s="23" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="E402" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F402" t="s">
-        <v>356</v>
-      </c>
-      <c r="G402" s="31" t="s">
-        <v>357</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="G402" s="5"/>
     </row>
     <row r="403" spans="1:7" ht="15" thickBot="1">
       <c r="A403" s="14"/>
@@ -40407,14 +40426,18 @@
       <c r="C403" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D403" s="21" t="s">
-        <v>699</v>
+      <c r="D403" s="23" t="s">
+        <v>698</v>
       </c>
       <c r="E403" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F403" s="3"/>
-      <c r="G403" s="14"/>
+      <c r="F403" t="s">
+        <v>356</v>
+      </c>
+      <c r="G403" s="31" t="s">
+        <v>357</v>
+      </c>
     </row>
     <row r="404" spans="1:7" ht="15" thickBot="1">
       <c r="A404" s="14"/>
@@ -40423,7 +40446,7 @@
         <v>765</v>
       </c>
       <c r="D404" s="21" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E404" s="3" t="s">
         <v>4</v>
@@ -40431,38 +40454,36 @@
       <c r="F404" s="3"/>
       <c r="G404" s="14"/>
     </row>
-    <row r="405" spans="1:7" ht="15.5">
+    <row r="405" spans="1:7" ht="15" thickBot="1">
+      <c r="A405" s="14"/>
+      <c r="B405" s="14"/>
       <c r="C405" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D405" s="24" t="s">
-        <v>701</v>
+      <c r="D405" s="21" t="s">
+        <v>700</v>
       </c>
       <c r="E405" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F405" t="s">
-        <v>397</v>
-      </c>
-      <c r="G405" s="5" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="406" spans="1:7">
+      <c r="F405" s="3"/>
+      <c r="G405" s="14"/>
+    </row>
+    <row r="406" spans="1:7" ht="15.5">
       <c r="C406" s="14" t="s">
         <v>765</v>
       </c>
       <c r="D406" s="24" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E406" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F406" t="s">
-        <v>399</v>
-      </c>
-      <c r="G406" t="s">
-        <v>597</v>
+        <v>397</v>
+      </c>
+      <c r="G406" s="5" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="407" spans="1:7">
@@ -40470,73 +40491,71 @@
         <v>765</v>
       </c>
       <c r="D407" s="24" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="E407" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F407" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G407" t="s">
         <v>597</v>
       </c>
     </row>
     <row r="408" spans="1:7">
-      <c r="A408" s="14"/>
-      <c r="B408" s="14"/>
       <c r="C408" s="14" t="s">
         <v>765</v>
       </c>
       <c r="D408" s="24" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E408" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F408" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G408" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="409" spans="1:7" ht="15.5">
+    <row r="409" spans="1:7">
       <c r="A409" s="14"/>
       <c r="B409" s="14"/>
       <c r="C409" s="14" t="s">
         <v>765</v>
       </c>
       <c r="D409" s="24" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E409" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F409" t="s">
-        <v>397</v>
-      </c>
-      <c r="G409" s="5" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="410" spans="1:7">
+        <v>401</v>
+      </c>
+      <c r="G409" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="410" spans="1:7" ht="15.5">
       <c r="A410" s="14"/>
       <c r="B410" s="14"/>
       <c r="C410" s="14" t="s">
         <v>765</v>
       </c>
       <c r="D410" s="24" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E410" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F410" t="s">
-        <v>399</v>
-      </c>
-      <c r="G410" t="s">
-        <v>597</v>
+        <v>397</v>
+      </c>
+      <c r="G410" s="5" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="411" spans="1:7">
@@ -40546,32 +40565,32 @@
         <v>765</v>
       </c>
       <c r="D411" s="24" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="E411" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F411" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G411" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="412" spans="1:7" ht="15" thickBot="1">
+    <row r="412" spans="1:7">
       <c r="A412" s="14"/>
       <c r="B412" s="14"/>
       <c r="C412" s="14" t="s">
         <v>765</v>
       </c>
       <c r="D412" s="24" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="E412" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F412" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G412" t="s">
         <v>597</v>
@@ -40583,17 +40602,17 @@
       <c r="C413" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D413" s="21" t="s">
-        <v>709</v>
-      </c>
-      <c r="E413" s="17" t="s">
+      <c r="D413" s="24" t="s">
+        <v>708</v>
+      </c>
+      <c r="E413" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F413" t="s">
-        <v>431</v>
-      </c>
-      <c r="G413" s="38" t="s">
-        <v>408</v>
+        <v>401</v>
+      </c>
+      <c r="G413" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="414" spans="1:7" ht="15" thickBot="1">
@@ -40603,16 +40622,16 @@
         <v>765</v>
       </c>
       <c r="D414" s="21" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="E414" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F414" t="s">
-        <v>433</v>
-      </c>
-      <c r="G414" t="s">
-        <v>419</v>
+        <v>431</v>
+      </c>
+      <c r="G414" s="38" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="415" spans="1:7" ht="15" thickBot="1">
@@ -40622,16 +40641,16 @@
         <v>765</v>
       </c>
       <c r="D415" s="21" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="E415" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F415" t="s">
-        <v>434</v>
-      </c>
-      <c r="G415" s="39" t="s">
-        <v>420</v>
+        <v>433</v>
+      </c>
+      <c r="G415" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="416" spans="1:7" ht="15" thickBot="1">
@@ -40641,16 +40660,16 @@
         <v>765</v>
       </c>
       <c r="D416" s="21" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E416" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F416" t="s">
-        <v>435</v>
-      </c>
-      <c r="G416" s="40" t="s">
-        <v>74</v>
+        <v>434</v>
+      </c>
+      <c r="G416" s="39" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="417" spans="1:7" ht="15" thickBot="1">
@@ -40660,16 +40679,16 @@
         <v>765</v>
       </c>
       <c r="D417" s="21" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E417" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F417" t="s">
-        <v>714</v>
-      </c>
-      <c r="G417" s="32" t="s">
-        <v>421</v>
+        <v>435</v>
+      </c>
+      <c r="G417" s="40" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="418" spans="1:7" ht="15" thickBot="1">
@@ -40679,16 +40698,16 @@
         <v>765</v>
       </c>
       <c r="D418" s="21" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="E418" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F418" t="s">
-        <v>437</v>
-      </c>
-      <c r="G418" t="s">
-        <v>74</v>
+        <v>714</v>
+      </c>
+      <c r="G418" s="32" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="419" spans="1:7" ht="15" thickBot="1">
@@ -40698,16 +40717,16 @@
         <v>765</v>
       </c>
       <c r="D419" s="21" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="E419" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F419" t="s">
-        <v>717</v>
-      </c>
-      <c r="G419">
-        <v>120</v>
+        <v>437</v>
+      </c>
+      <c r="G419" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="420" spans="1:7" ht="15" thickBot="1">
@@ -40717,16 +40736,16 @@
         <v>765</v>
       </c>
       <c r="D420" s="21" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E420" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F420" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="G420">
-        <v>30</v>
+        <v>120</v>
       </c>
     </row>
     <row r="421" spans="1:7" ht="15" thickBot="1">
@@ -40736,16 +40755,16 @@
         <v>765</v>
       </c>
       <c r="D421" s="21" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="E421" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F421" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="G421">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="422" spans="1:7" ht="15" thickBot="1">
@@ -40755,16 +40774,16 @@
         <v>765</v>
       </c>
       <c r="D422" s="21" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="E422" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F422" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="G422">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="423" spans="1:7" ht="15" thickBot="1">
@@ -40774,16 +40793,16 @@
         <v>765</v>
       </c>
       <c r="D423" s="21" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="E423" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F423" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="G423">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="424" spans="1:7" ht="15" thickBot="1">
@@ -40792,14 +40811,17 @@
       <c r="C424" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D424" s="20" t="s">
-        <v>726</v>
+      <c r="D424" s="21" t="s">
+        <v>724</v>
       </c>
       <c r="E424" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F424" t="s">
-        <v>443</v>
+        <v>725</v>
+      </c>
+      <c r="G424">
+        <v>90</v>
       </c>
     </row>
     <row r="425" spans="1:7" ht="15" thickBot="1">
@@ -40809,13 +40831,13 @@
         <v>765</v>
       </c>
       <c r="D425" s="20" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E425" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F425" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="426" spans="1:7" ht="15" thickBot="1">
@@ -40825,13 +40847,13 @@
         <v>765</v>
       </c>
       <c r="D426" s="20" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="E426" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F426" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="427" spans="1:7" ht="15" thickBot="1">
@@ -40841,13 +40863,13 @@
         <v>765</v>
       </c>
       <c r="D427" s="20" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E427" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F427" t="s">
-        <v>730</v>
+        <v>447</v>
       </c>
     </row>
     <row r="428" spans="1:7" ht="15" thickBot="1">
@@ -40857,13 +40879,13 @@
         <v>765</v>
       </c>
       <c r="D428" s="20" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="E428" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F428" t="s">
-        <v>448</v>
+        <v>730</v>
       </c>
     </row>
     <row r="429" spans="1:7" ht="15" thickBot="1">
@@ -40873,13 +40895,13 @@
         <v>765</v>
       </c>
       <c r="D429" s="20" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E429" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F429" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="430" spans="1:7" ht="15" thickBot="1">
@@ -40889,13 +40911,13 @@
         <v>765</v>
       </c>
       <c r="D430" s="20" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E430" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F430" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="431" spans="1:7" ht="15" thickBot="1">
@@ -40905,13 +40927,13 @@
         <v>765</v>
       </c>
       <c r="D431" s="20" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E431" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F431" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="432" spans="1:7" ht="15" thickBot="1">
@@ -40921,15 +40943,14 @@
         <v>765</v>
       </c>
       <c r="D432" s="20" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="E432" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F432" t="s">
-        <v>453</v>
-      </c>
-      <c r="G432" s="41"/>
+        <v>451</v>
+      </c>
     </row>
     <row r="433" spans="1:7" ht="15" thickBot="1">
       <c r="A433" s="14"/>
@@ -40937,18 +40958,16 @@
       <c r="C433" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D433" s="21" t="s">
-        <v>736</v>
+      <c r="D433" s="20" t="s">
+        <v>735</v>
       </c>
       <c r="E433" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F433" t="s">
-        <v>431</v>
-      </c>
-      <c r="G433" s="38" t="s">
-        <v>408</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="G433" s="41"/>
     </row>
     <row r="434" spans="1:7" ht="15" thickBot="1">
       <c r="A434" s="14"/>
@@ -40957,16 +40976,16 @@
         <v>765</v>
       </c>
       <c r="D434" s="21" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E434" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F434" t="s">
-        <v>433</v>
-      </c>
-      <c r="G434" t="s">
-        <v>419</v>
+        <v>431</v>
+      </c>
+      <c r="G434" s="38" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="435" spans="1:7" ht="15" thickBot="1">
@@ -40976,16 +40995,16 @@
         <v>765</v>
       </c>
       <c r="D435" s="21" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E435" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F435" t="s">
-        <v>434</v>
-      </c>
-      <c r="G435" s="39" t="s">
-        <v>420</v>
+        <v>433</v>
+      </c>
+      <c r="G435" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="436" spans="1:7" ht="15" thickBot="1">
@@ -40995,16 +41014,16 @@
         <v>765</v>
       </c>
       <c r="D436" s="21" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E436" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F436" t="s">
-        <v>435</v>
-      </c>
-      <c r="G436" s="40" t="s">
-        <v>74</v>
+        <v>434</v>
+      </c>
+      <c r="G436" s="39" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="437" spans="1:7" ht="15" thickBot="1">
@@ -41014,16 +41033,16 @@
         <v>765</v>
       </c>
       <c r="D437" s="21" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E437" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F437" t="s">
-        <v>741</v>
-      </c>
-      <c r="G437" s="32" t="s">
-        <v>421</v>
+        <v>435</v>
+      </c>
+      <c r="G437" s="40" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="438" spans="1:7" ht="15" thickBot="1">
@@ -41033,16 +41052,16 @@
         <v>765</v>
       </c>
       <c r="D438" s="21" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="E438" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F438" t="s">
-        <v>437</v>
-      </c>
-      <c r="G438" t="s">
-        <v>74</v>
+        <v>741</v>
+      </c>
+      <c r="G438" s="32" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="439" spans="1:7" ht="15" thickBot="1">
@@ -41052,16 +41071,16 @@
         <v>765</v>
       </c>
       <c r="D439" s="21" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E439" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F439" t="s">
-        <v>744</v>
-      </c>
-      <c r="G439">
-        <v>120</v>
+        <v>437</v>
+      </c>
+      <c r="G439" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="440" spans="1:7" ht="15" thickBot="1">
@@ -41071,16 +41090,16 @@
         <v>765</v>
       </c>
       <c r="D440" s="21" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="E440" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F440" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="G440">
-        <v>30</v>
+        <v>120</v>
       </c>
     </row>
     <row r="441" spans="1:7" ht="15" thickBot="1">
@@ -41090,16 +41109,16 @@
         <v>765</v>
       </c>
       <c r="D441" s="21" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="E441" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F441" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="G441">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="442" spans="1:7" ht="15" thickBot="1">
@@ -41109,16 +41128,16 @@
         <v>765</v>
       </c>
       <c r="D442" s="21" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="E442" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F442" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="G442">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="443" spans="1:7" ht="15" thickBot="1">
@@ -41128,16 +41147,16 @@
         <v>765</v>
       </c>
       <c r="D443" s="21" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="E443" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F443" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="G443">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="444" spans="1:7" ht="15" thickBot="1">
@@ -41146,14 +41165,17 @@
       <c r="C444" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D444" s="20" t="s">
-        <v>753</v>
+      <c r="D444" s="21" t="s">
+        <v>751</v>
       </c>
       <c r="E444" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F444" t="s">
-        <v>443</v>
+        <v>752</v>
+      </c>
+      <c r="G444">
+        <v>90</v>
       </c>
     </row>
     <row r="445" spans="1:7" ht="15" thickBot="1">
@@ -41163,13 +41185,13 @@
         <v>765</v>
       </c>
       <c r="D445" s="20" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E445" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F445" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="446" spans="1:7" ht="15" thickBot="1">
@@ -41179,13 +41201,13 @@
         <v>765</v>
       </c>
       <c r="D446" s="20" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="E446" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F446" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="447" spans="1:7" ht="15" thickBot="1">
@@ -41195,13 +41217,13 @@
         <v>765</v>
       </c>
       <c r="D447" s="20" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="E447" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F447" t="s">
-        <v>757</v>
+        <v>447</v>
       </c>
     </row>
     <row r="448" spans="1:7" ht="15" thickBot="1">
@@ -41211,13 +41233,13 @@
         <v>765</v>
       </c>
       <c r="D448" s="20" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="E448" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F448" t="s">
-        <v>448</v>
+        <v>757</v>
       </c>
     </row>
     <row r="449" spans="1:7" ht="15" thickBot="1">
@@ -41227,13 +41249,13 @@
         <v>765</v>
       </c>
       <c r="D449" s="20" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E449" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F449" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="450" spans="1:7" ht="15" thickBot="1">
@@ -41243,13 +41265,13 @@
         <v>765</v>
       </c>
       <c r="D450" s="20" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="E450" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F450" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="451" spans="1:7" ht="15" thickBot="1">
@@ -41259,13 +41281,13 @@
         <v>765</v>
       </c>
       <c r="D451" s="20" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="E451" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F451" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="452" spans="1:7" ht="15" thickBot="1">
@@ -41275,15 +41297,14 @@
         <v>765</v>
       </c>
       <c r="D452" s="20" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="E452" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F452" t="s">
-        <v>453</v>
-      </c>
-      <c r="G452" s="41"/>
+        <v>451</v>
+      </c>
     </row>
     <row r="453" spans="1:7" ht="15" thickBot="1">
       <c r="A453" s="14"/>
@@ -41291,18 +41312,16 @@
       <c r="C453" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D453" s="21" t="s">
-        <v>763</v>
+      <c r="D453" s="20" t="s">
+        <v>762</v>
       </c>
       <c r="E453" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F453" t="s">
-        <v>485</v>
-      </c>
-      <c r="G453" t="s">
-        <v>484</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="G453" s="41"/>
     </row>
     <row r="454" spans="1:7" ht="15" thickBot="1">
       <c r="A454" s="14"/>
@@ -41311,16 +41330,16 @@
         <v>765</v>
       </c>
       <c r="D454" s="21" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="E454" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F454" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="G454" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="455" spans="1:7" ht="15" thickBot="1">
@@ -41330,16 +41349,16 @@
         <v>765</v>
       </c>
       <c r="D455" s="21" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="E455" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F455" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G455" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="456" spans="1:7" ht="15" thickBot="1">
@@ -41349,16 +41368,16 @@
         <v>765</v>
       </c>
       <c r="D456" s="21" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E456" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F456" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="G456" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="457" spans="1:7" ht="15" thickBot="1">
@@ -41367,17 +41386,17 @@
       <c r="C457" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D457" s="20" t="s">
-        <v>768</v>
+      <c r="D457" s="21" t="s">
+        <v>767</v>
       </c>
       <c r="E457" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F457" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="G457" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
     </row>
     <row r="458" spans="1:7" ht="15" thickBot="1">
@@ -41387,16 +41406,16 @@
         <v>765</v>
       </c>
       <c r="D458" s="20" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E458" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F458" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="G458" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
     </row>
     <row r="459" spans="1:7" ht="15" thickBot="1">
@@ -41406,16 +41425,16 @@
         <v>765</v>
       </c>
       <c r="D459" s="20" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="E459" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F459" t="s">
-        <v>498</v>
-      </c>
-      <c r="G459" s="42" t="s">
-        <v>493</v>
+        <v>496</v>
+      </c>
+      <c r="G459" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="460" spans="1:7" ht="15" thickBot="1">
@@ -41425,16 +41444,16 @@
         <v>765</v>
       </c>
       <c r="D460" s="20" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="E460" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F460" t="s">
-        <v>499</v>
-      </c>
-      <c r="G460" t="s">
-        <v>494</v>
+        <v>498</v>
+      </c>
+      <c r="G460" s="42" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="461" spans="1:7" ht="15" thickBot="1">
@@ -41443,17 +41462,17 @@
       <c r="C461" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D461" s="21" t="s">
-        <v>772</v>
+      <c r="D461" s="20" t="s">
+        <v>771</v>
       </c>
       <c r="E461" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F461" t="s">
-        <v>524</v>
-      </c>
-      <c r="G461" s="42" t="s">
-        <v>501</v>
+        <v>499</v>
+      </c>
+      <c r="G461" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="462" spans="1:7" ht="15" thickBot="1">
@@ -41463,13 +41482,16 @@
         <v>765</v>
       </c>
       <c r="D462" s="21" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="E462" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F462" t="s">
-        <v>525</v>
+        <v>524</v>
+      </c>
+      <c r="G462" s="42" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="463" spans="1:7" ht="15" thickBot="1">
@@ -41479,15 +41501,14 @@
         <v>765</v>
       </c>
       <c r="D463" s="21" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="E463" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F463" t="s">
-        <v>526</v>
-      </c>
-      <c r="G463" s="43"/>
+        <v>525</v>
+      </c>
     </row>
     <row r="464" spans="1:7" ht="15" thickBot="1">
       <c r="A464" s="14"/>
@@ -41496,15 +41517,15 @@
         <v>765</v>
       </c>
       <c r="D464" s="21" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="E464" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F464" t="s">
-        <v>527</v>
-      </c>
-      <c r="G464" s="44"/>
+        <v>526</v>
+      </c>
+      <c r="G464" s="43"/>
     </row>
     <row r="465" spans="1:7" ht="15" thickBot="1">
       <c r="A465" s="14"/>
@@ -41513,13 +41534,13 @@
         <v>765</v>
       </c>
       <c r="D465" s="21" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="E465" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F465" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="G465" s="44"/>
     </row>
@@ -41530,14 +41551,15 @@
         <v>765</v>
       </c>
       <c r="D466" s="21" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E466" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F466" t="s">
-        <v>529</v>
-      </c>
+        <v>528</v>
+      </c>
+      <c r="G466" s="44"/>
     </row>
     <row r="467" spans="1:7" ht="15" thickBot="1">
       <c r="A467" s="14"/>
@@ -41546,13 +41568,13 @@
         <v>765</v>
       </c>
       <c r="D467" s="21" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="E467" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F467" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="468" spans="1:7" ht="15" thickBot="1">
@@ -41562,13 +41584,13 @@
         <v>765</v>
       </c>
       <c r="D468" s="21" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="E468" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F468" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="469" spans="1:7" ht="15" thickBot="1">
@@ -41578,13 +41600,13 @@
         <v>765</v>
       </c>
       <c r="D469" s="21" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="E469" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F469" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="470" spans="1:7" ht="15" thickBot="1">
@@ -41594,16 +41616,13 @@
         <v>765</v>
       </c>
       <c r="D470" s="21" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="E470" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F470" t="s">
-        <v>533</v>
-      </c>
-      <c r="G470" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
     </row>
     <row r="471" spans="1:7" ht="15" thickBot="1">
@@ -41613,16 +41632,16 @@
         <v>765</v>
       </c>
       <c r="D471" s="21" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="E471" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F471" t="s">
-        <v>534</v>
-      </c>
-      <c r="G471" s="43" t="s">
-        <v>520</v>
+        <v>533</v>
+      </c>
+      <c r="G471" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="472" spans="1:7" ht="15" thickBot="1">
@@ -41632,13 +41651,16 @@
         <v>765</v>
       </c>
       <c r="D472" s="21" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="E472" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F472" t="s">
-        <v>525</v>
+        <v>534</v>
+      </c>
+      <c r="G472" s="43" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="473" spans="1:7" ht="15" thickBot="1">
@@ -41648,16 +41670,13 @@
         <v>765</v>
       </c>
       <c r="D473" s="21" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="E473" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F473" t="s">
-        <v>535</v>
-      </c>
-      <c r="G473" s="43" t="s">
-        <v>511</v>
+        <v>525</v>
       </c>
     </row>
     <row r="474" spans="1:7" ht="15" thickBot="1">
@@ -41667,15 +41686,15 @@
         <v>765</v>
       </c>
       <c r="D474" s="21" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E474" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F474" t="s">
-        <v>536</v>
-      </c>
-      <c r="G474" s="44" t="s">
+        <v>535</v>
+      </c>
+      <c r="G474" s="43" t="s">
         <v>511</v>
       </c>
     </row>
@@ -41686,13 +41705,13 @@
         <v>765</v>
       </c>
       <c r="D475" s="21" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="E475" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F475" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="G475" s="44" t="s">
         <v>511</v>
@@ -41705,13 +41724,16 @@
         <v>765</v>
       </c>
       <c r="D476" s="21" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="E476" s="17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F476" t="s">
-        <v>529</v>
+        <v>537</v>
+      </c>
+      <c r="G476" s="44" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="477" spans="1:7" ht="15" thickBot="1">
@@ -41721,16 +41743,13 @@
         <v>765</v>
       </c>
       <c r="D477" s="21" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E477" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F477" t="s">
-        <v>538</v>
-      </c>
-      <c r="G477" s="45" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
     </row>
     <row r="478" spans="1:7" ht="15" thickBot="1">
@@ -41740,16 +41759,16 @@
         <v>765</v>
       </c>
       <c r="D478" s="21" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E478" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F478" t="s">
-        <v>531</v>
-      </c>
-      <c r="G478" s="44" t="s">
-        <v>511</v>
+        <v>538</v>
+      </c>
+      <c r="G478" s="45" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="479" spans="1:7" ht="15" thickBot="1">
@@ -41759,13 +41778,13 @@
         <v>765</v>
       </c>
       <c r="D479" s="21" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E479" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F479" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="G479" s="44" t="s">
         <v>511</v>
@@ -41778,16 +41797,16 @@
         <v>765</v>
       </c>
       <c r="D480" s="21" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E480" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F480" t="s">
-        <v>540</v>
-      </c>
-      <c r="G480" s="41" t="s">
-        <v>523</v>
+        <v>539</v>
+      </c>
+      <c r="G480" s="44" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="481" spans="1:7" ht="15" thickBot="1">
@@ -41796,17 +41815,17 @@
       <c r="C481" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D481" s="50" t="s">
-        <v>782</v>
+      <c r="D481" s="21" t="s">
+        <v>794</v>
       </c>
       <c r="E481" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F481" t="s">
-        <v>545</v>
-      </c>
-      <c r="G481" s="29" t="s">
-        <v>548</v>
+        <v>540</v>
+      </c>
+      <c r="G481" s="41" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="482" spans="1:7" ht="15" thickBot="1">
@@ -41816,16 +41835,16 @@
         <v>765</v>
       </c>
       <c r="D482" s="50" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="E482" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F482" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="G482" s="29" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="483" spans="1:7" ht="15" thickBot="1">
@@ -41835,16 +41854,16 @@
         <v>765</v>
       </c>
       <c r="D483" s="50" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="E483" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F483" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G483" s="29" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="484" spans="1:7" ht="15" thickBot="1">
@@ -41854,16 +41873,16 @@
         <v>765</v>
       </c>
       <c r="D484" s="50" t="s">
-        <v>795</v>
+        <v>784</v>
       </c>
       <c r="E484" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F484" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="G484" s="29" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="485" spans="1:7" ht="15" thickBot="1">
@@ -41873,16 +41892,16 @@
         <v>765</v>
       </c>
       <c r="D485" s="50" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="E485" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F485" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="G485" s="29" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="486" spans="1:7" ht="15" thickBot="1">
@@ -41892,16 +41911,16 @@
         <v>765</v>
       </c>
       <c r="D486" s="50" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E486" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F486" t="s">
-        <v>555</v>
-      </c>
-      <c r="G486" t="s">
-        <v>523</v>
+        <v>553</v>
+      </c>
+      <c r="G486" s="29" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="487" spans="1:7" ht="15" thickBot="1">
@@ -41910,14 +41929,17 @@
       <c r="C487" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D487" s="51" t="s">
-        <v>798</v>
+      <c r="D487" s="50" t="s">
+        <v>797</v>
       </c>
       <c r="E487" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F487" t="s">
-        <v>563</v>
+        <v>555</v>
+      </c>
+      <c r="G487" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="488" spans="1:7" ht="15" thickBot="1">
@@ -41927,16 +41949,13 @@
         <v>765</v>
       </c>
       <c r="D488" s="51" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="E488" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F488" s="48" t="s">
-        <v>572</v>
-      </c>
-      <c r="G488" t="s">
-        <v>558</v>
+        <v>4</v>
+      </c>
+      <c r="F488" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="489" spans="1:7" ht="15" thickBot="1">
@@ -41946,16 +41965,16 @@
         <v>765</v>
       </c>
       <c r="D489" s="51" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="E489" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="F489" t="s">
-        <v>564</v>
+        <v>7</v>
+      </c>
+      <c r="F489" s="48" t="s">
+        <v>572</v>
       </c>
       <c r="G489" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
     </row>
     <row r="490" spans="1:7" ht="15" thickBot="1">
@@ -41965,16 +41984,16 @@
         <v>765</v>
       </c>
       <c r="D490" s="51" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="E490" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F490" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="G490" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="491" spans="1:7" ht="15" thickBot="1">
@@ -41984,13 +42003,16 @@
         <v>765</v>
       </c>
       <c r="D491" s="51" t="s">
-        <v>811</v>
+        <v>801</v>
       </c>
       <c r="E491" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F491" t="s">
-        <v>568</v>
+        <v>566</v>
+      </c>
+      <c r="G491" t="s">
+        <v>567</v>
       </c>
     </row>
     <row r="492" spans="1:7" ht="15" thickBot="1">
@@ -42000,16 +42022,13 @@
         <v>765</v>
       </c>
       <c r="D492" s="51" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="E492" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F492" s="48" t="s">
-        <v>571</v>
-      </c>
-      <c r="G492" t="s">
-        <v>558</v>
+        <v>4</v>
+      </c>
+      <c r="F492" t="s">
+        <v>568</v>
       </c>
     </row>
     <row r="493" spans="1:7" ht="15" thickBot="1">
@@ -42019,16 +42038,16 @@
         <v>765</v>
       </c>
       <c r="D493" s="51" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="E493" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="F493" t="s">
-        <v>569</v>
+        <v>7</v>
+      </c>
+      <c r="F493" s="48" t="s">
+        <v>571</v>
       </c>
       <c r="G493" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="494" spans="1:7" ht="15" thickBot="1">
@@ -42038,13 +42057,16 @@
         <v>765</v>
       </c>
       <c r="D494" s="51" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="E494" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F494" t="s">
-        <v>570</v>
+        <v>569</v>
+      </c>
+      <c r="G494" t="s">
+        <v>557</v>
       </c>
     </row>
     <row r="495" spans="1:7" ht="15" thickBot="1">
@@ -42053,14 +42075,14 @@
       <c r="C495" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D495" s="52" t="s">
-        <v>802</v>
+      <c r="D495" s="51" t="s">
+        <v>814</v>
       </c>
       <c r="E495" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F495" t="s">
-        <v>585</v>
+        <v>570</v>
       </c>
     </row>
     <row r="496" spans="1:7" ht="15" thickBot="1">
@@ -42070,13 +42092,13 @@
         <v>765</v>
       </c>
       <c r="D496" s="52" t="s">
-        <v>815</v>
+        <v>802</v>
       </c>
       <c r="E496" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F496" t="s">
-        <v>575</v>
+        <v>585</v>
       </c>
     </row>
     <row r="497" spans="1:7" ht="15" thickBot="1">
@@ -42085,14 +42107,14 @@
       <c r="C497" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D497" s="20" t="s">
-        <v>803</v>
+      <c r="D497" s="52" t="s">
+        <v>815</v>
       </c>
       <c r="E497" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F497" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
     </row>
     <row r="498" spans="1:7" ht="15" thickBot="1">
@@ -42102,16 +42124,13 @@
         <v>765</v>
       </c>
       <c r="D498" s="20" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="E498" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F498" s="68" t="s">
-        <v>602</v>
-      </c>
-      <c r="G498" t="s">
-        <v>558</v>
+        <v>4</v>
+      </c>
+      <c r="F498" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="499" spans="1:7" ht="15" thickBot="1">
@@ -42121,13 +42140,16 @@
         <v>765</v>
       </c>
       <c r="D499" s="20" t="s">
-        <v>805</v>
-      </c>
-      <c r="E499" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="F499" t="s">
-        <v>581</v>
+        <v>804</v>
+      </c>
+      <c r="E499" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F499" s="68" t="s">
+        <v>602</v>
+      </c>
+      <c r="G499" t="s">
+        <v>558</v>
       </c>
     </row>
     <row r="500" spans="1:7" ht="15" thickBot="1">
@@ -42137,13 +42159,13 @@
         <v>765</v>
       </c>
       <c r="D500" s="20" t="s">
-        <v>816</v>
-      </c>
-      <c r="E500" s="17" t="s">
-        <v>4</v>
+        <v>805</v>
+      </c>
+      <c r="E500" s="19" t="s">
+        <v>12</v>
       </c>
       <c r="F500" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="501" spans="1:7" ht="15" thickBot="1">
@@ -42153,32 +42175,32 @@
         <v>765</v>
       </c>
       <c r="D501" s="20" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="E501" s="17" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F501" t="s">
-        <v>583</v>
-      </c>
-      <c r="G501" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="502" spans="1:7">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="502" spans="1:7" ht="15" thickBot="1">
       <c r="A502" s="14"/>
       <c r="B502" s="14"/>
       <c r="C502" s="14" t="s">
         <v>765</v>
       </c>
       <c r="D502" s="20" t="s">
-        <v>818</v>
-      </c>
-      <c r="E502" s="19" t="s">
-        <v>12</v>
+        <v>817</v>
+      </c>
+      <c r="E502" s="17" t="s">
+        <v>7</v>
       </c>
       <c r="F502" t="s">
-        <v>584</v>
+        <v>583</v>
+      </c>
+      <c r="G502" t="s">
+        <v>558</v>
       </c>
     </row>
     <row r="503" spans="1:7">
@@ -42187,14 +42209,14 @@
       <c r="C503" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D503" s="53" t="s">
-        <v>806</v>
+      <c r="D503" s="20" t="s">
+        <v>818</v>
       </c>
       <c r="E503" s="19" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F503" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="504" spans="1:7">
@@ -42204,13 +42226,13 @@
         <v>765</v>
       </c>
       <c r="D504" s="53" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="E504" s="19" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F504" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="505" spans="1:7">
@@ -42220,13 +42242,13 @@
         <v>765</v>
       </c>
       <c r="D505" s="53" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="E505" s="19" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F505" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="506" spans="1:7">
@@ -42236,13 +42258,13 @@
         <v>765</v>
       </c>
       <c r="D506" s="53" t="s">
-        <v>819</v>
+        <v>808</v>
       </c>
       <c r="E506" s="19" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F506" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="507" spans="1:7">
@@ -42252,13 +42274,13 @@
         <v>765</v>
       </c>
       <c r="D507" s="53" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="E507" s="19" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F507" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
     </row>
     <row r="508" spans="1:7">
@@ -42268,13 +42290,13 @@
         <v>765</v>
       </c>
       <c r="D508" s="53" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="E508" s="19" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F508" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="509" spans="1:7">
@@ -42283,12 +42305,14 @@
       <c r="C509" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D509" s="36" t="s">
-        <v>809</v>
-      </c>
-      <c r="E509" s="19"/>
+      <c r="D509" s="53" t="s">
+        <v>821</v>
+      </c>
+      <c r="E509" s="19" t="s">
+        <v>12</v>
+      </c>
       <c r="F509" t="s">
-        <v>613</v>
+        <v>591</v>
       </c>
     </row>
     <row r="510" spans="1:7">
@@ -42298,11 +42322,11 @@
         <v>765</v>
       </c>
       <c r="D510" s="36" t="s">
-        <v>822</v>
+        <v>809</v>
       </c>
       <c r="E510" s="19"/>
       <c r="F510" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="511" spans="1:7">
@@ -42312,11 +42336,11 @@
         <v>765</v>
       </c>
       <c r="D511" s="36" t="s">
-        <v>810</v>
+        <v>822</v>
       </c>
       <c r="E511" s="19"/>
       <c r="F511" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="512" spans="1:7">
@@ -42326,11 +42350,11 @@
         <v>765</v>
       </c>
       <c r="D512" s="36" t="s">
-        <v>823</v>
+        <v>810</v>
       </c>
       <c r="E512" s="19"/>
       <c r="F512" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="513" spans="1:7">
@@ -42339,17 +42363,12 @@
       <c r="C513" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D513" s="1" t="s">
-        <v>824</v>
-      </c>
-      <c r="E513" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F513" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="G513" s="3" t="s">
-        <v>149</v>
+      <c r="D513" s="36" t="s">
+        <v>823</v>
+      </c>
+      <c r="E513" s="19"/>
+      <c r="F513" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="514" spans="1:7">
@@ -42358,17 +42377,17 @@
       <c r="C514" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D514" s="18" t="s">
-        <v>825</v>
+      <c r="D514" s="1" t="s">
+        <v>824</v>
       </c>
       <c r="E514" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F514" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G514" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="515" spans="1:7">
@@ -42378,16 +42397,16 @@
         <v>765</v>
       </c>
       <c r="D515" s="18" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="E515" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F515" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G515" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="516" spans="1:7">
@@ -42397,16 +42416,16 @@
         <v>765</v>
       </c>
       <c r="D516" s="18" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="E516" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F516" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G516" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="517" spans="1:7">
@@ -42415,14 +42434,14 @@
       <c r="C517" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D517" s="1" t="s">
-        <v>828</v>
+      <c r="D517" s="18" t="s">
+        <v>827</v>
       </c>
       <c r="E517" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F517" s="4" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="G517" s="3" t="s">
         <v>149</v>
@@ -42434,17 +42453,17 @@
       <c r="C518" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="D518" s="18" t="s">
-        <v>829</v>
+      <c r="D518" s="1" t="s">
+        <v>828</v>
       </c>
       <c r="E518" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F518" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G518" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="519" spans="1:7">
@@ -42454,16 +42473,16 @@
         <v>765</v>
       </c>
       <c r="D519" s="18" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E519" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F519" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G519" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="520" spans="1:7">
@@ -42473,58 +42492,62 @@
         <v>765</v>
       </c>
       <c r="D520" s="18" t="s">
+        <v>830</v>
+      </c>
+      <c r="E520" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F520" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="G520" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="521" spans="1:7">
+      <c r="A521" s="14"/>
+      <c r="B521" s="14"/>
+      <c r="C521" s="14" t="s">
+        <v>765</v>
+      </c>
+      <c r="D521" s="18" t="s">
         <v>831</v>
       </c>
-      <c r="E520" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F520" s="4" t="s">
+      <c r="E521" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F521" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="G520" s="3" t="s">
+      <c r="G521" s="3" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="521" spans="1:7" ht="15.5">
-      <c r="A521" s="1"/>
-      <c r="B521" s="1"/>
-      <c r="C521" s="16" t="s">
-        <v>648</v>
-      </c>
-      <c r="D521" s="56" t="s">
-        <v>649</v>
-      </c>
-      <c r="E521" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F521" s="4"/>
-      <c r="G521" s="5"/>
-    </row>
-    <row r="522" spans="1:7">
+    <row r="522" spans="1:7" ht="15.5">
+      <c r="A522" s="1"/>
+      <c r="B522" s="1"/>
       <c r="C522" s="16" t="s">
         <v>648</v>
       </c>
-      <c r="D522" s="15" t="s">
-        <v>838</v>
+      <c r="D522" s="56" t="s">
+        <v>649</v>
       </c>
       <c r="E522" s="3" t="s">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="F522" s="4"/>
+      <c r="G522" s="5"/>
     </row>
     <row r="523" spans="1:7">
-      <c r="A523" s="14"/>
-      <c r="B523" s="14"/>
       <c r="C523" s="16" t="s">
         <v>648</v>
       </c>
       <c r="D523" s="15" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="E523" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F523" s="14"/>
-      <c r="G523" s="14"/>
     </row>
     <row r="524" spans="1:7">
       <c r="A524" s="14"/>
@@ -42533,7 +42556,7 @@
         <v>648</v>
       </c>
       <c r="D524" s="15" t="s">
-        <v>650</v>
+        <v>839</v>
       </c>
       <c r="E524" s="3" t="s">
         <v>2</v>
@@ -42544,13 +42567,15 @@
     <row r="525" spans="1:7">
       <c r="A525" s="14"/>
       <c r="B525" s="14"/>
-      <c r="C525" s="14" t="s">
-        <v>835</v>
-      </c>
-      <c r="D525" s="36" t="s">
-        <v>624</v>
-      </c>
-      <c r="E525" s="3"/>
+      <c r="C525" s="16" t="s">
+        <v>648</v>
+      </c>
+      <c r="D525" s="15" t="s">
+        <v>650</v>
+      </c>
+      <c r="E525" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="F525" s="14"/>
       <c r="G525" s="14"/>
     </row>
@@ -42561,12 +42586,10 @@
         <v>835</v>
       </c>
       <c r="D526" s="36" t="s">
-        <v>276</v>
+        <v>624</v>
       </c>
       <c r="E526" s="3"/>
-      <c r="F526" s="13" t="s">
-        <v>247</v>
-      </c>
+      <c r="F526" s="14"/>
       <c r="G526" s="14"/>
     </row>
     <row r="527" spans="1:7">
@@ -42576,11 +42599,11 @@
         <v>835</v>
       </c>
       <c r="D527" s="36" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E527" s="3"/>
       <c r="F527" s="13" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G527" s="14"/>
     </row>
@@ -42591,11 +42614,11 @@
         <v>835</v>
       </c>
       <c r="D528" s="36" t="s">
-        <v>651</v>
+        <v>277</v>
       </c>
       <c r="E528" s="3"/>
       <c r="F528" s="13" t="s">
-        <v>655</v>
+        <v>246</v>
       </c>
       <c r="G528" s="14"/>
     </row>
@@ -42606,11 +42629,11 @@
         <v>835</v>
       </c>
       <c r="D529" s="36" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E529" s="3"/>
       <c r="F529" s="13" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G529" s="14"/>
     </row>
@@ -42621,11 +42644,11 @@
         <v>835</v>
       </c>
       <c r="D530" s="36" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E530" s="3"/>
       <c r="F530" s="13" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G530" s="14"/>
     </row>
@@ -42636,21 +42659,27 @@
         <v>835</v>
       </c>
       <c r="D531" s="36" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="E531" s="3"/>
       <c r="F531" s="13" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="G531" s="14"/>
     </row>
     <row r="532" spans="1:7">
       <c r="A532" s="14"/>
       <c r="B532" s="14"/>
-      <c r="C532" s="14"/>
-      <c r="D532" s="36"/>
+      <c r="C532" s="14" t="s">
+        <v>835</v>
+      </c>
+      <c r="D532" s="36" t="s">
+        <v>654</v>
+      </c>
       <c r="E532" s="3"/>
-      <c r="F532" s="13"/>
+      <c r="F532" s="13" t="s">
+        <v>658</v>
+      </c>
       <c r="G532" s="14"/>
     </row>
     <row r="533" spans="1:7">
@@ -42707,44 +42736,44 @@
       <c r="F538" s="13"/>
       <c r="G538" s="14"/>
     </row>
-    <row r="539" spans="1:7" ht="15.5">
-      <c r="A539" s="1"/>
-      <c r="B539" s="1"/>
-      <c r="C539" s="1"/>
-      <c r="D539" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E539" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F539" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="G539" s="5"/>
+    <row r="539" spans="1:7">
+      <c r="A539" s="14"/>
+      <c r="B539" s="14"/>
+      <c r="C539" s="14"/>
+      <c r="D539" s="36"/>
+      <c r="E539" s="3"/>
+      <c r="F539" s="13"/>
+      <c r="G539" s="14"/>
     </row>
     <row r="540" spans="1:7" ht="15.5">
       <c r="A540" s="1"/>
       <c r="B540" s="1"/>
       <c r="C540" s="1"/>
       <c r="D540" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E540" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F540" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G540" s="5"/>
+    </row>
+    <row r="541" spans="1:7" ht="15.5">
+      <c r="A541" s="1"/>
+      <c r="B541" s="1"/>
+      <c r="C541" s="1"/>
+      <c r="D541" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="E540" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F540" s="4" t="s">
+      <c r="E541" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F541" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G540" s="5"/>
-    </row>
-    <row r="541" spans="1:7">
-      <c r="A541" s="14"/>
-      <c r="B541" s="14"/>
-      <c r="C541" s="14"/>
-      <c r="D541" s="15"/>
-      <c r="E541" s="3"/>
-      <c r="F541" s="14"/>
-      <c r="G541" s="14"/>
+      <c r="G541" s="5"/>
     </row>
     <row r="542" spans="1:7">
       <c r="A542" s="14"/>
@@ -42756,22 +42785,22 @@
       <c r="G542" s="14"/>
     </row>
     <row r="543" spans="1:7">
-      <c r="A543" s="1"/>
-      <c r="B543" s="1"/>
-      <c r="C543" s="1"/>
-      <c r="D543" s="1"/>
+      <c r="A543" s="14"/>
+      <c r="B543" s="14"/>
+      <c r="C543" s="14"/>
+      <c r="D543" s="15"/>
       <c r="E543" s="3"/>
-      <c r="F543" s="4"/>
-      <c r="G543" s="3"/>
-    </row>
-    <row r="544" spans="1:7" ht="15.5">
+      <c r="F543" s="14"/>
+      <c r="G543" s="14"/>
+    </row>
+    <row r="544" spans="1:7">
       <c r="A544" s="1"/>
       <c r="B544" s="1"/>
       <c r="C544" s="1"/>
-      <c r="D544" s="13"/>
+      <c r="D544" s="1"/>
       <c r="E544" s="3"/>
       <c r="F544" s="4"/>
-      <c r="G544" s="5"/>
+      <c r="G544" s="3"/>
     </row>
     <row r="545" spans="1:7" ht="15.5">
       <c r="A545" s="1"/>
@@ -42791,55 +42820,47 @@
       <c r="F546" s="4"/>
       <c r="G546" s="5"/>
     </row>
-    <row r="547" spans="1:7">
+    <row r="547" spans="1:7" ht="15.5">
       <c r="A547" s="1"/>
       <c r="B547" s="1"/>
-      <c r="C547" s="6"/>
-      <c r="D547" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="E547" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F547" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G547" s="3" t="s">
-        <v>21</v>
-      </c>
+      <c r="C547" s="1"/>
+      <c r="D547" s="13"/>
+      <c r="E547" s="3"/>
+      <c r="F547" s="4"/>
+      <c r="G547" s="5"/>
     </row>
     <row r="548" spans="1:7">
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
       <c r="C548" s="6"/>
       <c r="D548" s="11" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E548" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F548" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G548" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="549" spans="1:7">
       <c r="A549" s="1"/>
       <c r="B549" s="1"/>
       <c r="C549" s="6"/>
-      <c r="D549" s="6" t="s">
-        <v>25</v>
+      <c r="D549" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="E549" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F549" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G549" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="550" spans="1:7">
@@ -42847,320 +42868,320 @@
       <c r="B550" s="1"/>
       <c r="C550" s="6"/>
       <c r="D550" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E550" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F550" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G550" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="551" spans="1:7" ht="26">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="551" spans="1:7">
       <c r="A551" s="1"/>
       <c r="B551" s="1"/>
-      <c r="C551" s="1"/>
-      <c r="D551" s="1" t="s">
-        <v>31</v>
+      <c r="C551" s="6"/>
+      <c r="D551" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="E551" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F551" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G551" s="3">
-        <v>4</v>
+        <v>29</v>
+      </c>
+      <c r="G551" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="552" spans="1:7" ht="26">
       <c r="A552" s="1"/>
       <c r="B552" s="1"/>
-      <c r="C552" s="7"/>
-      <c r="D552" s="7" t="s">
-        <v>33</v>
+      <c r="C552" s="1"/>
+      <c r="D552" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E552" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F552" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G552" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="553" spans="1:7" ht="26">
+      <c r="A553" s="1"/>
+      <c r="B553" s="1"/>
+      <c r="C553" s="7"/>
+      <c r="D553" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E553" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F553" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G552" s="3">
+      <c r="G553" s="3">
         <v>10</v>
-      </c>
-    </row>
-    <row r="553" spans="1:7">
-      <c r="A553" s="12"/>
-      <c r="B553" s="12"/>
-      <c r="C553" s="12"/>
-      <c r="D553" s="159" t="s">
-        <v>35</v>
-      </c>
-      <c r="E553" s="157" t="s">
-        <v>4</v>
-      </c>
-      <c r="F553" s="158" t="s">
-        <v>36</v>
-      </c>
-      <c r="G553" s="3" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="554" spans="1:7">
       <c r="A554" s="12"/>
       <c r="B554" s="12"/>
       <c r="C554" s="12"/>
-      <c r="D554" s="159"/>
-      <c r="E554" s="157"/>
-      <c r="F554" s="158"/>
+      <c r="D554" s="159" t="s">
+        <v>35</v>
+      </c>
+      <c r="E554" s="157" t="s">
+        <v>4</v>
+      </c>
+      <c r="F554" s="158" t="s">
+        <v>36</v>
+      </c>
       <c r="G554" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="555" spans="1:7">
+      <c r="A555" s="12"/>
+      <c r="B555" s="12"/>
+      <c r="C555" s="12"/>
+      <c r="D555" s="159"/>
+      <c r="E555" s="157"/>
+      <c r="F555" s="158"/>
+      <c r="G555" s="3" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="556" spans="1:7">
-      <c r="A556" s="1"/>
-      <c r="B556" s="1"/>
-      <c r="C556" s="1"/>
-      <c r="D556" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E556" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F556" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G556" s="3">
-        <v>20</v>
       </c>
     </row>
     <row r="557" spans="1:7">
       <c r="A557" s="1"/>
       <c r="B557" s="1"/>
       <c r="C557" s="1"/>
-      <c r="D557" s="156" t="s">
-        <v>42</v>
-      </c>
-      <c r="E557" s="157" t="s">
-        <v>4</v>
-      </c>
-      <c r="F557" s="158" t="s">
-        <v>43</v>
+      <c r="D557" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E557" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F557" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="G557" s="3">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="558" spans="1:7">
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
       <c r="C558" s="1"/>
-      <c r="D558" s="156"/>
-      <c r="E558" s="157"/>
-      <c r="F558" s="158"/>
-      <c r="G558" s="3" t="s">
+      <c r="D558" s="156" t="s">
+        <v>42</v>
+      </c>
+      <c r="E558" s="157" t="s">
+        <v>4</v>
+      </c>
+      <c r="F558" s="158" t="s">
+        <v>43</v>
+      </c>
+      <c r="G558" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="559" spans="1:7">
+      <c r="A559" s="1"/>
+      <c r="B559" s="1"/>
+      <c r="C559" s="1"/>
+      <c r="D559" s="156"/>
+      <c r="E559" s="157"/>
+      <c r="F559" s="158"/>
+      <c r="G559" s="3" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="559" spans="1:7">
-      <c r="A559" s="12"/>
-      <c r="B559" s="12"/>
-      <c r="C559" s="12"/>
-      <c r="D559" s="159" t="s">
-        <v>45</v>
-      </c>
-      <c r="E559" s="157" t="s">
-        <v>4</v>
-      </c>
-      <c r="F559" s="158" t="s">
-        <v>46</v>
-      </c>
-      <c r="G559" s="3" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="560" spans="1:7">
       <c r="A560" s="12"/>
       <c r="B560" s="12"/>
       <c r="C560" s="12"/>
-      <c r="D560" s="159"/>
-      <c r="E560" s="157"/>
-      <c r="F560" s="158"/>
+      <c r="D560" s="159" t="s">
+        <v>45</v>
+      </c>
+      <c r="E560" s="157" t="s">
+        <v>4</v>
+      </c>
+      <c r="F560" s="158" t="s">
+        <v>46</v>
+      </c>
       <c r="G560" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="561" spans="1:7">
+      <c r="A561" s="12"/>
+      <c r="B561" s="12"/>
+      <c r="C561" s="12"/>
+      <c r="D561" s="159"/>
+      <c r="E561" s="157"/>
+      <c r="F561" s="158"/>
+      <c r="G561" s="3" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="562" spans="1:7">
-      <c r="A562" s="1"/>
-      <c r="B562" s="1"/>
-      <c r="C562" s="1"/>
-      <c r="D562" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E562" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F562" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G562" s="3">
-        <v>80</v>
       </c>
     </row>
     <row r="563" spans="1:7">
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
-      <c r="D563" s="156" t="s">
-        <v>52</v>
-      </c>
-      <c r="E563" s="157" t="s">
+      <c r="D563" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E563" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F563" s="158" t="s">
-        <v>53</v>
+      <c r="F563" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="G563" s="3">
-        <v>40</v>
+        <v>80</v>
       </c>
     </row>
     <row r="564" spans="1:7">
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
-      <c r="D564" s="156"/>
-      <c r="E564" s="157"/>
-      <c r="F564" s="158"/>
-      <c r="G564" s="3" t="s">
-        <v>44</v>
+      <c r="D564" s="156" t="s">
+        <v>52</v>
+      </c>
+      <c r="E564" s="157" t="s">
+        <v>2</v>
+      </c>
+      <c r="F564" s="158" t="s">
+        <v>53</v>
+      </c>
+      <c r="G564" s="3">
+        <v>40</v>
       </c>
     </row>
     <row r="565" spans="1:7">
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
-      <c r="D565" s="159" t="s">
-        <v>54</v>
-      </c>
-      <c r="E565" s="157" t="s">
-        <v>4</v>
-      </c>
-      <c r="F565" s="158" t="s">
-        <v>55</v>
-      </c>
+      <c r="D565" s="156"/>
+      <c r="E565" s="157"/>
+      <c r="F565" s="158"/>
       <c r="G565" s="3" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
     </row>
     <row r="566" spans="1:7">
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
-      <c r="D566" s="159"/>
-      <c r="E566" s="157"/>
-      <c r="F566" s="158"/>
+      <c r="D566" s="159" t="s">
+        <v>54</v>
+      </c>
+      <c r="E566" s="157" t="s">
+        <v>4</v>
+      </c>
+      <c r="F566" s="158" t="s">
+        <v>55</v>
+      </c>
       <c r="G566" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="567" spans="1:7">
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
       <c r="C567" s="1"/>
-      <c r="D567" s="159" t="s">
-        <v>58</v>
-      </c>
-      <c r="E567" s="157" t="s">
-        <v>4</v>
-      </c>
-      <c r="F567" s="158" t="s">
-        <v>59</v>
-      </c>
+      <c r="D567" s="159"/>
+      <c r="E567" s="157"/>
+      <c r="F567" s="158"/>
       <c r="G567" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="568" spans="1:7">
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
       <c r="C568" s="1"/>
-      <c r="D568" s="159"/>
-      <c r="E568" s="157"/>
-      <c r="F568" s="158"/>
+      <c r="D568" s="159" t="s">
+        <v>58</v>
+      </c>
+      <c r="E568" s="157" t="s">
+        <v>4</v>
+      </c>
+      <c r="F568" s="158" t="s">
+        <v>59</v>
+      </c>
       <c r="G568" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="569" spans="1:7">
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
       <c r="C569" s="1"/>
-      <c r="D569" s="159" t="s">
-        <v>62</v>
-      </c>
-      <c r="E569" s="157" t="s">
-        <v>4</v>
-      </c>
-      <c r="F569" s="158" t="s">
-        <v>63</v>
-      </c>
+      <c r="D569" s="159"/>
+      <c r="E569" s="157"/>
+      <c r="F569" s="158"/>
       <c r="G569" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="570" spans="1:7">
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
       <c r="C570" s="1"/>
-      <c r="D570" s="159"/>
-      <c r="E570" s="157"/>
-      <c r="F570" s="158"/>
+      <c r="D570" s="159" t="s">
+        <v>62</v>
+      </c>
+      <c r="E570" s="157" t="s">
+        <v>4</v>
+      </c>
+      <c r="F570" s="158" t="s">
+        <v>63</v>
+      </c>
       <c r="G570" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="571" spans="1:7" ht="63.5">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="571" spans="1:7">
       <c r="A571" s="1"/>
       <c r="B571" s="1"/>
       <c r="C571" s="1"/>
-      <c r="D571" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E571" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F571" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="G571" s="5"/>
-    </row>
-    <row r="572" spans="1:7" ht="26">
+      <c r="D571" s="159"/>
+      <c r="E571" s="157"/>
+      <c r="F571" s="158"/>
+      <c r="G571" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="572" spans="1:7" ht="63.5">
       <c r="A572" s="1"/>
       <c r="B572" s="1"/>
       <c r="C572" s="1"/>
       <c r="D572" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E572" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F572" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G572" s="3">
-        <v>100</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="G572" s="5"/>
     </row>
     <row r="573" spans="1:7" ht="26">
       <c r="A573" s="1"/>
       <c r="B573" s="1"/>
       <c r="C573" s="1"/>
       <c r="D573" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E573" s="3" t="s">
         <v>2</v>
@@ -43172,49 +43193,55 @@
         <v>100</v>
       </c>
     </row>
-    <row r="574" spans="1:7" ht="38.5">
+    <row r="574" spans="1:7" ht="26">
       <c r="A574" s="1"/>
       <c r="B574" s="1"/>
       <c r="C574" s="1"/>
       <c r="D574" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E574" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F574" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="G574" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="575" spans="1:7">
+        <v>81</v>
+      </c>
+      <c r="G574" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="575" spans="1:7" ht="38.5">
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
       <c r="C575" s="1"/>
-      <c r="D575" s="156" t="s">
-        <v>86</v>
-      </c>
-      <c r="E575" s="157" t="s">
-        <v>4</v>
-      </c>
-      <c r="F575" s="158" t="s">
-        <v>87</v>
+      <c r="D575" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E575" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F575" s="4" t="s">
+        <v>84</v>
       </c>
       <c r="G575" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="576" spans="1:7">
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
-      <c r="D576" s="156"/>
-      <c r="E576" s="157"/>
-      <c r="F576" s="158"/>
+      <c r="D576" s="156" t="s">
+        <v>86</v>
+      </c>
+      <c r="E576" s="157" t="s">
+        <v>4</v>
+      </c>
+      <c r="F576" s="158" t="s">
+        <v>87</v>
+      </c>
       <c r="G576" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="577" spans="1:7">
@@ -43225,35 +43252,35 @@
       <c r="E577" s="157"/>
       <c r="F577" s="158"/>
       <c r="G577" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="578" spans="1:7">
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
-      <c r="D578" s="156" t="s">
-        <v>91</v>
-      </c>
-      <c r="E578" s="157" t="s">
-        <v>4</v>
-      </c>
-      <c r="F578" s="158" t="s">
-        <v>92</v>
-      </c>
+      <c r="D578" s="156"/>
+      <c r="E578" s="157"/>
+      <c r="F578" s="158"/>
       <c r="G578" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="579" spans="1:7">
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
-      <c r="D579" s="156"/>
-      <c r="E579" s="157"/>
-      <c r="F579" s="158"/>
+      <c r="D579" s="156" t="s">
+        <v>91</v>
+      </c>
+      <c r="E579" s="157" t="s">
+        <v>4</v>
+      </c>
+      <c r="F579" s="158" t="s">
+        <v>92</v>
+      </c>
       <c r="G579" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="580" spans="1:7">
@@ -43264,36 +43291,32 @@
       <c r="E580" s="157"/>
       <c r="F580" s="158"/>
       <c r="G580" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="581" spans="1:7" ht="15.5">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="581" spans="1:7">
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
-      <c r="D581" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E581" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F581" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G581" s="5"/>
+      <c r="D581" s="156"/>
+      <c r="E581" s="157"/>
+      <c r="F581" s="158"/>
+      <c r="G581" s="3" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="582" spans="1:7" ht="15.5">
       <c r="A582" s="1"/>
       <c r="B582" s="1"/>
       <c r="C582" s="1"/>
       <c r="D582" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E582" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F582" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G582" s="5"/>
     </row>
@@ -43302,13 +43325,13 @@
       <c r="B583" s="1"/>
       <c r="C583" s="1"/>
       <c r="D583" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E583" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F583" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G583" s="5"/>
     </row>
@@ -43317,13 +43340,13 @@
       <c r="B584" s="1"/>
       <c r="C584" s="1"/>
       <c r="D584" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E584" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F584" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G584" s="5"/>
     </row>
@@ -43332,13 +43355,13 @@
       <c r="B585" s="1"/>
       <c r="C585" s="1"/>
       <c r="D585" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E585" s="3" t="s">
-        <v>102</v>
+        <v>2</v>
       </c>
       <c r="F585" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G585" s="5"/>
     </row>
@@ -43347,13 +43370,13 @@
       <c r="B586" s="1"/>
       <c r="C586" s="1"/>
       <c r="D586" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E586" s="3" t="s">
         <v>102</v>
       </c>
       <c r="F586" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G586" s="5"/>
     </row>
@@ -43362,13 +43385,13 @@
       <c r="B587" s="1"/>
       <c r="C587" s="1"/>
       <c r="D587" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E587" s="3" t="s">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="F587" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G587" s="5"/>
     </row>
@@ -43377,24 +43400,30 @@
       <c r="B588" s="1"/>
       <c r="C588" s="1"/>
       <c r="D588" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E588" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F588" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G588" s="5"/>
+    </row>
+    <row r="589" spans="1:7" ht="15.5">
+      <c r="A589" s="1"/>
+      <c r="B589" s="1"/>
+      <c r="C589" s="1"/>
+      <c r="D589" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E588" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F588" s="4" t="s">
+      <c r="E589" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F589" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="G588" s="5"/>
-    </row>
-    <row r="590" spans="1:7">
-      <c r="A590" s="1"/>
-      <c r="B590" s="1"/>
-      <c r="C590" s="1"/>
-      <c r="D590" s="1"/>
-      <c r="E590" s="3"/>
-      <c r="F590" s="4"/>
-      <c r="G590" s="3"/>
+      <c r="G589" s="5"/>
     </row>
     <row r="591" spans="1:7">
       <c r="A591" s="1"/>
@@ -43423,33 +43452,27 @@
       <c r="F593" s="4"/>
       <c r="G593" s="3"/>
     </row>
-    <row r="596" spans="1:7" ht="15.5">
-      <c r="A596" s="1"/>
-      <c r="B596" s="1"/>
-      <c r="C596" s="1"/>
-      <c r="D596" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="E596" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F596" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="G596" s="5"/>
+    <row r="594" spans="1:7">
+      <c r="A594" s="1"/>
+      <c r="B594" s="1"/>
+      <c r="C594" s="1"/>
+      <c r="D594" s="1"/>
+      <c r="E594" s="3"/>
+      <c r="F594" s="4"/>
+      <c r="G594" s="3"/>
     </row>
     <row r="597" spans="1:7" ht="15.5">
       <c r="A597" s="1"/>
       <c r="B597" s="1"/>
       <c r="C597" s="1"/>
       <c r="D597" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E597" s="3" t="s">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="F597" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G597" s="5"/>
     </row>
@@ -43458,43 +43481,43 @@
       <c r="B598" s="1"/>
       <c r="C598" s="1"/>
       <c r="D598" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E598" s="3" t="s">
         <v>68</v>
       </c>
       <c r="F598" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G598" s="5"/>
+    </row>
+    <row r="599" spans="1:7" ht="15.5">
+      <c r="A599" s="1"/>
+      <c r="B599" s="1"/>
+      <c r="C599" s="1"/>
+      <c r="D599" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E599" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F599" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="G598" s="5"/>
-    </row>
-    <row r="601" spans="1:7" ht="15.5">
-      <c r="A601" s="1"/>
-      <c r="B601" s="1"/>
-      <c r="C601" s="1"/>
-      <c r="D601" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E601" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F601" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G601" s="5"/>
+      <c r="G599" s="5"/>
     </row>
     <row r="602" spans="1:7" ht="15.5">
       <c r="A602" s="1"/>
       <c r="B602" s="1"/>
       <c r="C602" s="1"/>
       <c r="D602" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E602" s="3" t="s">
         <v>2</v>
       </c>
       <c r="F602" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G602" s="5"/>
     </row>
@@ -43503,48 +43526,46 @@
       <c r="B603" s="1"/>
       <c r="C603" s="1"/>
       <c r="D603" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E603" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F603" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="G603" s="5"/>
+    </row>
+    <row r="604" spans="1:7" ht="15.5">
+      <c r="A604" s="1"/>
+      <c r="B604" s="1"/>
+      <c r="C604" s="1"/>
+      <c r="D604" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="E603" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F603" s="4" t="s">
+      <c r="E604" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F604" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="G603" s="5"/>
-    </row>
-    <row r="605" spans="1:7">
-      <c r="A605" s="1"/>
-      <c r="B605" s="1"/>
-      <c r="C605" s="1"/>
-      <c r="D605" s="1" t="s">
+      <c r="G604" s="5"/>
+    </row>
+    <row r="606" spans="1:7">
+      <c r="A606" s="1"/>
+      <c r="B606" s="1"/>
+      <c r="C606" s="1"/>
+      <c r="D606" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E605" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F605" s="4" t="s">
+      <c r="E606" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F606" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="G605" s="3" t="s">
+      <c r="G606" s="3" t="s">
         <v>126</v>
-      </c>
-    </row>
-    <row r="607" spans="1:7">
-      <c r="A607" s="1"/>
-      <c r="B607" s="1"/>
-      <c r="C607" s="1"/>
-      <c r="D607" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E607" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F607" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="G607" s="3" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="608" spans="1:7">
@@ -43552,45 +43573,47 @@
       <c r="B608" s="1"/>
       <c r="C608" s="1"/>
       <c r="D608" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E608" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F608" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="G608" s="3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="609" spans="1:7" ht="15.5">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="609" spans="1:7">
       <c r="A609" s="1"/>
       <c r="B609" s="1"/>
       <c r="C609" s="1"/>
       <c r="D609" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E609" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F609" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="G609" s="5"/>
+        <v>140</v>
+      </c>
+      <c r="G609" s="3" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="610" spans="1:7" ht="15.5">
       <c r="A610" s="1"/>
       <c r="B610" s="1"/>
       <c r="C610" s="1"/>
       <c r="D610" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E610" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F610" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G610" s="5"/>
     </row>
@@ -43598,34 +43621,37 @@
       <c r="A611" s="1"/>
       <c r="B611" s="1"/>
       <c r="C611" s="1"/>
-      <c r="D611" s="28"/>
-      <c r="E611" s="3"/>
-      <c r="F611" s="4"/>
+      <c r="D611" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E611" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F611" s="4" t="s">
+        <v>145</v>
+      </c>
       <c r="G611" s="5"/>
     </row>
-    <row r="612" spans="1:7" ht="26">
-      <c r="A612" s="27"/>
-      <c r="B612" s="27"/>
-      <c r="C612" s="27"/>
+    <row r="612" spans="1:7" ht="15.5">
+      <c r="A612" s="1"/>
+      <c r="B612" s="1"/>
+      <c r="C612" s="1"/>
       <c r="D612" s="28"/>
       <c r="E612" s="3"/>
-      <c r="F612" s="4" t="s">
+      <c r="F612" s="4"/>
+      <c r="G612" s="5"/>
+    </row>
+    <row r="613" spans="1:7" ht="26">
+      <c r="A613" s="27"/>
+      <c r="B613" s="27"/>
+      <c r="C613" s="27"/>
+      <c r="D613" s="28"/>
+      <c r="E613" s="3"/>
+      <c r="F613" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="G612" s="3" t="s">
+      <c r="G613" s="3" t="s">
         <v>135</v>
-      </c>
-    </row>
-    <row r="620" spans="1:7">
-      <c r="A620" s="1"/>
-      <c r="B620" s="1"/>
-      <c r="C620" s="1"/>
-      <c r="D620" s="67" t="s">
-        <v>279</v>
-      </c>
-      <c r="E620" s="19"/>
-      <c r="F620" t="s">
-        <v>842</v>
       </c>
     </row>
     <row r="621" spans="1:7">
@@ -43633,11 +43659,11 @@
       <c r="B621" s="1"/>
       <c r="C621" s="1"/>
       <c r="D621" s="67" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E621" s="19"/>
       <c r="F621" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="622" spans="1:7">
@@ -43645,11 +43671,11 @@
       <c r="B622" s="1"/>
       <c r="C622" s="1"/>
       <c r="D622" s="67" t="s">
-        <v>592</v>
+        <v>278</v>
       </c>
       <c r="E622" s="19"/>
       <c r="F622" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="623" spans="1:7">
@@ -43657,11 +43683,11 @@
       <c r="B623" s="1"/>
       <c r="C623" s="1"/>
       <c r="D623" s="67" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E623" s="19"/>
       <c r="F623" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="624" spans="1:7">
@@ -43669,51 +43695,63 @@
       <c r="B624" s="1"/>
       <c r="C624" s="1"/>
       <c r="D624" s="67" t="s">
-        <v>840</v>
+        <v>593</v>
       </c>
       <c r="E624" s="19"/>
+      <c r="F624" t="s">
+        <v>844</v>
+      </c>
     </row>
     <row r="625" spans="1:6">
       <c r="A625" s="1"/>
       <c r="B625" s="1"/>
       <c r="C625" s="1"/>
       <c r="D625" s="67" t="s">
+        <v>840</v>
+      </c>
+      <c r="E625" s="19"/>
+    </row>
+    <row r="626" spans="1:6">
+      <c r="A626" s="1"/>
+      <c r="B626" s="1"/>
+      <c r="C626" s="1"/>
+      <c r="D626" s="67" t="s">
         <v>845</v>
       </c>
-      <c r="E625" s="19"/>
-      <c r="F625" s="48" t="s">
+      <c r="E626" s="19"/>
+      <c r="F626" s="48" t="s">
         <v>609</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D553:D554"/>
-    <mergeCell ref="E553:E554"/>
-    <mergeCell ref="F553:F554"/>
-    <mergeCell ref="D557:D558"/>
-    <mergeCell ref="E557:E558"/>
-    <mergeCell ref="F557:F558"/>
-    <mergeCell ref="D559:D560"/>
-    <mergeCell ref="E559:E560"/>
-    <mergeCell ref="F559:F560"/>
-    <mergeCell ref="D563:D564"/>
-    <mergeCell ref="E563:E564"/>
-    <mergeCell ref="F563:F564"/>
-    <mergeCell ref="D565:D566"/>
-    <mergeCell ref="E565:E566"/>
-    <mergeCell ref="F565:F566"/>
-    <mergeCell ref="D567:D568"/>
-    <mergeCell ref="E567:E568"/>
-    <mergeCell ref="F567:F568"/>
-    <mergeCell ref="D578:D580"/>
-    <mergeCell ref="E578:E580"/>
-    <mergeCell ref="F578:F580"/>
-    <mergeCell ref="D569:D570"/>
-    <mergeCell ref="E569:E570"/>
-    <mergeCell ref="F569:F570"/>
-    <mergeCell ref="D575:D577"/>
-    <mergeCell ref="E575:E577"/>
-    <mergeCell ref="F575:F577"/>
+    <mergeCell ref="D554:D555"/>
+    <mergeCell ref="E554:E555"/>
+    <mergeCell ref="F554:F555"/>
+    <mergeCell ref="D558:D559"/>
+    <mergeCell ref="E558:E559"/>
+    <mergeCell ref="F558:F559"/>
+    <mergeCell ref="D560:D561"/>
+    <mergeCell ref="E560:E561"/>
+    <mergeCell ref="F560:F561"/>
+    <mergeCell ref="D564:D565"/>
+    <mergeCell ref="E564:E565"/>
+    <mergeCell ref="F564:F565"/>
+    <mergeCell ref="D566:D567"/>
+    <mergeCell ref="E566:E567"/>
+    <mergeCell ref="F566:F567"/>
+    <mergeCell ref="D568:D569"/>
+    <mergeCell ref="E568:E569"/>
+    <mergeCell ref="F568:F569"/>
+    <mergeCell ref="D579:D581"/>
+    <mergeCell ref="E579:E581"/>
+    <mergeCell ref="F579:F581"/>
+    <mergeCell ref="D570:D571"/>
+    <mergeCell ref="E570:E571"/>
+    <mergeCell ref="F570:F571"/>
+    <mergeCell ref="D576:D578"/>
+    <mergeCell ref="E576:E578"/>
+    <mergeCell ref="F576:F578"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1" display="Abbreviation of the journal name. We use WoS abbreviations that can be found here: https://images.webofknowledge.com/images/help/WOS/A_abrvjt.html" xr:uid="{6BB52E4D-01E2-44A6-B6CC-352383FA2940}"/>

--- a/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
+++ b/02.FOMD/02.metadata_structure/10_FOMD_metadata_synthesis_short.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Evidence_Hub/02.FOMD/02.metadata_structure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3077" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E8218A6-A563-4D3D-A425-2A9DFD55F8A1}"/>
+  <xr:revisionPtr revIDLastSave="3078" documentId="14_{431D3801-6596-4146-883F-336ABD7CEFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB51178B-E852-4776-9DF7-67E5D25EF38A}"/>
   <bookViews>
-    <workbookView xWindow="57490" yWindow="-110" windowWidth="29020" windowHeight="15700" activeTab="2" xr2:uid="{FAB1A633-BA4D-4813-8605-DC3F4755D7C7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{FAB1A633-BA4D-4813-8605-DC3F4755D7C7}"/>
   </bookViews>
   <sheets>
     <sheet name="10_FOMD_metadata_synthesis" sheetId="1" r:id="rId1"/>
@@ -12384,12 +12384,12 @@
     <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="63" fillId="63" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -31686,7 +31686,7 @@
       <c r="L544" s="12"/>
       <c r="M544" s="12"/>
       <c r="N544" s="12"/>
-      <c r="O544" s="159" t="s">
+      <c r="O544" s="156" t="s">
         <v>35</v>
       </c>
       <c r="P544" s="157" t="s">
@@ -31714,7 +31714,7 @@
       <c r="L545" s="12"/>
       <c r="M545" s="12"/>
       <c r="N545" s="12"/>
-      <c r="O545" s="159"/>
+      <c r="O545" s="156"/>
       <c r="P545" s="157"/>
       <c r="Q545" s="158"/>
       <c r="R545" s="3" t="s">
@@ -31764,7 +31764,7 @@
       <c r="L548" s="1"/>
       <c r="M548" s="1"/>
       <c r="N548" s="1"/>
-      <c r="O548" s="156" t="s">
+      <c r="O548" s="159" t="s">
         <v>42</v>
       </c>
       <c r="P548" s="157" t="s">
@@ -31792,7 +31792,7 @@
       <c r="L549" s="1"/>
       <c r="M549" s="1"/>
       <c r="N549" s="1"/>
-      <c r="O549" s="156"/>
+      <c r="O549" s="159"/>
       <c r="P549" s="157"/>
       <c r="Q549" s="158"/>
       <c r="R549" s="3" t="s">
@@ -31814,7 +31814,7 @@
       <c r="L550" s="12"/>
       <c r="M550" s="12"/>
       <c r="N550" s="12"/>
-      <c r="O550" s="159" t="s">
+      <c r="O550" s="156" t="s">
         <v>45</v>
       </c>
       <c r="P550" s="157" t="s">
@@ -31842,7 +31842,7 @@
       <c r="L551" s="12"/>
       <c r="M551" s="12"/>
       <c r="N551" s="12"/>
-      <c r="O551" s="159"/>
+      <c r="O551" s="156"/>
       <c r="P551" s="157"/>
       <c r="Q551" s="158"/>
       <c r="R551" s="3" t="s">
@@ -31892,7 +31892,7 @@
       <c r="L554" s="1"/>
       <c r="M554" s="1"/>
       <c r="N554" s="1"/>
-      <c r="O554" s="156" t="s">
+      <c r="O554" s="159" t="s">
         <v>52</v>
       </c>
       <c r="P554" s="157" t="s">
@@ -31920,7 +31920,7 @@
       <c r="L555" s="1"/>
       <c r="M555" s="1"/>
       <c r="N555" s="1"/>
-      <c r="O555" s="156"/>
+      <c r="O555" s="159"/>
       <c r="P555" s="157"/>
       <c r="Q555" s="158"/>
       <c r="R555" s="3" t="s">
@@ -31942,7 +31942,7 @@
       <c r="L556" s="1"/>
       <c r="M556" s="1"/>
       <c r="N556" s="1"/>
-      <c r="O556" s="159" t="s">
+      <c r="O556" s="156" t="s">
         <v>54</v>
       </c>
       <c r="P556" s="157" t="s">
@@ -31970,7 +31970,7 @@
       <c r="L557" s="1"/>
       <c r="M557" s="1"/>
       <c r="N557" s="1"/>
-      <c r="O557" s="159"/>
+      <c r="O557" s="156"/>
       <c r="P557" s="157"/>
       <c r="Q557" s="158"/>
       <c r="R557" s="3" t="s">
@@ -31992,7 +31992,7 @@
       <c r="L558" s="1"/>
       <c r="M558" s="1"/>
       <c r="N558" s="1"/>
-      <c r="O558" s="159" t="s">
+      <c r="O558" s="156" t="s">
         <v>58</v>
       </c>
       <c r="P558" s="157" t="s">
@@ -32020,7 +32020,7 @@
       <c r="L559" s="1"/>
       <c r="M559" s="1"/>
       <c r="N559" s="1"/>
-      <c r="O559" s="159"/>
+      <c r="O559" s="156"/>
       <c r="P559" s="157"/>
       <c r="Q559" s="158"/>
       <c r="R559" s="3" t="s">
@@ -32042,7 +32042,7 @@
       <c r="L560" s="1"/>
       <c r="M560" s="1"/>
       <c r="N560" s="1"/>
-      <c r="O560" s="159" t="s">
+      <c r="O560" s="156" t="s">
         <v>62</v>
       </c>
       <c r="P560" s="157" t="s">
@@ -32070,7 +32070,7 @@
       <c r="L561" s="1"/>
       <c r="M561" s="1"/>
       <c r="N561" s="1"/>
-      <c r="O561" s="159"/>
+      <c r="O561" s="156"/>
       <c r="P561" s="157"/>
       <c r="Q561" s="158"/>
       <c r="R561" s="3" t="s">
@@ -32202,7 +32202,7 @@
       <c r="L566" s="1"/>
       <c r="M566" s="1"/>
       <c r="N566" s="1"/>
-      <c r="O566" s="156" t="s">
+      <c r="O566" s="159" t="s">
         <v>86</v>
       </c>
       <c r="P566" s="157" t="s">
@@ -32230,7 +32230,7 @@
       <c r="L567" s="1"/>
       <c r="M567" s="1"/>
       <c r="N567" s="1"/>
-      <c r="O567" s="156"/>
+      <c r="O567" s="159"/>
       <c r="P567" s="157"/>
       <c r="Q567" s="158"/>
       <c r="R567" s="3" t="s">
@@ -32252,7 +32252,7 @@
       <c r="L568" s="1"/>
       <c r="M568" s="1"/>
       <c r="N568" s="1"/>
-      <c r="O568" s="156"/>
+      <c r="O568" s="159"/>
       <c r="P568" s="157"/>
       <c r="Q568" s="158"/>
       <c r="R568" s="3" t="s">
@@ -32274,7 +32274,7 @@
       <c r="L569" s="1"/>
       <c r="M569" s="1"/>
       <c r="N569" s="1"/>
-      <c r="O569" s="156" t="s">
+      <c r="O569" s="159" t="s">
         <v>91</v>
       </c>
       <c r="P569" s="157" t="s">
@@ -32302,7 +32302,7 @@
       <c r="L570" s="1"/>
       <c r="M570" s="1"/>
       <c r="N570" s="1"/>
-      <c r="O570" s="156"/>
+      <c r="O570" s="159"/>
       <c r="P570" s="157"/>
       <c r="Q570" s="158"/>
       <c r="R570" s="3" t="s">
@@ -32324,7 +32324,7 @@
       <c r="L571" s="1"/>
       <c r="M571" s="1"/>
       <c r="N571" s="1"/>
-      <c r="O571" s="156"/>
+      <c r="O571" s="159"/>
       <c r="P571" s="157"/>
       <c r="Q571" s="158"/>
       <c r="R571" s="3" t="s">
@@ -33093,6 +33093,24 @@
   </sheetData>
   <autoFilter ref="A1:S321" xr:uid="{82619C4B-D6B1-486E-87C6-D2252668E253}"/>
   <mergeCells count="27">
+    <mergeCell ref="O544:O545"/>
+    <mergeCell ref="P544:P545"/>
+    <mergeCell ref="Q544:Q545"/>
+    <mergeCell ref="O548:O549"/>
+    <mergeCell ref="P548:P549"/>
+    <mergeCell ref="Q548:Q549"/>
+    <mergeCell ref="O558:O559"/>
+    <mergeCell ref="P558:P559"/>
+    <mergeCell ref="Q558:Q559"/>
+    <mergeCell ref="O560:O561"/>
+    <mergeCell ref="P560:P561"/>
+    <mergeCell ref="Q560:Q561"/>
+    <mergeCell ref="O566:O568"/>
+    <mergeCell ref="P566:P568"/>
+    <mergeCell ref="Q566:Q568"/>
+    <mergeCell ref="O569:O571"/>
+    <mergeCell ref="P569:P571"/>
+    <mergeCell ref="Q569:Q571"/>
     <mergeCell ref="O556:O557"/>
     <mergeCell ref="P556:P557"/>
     <mergeCell ref="Q556:Q557"/>
@@ -33102,24 +33120,6 @@
     <mergeCell ref="P554:P555"/>
     <mergeCell ref="Q554:Q555"/>
     <mergeCell ref="O550:O551"/>
-    <mergeCell ref="O566:O568"/>
-    <mergeCell ref="P566:P568"/>
-    <mergeCell ref="Q566:Q568"/>
-    <mergeCell ref="O569:O571"/>
-    <mergeCell ref="P569:P571"/>
-    <mergeCell ref="Q569:Q571"/>
-    <mergeCell ref="O558:O559"/>
-    <mergeCell ref="P558:P559"/>
-    <mergeCell ref="Q558:Q559"/>
-    <mergeCell ref="O560:O561"/>
-    <mergeCell ref="P560:P561"/>
-    <mergeCell ref="Q560:Q561"/>
-    <mergeCell ref="O544:O545"/>
-    <mergeCell ref="P544:P545"/>
-    <mergeCell ref="Q544:Q545"/>
-    <mergeCell ref="O548:O549"/>
-    <mergeCell ref="P548:P549"/>
-    <mergeCell ref="Q548:Q549"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="Q7" r:id="rId1" display="Abbreviation of the journal name. We use WoS abbreviations that can be found here: https://images.webofknowledge.com/images/help/WOS/A_abrvjt.html" xr:uid="{B4DADD6B-F846-45B3-933B-5F25CC9FEF24}"/>
@@ -39268,8 +39268,8 @@
       </c>
     </row>
     <row r="326" spans="1:7">
-      <c r="C326" s="137" t="s">
-        <v>1552</v>
+      <c r="C326" s="84" t="s">
+        <v>1630</v>
       </c>
       <c r="D326" s="154" t="s">
         <v>1653</v>
@@ -42935,7 +42935,7 @@
       <c r="A554" s="12"/>
       <c r="B554" s="12"/>
       <c r="C554" s="12"/>
-      <c r="D554" s="159" t="s">
+      <c r="D554" s="156" t="s">
         <v>35</v>
       </c>
       <c r="E554" s="157" t="s">
@@ -42952,7 +42952,7 @@
       <c r="A555" s="12"/>
       <c r="B555" s="12"/>
       <c r="C555" s="12"/>
-      <c r="D555" s="159"/>
+      <c r="D555" s="156"/>
       <c r="E555" s="157"/>
       <c r="F555" s="158"/>
       <c r="G555" s="3" t="s">
@@ -42980,7 +42980,7 @@
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
       <c r="C558" s="1"/>
-      <c r="D558" s="156" t="s">
+      <c r="D558" s="159" t="s">
         <v>42</v>
       </c>
       <c r="E558" s="157" t="s">
@@ -42997,7 +42997,7 @@
       <c r="A559" s="1"/>
       <c r="B559" s="1"/>
       <c r="C559" s="1"/>
-      <c r="D559" s="156"/>
+      <c r="D559" s="159"/>
       <c r="E559" s="157"/>
       <c r="F559" s="158"/>
       <c r="G559" s="3" t="s">
@@ -43008,7 +43008,7 @@
       <c r="A560" s="12"/>
       <c r="B560" s="12"/>
       <c r="C560" s="12"/>
-      <c r="D560" s="159" t="s">
+      <c r="D560" s="156" t="s">
         <v>45</v>
       </c>
       <c r="E560" s="157" t="s">
@@ -43025,7 +43025,7 @@
       <c r="A561" s="12"/>
       <c r="B561" s="12"/>
       <c r="C561" s="12"/>
-      <c r="D561" s="159"/>
+      <c r="D561" s="156"/>
       <c r="E561" s="157"/>
       <c r="F561" s="158"/>
       <c r="G561" s="3" t="s">
@@ -43053,7 +43053,7 @@
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
-      <c r="D564" s="156" t="s">
+      <c r="D564" s="159" t="s">
         <v>52</v>
       </c>
       <c r="E564" s="157" t="s">
@@ -43070,7 +43070,7 @@
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
-      <c r="D565" s="156"/>
+      <c r="D565" s="159"/>
       <c r="E565" s="157"/>
       <c r="F565" s="158"/>
       <c r="G565" s="3" t="s">
@@ -43081,7 +43081,7 @@
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
-      <c r="D566" s="159" t="s">
+      <c r="D566" s="156" t="s">
         <v>54</v>
       </c>
       <c r="E566" s="157" t="s">
@@ -43098,7 +43098,7 @@
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
       <c r="C567" s="1"/>
-      <c r="D567" s="159"/>
+      <c r="D567" s="156"/>
       <c r="E567" s="157"/>
       <c r="F567" s="158"/>
       <c r="G567" s="3" t="s">
@@ -43109,7 +43109,7 @@
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
       <c r="C568" s="1"/>
-      <c r="D568" s="159" t="s">
+      <c r="D568" s="156" t="s">
         <v>58</v>
       </c>
       <c r="E568" s="157" t="s">
@@ -43126,7 +43126,7 @@
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
       <c r="C569" s="1"/>
-      <c r="D569" s="159"/>
+      <c r="D569" s="156"/>
       <c r="E569" s="157"/>
       <c r="F569" s="158"/>
       <c r="G569" s="3" t="s">
@@ -43137,7 +43137,7 @@
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
       <c r="C570" s="1"/>
-      <c r="D570" s="159" t="s">
+      <c r="D570" s="156" t="s">
         <v>62</v>
       </c>
       <c r="E570" s="157" t="s">
@@ -43154,7 +43154,7 @@
       <c r="A571" s="1"/>
       <c r="B571" s="1"/>
       <c r="C571" s="1"/>
-      <c r="D571" s="159"/>
+      <c r="D571" s="156"/>
       <c r="E571" s="157"/>
       <c r="F571" s="158"/>
       <c r="G571" s="3" t="s">
@@ -43231,7 +43231,7 @@
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
-      <c r="D576" s="156" t="s">
+      <c r="D576" s="159" t="s">
         <v>86</v>
       </c>
       <c r="E576" s="157" t="s">
@@ -43248,7 +43248,7 @@
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
       <c r="C577" s="1"/>
-      <c r="D577" s="156"/>
+      <c r="D577" s="159"/>
       <c r="E577" s="157"/>
       <c r="F577" s="158"/>
       <c r="G577" s="3" t="s">
@@ -43259,7 +43259,7 @@
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
-      <c r="D578" s="156"/>
+      <c r="D578" s="159"/>
       <c r="E578" s="157"/>
       <c r="F578" s="158"/>
       <c r="G578" s="3" t="s">
@@ -43270,7 +43270,7 @@
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
-      <c r="D579" s="156" t="s">
+      <c r="D579" s="159" t="s">
         <v>91</v>
       </c>
       <c r="E579" s="157" t="s">
@@ -43287,7 +43287,7 @@
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
-      <c r="D580" s="156"/>
+      <c r="D580" s="159"/>
       <c r="E580" s="157"/>
       <c r="F580" s="158"/>
       <c r="G580" s="3" t="s">
@@ -43298,7 +43298,7 @@
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
-      <c r="D581" s="156"/>
+      <c r="D581" s="159"/>
       <c r="E581" s="157"/>
       <c r="F581" s="158"/>
       <c r="G581" s="3" t="s">
@@ -43725,24 +43725,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D554:D555"/>
-    <mergeCell ref="E554:E555"/>
-    <mergeCell ref="F554:F555"/>
-    <mergeCell ref="D558:D559"/>
-    <mergeCell ref="E558:E559"/>
-    <mergeCell ref="F558:F559"/>
-    <mergeCell ref="D560:D561"/>
-    <mergeCell ref="E560:E561"/>
-    <mergeCell ref="F560:F561"/>
-    <mergeCell ref="D564:D565"/>
-    <mergeCell ref="E564:E565"/>
-    <mergeCell ref="F564:F565"/>
-    <mergeCell ref="D566:D567"/>
-    <mergeCell ref="E566:E567"/>
-    <mergeCell ref="F566:F567"/>
-    <mergeCell ref="D568:D569"/>
-    <mergeCell ref="E568:E569"/>
-    <mergeCell ref="F568:F569"/>
     <mergeCell ref="D579:D581"/>
     <mergeCell ref="E579:E581"/>
     <mergeCell ref="F579:F581"/>
@@ -43752,6 +43734,24 @@
     <mergeCell ref="D576:D578"/>
     <mergeCell ref="E576:E578"/>
     <mergeCell ref="F576:F578"/>
+    <mergeCell ref="D566:D567"/>
+    <mergeCell ref="E566:E567"/>
+    <mergeCell ref="F566:F567"/>
+    <mergeCell ref="D568:D569"/>
+    <mergeCell ref="E568:E569"/>
+    <mergeCell ref="F568:F569"/>
+    <mergeCell ref="D560:D561"/>
+    <mergeCell ref="E560:E561"/>
+    <mergeCell ref="F560:F561"/>
+    <mergeCell ref="D564:D565"/>
+    <mergeCell ref="E564:E565"/>
+    <mergeCell ref="F564:F565"/>
+    <mergeCell ref="D554:D555"/>
+    <mergeCell ref="E554:E555"/>
+    <mergeCell ref="F554:F555"/>
+    <mergeCell ref="D558:D559"/>
+    <mergeCell ref="E558:E559"/>
+    <mergeCell ref="F558:F559"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1" display="Abbreviation of the journal name. We use WoS abbreviations that can be found here: https://images.webofknowledge.com/images/help/WOS/A_abrvjt.html" xr:uid="{6BB52E4D-01E2-44A6-B6CC-352383FA2940}"/>
@@ -43763,6 +43763,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4e0e0d96de7fb32b1678b66c28514d8e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" xmlns:ns3="432dd258-9dce-4cb3-b611-c68c0fbce7f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac451aab8c96dec805c937cbafca7133" ns2:_="" ns3:_="">
     <xsd:import namespace="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
@@ -43963,27 +43983,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63F80AE0-5CF8-441A-8E3E-6D76A3390D5E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
+    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0C90B0A-DBBE-4147-B2EE-79946A8DC171}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC19592A-9F30-4B32-9428-1D9634B8A0D4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -44000,23 +44019,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0C90B0A-DBBE-4147-B2EE-79946A8DC171}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63F80AE0-5CF8-441A-8E3E-6D76A3390D5E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
-    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>